--- a/bugun_oranlar.xlsx
+++ b/bugun_oranlar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G156"/>
+  <dimension ref="A1:G220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,23 +456,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Kayserispor vs İstanbulspor</t>
+          <t>OFK Mladost DG U19 vs Kairat Almaty U19</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="E2" t="n">
         <v>1.43</v>
       </c>
-      <c r="C2" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="D2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1.68</v>
-      </c>
       <c r="F2" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -483,23 +483,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gaziantep FK vs Fenerbahçe</t>
+          <t>Bristol vs Lincoln City</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.5</v>
+        <v>1.87</v>
       </c>
       <c r="C3" t="n">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.55</v>
+        <v>3.8</v>
       </c>
       <c r="E3" t="n">
-        <v>1.72</v>
+        <v>1.94</v>
       </c>
       <c r="F3" t="n">
-        <v>2.18</v>
+        <v>1.78</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -510,23 +510,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gaziantep Bb U19 vs Fenerbahçe U19</t>
+          <t>Middlesbrough vs Millwall</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.73</v>
+        <v>1.51</v>
       </c>
       <c r="C4" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="D4" t="n">
-        <v>2.14</v>
+        <v>5.5</v>
       </c>
       <c r="E4" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="F4" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -537,23 +537,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Leeds United vs Newcastle</t>
+          <t>Notts County Reserves vs Mansfield Town Reserves</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
       <c r="C5" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9</v>
+        <v>1.84</v>
       </c>
       <c r="E5" t="n">
-        <v>1.84</v>
+        <v>1.41</v>
       </c>
       <c r="F5" t="n">
-        <v>2.01</v>
+        <v>2.6</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -564,23 +564,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Aveley vs Wingate &amp; Finchley</t>
+          <t>Hashtag United vs Takeley</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="F6" t="n">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -591,23 +591,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Barwell vs Sutton Coldfield Town</t>
+          <t>Egham Town vs Harrow Borough</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.9</v>
+        <v>1.87</v>
       </c>
       <c r="C7" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="D7" t="n">
-        <v>2.04</v>
+        <v>3.15</v>
       </c>
       <c r="E7" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -618,23 +618,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Blackburn U21 vs Reading U21</t>
+          <t>AFC Stoneham vs Ashford Town (Middx) Lfc</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="C8" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="D8" t="n">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="E8" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="F8" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -645,23 +645,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nottingham Forest U21 vs Burnley U21</t>
+          <t>Enfield Town vs Dartford</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.55</v>
+        <v>2.4</v>
       </c>
       <c r="C9" t="n">
-        <v>4.15</v>
+        <v>3.4</v>
       </c>
       <c r="D9" t="n">
-        <v>4.33</v>
+        <v>2.4</v>
       </c>
       <c r="E9" t="n">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="F9" t="n">
-        <v>2.6</v>
+        <v>2.11</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -672,23 +672,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>West Ham U21 vs Liverpool U21</t>
+          <t>Lewes vs Carshalton Athletic</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.31</v>
+        <v>2.8</v>
       </c>
       <c r="C10" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="D10" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="E10" t="n">
-        <v>1.33</v>
+        <v>1.66</v>
       </c>
       <c r="F10" t="n">
-        <v>2.8</v>
+        <v>2.06</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -699,23 +699,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Swansea City U21 vs Huddersfield U21</t>
+          <t>Ramsgate vs Maldon &amp; Tiptree</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="C11" t="n">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="E11" t="n">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="F11" t="n">
-        <v>3.7</v>
+        <v>2.45</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -726,23 +726,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sheffield Utd U21 vs Cardiff U21</t>
+          <t>Cray Wanderers vs St. Albans City</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.95</v>
+        <v>2.68</v>
       </c>
       <c r="C12" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="D12" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="E12" t="n">
-        <v>1.35</v>
+        <v>1.64</v>
       </c>
       <c r="F12" t="n">
-        <v>2.8</v>
+        <v>2.11</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -753,23 +753,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Swindon Supermarine vs Bristol Manor Farm</t>
+          <t>Leatherhead vs AFC Whyteleafe</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.51</v>
+        <v>1.66</v>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="D13" t="n">
-        <v>4.75</v>
+        <v>3.7</v>
       </c>
       <c r="E13" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="F13" t="n">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -780,23 +780,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Villarreal vs Real Betis</t>
+          <t>Brentwood Town vs Stanway Rovers</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.99</v>
+        <v>1.47</v>
       </c>
       <c r="C14" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="F14" t="n">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -807,23 +807,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Celta Fortuna vs Eibar</t>
+          <t>Welling United vs Cheshunt</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.05</v>
+        <v>1.79</v>
       </c>
       <c r="C15" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="E15" t="n">
-        <v>2.08</v>
+        <v>1.64</v>
       </c>
       <c r="F15" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -834,23 +834,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Torino vs AS Roma</t>
+          <t>Eastbourne Borough vs Chatham Town</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>2.31</v>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="D16" t="n">
-        <v>1.57</v>
+        <v>2.54</v>
       </c>
       <c r="E16" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -861,23 +861,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Como vs Parma</t>
+          <t>Whitehawk vs Three Bridges</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.22</v>
+        <v>2.5</v>
       </c>
       <c r="C17" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>2.3</v>
       </c>
       <c r="E17" t="n">
-        <v>1.66</v>
+        <v>1.51</v>
       </c>
       <c r="F17" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -888,23 +888,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Inter vs Udinese</t>
+          <t>Chesterfield vs Manchester City U21</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.22</v>
+        <v>2.11</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>2.77</v>
       </c>
       <c r="E18" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="F18" t="n">
-        <v>2.7</v>
+        <v>1.41</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AS Roma U20 vs Como U20</t>
+          <t>Swindon vs Crystal Palace U21</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="C19" t="n">
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>4.15</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="F19" t="n">
-        <v>2.16</v>
+        <v>1.47</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -942,23 +942,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Red Star vs Metz</t>
+          <t>Wycombe vs Chelsea U21</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.37</v>
+        <v>1.78</v>
       </c>
       <c r="C20" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="D20" t="n">
-        <v>2.77</v>
+        <v>3.5</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>1.38</v>
       </c>
       <c r="F20" t="n">
-        <v>1.71</v>
+        <v>2.73</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -969,23 +969,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen (K) vs Bayern Munchen (K)</t>
+          <t>Leyton Orient vs Arsenal U21</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7</v>
+        <v>1.57</v>
       </c>
       <c r="C21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D21" t="n">
         <v>4.5</v>
       </c>
-      <c r="D21" t="n">
-        <v>1.3</v>
-      </c>
       <c r="E21" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="F21" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -996,23 +996,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Rio Ave vs Estrela</t>
+          <t>York vs Newcastle U21</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.55</v>
+        <v>1.35</v>
       </c>
       <c r="C22" t="n">
-        <v>3.2</v>
+        <v>4.75</v>
       </c>
       <c r="D22" t="n">
-        <v>2.58</v>
+        <v>6.5</v>
       </c>
       <c r="E22" t="n">
-        <v>2.04</v>
+        <v>1.4</v>
       </c>
       <c r="F22" t="n">
-        <v>1.68</v>
+        <v>2.63</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1023,23 +1023,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Moreirense vs Maritimo Funchal</t>
+          <t>Berkhamsted vs Uxbridge</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.59</v>
+        <v>2.27</v>
       </c>
       <c r="C23" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="D23" t="n">
         <v>2.63</v>
       </c>
       <c r="E23" t="n">
-        <v>2.23</v>
+        <v>1.68</v>
       </c>
       <c r="F23" t="n">
-        <v>1.55</v>
+        <v>2.03</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1050,20 +1050,20 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Braga vs Estoril</t>
+          <t>Peterborough vs Barnsley</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.38</v>
+        <v>2.2</v>
       </c>
       <c r="C24" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="D24" t="n">
-        <v>6.5</v>
+        <v>2.9</v>
       </c>
       <c r="E24" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="F24" t="n">
         <v>2.06</v>
@@ -1077,23 +1077,23 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sporting CP B vs Sc Lusitania</t>
+          <t>West Ham vs Fulham</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.14</v>
+        <v>2.73</v>
       </c>
       <c r="C25" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="D25" t="n">
-        <v>3.1</v>
+        <v>2.31</v>
       </c>
       <c r="E25" t="n">
-        <v>2.16</v>
+        <v>1.66</v>
       </c>
       <c r="F25" t="n">
-        <v>1.6</v>
+        <v>2.11</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1104,23 +1104,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FC Porto B vs Vizela</t>
+          <t>Reading vs Brentford</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.4</v>
+        <v>7.5</v>
       </c>
       <c r="C26" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1.94</v>
+        <v>1.33</v>
       </c>
       <c r="E26" t="n">
-        <v>2.04</v>
+        <v>1.35</v>
       </c>
       <c r="F26" t="n">
-        <v>1.66</v>
+        <v>2.8</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1131,23 +1131,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Moreirense FC U23 vs Braga U23</t>
+          <t>Liverpool vs Tottenham</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.39</v>
+        <v>1.68</v>
       </c>
       <c r="C27" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>2.45</v>
+        <v>4.2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.66</v>
+        <v>1.45</v>
       </c>
       <c r="F27" t="n">
-        <v>2.06</v>
+        <v>1.47</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1158,23 +1158,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Uniao de Leiria U23 vs Benfica U23</t>
+          <t>Ipswich Town vs Arsenal</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.7</v>
+        <v>8</v>
       </c>
       <c r="C28" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>2.23</v>
+        <v>1.33</v>
       </c>
       <c r="E28" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="F28" t="n">
-        <v>1.99</v>
+        <v>2.33</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1185,23 +1185,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jong PSV vs Jong AZ Alkmaar</t>
+          <t>Aldershot vs Yeovil</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="D29" t="n">
-        <v>2.31</v>
+        <v>2.9</v>
       </c>
       <c r="E29" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="F29" t="n">
-        <v>3.5</v>
+        <v>1.95</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1212,23 +1212,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Jong Utrecht vs Jong Ajax</t>
+          <t>Solihull Moors vs Barrow</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="C30" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="D30" t="n">
-        <v>2.63</v>
+        <v>2.37</v>
       </c>
       <c r="E30" t="n">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="F30" t="n">
-        <v>2.73</v>
+        <v>2.03</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1239,23 +1239,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Portland Timbers II vs St Louis City II</t>
+          <t>Carlisle vs Forest Green</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.34</v>
+        <v>1.97</v>
       </c>
       <c r="C31" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="D31" t="n">
-        <v>2.45</v>
+        <v>3.05</v>
       </c>
       <c r="E31" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="F31" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1266,23 +1266,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CA Fenix vs Centro Espanyol</t>
+          <t>Harrogate vs AFC Fylde</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3.5</v>
+        <v>1.99</v>
       </c>
       <c r="C32" t="n">
-        <v>2.77</v>
+        <v>3.7</v>
       </c>
       <c r="D32" t="n">
-        <v>2.09</v>
+        <v>3.05</v>
       </c>
       <c r="E32" t="n">
-        <v>2.9</v>
+        <v>1.51</v>
       </c>
       <c r="F32" t="n">
-        <v>1.33</v>
+        <v>2.4</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1293,23 +1293,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CA Defensores de Belgrano vs Deportivo Madryn</t>
+          <t>Worthing vs AFC Hornchurch</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="C33" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="D33" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="E33" t="n">
-        <v>2.77</v>
+        <v>1.55</v>
       </c>
       <c r="F33" t="n">
-        <v>1.38</v>
+        <v>2.27</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1320,23 +1320,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ezeiza vs Deportivo Metalurgico</t>
+          <t>Boston United vs Woking</t>
         </is>
       </c>
       <c r="B34" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="C34" t="n">
         <v>3.3</v>
       </c>
-      <c r="C34" t="n">
-        <v>2.6</v>
-      </c>
       <c r="D34" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="E34" t="n">
-        <v>2.68</v>
+        <v>1.81</v>
       </c>
       <c r="F34" t="n">
-        <v>1.45</v>
+        <v>1.9</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1347,23 +1347,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Neftchi Fargona vs Al Quwa/Jawiya</t>
+          <t>Wealdstone vs Halifax</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.55</v>
+        <v>2.2</v>
       </c>
       <c r="C35" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="D35" t="n">
-        <v>5.5</v>
+        <v>2.73</v>
       </c>
       <c r="E35" t="n">
-        <v>1.92</v>
+        <v>1.66</v>
       </c>
       <c r="F35" t="n">
-        <v>1.79</v>
+        <v>2.08</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1374,23 +1374,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Al-Shamal vs Al-Ittihad</t>
+          <t>Southend vs Tamworth</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4.33</v>
+        <v>1.53</v>
       </c>
       <c r="C36" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="D36" t="n">
-        <v>1.66</v>
+        <v>4.5</v>
       </c>
       <c r="E36" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="F36" t="n">
-        <v>2.25</v>
+        <v>2.54</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1401,23 +1401,23 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai vs Tractor Sazi FC</t>
+          <t>Sutton Utd vs Eastleigh</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.62</v>
+        <v>1.99</v>
       </c>
       <c r="C37" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="D37" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="F37" t="n">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1428,23 +1428,23 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Al Ahli Jeddah vs Pakhtakor Tashkent</t>
+          <t>Truro vs Salisbury</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.22</v>
+        <v>1.68</v>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="D38" t="n">
-        <v>10</v>
+        <v>3.8</v>
       </c>
       <c r="E38" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="F38" t="n">
-        <v>2.8</v>
+        <v>2.12</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1455,23 +1455,23 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Al-Qadsiah Al Khubar vs Al Wasl</t>
+          <t>Billericay Town vs Braintree</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.41</v>
+        <v>1.66</v>
       </c>
       <c r="C39" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="D39" t="n">
-        <v>6</v>
+        <v>4.15</v>
       </c>
       <c r="E39" t="n">
-        <v>1.41</v>
+        <v>1.66</v>
       </c>
       <c r="F39" t="n">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1482,23 +1482,23 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Esteghlal Tehran vs Al Sadd</t>
+          <t>Heaton Stannington vs Dunston Uts</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3.6</v>
+        <v>2.73</v>
       </c>
       <c r="C40" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="D40" t="n">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="F40" t="n">
-        <v>1.71</v>
+        <v>1.98</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1509,23 +1509,23 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Shan United FC vs Ezra FC</t>
+          <t>Bradford Park Avenue vs Beverley Town FC</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>1.45</v>
       </c>
       <c r="C41" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="D41" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="E41" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="F41" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1536,23 +1536,23 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Çin (K) vs Hong Kong (K)</t>
+          <t>North Ferriby vs Matlock Town</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.02</v>
+        <v>3.6</v>
       </c>
       <c r="C42" t="n">
-        <v>12</v>
+        <v>3.6</v>
       </c>
       <c r="D42" t="n">
-        <v>23</v>
+        <v>1.75</v>
       </c>
       <c r="E42" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="F42" t="n">
-        <v>1.26</v>
+        <v>2.12</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1563,23 +1563,23 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Japonya (K) vs Tayland (K)</t>
+          <t>Hallam vs Liversedge</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C43" t="n">
-        <v>41</v>
+        <v>3.5</v>
       </c>
       <c r="D43" t="n">
-        <v>1.06</v>
+        <v>1.95</v>
       </c>
       <c r="E43" t="n">
-        <v>1.06</v>
+        <v>1.55</v>
       </c>
       <c r="F43" t="n">
-        <v>7</v>
+        <v>2.25</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1590,23 +1590,23 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Güney Kore (K) vs Myanmar (K)</t>
+          <t>Bridlington Town vs West Auckland Town</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C44" t="n">
-        <v>41</v>
+        <v>3.5</v>
       </c>
       <c r="D44" t="n">
-        <v>1.06</v>
+        <v>3</v>
       </c>
       <c r="E44" t="n">
-        <v>1.06</v>
+        <v>1.62</v>
       </c>
       <c r="F44" t="n">
-        <v>6.5</v>
+        <v>2.1</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1617,17 +1617,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Safa vs Sabah</t>
+          <t>Pontefract Collieries vs Blyth Spartans</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>6</v>
+        <v>1.55</v>
       </c>
       <c r="C45" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D45" t="n">
         <v>4.5</v>
-      </c>
-      <c r="D45" t="n">
-        <v>1.38</v>
       </c>
       <c r="E45" t="n">
         <v>1.53</v>
@@ -1644,23 +1644,23 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Qalali vs Umm Al Hassam</t>
+          <t>Consett vs Silsden</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>8.5</v>
+        <v>1.68</v>
       </c>
       <c r="C46" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="D46" t="n">
-        <v>1.25</v>
+        <v>3.7</v>
       </c>
       <c r="E46" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="F46" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1671,23 +1671,23 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Bouri Cultural SC vs Al Shabab Manana</t>
+          <t>Ashington vs Garforth Town</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="C47" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="D47" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="E47" t="n">
-        <v>1.99</v>
+        <v>1.66</v>
       </c>
       <c r="F47" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1698,23 +1698,23 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Isa Town vs Budaiya</t>
+          <t>Carlton Town vs Long Eaton United</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="C48" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="D48" t="n">
-        <v>1.91</v>
+        <v>3.8</v>
       </c>
       <c r="E48" t="n">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="F48" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1725,23 +1725,23 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Drukpa FC vs Royal Thimphu College</t>
+          <t>Boldmere St Michaels vs Coventry United</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2.06</v>
+        <v>2.37</v>
       </c>
       <c r="C49" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="D49" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="E49" t="n">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="F49" t="n">
-        <v>2.31</v>
+        <v>2.08</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -1752,23 +1752,23 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Club Ingenieros vs Hiska Nacional</t>
+          <t>Mickleover Sports vs Coleshill Town</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2.63</v>
+        <v>1.92</v>
       </c>
       <c r="C50" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="D50" t="n">
-        <v>2.1</v>
+        <v>3.15</v>
       </c>
       <c r="E50" t="n">
-        <v>1.3</v>
+        <v>1.58</v>
       </c>
       <c r="F50" t="n">
-        <v>3.15</v>
+        <v>2.16</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -1779,23 +1779,23 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Nacional Potosi U19 vs Universitario de Vinto U19</t>
+          <t>Nuneaton Town vs Wellingborough Town</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1.53</v>
+        <v>2.9</v>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="D51" t="n">
-        <v>4.75</v>
+        <v>2.06</v>
       </c>
       <c r="E51" t="n">
-        <v>1.3</v>
+        <v>1.58</v>
       </c>
       <c r="F51" t="n">
-        <v>3.15</v>
+        <v>2.18</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -1806,23 +1806,23 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Barra Mansa FC vs 7 De Abril RJ</t>
+          <t>Stalybridge Celtic vs Wythenshawe Town</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1.92</v>
+        <v>1.66</v>
       </c>
       <c r="C52" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="D52" t="n">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="E52" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="F52" t="n">
-        <v>2.02</v>
+        <v>2.35</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -1833,23 +1833,23 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Planalto EC U20 vs Goias EC U20</t>
+          <t>Hanley Town vs 1874 Northwich</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>8.5</v>
+        <v>1.6</v>
       </c>
       <c r="C53" t="n">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="D53" t="n">
-        <v>1.28</v>
+        <v>4.25</v>
       </c>
       <c r="E53" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="F53" t="n">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -1860,23 +1860,23 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Ludogorets vs Septemvri Sofia</t>
+          <t>Runcorn Linnets vs Atherton Collieries</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1.22</v>
+        <v>1.76</v>
       </c>
       <c r="C54" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="D54" t="n">
-        <v>10</v>
+        <v>3.6</v>
       </c>
       <c r="E54" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="F54" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -1887,23 +1887,23 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Hebar Pazardzhik vs Etar Veliko Tarnovo</t>
+          <t>Bromley U21 vs Ipswich U21</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1.96</v>
+        <v>2.77</v>
       </c>
       <c r="C55" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="D55" t="n">
-        <v>3.1</v>
+        <v>2.04</v>
       </c>
       <c r="E55" t="n">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="F55" t="n">
-        <v>2.27</v>
+        <v>2.8</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -1914,23 +1914,23 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Midtjylland vs Brondby</t>
+          <t>Gillingham FC U21 vs Birmingham U21</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1.75</v>
+        <v>4.75</v>
       </c>
       <c r="C56" t="n">
-        <v>3.8</v>
+        <v>4.25</v>
       </c>
       <c r="D56" t="n">
-        <v>3.8</v>
+        <v>1.43</v>
       </c>
       <c r="E56" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="F56" t="n">
-        <v>2.23</v>
+        <v>2.73</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -1941,23 +1941,23 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Tartu JK Welco vs Nomme Kalju FC U21</t>
+          <t>Coventry City U21 vs Barnsley U21</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1.16</v>
+        <v>2.07</v>
       </c>
       <c r="C57" t="n">
-        <v>7</v>
+        <v>3.8</v>
       </c>
       <c r="D57" t="n">
-        <v>10</v>
+        <v>2.7</v>
       </c>
       <c r="E57" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="F57" t="n">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -1968,23 +1968,23 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Johvi FC Phoenix vs JK Tallinna Kalev II</t>
+          <t>Peterborough United U21 vs Bristol City U21</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1.47</v>
+        <v>2.05</v>
       </c>
       <c r="C58" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="D58" t="n">
-        <v>4.25</v>
+        <v>2.68</v>
       </c>
       <c r="E58" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="F58" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -1995,23 +1995,23 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Tabasalu Charma vs Tallinna JK Legion</t>
+          <t>Wigan U21 vs Colchester U21</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="C59" t="n">
         <v>4.5</v>
       </c>
       <c r="D59" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="E59" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="F59" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2022,23 +2022,23 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Inter Turku vs VPS</t>
+          <t>Millwall U21 vs Bolton Wanderers U21</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="C60" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="D60" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="E60" t="n">
-        <v>1.96</v>
+        <v>1.43</v>
       </c>
       <c r="F60" t="n">
-        <v>1.74</v>
+        <v>1.45</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2049,23 +2049,23 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Meshakhte Tkibuli vs FC Rustavi</t>
+          <t>Worcester Raiders vs Slimbridge AFC</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4.33</v>
+        <v>2.25</v>
       </c>
       <c r="C61" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="D61" t="n">
-        <v>1.66</v>
+        <v>2.5</v>
       </c>
       <c r="E61" t="n">
-        <v>2.01</v>
+        <v>1.43</v>
       </c>
       <c r="F61" t="n">
-        <v>1.7</v>
+        <v>2.45</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2076,23 +2076,23 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi vs FC Samgurali Tskaltubo</t>
+          <t>Weymouth vs Shaftesbury</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1.91</v>
+        <v>1.47</v>
       </c>
       <c r="C62" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="D62" t="n">
-        <v>3.28</v>
+        <v>4.75</v>
       </c>
       <c r="E62" t="n">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="F62" t="n">
-        <v>1.94</v>
+        <v>2.39</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2103,23 +2103,23 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi vs FC Gagra</t>
+          <t>Sporting Club Inkberrow vs Bishop's Cleeve</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1.64</v>
+        <v>2.4</v>
       </c>
       <c r="C63" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="D63" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="E63" t="n">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="F63" t="n">
-        <v>1.81</v>
+        <v>2.14</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2130,23 +2130,23 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Gorica vs Varazdin</t>
+          <t>Biggleswade Town vs Welwyn Garden City</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3.15</v>
+        <v>2.45</v>
       </c>
       <c r="C64" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="D64" t="n">
-        <v>2.12</v>
+        <v>2.27</v>
       </c>
       <c r="E64" t="n">
-        <v>1.97</v>
+        <v>1.47</v>
       </c>
       <c r="F64" t="n">
-        <v>1.75</v>
+        <v>2.36</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2157,23 +2157,23 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Prayag United vs Mohun Bagan SG Reserves</t>
+          <t>Milton Keynes Irish vs Thame United FC</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="C65" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="D65" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="E65" t="n">
         <v>1.43</v>
       </c>
-      <c r="E65" t="n">
-        <v>1.87</v>
-      </c>
       <c r="F65" t="n">
-        <v>1.81</v>
+        <v>2.4</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2184,23 +2184,23 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>East Bengal II vs Mohammedan SC Reserves</t>
+          <t>Barton Rovers vs Didcot Town</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="C66" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="D66" t="n">
-        <v>4.2</v>
+        <v>1.81</v>
       </c>
       <c r="E66" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="F66" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2211,23 +2211,23 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Mawpat vs Smit</t>
+          <t>Rayo Vallecano vs Espanyol</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1.6</v>
+        <v>2.33</v>
       </c>
       <c r="C67" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="D67" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="E67" t="n">
-        <v>1.47</v>
+        <v>1.97</v>
       </c>
       <c r="F67" t="n">
-        <v>2.27</v>
+        <v>1.87</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2238,14 +2238,14 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Al Naft vs Karbala Fc</t>
+          <t>Alaves vs Valencia</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="C68" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="D68" t="n">
         <v>5</v>
@@ -2254,7 +2254,7 @@
         <v>2.2</v>
       </c>
       <c r="F68" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2265,23 +2265,23 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Al Jolan SC vs Newroz SC</t>
+          <t>Elche vs Real Madrid</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2.63</v>
+        <v>11</v>
       </c>
       <c r="C69" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D69" t="n">
-        <v>2.45</v>
+        <v>1.2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.23</v>
+        <v>1.33</v>
       </c>
       <c r="F69" t="n">
-        <v>1.55</v>
+        <v>3.3</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2292,23 +2292,23 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Erbil SC vs Al Karma</t>
+          <t>Genoa vs Sudtirol</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2.7</v>
+        <v>1.57</v>
       </c>
       <c r="C70" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="D70" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="E70" t="n">
-        <v>2.16</v>
+        <v>1.87</v>
       </c>
       <c r="F70" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -2319,23 +2319,23 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Dundalk FC vs St Patrick's Athletic</t>
+          <t>Fiorentina vs Pisa</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>3</v>
+        <v>1.38</v>
       </c>
       <c r="C71" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="D71" t="n">
-        <v>2.11</v>
+        <v>7</v>
       </c>
       <c r="E71" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="F71" t="n">
-        <v>2.02</v>
+        <v>2.31</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -2346,23 +2346,23 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Waterford FC vs Derry City</t>
+          <t>Crotone vs Inter Milano U23</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2.59</v>
+        <v>1.97</v>
       </c>
       <c r="C72" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="D72" t="n">
-        <v>2.37</v>
+        <v>3.5</v>
       </c>
       <c r="E72" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="F72" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -2373,23 +2373,23 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Shelbourne vs Drogheda United</t>
+          <t>Picerno vs Catania</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1.79</v>
+        <v>3.15</v>
       </c>
       <c r="C73" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="D73" t="n">
-        <v>4</v>
+        <v>2.18</v>
       </c>
       <c r="E73" t="n">
-        <v>1.86</v>
+        <v>2.34</v>
       </c>
       <c r="F73" t="n">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -2400,23 +2400,23 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sligo Rovers FC vs Galway United</t>
+          <t>Casertana vs Altamura</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>3</v>
+        <v>1.66</v>
       </c>
       <c r="C74" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="D74" t="n">
-        <v>2.09</v>
+        <v>4.5</v>
       </c>
       <c r="E74" t="n">
-        <v>1.68</v>
+        <v>2.06</v>
       </c>
       <c r="F74" t="n">
-        <v>2.03</v>
+        <v>1.66</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -2427,23 +2427,23 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Midleton FC vs Rockmount</t>
+          <t>Giugliano vs Cosenza</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="C75" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="D75" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="E75" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="F75" t="n">
         <v>1.64</v>
-      </c>
-      <c r="F75" t="n">
-        <v>2.05</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -2454,23 +2454,23 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Douglas Hall vs Carrigaline United</t>
+          <t>Scafatese vs Monopoli</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1.87</v>
+        <v>2.63</v>
       </c>
       <c r="C76" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="D76" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="E76" t="n">
-        <v>1.72</v>
+        <v>2.45</v>
       </c>
       <c r="F76" t="n">
-        <v>1.94</v>
+        <v>1.47</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -2481,23 +2481,23 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Hapoel Haifa vs Bnei Sakhnin FC</t>
+          <t>Cavese vs Sorrento</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1.87</v>
+        <v>2.16</v>
       </c>
       <c r="C77" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="D77" t="n">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="E77" t="n">
-        <v>2.06</v>
+        <v>2.45</v>
       </c>
       <c r="F77" t="n">
-        <v>1.68</v>
+        <v>1.45</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -2508,23 +2508,23 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan vs Maccabi Netanya</t>
+          <t>Barletta vs Salernitana</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>4.33</v>
+        <v>2.55</v>
       </c>
       <c r="C78" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="D78" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="E78" t="n">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="F78" t="n">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -2535,23 +2535,23 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Hapoel Ironi Kiryat Shmona vs Maccabi Haifa FC</t>
+          <t>Casarano vs Audace Cerignola</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>3.4</v>
+        <v>2.27</v>
       </c>
       <c r="C79" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="D79" t="n">
-        <v>1.86</v>
+        <v>2.77</v>
       </c>
       <c r="E79" t="n">
-        <v>1.66</v>
+        <v>1.93</v>
       </c>
       <c r="F79" t="n">
-        <v>2.09</v>
+        <v>1.76</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -2562,23 +2562,23 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Maccabi Tel-Aviv vs Hapoel Tel-Aviv</t>
+          <t>Foggia vs Savoia</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>2.11</v>
+        <v>1.74</v>
       </c>
       <c r="C80" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="D80" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="E80" t="n">
-        <v>1.53</v>
+        <v>2.04</v>
       </c>
       <c r="F80" t="n">
-        <v>2.33</v>
+        <v>1.68</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -2589,23 +2589,23 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya vs KAFR Qasim</t>
+          <t>Bari vs Potenza</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="C81" t="n">
         <v>3.3</v>
       </c>
       <c r="D81" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="E81" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="F81" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -2616,23 +2616,23 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>IFK Haninge vs Syrianska FC</t>
+          <t>Duisburg vs Havelse</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="C82" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="D82" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="E82" t="n">
-        <v>1.16</v>
+        <v>1.41</v>
       </c>
       <c r="F82" t="n">
-        <v>4.25</v>
+        <v>2.63</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -2643,23 +2643,23 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>IK Sirius FK vs Degerfors IF</t>
+          <t>Meppen vs Viktoria Koln</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1.41</v>
+        <v>2.63</v>
       </c>
       <c r="C83" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="D83" t="n">
-        <v>6</v>
+        <v>2.26</v>
       </c>
       <c r="E83" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="F83" t="n">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -2670,23 +2670,23 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Djurgardens IF vs GAIS</t>
+          <t>Wurzburger Kickers vs Aachen</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1.47</v>
+        <v>3.1</v>
       </c>
       <c r="C84" t="n">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="D84" t="n">
-        <v>5</v>
+        <v>1.99</v>
       </c>
       <c r="E84" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="F84" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -2697,23 +2697,23 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Norrby IF vs Varbergs BoIS FC</t>
+          <t>Jahn Regensburg vs Fortuna Dusseldorf</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="C85" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="D85" t="n">
-        <v>2.27</v>
+        <v>2.09</v>
       </c>
       <c r="E85" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="F85" t="n">
-        <v>1.99</v>
+        <v>2.2</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -2724,23 +2724,23 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Orebro SK vs United IK Nordic</t>
+          <t>Sonnenhof vs Veri</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="C86" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="D86" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="E86" t="n">
-        <v>1.68</v>
+        <v>1.32</v>
       </c>
       <c r="F86" t="n">
-        <v>2.02</v>
+        <v>3</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -2751,23 +2751,23 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Ostersunds FK vs Helsingborgs IF</t>
+          <t>Hallescher vs Carl Zeiss Jena</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1.87</v>
+        <v>2.45</v>
       </c>
       <c r="C87" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="D87" t="n">
-        <v>3.6</v>
+        <v>2.55</v>
       </c>
       <c r="E87" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="F87" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -2778,23 +2778,23 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Vikingur Reykjavik vs Keflavik</t>
+          <t>FSV Zwickau vs VSG Altglienicke</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1.22</v>
+        <v>2.73</v>
       </c>
       <c r="C88" t="n">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="D88" t="n">
-        <v>9</v>
+        <v>2.2</v>
       </c>
       <c r="E88" t="n">
-        <v>1.22</v>
+        <v>1.68</v>
       </c>
       <c r="F88" t="n">
-        <v>3.7</v>
+        <v>2.07</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -2805,23 +2805,23 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>FC Osaka vs Ehime FC</t>
+          <t>Drochtersen / Assel vs Kickers Emden</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>3.05</v>
+        <v>1.81</v>
       </c>
       <c r="C89" t="n">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="D89" t="n">
-        <v>2.01</v>
+        <v>3.3</v>
       </c>
       <c r="E89" t="n">
-        <v>1.85</v>
+        <v>1.38</v>
       </c>
       <c r="F89" t="n">
-        <v>1.84</v>
+        <v>2.73</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -2832,23 +2832,23 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Mladost DG vs FK Buducnost Podgorica</t>
+          <t>Gil Vicente FC U23 vs Portimonense U23</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>2.6</v>
+        <v>1.78</v>
       </c>
       <c r="C90" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="D90" t="n">
-        <v>2.45</v>
+        <v>3.7</v>
       </c>
       <c r="E90" t="n">
-        <v>2.18</v>
+        <v>1.7</v>
       </c>
       <c r="F90" t="n">
-        <v>1.58</v>
+        <v>2</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -2859,23 +2859,23 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>OFK Petrovac vs FK Arsenal Tivat</t>
+          <t>SC Farense U23 vs Leixoes U23</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1.66</v>
+        <v>2.25</v>
       </c>
       <c r="C91" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="D91" t="n">
-        <v>4.75</v>
+        <v>2.73</v>
       </c>
       <c r="E91" t="n">
-        <v>2.34</v>
+        <v>1.79</v>
       </c>
       <c r="F91" t="n">
-        <v>1.51</v>
+        <v>1.87</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -2886,23 +2886,23 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Mornar Bar vs FK Otrant-Olympic</t>
+          <t>Famalicao U23 vs Rio Ave U23</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="C92" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="D92" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="E92" t="n">
-        <v>2.2</v>
+        <v>1.58</v>
       </c>
       <c r="F92" t="n">
-        <v>1.57</v>
+        <v>2.18</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -2913,23 +2913,23 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Freedom24 Krasava Ypsonas vs Aris Limmasol</t>
+          <t>Vizela U23 vs Maritimo U23</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>4.25</v>
+        <v>1.84</v>
       </c>
       <c r="C93" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="D93" t="n">
-        <v>1.64</v>
+        <v>3.5</v>
       </c>
       <c r="E93" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="F93" t="n">
-        <v>2.09</v>
+        <v>1.9</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -2940,23 +2940,23 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Tigres FC vs Bogota FC</t>
+          <t>Sporting Lisboa U23 vs Academico Viseu U23</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="C94" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="D94" t="n">
-        <v>3.05</v>
+        <v>2.4</v>
       </c>
       <c r="E94" t="n">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="F94" t="n">
-        <v>1.47</v>
+        <v>1.87</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -2967,23 +2967,23 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Leones Reserves vs Universidad de Antioquia</t>
+          <t>Torreense U23 vs Estoril U23</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="C95" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="D95" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="E95" t="n">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="F95" t="n">
-        <v>3.3</v>
+        <v>2.12</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -2994,23 +2994,23 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CD Ciclos vs Molino Viejo</t>
+          <t>Penafiel U23 vs Santa Clara U23</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>5</v>
+        <v>2.45</v>
       </c>
       <c r="C96" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="D96" t="n">
-        <v>1.41</v>
+        <v>2.45</v>
       </c>
       <c r="E96" t="n">
-        <v>1.28</v>
+        <v>1.79</v>
       </c>
       <c r="F96" t="n">
-        <v>3.3</v>
+        <v>1.87</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -3021,23 +3021,23 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Seoul City (K) vs Jeonbuk Hwacheon (K)</t>
+          <t>Ajax vs Willem II</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>5</v>
+        <v>1.12</v>
       </c>
       <c r="C97" t="n">
+        <v>8</v>
+      </c>
+      <c r="D97" t="n">
+        <v>15</v>
+      </c>
+      <c r="E97" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F97" t="n">
         <v>3.8</v>
-      </c>
-      <c r="D97" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="E97" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F97" t="n">
-        <v>2</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -3048,23 +3048,23 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Coleraine Reserves vs Cliftonville Reserves</t>
+          <t>Vitesse U21 vs NAC Breda U21</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="C98" t="n">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="D98" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="E98" t="n">
-        <v>1.58</v>
+        <v>1.28</v>
       </c>
       <c r="F98" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -3075,23 +3075,23 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Crusaders Reserves vs Linfield Reserves</t>
+          <t>NEC Nijmegen U19 vs Feyenoord U19</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="C99" t="n">
-        <v>3.8</v>
+        <v>4.15</v>
       </c>
       <c r="D99" t="n">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="E99" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="F99" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -3102,23 +3102,23 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>FK Rigas FS II vs Skanstes SK</t>
+          <t>Ajax U19 vs AZ Alkmaar U19</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>2.26</v>
+        <v>2.11</v>
       </c>
       <c r="C100" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="D100" t="n">
-        <v>2.35</v>
+        <v>2.68</v>
       </c>
       <c r="E100" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="F100" t="n">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -3129,23 +3129,23 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>FA Siauliai B vs BE1 NFA</t>
+          <t>CA Claypole vs Sacachispas</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="C101" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="D101" t="n">
-        <v>1.53</v>
+        <v>2.09</v>
       </c>
       <c r="E101" t="n">
-        <v>1.55</v>
+        <v>2.63</v>
       </c>
       <c r="F101" t="n">
-        <v>2.23</v>
+        <v>1.41</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -3156,23 +3156,23 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Gzira United FC vs Saint Patrick FC Zabbar</t>
+          <t>CA Sarmiento Reserves vs Racing Club De Avellaneda Reserves</t>
         </is>
       </c>
       <c r="B102" t="n">
         <v>2.55</v>
       </c>
       <c r="C102" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="D102" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="E102" t="n">
-        <v>1.87</v>
+        <v>2.11</v>
       </c>
       <c r="F102" t="n">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -3183,23 +3183,23 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Talaea El Gaish vs Smouha</t>
+          <t>Defensa Y Justicia Reserves vs Central Cordoba Reserves</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>2.5</v>
+        <v>1.66</v>
       </c>
       <c r="C103" t="n">
-        <v>2.68</v>
+        <v>3.6</v>
       </c>
       <c r="D103" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="E103" t="n">
-        <v>3.2</v>
+        <v>1.72</v>
       </c>
       <c r="F103" t="n">
-        <v>1.3</v>
+        <v>1.97</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -3210,23 +3210,23 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra FC vs National Bank of Egypt SC</t>
+          <t>CA Aldosivi Reserves vs Velez Sarsfield Reserves</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>2.45</v>
+        <v>4</v>
       </c>
       <c r="C104" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="D104" t="n">
-        <v>2.68</v>
+        <v>1.72</v>
       </c>
       <c r="E104" t="n">
-        <v>2.37</v>
+        <v>2.03</v>
       </c>
       <c r="F104" t="n">
-        <v>1.51</v>
+        <v>1.68</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -3237,23 +3237,23 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Bodo/Glimt vs Sandefjord</t>
+          <t>Ca Independiente Reserves vs Colon Reserves</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1.16</v>
+        <v>1.53</v>
       </c>
       <c r="C105" t="n">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="D105" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E105" t="n">
-        <v>1.22</v>
+        <v>1.87</v>
       </c>
       <c r="F105" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -3264,23 +3264,23 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Asker Fotball vs KFUM 2</t>
+          <t>Argentinos Juniors Reserves vs CA River Plate Reserves</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>1.11</v>
+        <v>3.3</v>
       </c>
       <c r="C106" t="n">
-        <v>8</v>
+        <v>3.2</v>
       </c>
       <c r="D106" t="n">
-        <v>11</v>
+        <v>1.96</v>
       </c>
       <c r="E106" t="n">
-        <v>1.09</v>
+        <v>2</v>
       </c>
       <c r="F106" t="n">
-        <v>6</v>
+        <v>1.7</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -3291,23 +3291,23 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Akra vs Odds Ballklubb II</t>
+          <t>Centro Espanol Reserve vs Leandro N. Alem Reserves</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>3.7</v>
+        <v>1.22</v>
       </c>
       <c r="C107" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="D107" t="n">
-        <v>1.62</v>
+        <v>9</v>
       </c>
       <c r="E107" t="n">
-        <v>1.16</v>
+        <v>1.57</v>
       </c>
       <c r="F107" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -3318,23 +3318,23 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Viking (A) vs Varhaug</t>
+          <t>El Porvenir Reserves vs Canuelas FC Reserves</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>1.33</v>
+        <v>2.15</v>
       </c>
       <c r="C108" t="n">
-        <v>5</v>
+        <v>3.05</v>
       </c>
       <c r="D108" t="n">
-        <v>5.5</v>
+        <v>2.8</v>
       </c>
       <c r="E108" t="n">
-        <v>1.18</v>
+        <v>2.03</v>
       </c>
       <c r="F108" t="n">
-        <v>4</v>
+        <v>1.64</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -3345,23 +3345,23 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Aalesund FK II vs Spjelkavik</t>
+          <t>Victoriano Arenas Reserves vs CA Lugano Reserves</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="C109" t="n">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="D109" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="E109" t="n">
-        <v>1.18</v>
+        <v>1.72</v>
       </c>
       <c r="F109" t="n">
-        <v>3.8</v>
+        <v>1.96</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -3372,23 +3372,23 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Aasane Fotball II vs Brann 2</t>
+          <t>Defensores de Cambaceres Reserves vs Central Ballester Reserves</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>2.12</v>
+        <v>1.18</v>
       </c>
       <c r="C110" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="D110" t="n">
-        <v>2.4</v>
+        <v>9.5</v>
       </c>
       <c r="E110" t="n">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="F110" t="n">
-        <v>4.75</v>
+        <v>2.7</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -3399,23 +3399,23 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>FK Fauske/Sprint vs Stromsgodset (A)</t>
+          <t>Leones de Rosario Reserves vs Sacachispas Reserves</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>2.5</v>
+        <v>1.72</v>
       </c>
       <c r="C111" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="D111" t="n">
-        <v>2.12</v>
+        <v>3.8</v>
       </c>
       <c r="E111" t="n">
-        <v>1.13</v>
+        <v>1.76</v>
       </c>
       <c r="F111" t="n">
-        <v>4.5</v>
+        <v>1.92</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -3426,23 +3426,23 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Skjetten vs Tromso 2</t>
+          <t>Excursionistas Reserves vs San Martin Burzaco Reserves</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1.66</v>
+        <v>1.33</v>
       </c>
       <c r="C112" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="D112" t="n">
-        <v>3.6</v>
+        <v>6.5</v>
       </c>
       <c r="E112" t="n">
-        <v>1.22</v>
+        <v>1.51</v>
       </c>
       <c r="F112" t="n">
-        <v>3.8</v>
+        <v>2.36</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -3453,23 +3453,23 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Skedsmo vs Lillestrom (A)</t>
+          <t>Gol Gohar vs Al Jazira SC</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>1.68</v>
+        <v>4</v>
       </c>
       <c r="C113" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="D113" t="n">
-        <v>3.4</v>
+        <v>1.72</v>
       </c>
       <c r="E113" t="n">
-        <v>1.16</v>
+        <v>1.94</v>
       </c>
       <c r="F113" t="n">
-        <v>4.15</v>
+        <v>1.76</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -3480,23 +3480,23 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Benjamin Aceval vs Paraguari AC</t>
+          <t>Arkadag vs Al-Muharraq</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>2</v>
+        <v>2.68</v>
       </c>
       <c r="C114" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="D114" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="E114" t="n">
-        <v>2.07</v>
+        <v>2.26</v>
       </c>
       <c r="F114" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -3507,23 +3507,23 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Club Guarani Asuncion Reserves vs Cerro Porteno Reserve</t>
+          <t>Kashima Antlers vs Newcastle Jets</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>1.98</v>
+        <v>1.27</v>
       </c>
       <c r="C115" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="D115" t="n">
+        <v>8</v>
+      </c>
+      <c r="E115" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="F115" t="n">
         <v>3</v>
-      </c>
-      <c r="E115" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="F115" t="n">
-        <v>2.02</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -3534,23 +3534,23 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Rubio Nu Reserve vs Nacional Asunción Reserve</t>
+          <t>Daejeon Citizen vs Kyoto</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>19</v>
+        <v>2.03</v>
       </c>
       <c r="C116" t="n">
-        <v>12</v>
+        <v>3.5</v>
       </c>
       <c r="D116" t="n">
-        <v>1.05</v>
+        <v>3.2</v>
       </c>
       <c r="E116" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="F116" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -3561,23 +3561,23 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Radomiak Radom vs Piast Gliwice</t>
+          <t>Gamba Osaka vs Cong Anh Ha Noi</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>2.34</v>
+        <v>1.41</v>
       </c>
       <c r="C117" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D117" t="n">
-        <v>2.63</v>
+        <v>6</v>
       </c>
       <c r="E117" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="F117" t="n">
-        <v>2.07</v>
+        <v>2.39</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -3588,23 +3588,23 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Stal Mielec vs Termalica BB Nieciecza</t>
+          <t>Ratchaburi vs Shanghai Port</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="C118" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="D118" t="n">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="E118" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="F118" t="n">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -3615,23 +3615,23 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Ballkani vs Dukagjini</t>
+          <t>Johor DT vs Buriram United</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="C119" t="n">
-        <v>3.15</v>
+        <v>4.15</v>
       </c>
       <c r="D119" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="E119" t="n">
-        <v>2.01</v>
+        <v>1.6</v>
       </c>
       <c r="F119" t="n">
-        <v>1.68</v>
+        <v>2.18</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -3642,23 +3642,23 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>KF Llapi Podujeve vs Malisheva</t>
+          <t>Beijing Guoan vs Pohang Steelers</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>2.8</v>
+        <v>1.81</v>
       </c>
       <c r="C120" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="D120" t="n">
-        <v>2.18</v>
+        <v>3.8</v>
       </c>
       <c r="E120" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="F120" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -3669,23 +3669,23 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>U Cluj vs Otelul Galati</t>
+          <t>Al Ain vs Al Nassr</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>1.71</v>
+        <v>4.15</v>
       </c>
       <c r="C121" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="D121" t="n">
-        <v>4.25</v>
+        <v>1.66</v>
       </c>
       <c r="E121" t="n">
-        <v>1.76</v>
+        <v>1.51</v>
       </c>
       <c r="F121" t="n">
-        <v>1.92</v>
+        <v>2.39</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -3696,23 +3696,23 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>FCSB vs Petrolul Ploiesti</t>
+          <t>Al Hilal vs Al-Gharafa</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>1.37</v>
+        <v>1.05</v>
       </c>
       <c r="C122" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="D122" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E122" t="n">
-        <v>1.6</v>
+        <v>1.22</v>
       </c>
       <c r="F122" t="n">
-        <v>2.15</v>
+        <v>3.7</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -3723,23 +3723,23 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Dinamo Barnaul vs KDV Tomsk</t>
+          <t>Vietnam U23 vs Kuveyt U23</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>4.75</v>
+        <v>1.81</v>
       </c>
       <c r="C123" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="D123" t="n">
-        <v>1.53</v>
+        <v>3.7</v>
       </c>
       <c r="E123" t="n">
-        <v>1.64</v>
+        <v>2.01</v>
       </c>
       <c r="F123" t="n">
-        <v>2.08</v>
+        <v>1.7</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -3750,23 +3750,23 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Spartak Kostroma vs Neftekhimik Nizhnekamsk</t>
+          <t>Katar U23 vs Güney Kore U23</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>1.71</v>
+        <v>15</v>
       </c>
       <c r="C124" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="D124" t="n">
-        <v>4.5</v>
+        <v>1.13</v>
       </c>
       <c r="E124" t="n">
-        <v>2</v>
+        <v>1.58</v>
       </c>
       <c r="F124" t="n">
-        <v>1.74</v>
+        <v>2.2</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -3777,23 +3777,23 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Kamaz Nab Chelny vs FC Chelyabinsk</t>
+          <t>South Melbourne vs Queensland Lions</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>1.98</v>
+        <v>1.71</v>
       </c>
       <c r="C125" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="D125" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="E125" t="n">
-        <v>2.23</v>
+        <v>1.68</v>
       </c>
       <c r="F125" t="n">
-        <v>1.58</v>
+        <v>2.06</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -3804,23 +3804,23 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Shinnik Yaroslav vs Ural Yekaterinburg</t>
+          <t>UFC Fehring vs FC Grossklein</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>3.3</v>
+        <v>2.77</v>
       </c>
       <c r="C126" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="D126" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="E126" t="n">
-        <v>2.12</v>
+        <v>1.35</v>
       </c>
       <c r="F126" t="n">
-        <v>1.64</v>
+        <v>2.8</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -3831,23 +3831,23 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Veles Moscow vs Sochi</t>
+          <t>Furstenfeld vs SV Lebring</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>3.5</v>
+        <v>2.39</v>
       </c>
       <c r="C127" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="D127" t="n">
-        <v>2.04</v>
+        <v>2.31</v>
       </c>
       <c r="E127" t="n">
-        <v>2.11</v>
+        <v>1.38</v>
       </c>
       <c r="F127" t="n">
-        <v>1.66</v>
+        <v>2.7</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -3858,23 +3858,23 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Zemun vs Radnik Surdulica</t>
+          <t>SV Wildon vs SV Rohrbach/Lafnitz</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>3.1</v>
+        <v>1.83</v>
       </c>
       <c r="C128" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D128" t="n">
         <v>3.15</v>
       </c>
-      <c r="D128" t="n">
-        <v>2.1</v>
-      </c>
       <c r="E128" t="n">
-        <v>2.12</v>
+        <v>1.38</v>
       </c>
       <c r="F128" t="n">
-        <v>1.64</v>
+        <v>2.73</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -3885,20 +3885,24 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ZFK Radnicki 1923 (K) vs ZFK Spartak Subotica (K)</t>
+          <t>Ilzer SV vs SV Pachern</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>19</v>
+        <v>1.22</v>
       </c>
       <c r="C129" t="n">
-        <v>9</v>
+        <v>5.5</v>
       </c>
       <c r="D129" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
+        <v>8.5</v>
+      </c>
+      <c r="E129" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="F129" t="n">
+        <v>2.9</v>
+      </c>
       <c r="G129" t="inlineStr">
         <is>
           <t>-</t>
@@ -3908,23 +3912,23 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Geylang United FC vs Tanjong Pagar United FC</t>
+          <t>SK Vorwarts Steyr vs SV Sedda Bad Schallerbach</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>1.47</v>
+        <v>1.97</v>
       </c>
       <c r="C130" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="D130" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="E130" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="F130" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -3935,23 +3939,23 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Vion Zlate Moravce vs MFK Zvolen</t>
+          <t>CDT Real Oruro vs Real Potosi</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>1.72</v>
+        <v>2.9</v>
       </c>
       <c r="C131" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="D131" t="n">
-        <v>3.7</v>
+        <v>2.03</v>
       </c>
       <c r="E131" t="n">
-        <v>1.68</v>
+        <v>1.51</v>
       </c>
       <c r="F131" t="n">
-        <v>2.04</v>
+        <v>2.36</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -3962,23 +3966,23 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Ns Mura U19 vs NK Triglav Kranj U19</t>
+          <t>Lokomotiv G.O. vs OFC Nesebar</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>2.12</v>
+        <v>1.74</v>
       </c>
       <c r="C132" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="D132" t="n">
-        <v>2.73</v>
+        <v>4.15</v>
       </c>
       <c r="E132" t="n">
-        <v>1.53</v>
+        <v>2.07</v>
       </c>
       <c r="F132" t="n">
-        <v>2.26</v>
+        <v>1.64</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -3989,23 +3993,23 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>NK Aluminij U19 vs NK Bravo U19</t>
+          <t>Ludogorets II vs Fratria</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="C133" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="D133" t="n">
-        <v>1.81</v>
+        <v>2.02</v>
       </c>
       <c r="E133" t="n">
-        <v>1.38</v>
+        <v>1.84</v>
       </c>
       <c r="F133" t="n">
-        <v>2.55</v>
+        <v>1.85</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -4016,23 +4020,23 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>NK Brezice U19 vs Jadran Dekani U19</t>
+          <t>Trinec vs Mlada Boleslav</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C134" t="n">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="D134" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="E134" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="F134" t="n">
-        <v>2.73</v>
+        <v>3.2</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -4043,23 +4047,23 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Al Okhdood U21 vs AL Taawoun U21</t>
+          <t>Graffin Vlasim vs Slovan Liberec</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>3.6</v>
+        <v>8</v>
       </c>
       <c r="C135" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D135" t="n">
-        <v>1.79</v>
+        <v>1.22</v>
       </c>
       <c r="E135" t="n">
-        <v>1.72</v>
+        <v>1.33</v>
       </c>
       <c r="F135" t="n">
-        <v>1.92</v>
+        <v>2.9</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -4070,23 +4074,23 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>AL Hazem U21 vs Al-Fateh Al-Ahsa U21</t>
+          <t>Skovshoved IF vs FC Kopenhag</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>3.5</v>
+        <v>29</v>
       </c>
       <c r="C136" t="n">
-        <v>3.5</v>
+        <v>17</v>
       </c>
       <c r="D136" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="E136" t="n">
         <v>1.66</v>
       </c>
       <c r="F136" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -4097,23 +4101,23 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Al Orobah U21 vs Al-Faisaly Harmah U21</t>
+          <t>Hellerup vs Esbjerg</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>2.6</v>
+        <v>4.33</v>
       </c>
       <c r="C137" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="D137" t="n">
-        <v>2.31</v>
+        <v>1.58</v>
       </c>
       <c r="E137" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="F137" t="n">
-        <v>1.9</v>
+        <v>2.27</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -4124,23 +4128,23 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>AL Ittihad Jeddah U21 vs Al-Qadisiyah Khobar U21</t>
+          <t>Nordsjaelland (K) vs Midtjylland (K)</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>2.01</v>
+        <v>1.51</v>
       </c>
       <c r="C138" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="D138" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="E138" t="n">
-        <v>1.75</v>
+        <v>1.37</v>
       </c>
       <c r="F138" t="n">
-        <v>1.94</v>
+        <v>2.73</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -4151,23 +4155,23 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Al-Bukayriyah FC vs Damac FC</t>
+          <t>Silkeborg U19 vs FC Copenhagen U19</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="C139" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="D139" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="E139" t="n">
-        <v>2.27</v>
+        <v>1.41</v>
       </c>
       <c r="F139" t="n">
-        <v>1.53</v>
+        <v>2.63</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -4178,17 +4182,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Al-Ula vs Jeddah Club</t>
+          <t>Aston Villa U21 vs Real Sociedad U21</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1.13</v>
+        <v>3.7</v>
       </c>
       <c r="C140" t="n">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="D140" t="n">
-        <v>13.25</v>
+        <v>1.7</v>
       </c>
       <c r="E140" t="n">
         <v>1.53</v>
@@ -4205,23 +4209,23 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Al Wahda Mecca vs Al Akhdoud</t>
+          <t>Tottenham U21 vs GNK Dinamo Zagreb U21</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="C141" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="D141" t="n">
-        <v>3.28</v>
+        <v>2.77</v>
       </c>
       <c r="E141" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="F141" t="n">
-        <v>1.84</v>
+        <v>2.25</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -4232,23 +4236,23 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Al Najma (SAUD) vs Al Raed Buraidah</t>
+          <t>JK Trans Narva II vs Tartu Tammeka U21</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>2.31</v>
+        <v>1.2</v>
       </c>
       <c r="C142" t="n">
-        <v>3.28</v>
+        <v>6</v>
       </c>
       <c r="D142" t="n">
-        <v>2.63</v>
+        <v>7.5</v>
       </c>
       <c r="E142" t="n">
-        <v>1.87</v>
+        <v>1.18</v>
       </c>
       <c r="F142" t="n">
-        <v>1.81</v>
+        <v>4.33</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -4259,23 +4263,23 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Dynamo Kiev vs Epitsentr Dunayivtsi</t>
+          <t>Levadia Tallinn U19 vs JK Tulevik Viljandi</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="C143" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="D143" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="E143" t="n">
-        <v>1.62</v>
+        <v>1.16</v>
       </c>
       <c r="F143" t="n">
-        <v>2.14</v>
+        <v>4.5</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -4286,23 +4290,23 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk vs Chornomorets Odessa</t>
+          <t>Barry Town vs Ammanford</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="C144" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="D144" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E144" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="F144" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -4313,23 +4317,23 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Polissya Zhytomyr II vs Ahrobiznes Volochysk</t>
+          <t>Connah's Quay vs Airbus</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>2.5</v>
+        <v>1.43</v>
       </c>
       <c r="C145" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="D145" t="n">
-        <v>2.45</v>
+        <v>5.5</v>
       </c>
       <c r="E145" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="F145" t="n">
-        <v>1.79</v>
+        <v>2.25</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -4340,23 +4344,23 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>FC Oleksandriya vs FC Viktoriya Sumy</t>
+          <t>Trefelin vs Cambrian &amp; Clydach</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>1.81</v>
+        <v>3.4</v>
       </c>
       <c r="C146" t="n">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="D146" t="n">
-        <v>3.8</v>
+        <v>1.84</v>
       </c>
       <c r="E146" t="n">
-        <v>2.08</v>
+        <v>1.62</v>
       </c>
       <c r="F146" t="n">
-        <v>1.66</v>
+        <v>2.12</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -4367,23 +4371,23 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Mar de Fondo vs CA Terremoto Buceo</t>
+          <t>Llandudno vs Caernarfon Town</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="C147" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="D147" t="n">
-        <v>2.34</v>
+        <v>1.98</v>
       </c>
       <c r="E147" t="n">
-        <v>2.01</v>
+        <v>1.58</v>
       </c>
       <c r="F147" t="n">
-        <v>1.66</v>
+        <v>2.22</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -4394,23 +4398,23 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Juventud De Las Piedras Reserves vs Montevideo City Torque Reserve</t>
+          <t>The New Saints vs Flint Town United</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>2.18</v>
+        <v>1.12</v>
       </c>
       <c r="C148" t="n">
-        <v>3.4</v>
+        <v>7.5</v>
       </c>
       <c r="D148" t="n">
-        <v>2.68</v>
+        <v>13.25</v>
       </c>
       <c r="E148" t="n">
-        <v>1.66</v>
+        <v>1.22</v>
       </c>
       <c r="F148" t="n">
-        <v>2.02</v>
+        <v>3.7</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -4421,23 +4425,23 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Nacional de Montevideo Reserves vs Ca Penarol Reserves</t>
+          <t>Holywell vs Colwyn Bay</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>2.09</v>
+        <v>7.5</v>
       </c>
       <c r="C149" t="n">
-        <v>3.28</v>
+        <v>5</v>
       </c>
       <c r="D149" t="n">
-        <v>2.9</v>
+        <v>1.28</v>
       </c>
       <c r="E149" t="n">
-        <v>1.81</v>
+        <v>1.47</v>
       </c>
       <c r="F149" t="n">
-        <v>1.87</v>
+        <v>2.4</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -4448,23 +4452,23 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Boston River Reserves vs Cerro Largo FC Reserves</t>
+          <t>Penybont vs Briton Ferry Athletic</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>2</v>
+        <v>1.51</v>
       </c>
       <c r="C150" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="D150" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="E150" t="n">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="F150" t="n">
-        <v>2.11</v>
+        <v>1.81</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -4475,23 +4479,23 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Club Oriental Reserves vs CA River Plate Montevideo Reserves</t>
+          <t>NK Bjelovar vs Karlovac</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>2.63</v>
+        <v>4.25</v>
       </c>
       <c r="C151" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="D151" t="n">
-        <v>2.23</v>
+        <v>1.6</v>
       </c>
       <c r="E151" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="F151" t="n">
-        <v>1.96</v>
+        <v>2.18</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -4502,23 +4506,23 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Racing Club de Montevideo Reserves vs Deportivo Maldonado Reserves</t>
+          <t>Coal India SPA vs Bhawanipore</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>2.27</v>
+        <v>4.75</v>
       </c>
       <c r="C152" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="D152" t="n">
-        <v>2.58</v>
+        <v>1.6</v>
       </c>
       <c r="E152" t="n">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="F152" t="n">
-        <v>1.95</v>
+        <v>1.66</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -4529,23 +4533,23 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Defensor Sporting Reserves vs Central Espanol Reserves</t>
+          <t>MLS FC Lawngtlai vs Dinthar</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>1.64</v>
+        <v>2.11</v>
       </c>
       <c r="C153" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="D153" t="n">
-        <v>4</v>
+        <v>2.73</v>
       </c>
       <c r="E153" t="n">
         <v>1.58</v>
       </c>
       <c r="F153" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -4556,23 +4560,23 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Liverpool Montevideo Reserves vs Colon Montevideo Reserves</t>
+          <t>Ramthar vs Kanan</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>1.81</v>
+        <v>1.53</v>
       </c>
       <c r="C154" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="D154" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="E154" t="n">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="F154" t="n">
-        <v>2.12</v>
+        <v>2.45</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -4583,23 +4587,23 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Panionios NFC vs Apollon Kalamarias</t>
+          <t>Sohryngkham vs Mawryngkneng</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="C155" t="n">
-        <v>4.33</v>
+        <v>3.15</v>
       </c>
       <c r="D155" t="n">
-        <v>9</v>
+        <v>2.37</v>
       </c>
       <c r="E155" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="F155" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -4610,25 +4614,1751 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Panthrakikos vs PAOK Salonic B</t>
+          <t>South United vs Real Bengaluru</t>
         </is>
       </c>
       <c r="B156" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="C156" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D156" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E156" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="F156" t="n">
+        <v>3</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Bengaluru United vs Kickstart FC</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C157" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D157" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E157" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="F157" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Blarney United vs College Corinthians FC</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C158" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D158" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="E158" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F158" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Stenhousemuir vs Partick Thistle</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="C159" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D159" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="E159" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="F159" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Falkirk vs Hearts</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C160" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D160" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="E160" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="F160" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Hibernian vs Kilmarnock</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="C161" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D161" t="n">
+        <v>6</v>
+      </c>
+      <c r="E161" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F161" t="n">
         <v>2.45</v>
       </c>
-      <c r="C156" t="n">
-        <v>3</v>
-      </c>
-      <c r="D156" t="n">
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Motherwell vs Aberdeen</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="C162" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D162" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E162" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="F162" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Ross County vs Queen of the South</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="C163" t="n">
+        <v>5</v>
+      </c>
+      <c r="D163" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E163" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F163" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Ironi Tiberias vs Hapoel Jerusalem FC</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C164" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D164" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E164" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="F164" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Beitar Jerusalem vs Maccabi Petach Tikva</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="C165" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D165" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E165" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="F165" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Maccabi Tel Aviv U19 vs Hapoel Rishon Lezion U19</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="C166" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D166" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="E166" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F166" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Hapoel Hadera U19 vs Hapoel Katamon Jerusalem U19</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="C167" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D167" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="E167" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F167" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Hapoel Beer Sheva U19 vs Hapoel Tel Aviv U19</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C168" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D168" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="E168" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="F168" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Maccabi Haifa U19 vs Maccabi Petach Tikva U19</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="C169" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D169" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E169" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F169" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Hapoel Nir Ramat Hasharon U19 vs Hapoel Kiryat Shmona U19</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="C170" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D170" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="E170" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F170" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Hapoel Petach Tikva U19 vs Maccabi Herzliya U19</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="C171" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D171" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E171" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="F171" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Hapoel Kfar Saba U19 vs Hapoel Haifa U19</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="C172" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D172" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="E172" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="F172" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Hapoel Raanana U19 vs Bnei Yehuda Tel Aviv U19</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C173" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D173" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E173" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="F173" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>SC Newe Yosef U19 vs Maccabi Tzur Shalom U19</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="C174" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D174" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E174" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="F174" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Landskrona Bois vs GIF Sundsvall</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="C175" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D175" t="n">
+        <v>7</v>
+      </c>
+      <c r="E175" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F175" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>IK Brage Borlange vs Sandvikens IF</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C176" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D176" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="E176" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F176" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>IFK Varnamo vs Osters IF</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="C177" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D177" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E177" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F177" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Grasshopper vs Sion</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C178" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D178" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="E178" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="F178" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Fram Reykjavik vs Breidablik Kopavogur</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C179" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D179" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E179" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F179" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>FK Jezero Plav vs FK Bokelj Kotor</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="C180" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D180" t="n">
         <v>2.63</v>
       </c>
-      <c r="E156" t="n">
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Belen Arco Zaragoza vs Politecnico J.I.C.</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="C181" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D181" t="n">
         <v>2.27</v>
       </c>
-      <c r="F156" t="n">
+      <c r="E181" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F181" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Soccer Law vs Dimelo Jara</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="C182" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D182" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="E182" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="F182" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Glentoran vs Coleraine</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C183" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D183" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E183" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="F183" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Portadown FC vs Linfield</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>7</v>
+      </c>
+      <c r="C184" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D184" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E184" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F184" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Limavady United vs Bangor</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="C185" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D185" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E185" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F185" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Crusaders FC vs Dungannon Swifts</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C186" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D186" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="E186" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F186" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Larne vs Cliftonville FC</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C187" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D187" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E187" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F187" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Ballymena United FC vs Carrick Rangers</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C188" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D188" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E188" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F188" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Dergview Fc vs Portstewart</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C189" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D189" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E189" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F189" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Ballyclare Comrades vs Knockbreda</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
         <v>1.55</v>
       </c>
-      <c r="G156" t="inlineStr">
+      <c r="C190" t="n">
+        <v>4</v>
+      </c>
+      <c r="D190" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E190" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F190" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>SK Super Nova vs Riga</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>9</v>
+      </c>
+      <c r="C191" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D191" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E191" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="F191" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Wady Degla vs Al Moqawloon Al Arab</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="C192" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D192" t="n">
+        <v>4</v>
+      </c>
+      <c r="E192" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="F192" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Asyut Cement Petroleum vs Modern Sport FC</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C193" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D193" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="E193" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F193" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Al Ahly Cairo vs Abu Qir Semad FC</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="C194" t="n">
+        <v>5</v>
+      </c>
+      <c r="D194" t="n">
+        <v>10</v>
+      </c>
+      <c r="E194" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F194" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Al Masry Club vs Al Ittihad Al Sakandary</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="C195" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D195" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E195" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="F195" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Liga Desportiva De Sofala vs Clube Ferroviario De Maputo</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="C196" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="D196" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E196" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F196" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>FC Bunyodkor vs Lokomotiv Tashkent FK</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="C197" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D197" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="E197" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="F197" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Andijan vs Olympic Mobiuz</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="C198" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D198" t="n">
+        <v>7</v>
+      </c>
+      <c r="E198" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F198" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Club Atletico Tembetary vs Club Sportivo Carapegua</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="C199" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D199" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E199" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="F199" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Rakow Czestochowa vs Zaglebie Lubin</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="C200" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D200" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E200" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="F200" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Korona Kielce vs Gornik Zabrze</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="C201" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D201" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E201" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="F201" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Widzew Lodz II vs Polonia Bytom</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>6</v>
+      </c>
+      <c r="C202" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="D202" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E202" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="F202" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>CSM Resita vs FC Bacau</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C203" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D203" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E203" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="F203" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>SSU Politehnica Timisoara (W) vs CFF Olimpia Cluj (K)</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C204" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D204" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E204" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="F204" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Etoile de L'Est vs Gicumbi FC</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C205" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D205" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="E205" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="F205" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Kiyovu Sport vs Bugesera FC</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="C206" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D206" t="n">
+        <v>4</v>
+      </c>
+      <c r="E206" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F206" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Etincelles FC vs Musanze FC</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C207" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D207" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E207" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="F207" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Tj Druzstevnik Velke Ludince vs DAC Dunajska</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>46</v>
+      </c>
+      <c r="C208" t="n">
+        <v>17</v>
+      </c>
+      <c r="D208" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E208" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="F208" t="n">
+        <v>5</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Al Adalah vs Al Jandal</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>2</v>
+      </c>
+      <c r="C209" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D209" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E209" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="F209" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Al-Orubah vs Al-Jeel</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C210" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D210" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E210" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="F210" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Chiangmai United FC vs Khon Kaen United</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C211" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D211" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="E211" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="F211" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Police Tero FC vs Songkhla FC</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="C212" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="D212" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E212" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F212" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>PT Satun vs Muang Thong United</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C213" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D213" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E213" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="F213" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Villa SC vs Kigezi Homeboys</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C214" t="n">
+        <v>4</v>
+      </c>
+      <c r="D214" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E214" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="F214" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Bul FC vs Blacks Power</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C215" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D215" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E215" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F215" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>NEC FC Bugolobi vs Uganda Revenue Authority SC</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>2</v>
+      </c>
+      <c r="C216" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D216" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E216" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="F216" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Shakhtar Donetsk U21 vs FC Chernomorets Odessa U21</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="C217" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D217" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="E217" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="F217" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Montevideo Wanderers Reserves vs La Luz Reserves</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="C218" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D218" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E218" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F218" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Albion Reserves vs CA Progreso Reserves</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="C219" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D219" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="E219" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F219" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Liverpool Montevideo Reserves vs Colon Montevideo Reserves</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="C220" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D220" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E220" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F220" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G220" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/bugun_oranlar.xlsx
+++ b/bugun_oranlar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H123"/>
+  <dimension ref="A1:H149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,28 +461,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>St Ives Town vs Corby Town</t>
+          <t>Bayern Munchen (K) vs Manchester City (K)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="F2" t="n">
-        <v>1.58</v>
+        <v>1.32</v>
       </c>
       <c r="G2" t="n">
-        <v>2.18</v>
+        <v>3.05</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -493,28 +493,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Coleshill Town vs Sutton Coldfield Town</t>
+          <t>Inter Milano (K) vs BK Hacken (K)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2.35</v>
+        <v>2.07</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="E3" t="n">
-        <v>2.45</v>
+        <v>3.05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="G3" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -525,28 +525,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bournemouth U21 vs Stoke U21</t>
+          <t>Real Madrid (K) vs Paris Saint Germain (K)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="D4" t="n">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="F4" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -557,28 +557,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bolton Wanderers U21 vs Queens Park Rangers U21</t>
+          <t>Arsenal (K) vs Koge (K)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.87</v>
+        <v>1.05</v>
       </c>
       <c r="D5" t="n">
-        <v>3.8</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>3.05</v>
+        <v>23</v>
       </c>
       <c r="F5" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="G5" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -589,28 +589,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Redditch United vs Racing Club Warwick</t>
+          <t>Juventus (K) vs SL Benfica (Kadınlar)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="D6" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="F6" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="G6" t="n">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -621,28 +621,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Trento vs Pro Vercelli</t>
+          <t>Farnborough vs Uxbridge</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="D7" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9</v>
+        <v>1.43</v>
       </c>
       <c r="G7" t="n">
-        <v>1.79</v>
+        <v>2.6</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -653,28 +653,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Treviso vs Desenzano Calvina</t>
+          <t>Wingate &amp; Finchley vs Hemel Hempstead Town</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.01</v>
+        <v>4.5</v>
       </c>
       <c r="D8" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>3.4</v>
+        <v>1.58</v>
       </c>
       <c r="F8" t="n">
-        <v>2.33</v>
+        <v>1.55</v>
       </c>
       <c r="G8" t="n">
-        <v>1.53</v>
+        <v>2.3</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -685,28 +685,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi vs Lumezzane</t>
+          <t>Truro vs Merthyr Town</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2.12</v>
+        <v>1.72</v>
       </c>
       <c r="D9" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="E9" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="F9" t="n">
-        <v>2.25</v>
+        <v>1.58</v>
       </c>
       <c r="G9" t="n">
-        <v>1.55</v>
+        <v>2.23</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -717,28 +717,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Guidonia Montecelio vs Livorno</t>
+          <t>Gainsborough Trinity vs Leamington</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2.31</v>
+        <v>1.97</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="F10" t="n">
-        <v>2.31</v>
+        <v>1.74</v>
       </c>
       <c r="G10" t="n">
-        <v>1.51</v>
+        <v>1.97</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -749,28 +749,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pianese vs Sambenedettese</t>
+          <t>Chippenham Town vs Yate Town</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="E11" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="F11" t="n">
-        <v>2.33</v>
+        <v>1.6</v>
       </c>
       <c r="G11" t="n">
-        <v>1.51</v>
+        <v>2.18</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -781,28 +781,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Spezia vs Vis Pesaro</t>
+          <t>Worksop Town vs Telford</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.2</v>
+        <v>2.18</v>
       </c>
       <c r="D12" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="E12" t="n">
-        <v>10</v>
+        <v>2.73</v>
       </c>
       <c r="F12" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="G12" t="n">
-        <v>2.31</v>
+        <v>2.04</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -813,28 +813,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>US Fezzanese vs Gozzano</t>
+          <t>Dag &amp; Red vs Waltham Abbey</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.15</v>
+        <v>1.41</v>
       </c>
       <c r="D13" t="n">
-        <v>3.05</v>
+        <v>4.33</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2</v>
+        <v>1.47</v>
       </c>
       <c r="G13" t="n">
-        <v>1.58</v>
+        <v>2.4</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -850,23 +850,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Chievo Verona vs Virtus Bergamo</t>
+          <t>Bowers &amp; Pitsea vs Grays Athletic</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.6</v>
+        <v>1.97</v>
       </c>
       <c r="D14" t="n">
         <v>3.4</v>
       </c>
       <c r="E14" t="n">
-        <v>4.75</v>
+        <v>3.15</v>
       </c>
       <c r="F14" t="n">
-        <v>2.03</v>
+        <v>1.72</v>
       </c>
       <c r="G14" t="n">
-        <v>1.68</v>
+        <v>1.97</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -877,28 +877,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SC Paderborn 07 II vs BV Borussia 09 Dortmund II</t>
+          <t>Cambridge City vs Witham Town</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2.8</v>
+        <v>1.62</v>
       </c>
       <c r="D15" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="F15" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="G15" t="n">
-        <v>2.31</v>
+        <v>2.18</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -909,28 +909,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Werder Bremen (K) vs Stuttgart (K)</t>
+          <t>Concord Rangers vs Buckhurst Hill</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="D16" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="E16" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="F16" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="G16" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -941,28 +941,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>43 dk içinde</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Vizela U23 vs Farense U23</t>
+          <t>Newmarket Town vs Brightlingsea Regent</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2.45</v>
+        <v>1.71</v>
       </c>
       <c r="D17" t="n">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="G17" t="n">
-        <v>1.87</v>
+        <v>2.14</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -973,28 +973,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Uniao de Leiria U23 vs Gil Vicente U23</t>
+          <t>Felixstowe &amp; Walton United FC vs AFC Sudbury</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2.16</v>
+        <v>1.64</v>
       </c>
       <c r="D18" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="E18" t="n">
-        <v>2.8</v>
+        <v>4.15</v>
       </c>
       <c r="F18" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="G18" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1005,28 +1005,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Porto (K) vs Braga (W)</t>
+          <t>Wroxham vs Gorleston</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="D19" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="E19" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="F19" t="n">
-        <v>1.66</v>
+        <v>1.87</v>
       </c>
       <c r="G19" t="n">
-        <v>1.99</v>
+        <v>1.8</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1037,28 +1037,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Botswana U20 vs Malawi U20</t>
+          <t>Fakenham Town vs Mulbarton Wanderers</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2.55</v>
+        <v>2.39</v>
       </c>
       <c r="D20" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="E20" t="n">
-        <v>2.63</v>
+        <v>2.35</v>
       </c>
       <c r="F20" t="n">
-        <v>2.7</v>
+        <v>1.47</v>
       </c>
       <c r="G20" t="n">
-        <v>1.41</v>
+        <v>2.4</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1069,28 +1069,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>South Africa U20 vs Angola U20</t>
+          <t>Hashtag United vs Walthamstow</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="E21" t="n">
-        <v>3.8</v>
+        <v>6.5</v>
       </c>
       <c r="F21" t="n">
-        <v>2.12</v>
+        <v>1.47</v>
       </c>
       <c r="G21" t="n">
-        <v>1.51</v>
+        <v>2.4</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1101,26 +1101,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1 de Maio de Benguela vs CD Lunda-Sul</t>
+          <t>Takeley vs Redbridge</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2.15</v>
+        <v>3.28</v>
       </c>
       <c r="D22" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="E22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="F22" t="inlineStr"/>
+        <v>1.87</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.58</v>
+      </c>
       <c r="G22" t="n">
-        <v>1.41</v>
+        <v>2.22</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1131,28 +1133,28 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CSD Central Ballester vs Central Cordoba de Rosario</t>
+          <t>Egham Town vs Ascot United</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3.1</v>
+        <v>1.74</v>
       </c>
       <c r="D23" t="n">
-        <v>2.77</v>
+        <v>3.8</v>
       </c>
       <c r="E23" t="n">
-        <v>2.27</v>
+        <v>3.4</v>
       </c>
       <c r="F23" t="n">
-        <v>2.8</v>
+        <v>1.43</v>
       </c>
       <c r="G23" t="n">
-        <v>1.35</v>
+        <v>2.4</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1163,28 +1165,28 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sacachispas vs Victoriano Arenas</t>
+          <t>Binfield vs Moneyfields</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1.93</v>
+        <v>3.8</v>
       </c>
       <c r="D24" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="E24" t="n">
-        <v>3.8</v>
+        <v>1.66</v>
       </c>
       <c r="F24" t="n">
-        <v>2.8</v>
+        <v>1.45</v>
       </c>
       <c r="G24" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1195,28 +1197,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sportivo Barracas vs Canuelas</t>
+          <t>Winchester City vs Bognor Regis Town</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.63</v>
+        <v>2.14</v>
       </c>
       <c r="D25" t="n">
-        <v>2.77</v>
+        <v>3.5</v>
       </c>
       <c r="E25" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="F25" t="n">
-        <v>2.8</v>
+        <v>1.55</v>
       </c>
       <c r="G25" t="n">
-        <v>1.35</v>
+        <v>2.27</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1227,28 +1229,28 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>El Porvenir vs Deportivo Espanol</t>
+          <t>South Park Reigate vs Cray Valley Paper Mills</t>
         </is>
       </c>
       <c r="C26" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E26" t="n">
         <v>2.8</v>
       </c>
-      <c r="D26" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E26" t="n">
-        <v>2.58</v>
-      </c>
       <c r="F26" t="n">
-        <v>3.1</v>
+        <v>1.55</v>
       </c>
       <c r="G26" t="n">
-        <v>1.3</v>
+        <v>2.22</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1259,28 +1261,28 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CA Claypole vs Yupanqui</t>
+          <t>AFC Croydon Athletic vs Erith Town</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2.12</v>
+        <v>1.45</v>
       </c>
       <c r="D27" t="n">
-        <v>2.9</v>
+        <v>4.33</v>
       </c>
       <c r="E27" t="n">
-        <v>3.28</v>
+        <v>5</v>
       </c>
       <c r="F27" t="n">
-        <v>3.1</v>
+        <v>1.41</v>
       </c>
       <c r="G27" t="n">
-        <v>1.43</v>
+        <v>2.68</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1291,28 +1293,28 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CA Fenix vs Deportivo Muniz</t>
+          <t>Faversham Town vs Whitstable Town</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2.31</v>
+        <v>1.66</v>
       </c>
       <c r="D28" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="E28" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="F28" t="n">
-        <v>2.73</v>
+        <v>1.38</v>
       </c>
       <c r="G28" t="n">
-        <v>1.38</v>
+        <v>2.77</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1323,28 +1325,28 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tristan Suarez vs CA Atlanta</t>
+          <t>Brentwood Town vs Maldon &amp; Tiptree</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.95</v>
+        <v>1.66</v>
       </c>
       <c r="D29" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="E29" t="n">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="F29" t="n">
-        <v>2.9</v>
+        <v>1.47</v>
       </c>
       <c r="G29" t="n">
-        <v>1.35</v>
+        <v>2.4</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1355,28 +1357,28 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Club Atletico Aldosivi vs Atletico Tucuman</t>
+          <t>Three Bridges vs Leatherhead</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="D30" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="E30" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G30" t="n">
         <v>2.45</v>
-      </c>
-      <c r="F30" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="G30" t="n">
-        <v>1.43</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1387,28 +1389,28 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Villa San Carlos Reserves vs Deportivo Laferrere Reserves</t>
+          <t>York vs Rotherham</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1.66</v>
+        <v>2.14</v>
       </c>
       <c r="D31" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="E31" t="n">
-        <v>4.15</v>
+        <v>2.8</v>
       </c>
       <c r="F31" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="G31" t="n">
-        <v>1.78</v>
+        <v>2.27</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1419,28 +1421,28 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Deportivo Metalurgico U20 vs Defensores de Glew U20</t>
+          <t>Chesterfield vs Port Vale</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1.83</v>
+        <v>2.12</v>
       </c>
       <c r="D32" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="E32" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="F32" t="n">
-        <v>1.87</v>
+        <v>1.58</v>
       </c>
       <c r="G32" t="n">
-        <v>1.79</v>
+        <v>2.23</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1451,28 +1453,28 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>D10 FC U20 vs San Martin-Monte Grande U20</t>
+          <t>Notts County vs Grimsby</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>2.45</v>
       </c>
       <c r="D33" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="E33" t="n">
-        <v>1.53</v>
+        <v>2.4</v>
       </c>
       <c r="F33" t="n">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="G33" t="n">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1483,28 +1485,28 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sacachispas U20 vs Leandro Niceforo Alem U20</t>
+          <t>Leicester City vs Fulham U21</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2.55</v>
+        <v>1.16</v>
       </c>
       <c r="D34" t="n">
-        <v>3.4</v>
+        <v>6.5</v>
       </c>
       <c r="E34" t="n">
-        <v>2.31</v>
+        <v>10</v>
       </c>
       <c r="F34" t="n">
-        <v>1.6</v>
+        <v>1.18</v>
       </c>
       <c r="G34" t="n">
-        <v>2.08</v>
+        <v>4.2</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1515,28 +1517,28 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Japonya (K) vs Çin Taipei (K)</t>
+          <t>Swindon vs Newport</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>15</v>
+        <v>1.96</v>
       </c>
       <c r="D35" t="n">
-        <v>34</v>
+        <v>3.5</v>
       </c>
       <c r="E35" t="n">
-        <v>2.5</v>
+        <v>3.28</v>
       </c>
       <c r="F35" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="G35" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1547,28 +1549,28 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Vietnam (K) vs Tayland (K)</t>
+          <t>Luton vs Ipswich U21</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2.07</v>
+        <v>1.2</v>
       </c>
       <c r="D36" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>3.1</v>
+        <v>9</v>
       </c>
       <c r="F36" t="n">
-        <v>1.97</v>
+        <v>1.2</v>
       </c>
       <c r="G36" t="n">
-        <v>1.74</v>
+        <v>3.8</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1579,28 +1581,28 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Club Ingenieros vs Club 26 de Febrero Colquiri</t>
+          <t>Crewe vs Aston Villa U21</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2.59</v>
+        <v>1.35</v>
       </c>
       <c r="D37" t="n">
-        <v>3.7</v>
+        <v>4.75</v>
       </c>
       <c r="E37" t="n">
-        <v>2.15</v>
+        <v>5.5</v>
       </c>
       <c r="F37" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="G37" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1611,28 +1613,28 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AB Boliviano U19 vs San Antonio Bulo Bulo U19</t>
+          <t>Gillingham vs Cambridge Utd</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="D38" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="E38" t="n">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="F38" t="n">
-        <v>1.43</v>
+        <v>1.81</v>
       </c>
       <c r="G38" t="n">
-        <v>2.55</v>
+        <v>1.87</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1648,23 +1650,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Always Ready U19 vs Club Aurora U19</t>
+          <t>Rochdale vs Liverpool U21</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="E39" t="n">
         <v>2.9</v>
       </c>
       <c r="F39" t="n">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="G39" t="n">
-        <v>2.01</v>
+        <v>2.54</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -1675,28 +1677,28 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Rio de Janeiro vs Santa Cruz RJ</t>
+          <t>Burton vs Nottingham Forest U21</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3.8</v>
+        <v>1.51</v>
       </c>
       <c r="D40" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="E40" t="n">
-        <v>1.7</v>
+        <v>4.75</v>
       </c>
       <c r="F40" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="G40" t="n">
-        <v>2.4</v>
+        <v>2.73</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -1707,28 +1709,28 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>7 De Abril RJ vs SE Paraty RJ</t>
+          <t>Barnsley vs Leeds U21</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="D41" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="E41" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="F41" t="n">
-        <v>1.68</v>
+        <v>1.28</v>
       </c>
       <c r="G41" t="n">
-        <v>2.01</v>
+        <v>3.3</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -1739,28 +1741,28 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Campineira U20 vs Independente Rio Verde U20</t>
+          <t>Oldham vs Fleetwood Town</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2.27</v>
+        <v>2.16</v>
       </c>
       <c r="D42" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="E42" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="F42" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="G42" t="n">
-        <v>2.01</v>
+        <v>2.14</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -1776,23 +1778,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Jabaquara SP U20 vs Santos FC U20</t>
+          <t>Plymouth vs Crystal Palace U21</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>9</v>
+        <v>1.25</v>
       </c>
       <c r="D43" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="E43" t="n">
-        <v>1.22</v>
+        <v>7.5</v>
       </c>
       <c r="F43" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="G43" t="n">
-        <v>2.27</v>
+        <v>3.5</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -1808,23 +1810,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CA Bandeirante SP U20 vs Red Bull Bragantino SP U20</t>
+          <t>MK Dons vs Crawley</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>13.25</v>
+        <v>1.35</v>
       </c>
       <c r="D44" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E44" t="n">
-        <v>1.12</v>
+        <v>6</v>
       </c>
       <c r="F44" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="G44" t="n">
-        <v>2.73</v>
+        <v>3.2</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -1840,23 +1842,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SC Paulinense SP U20 vs Ibrachina U20</t>
+          <t>Salford vs Sheffield Wednesday</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>7.5</v>
+        <v>2.9</v>
       </c>
       <c r="D45" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="E45" t="n">
-        <v>1.33</v>
+        <v>2.08</v>
       </c>
       <c r="F45" t="n">
-        <v>1.86</v>
+        <v>1.55</v>
       </c>
       <c r="G45" t="n">
-        <v>1.83</v>
+        <v>2.26</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -1872,23 +1874,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>EC XV de Novembro de Jau SP U20 vs Corinthians U20</t>
+          <t>Walsall vs Stevenage</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>7</v>
+        <v>2.63</v>
       </c>
       <c r="D46" t="n">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="E46" t="n">
-        <v>1.33</v>
+        <v>2.4</v>
       </c>
       <c r="F46" t="n">
-        <v>1.62</v>
+        <v>2.02</v>
       </c>
       <c r="G46" t="n">
-        <v>2.11</v>
+        <v>1.71</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -1904,23 +1906,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sao Bernardo SP U20 vs Sao Paulo FC U20</t>
+          <t>Tranmere vs Shrewsbury</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4.75</v>
+        <v>2.2</v>
       </c>
       <c r="D47" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="E47" t="n">
-        <v>1.53</v>
+        <v>2.9</v>
       </c>
       <c r="F47" t="n">
-        <v>1.78</v>
+        <v>2.02</v>
       </c>
       <c r="G47" t="n">
-        <v>1.9</v>
+        <v>1.71</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -1931,28 +1933,28 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ituano SP U20 vs Palmeiras U20</t>
+          <t>Cheltenham vs Exeter</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>9.5</v>
+        <v>2.35</v>
       </c>
       <c r="D48" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="E48" t="n">
-        <v>1.22</v>
+        <v>2.6</v>
       </c>
       <c r="F48" t="n">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="G48" t="n">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -1963,28 +1965,28 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Sportist Svoge vs Vihren Sandanski</t>
+          <t>Wigan vs Blackpool</t>
         </is>
       </c>
       <c r="C49" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="D49" t="n">
         <v>3.7</v>
       </c>
-      <c r="D49" t="n">
-        <v>3.2</v>
-      </c>
       <c r="E49" t="n">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="F49" t="n">
-        <v>2.1</v>
+        <v>1.45</v>
       </c>
       <c r="G49" t="n">
-        <v>1.62</v>
+        <v>2.45</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -1995,28 +1997,28 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Dobrudzha Dobrich vs CSKA Sofia II</t>
+          <t>Accrington vs Sunderland U21</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>3.4</v>
+        <v>1.96</v>
       </c>
       <c r="D50" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="E50" t="n">
-        <v>1.87</v>
+        <v>3</v>
       </c>
       <c r="F50" t="n">
-        <v>1.83</v>
+        <v>1.38</v>
       </c>
       <c r="G50" t="n">
-        <v>1.85</v>
+        <v>2.77</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2027,28 +2029,28 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Pfc Spartak Pleven vs Ludogorets II</t>
+          <t>Peterborough vs Colchester</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2.34</v>
+        <v>1.76</v>
       </c>
       <c r="D51" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="E51" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="F51" t="n">
-        <v>1.99</v>
+        <v>1.47</v>
       </c>
       <c r="G51" t="n">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2059,28 +2061,28 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Montana vs Hebar Pazardzhik</t>
+          <t>Bromley vs Brentford U21</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="E52" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="F52" t="n">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="G52" t="n">
-        <v>1.93</v>
+        <v>2.16</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2091,28 +2093,28 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Koge vs Hobro</t>
+          <t>Bradford vs Newcastle U21</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2.4</v>
+        <v>1.16</v>
       </c>
       <c r="D53" t="n">
-        <v>3.3</v>
+        <v>6.5</v>
       </c>
       <c r="E53" t="n">
-        <v>2.59</v>
+        <v>11</v>
       </c>
       <c r="F53" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="G53" t="n">
-        <v>1.83</v>
+        <v>3.1</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2123,28 +2125,28 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>42 dk içinde</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Sonderjyske U21 vs Silkeborg IF U21</t>
+          <t>Taunton Town vs Bath City</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="D54" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="E54" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="F54" t="n">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="G54" t="n">
-        <v>3.15</v>
+        <v>2.33</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -2155,28 +2157,28 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Dominica vs Anguilla</t>
+          <t>Hartpury University vs Worcester Raiders</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1.2</v>
+        <v>1.85</v>
       </c>
       <c r="D55" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="E55" t="n">
-        <v>10</v>
+        <v>3.2</v>
       </c>
       <c r="F55" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="G55" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -2187,28 +2189,28 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Manta FC vs Orense SC</t>
+          <t>Berkhamsted vs Hanworth Villa</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="D56" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="E56" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="F56" t="n">
-        <v>2.18</v>
+        <v>1.84</v>
       </c>
       <c r="G56" t="n">
-        <v>1.6</v>
+        <v>1.84</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2219,28 +2221,28 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nomme Kalju FC U21 vs Nomme Utd U21</t>
+          <t>Chichester City vs Chertsey Town</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>3.4</v>
+        <v>2.73</v>
       </c>
       <c r="D57" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="E57" t="n">
-        <v>1.68</v>
+        <v>2.05</v>
       </c>
       <c r="F57" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="G57" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2251,28 +2253,28 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Great Olympics vs Attram De Visser</t>
+          <t>Plymouth Parkway vs Frome Town</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2.63</v>
+        <v>2.04</v>
       </c>
       <c r="D58" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="E58" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="F58" t="n">
-        <v>2.58</v>
+        <v>1.58</v>
       </c>
       <c r="G58" t="n">
-        <v>1.4</v>
+        <v>2.18</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2283,28 +2285,28 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Antigua GFC Reserves vs CSD Municipal Reserves</t>
+          <t>Malvern Town vs Gloucester City</t>
         </is>
       </c>
       <c r="C59" t="n">
+        <v>4</v>
+      </c>
+      <c r="D59" t="n">
         <v>3.8</v>
       </c>
-      <c r="D59" t="n">
-        <v>3.7</v>
-      </c>
       <c r="E59" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="F59" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="G59" t="n">
-        <v>2.27</v>
+        <v>2.36</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -2315,28 +2317,28 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Suchitepequez Reserves vs Xelaju Reserves</t>
+          <t>Blyth Spartans vs Ossett United</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2.5</v>
+        <v>1.76</v>
       </c>
       <c r="D60" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="E60" t="n">
-        <v>2.35</v>
+        <v>3.6</v>
       </c>
       <c r="F60" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="G60" t="n">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2347,28 +2349,28 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FC Rustavi vs Iberia 1999</t>
+          <t>West Auckland Town vs Heaton Stannington</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="D61" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="E61" t="n">
-        <v>2.63</v>
+        <v>2.27</v>
       </c>
       <c r="F61" t="n">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="G61" t="n">
-        <v>1.64</v>
+        <v>2.06</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -2379,28 +2381,28 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FC Spaeri vs Dila Gori</t>
+          <t>Liversedge vs Silsden</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2.68</v>
+        <v>1.6</v>
       </c>
       <c r="D62" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="E62" t="n">
-        <v>2.27</v>
+        <v>4</v>
       </c>
       <c r="F62" t="n">
-        <v>1.86</v>
+        <v>1.51</v>
       </c>
       <c r="G62" t="n">
-        <v>1.81</v>
+        <v>2.35</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -2411,28 +2413,28 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>11 dk içinde</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Mylliem SC vs Meghalaya</t>
+          <t>Beverley Town FC vs Pontefract Collieries</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="D63" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="E63" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="F63" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="G63" t="n">
-        <v>1.4</v>
+        <v>2.31</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -2443,28 +2445,28 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ASC And Center vs Kodagu FC</t>
+          <t>Garforth Town vs Lincoln United</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>7</v>
+        <v>1.84</v>
       </c>
       <c r="D64" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="E64" t="n">
-        <v>1.28</v>
+        <v>3.3</v>
       </c>
       <c r="F64" t="n">
-        <v>1.33</v>
+        <v>1.58</v>
       </c>
       <c r="G64" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -2475,28 +2477,28 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Kadhimiya SC vs Al Hussein</t>
+          <t>Rushden And Diamonds vs Bedworth United</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1.8</v>
+        <v>2.16</v>
       </c>
       <c r="D65" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="E65" t="n">
-        <v>4.33</v>
+        <v>2.77</v>
       </c>
       <c r="F65" t="n">
-        <v>2.54</v>
+        <v>1.76</v>
       </c>
       <c r="G65" t="n">
-        <v>1.41</v>
+        <v>1.92</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -2507,28 +2509,28 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Al Etisalat vs Maysan SC</t>
+          <t>Long Eaton United vs Loughborough Students</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1.7</v>
+        <v>2.68</v>
       </c>
       <c r="D66" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="E66" t="n">
-        <v>4.5</v>
+        <v>2.15</v>
       </c>
       <c r="F66" t="n">
-        <v>2.33</v>
+        <v>1.51</v>
       </c>
       <c r="G66" t="n">
-        <v>1.47</v>
+        <v>2.35</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -2539,28 +2541,28 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Niroye Zamini vs FC Fard</t>
+          <t>Nuneaton Town vs Grantham Town</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="D67" t="n">
-        <v>2.73</v>
+        <v>3.5</v>
       </c>
       <c r="E67" t="n">
-        <v>2.77</v>
+        <v>2.63</v>
       </c>
       <c r="F67" t="n">
-        <v>2.9</v>
+        <v>1.55</v>
       </c>
       <c r="G67" t="n">
-        <v>1.35</v>
+        <v>2.26</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -2571,28 +2573,28 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Shahin Bandar Ameri vs Pars Jonoubi Jam</t>
+          <t>Congleton Town vs Bootle</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2.63</v>
+        <v>5</v>
       </c>
       <c r="D68" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="E68" t="n">
-        <v>2.7</v>
+        <v>1.43</v>
       </c>
       <c r="F68" t="n">
-        <v>2.9</v>
+        <v>1.45</v>
       </c>
       <c r="G68" t="n">
-        <v>1.35</v>
+        <v>2.45</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -2603,28 +2605,28 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Arlanda vs Hammarby Talang Ff</t>
+          <t>Mossley vs 1874 Northwich</t>
         </is>
       </c>
       <c r="C69" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="D69" t="n">
         <v>3.8</v>
       </c>
-      <c r="D69" t="n">
-        <v>3.7</v>
-      </c>
       <c r="E69" t="n">
-        <v>1.68</v>
+        <v>5.5</v>
       </c>
       <c r="F69" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="G69" t="n">
-        <v>2.12</v>
+        <v>1.9</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -2635,28 +2637,28 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Vasalunds/Essinge IF vs Assyriska Ff</t>
+          <t>Chasetown vs Padiham</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2.09</v>
+        <v>1.53</v>
       </c>
       <c r="D70" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="E70" t="n">
-        <v>2.8</v>
+        <v>4.75</v>
       </c>
       <c r="F70" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="G70" t="n">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -2667,28 +2669,28 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Jonkopings Sodra vs Skovde AIK</t>
+          <t>Prescot Cables vs Lichfield City</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1.51</v>
+        <v>1.14</v>
       </c>
       <c r="D71" t="n">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="E71" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F71" t="n">
-        <v>1.78</v>
+        <v>1.37</v>
       </c>
       <c r="G71" t="n">
-        <v>1.91</v>
+        <v>2.8</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -2699,28 +2701,28 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Angelholms FF vs Eskilsminne IF</t>
+          <t>Stafford Rangers vs Wythenshawe Town</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="D72" t="n">
         <v>3.5</v>
       </c>
       <c r="E72" t="n">
-        <v>2.4</v>
+        <v>3.05</v>
       </c>
       <c r="F72" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="G72" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -2731,28 +2733,28 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Bogota FC vs Barranquilla FC</t>
+          <t>Leek Town vs Hyde United</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1.74</v>
+        <v>2.4</v>
       </c>
       <c r="D73" t="n">
         <v>3.4</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="F73" t="n">
-        <v>1.92</v>
+        <v>1.62</v>
       </c>
       <c r="G73" t="n">
-        <v>1.76</v>
+        <v>2.12</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -2763,28 +2765,28 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Carrick Rangers Reserves vs Coleraine Reserves</t>
+          <t>Cleethorpes Town vs Redcar Athletic</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3.28</v>
+        <v>2.4</v>
       </c>
       <c r="D74" t="n">
-        <v>4.25</v>
+        <v>3.2</v>
       </c>
       <c r="E74" t="n">
-        <v>1.7</v>
+        <v>2.45</v>
       </c>
       <c r="F74" t="n">
-        <v>1.16</v>
+        <v>1.87</v>
       </c>
       <c r="G74" t="n">
-        <v>4.15</v>
+        <v>1.79</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -2795,28 +2797,28 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Dungannon Swifts Reserves vs Portadown Reserves</t>
+          <t>Bristol City U21 vs Hull City U21</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1.8</v>
+        <v>1.51</v>
       </c>
       <c r="D75" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="E75" t="n">
-        <v>2.8</v>
+        <v>4.25</v>
       </c>
       <c r="F75" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="G75" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -2827,28 +2829,28 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Larne Reserves vs Linfield Reserves</t>
+          <t>Leiston vs Peterborough Sports</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2.37</v>
+        <v>2.14</v>
       </c>
       <c r="D76" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="E76" t="n">
-        <v>2.12</v>
+        <v>2.77</v>
       </c>
       <c r="F76" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="G76" t="n">
-        <v>3.6</v>
+        <v>2.16</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -2859,28 +2861,28 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Glentoran Reserves vs Ballymena United Reserves</t>
+          <t>Bury Town vs Hitchin Town</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1.18</v>
+        <v>1.45</v>
       </c>
       <c r="D77" t="n">
-        <v>5.5</v>
+        <v>4.15</v>
       </c>
       <c r="E77" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="F77" t="n">
-        <v>1.2</v>
+        <v>1.57</v>
       </c>
       <c r="G77" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -2891,28 +2893,28 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Cliftonville Reserves vs Bangor Reserves</t>
+          <t>Worcester City vs Banbury United</t>
         </is>
       </c>
       <c r="C78" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D78" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E78" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F78" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G78" t="n">
         <v>1.62</v>
-      </c>
-      <c r="D78" t="n">
-        <v>4</v>
-      </c>
-      <c r="E78" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F78" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="G78" t="n">
-        <v>3.3</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -2923,28 +2925,28 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>KFUM 2 vs Ready</t>
+          <t>Rushall Olympic vs Kettering Town</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="D79" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="E79" t="n">
-        <v>1.66</v>
+        <v>2.36</v>
       </c>
       <c r="F79" t="n">
-        <v>1.12</v>
+        <v>1.71</v>
       </c>
       <c r="G79" t="n">
-        <v>4.5</v>
+        <v>1.98</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -2955,28 +2957,28 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Odds Ballklubb II vs Stabaek If 2</t>
+          <t>Stratford Town vs Bromsgrove Sporting</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2.15</v>
+        <v>3.5</v>
       </c>
       <c r="D80" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="E80" t="n">
-        <v>2.37</v>
+        <v>1.81</v>
       </c>
       <c r="F80" t="n">
-        <v>1.1</v>
+        <v>1.74</v>
       </c>
       <c r="G80" t="n">
-        <v>5</v>
+        <v>1.95</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -2987,28 +2989,28 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Staal Jorpeland vs Viking (A)</t>
+          <t>Stourbridge vs Real Bedford</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="D81" t="n">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="E81" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="F81" t="n">
-        <v>1.14</v>
+        <v>1.53</v>
       </c>
       <c r="G81" t="n">
-        <v>4.25</v>
+        <v>2.27</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -3019,28 +3021,28 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Madla vs FK Haugesund II</t>
+          <t>Anstey Nomads vs Alvechurch</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1.47</v>
+        <v>2.08</v>
       </c>
       <c r="D82" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="E82" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="F82" t="n">
-        <v>1.2</v>
+        <v>1.87</v>
       </c>
       <c r="G82" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -3056,23 +3058,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Spjelkavik vs Rosenborg BK II</t>
+          <t>Academico Viseu U23 vs Estoril U23</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="D83" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="E83" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="F83" t="n">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="G83" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -3083,28 +3085,28 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Nardo FK Trondheim vs Ranheim 2</t>
+          <t>Volendam vs SV Spakenburg</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1.47</v>
+        <v>3.3</v>
       </c>
       <c r="D84" t="n">
-        <v>4.75</v>
+        <v>3.7</v>
       </c>
       <c r="E84" t="n">
-        <v>4.33</v>
+        <v>1.86</v>
       </c>
       <c r="F84" t="n">
-        <v>1.08</v>
+        <v>1.5</v>
       </c>
       <c r="G84" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -3115,28 +3117,28 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Brumunddal vs Sandefjord 2</t>
+          <t>Sportlust '46 vs Excelsior Maassluis</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>8.5</v>
+        <v>2.9</v>
       </c>
       <c r="D85" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="E85" t="n">
-        <v>1.18</v>
+        <v>2.08</v>
       </c>
       <c r="F85" t="n">
-        <v>1.09</v>
+        <v>1.6</v>
       </c>
       <c r="G85" t="n">
-        <v>5</v>
+        <v>2.18</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -3147,28 +3149,28 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Lyn Oslo 2 vs Sarpsborg 08 2</t>
+          <t>HHC Hardenberg vs BVV Barendrecht</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="D86" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="E86" t="n">
         <v>4.5</v>
       </c>
       <c r="F86" t="n">
-        <v>1.1</v>
+        <v>1.47</v>
       </c>
       <c r="G86" t="n">
-        <v>4.75</v>
+        <v>2.45</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -3179,28 +3181,28 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Brann 2 vs Fk Fyllingsdalen</t>
+          <t>Excelsior '31 FC vs AFC '34 Alkmaar</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="D87" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="E87" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F87" t="n">
-        <v>1.09</v>
+        <v>1.38</v>
       </c>
       <c r="G87" t="n">
-        <v>5</v>
+        <v>2.73</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -3211,28 +3213,28 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Tromso 2 vs Kongsvinger 2</t>
+          <t>Staphorst vs SC Genemuiden</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1.45</v>
+        <v>3.3</v>
       </c>
       <c r="D88" t="n">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="E88" t="n">
-        <v>4.5</v>
+        <v>1.85</v>
       </c>
       <c r="F88" t="n">
-        <v>1.16</v>
+        <v>1.57</v>
       </c>
       <c r="G88" t="n">
-        <v>4.15</v>
+        <v>2.25</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -3243,28 +3245,28 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>FC Pakhtakor Tashkent II vs PFC Shurtan</t>
+          <t>Eemdijk vs RBC Roosendaal</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>5.5</v>
+        <v>2.8</v>
       </c>
       <c r="D89" t="n">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="E89" t="n">
-        <v>1.41</v>
+        <v>2.02</v>
       </c>
       <c r="F89" t="n">
-        <v>1.55</v>
+        <v>1.32</v>
       </c>
       <c r="G89" t="n">
-        <v>2.23</v>
+        <v>3.05</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -3275,28 +3277,28 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Lochin vs Respublika FA</t>
+          <t>ACV Assen vs VV Hoogeveen</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="D90" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="E90" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="F90" t="n">
-        <v>1.66</v>
+        <v>1.28</v>
       </c>
       <c r="G90" t="n">
-        <v>2.05</v>
+        <v>3.3</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -3307,28 +3309,28 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Xorazm Urganch vs PFK Qizilqum Zarafshon</t>
+          <t>GVVV Veenendaal vs SV DVS'33 Ermelo</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>2.08</v>
+        <v>1.4</v>
       </c>
       <c r="D91" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="E91" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="F91" t="n">
-        <v>2.23</v>
+        <v>1.43</v>
       </c>
       <c r="G91" t="n">
-        <v>1.55</v>
+        <v>2.6</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -3339,28 +3341,28 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Benjamin Aceval vs Club Atletico Tembetary</t>
+          <t>Rijnvogels vs Vv Sint Bavo</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="D92" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="E92" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="F92" t="n">
-        <v>1.86</v>
+        <v>1.55</v>
       </c>
       <c r="G92" t="n">
-        <v>1.81</v>
+        <v>2.27</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -3371,28 +3373,28 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>San Lorenzo Reserves vs Olimpia Asuncion Reserves</t>
+          <t>Groene Ster vs Amsterdam Fc</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>10</v>
+        <v>3.8</v>
       </c>
       <c r="D93" t="n">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="E93" t="n">
-        <v>1.16</v>
+        <v>1.62</v>
       </c>
       <c r="F93" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="G93" t="n">
-        <v>3.6</v>
+        <v>2.73</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -3403,28 +3405,28 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Otelul Galati vs Corvinul Hunedoara</t>
+          <t>Koninklijke HFC vs DOVO Veenendaal</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2.63</v>
+        <v>1.64</v>
       </c>
       <c r="D94" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="E94" t="n">
-        <v>2.55</v>
+        <v>4.15</v>
       </c>
       <c r="F94" t="n">
-        <v>2.18</v>
+        <v>1.55</v>
       </c>
       <c r="G94" t="n">
-        <v>1.62</v>
+        <v>2.27</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -3440,23 +3442,23 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Petrolul Ploiesti vs Csikszereda</t>
+          <t>EVV Echt vs RKSV Halsteren</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1.64</v>
+        <v>1.86</v>
       </c>
       <c r="D95" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="E95" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="F95" t="n">
-        <v>1.78</v>
+        <v>1.33</v>
       </c>
       <c r="G95" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -3467,28 +3469,28 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>54 dk içinde</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Amkar Perm vs Dynamo Moscow II</t>
+          <t>DC Power (W) vs Fort Lauderdale United (W)</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1.22</v>
+        <v>1.55</v>
       </c>
       <c r="D96" t="n">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="E96" t="n">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="F96" t="n">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="G96" t="n">
-        <v>3.7</v>
+        <v>1.93</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -3499,28 +3501,28 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Dinamo Kirov vs FK Sokol Saratov</t>
+          <t>Velez Sarsfield Reserves vs Ferro Carril Oeste Reserves</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="D97" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="E97" t="n">
-        <v>4.75</v>
+        <v>7</v>
       </c>
       <c r="F97" t="n">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="G97" t="n">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -3531,28 +3533,28 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Mashuk Pyatigorsk vs FC Volgar Astrakhan</t>
+          <t>San Lorenzo Reserves vs Ca Huracan Reserves</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="D98" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="E98" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="F98" t="n">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="G98" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -3563,28 +3565,28 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Chertanovo Moscow vs FK Kosmos</t>
+          <t>Uribelarrea FC vs Nautico Hacoaj</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1.51</v>
+        <v>2.63</v>
       </c>
       <c r="D99" t="n">
-        <v>3.8</v>
+        <v>2.73</v>
       </c>
       <c r="E99" t="n">
-        <v>5</v>
+        <v>2.63</v>
       </c>
       <c r="F99" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="G99" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -3595,25 +3597,25 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Kvant Obninsk vs Avangard Kursk</t>
+          <t>FCM Traiskirchen vs Kremser SC</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>5</v>
+        <v>1.68</v>
       </c>
       <c r="D100" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="E100" t="n">
-        <v>1.38</v>
+        <v>3.6</v>
       </c>
       <c r="F100" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="G100" t="n">
         <v>2.8</v>
@@ -3627,28 +3629,28 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Backa Topola vs Dubocica</t>
+          <t>Austria Klagenfurt vs SV Donau Klagenfurt</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1.16</v>
+        <v>1.37</v>
       </c>
       <c r="D101" t="n">
-        <v>6</v>
+        <v>4.33</v>
       </c>
       <c r="E101" t="n">
-        <v>12</v>
+        <v>6.5</v>
       </c>
       <c r="F101" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="G101" t="n">
-        <v>2.45</v>
+        <v>2.16</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -3659,28 +3661,28 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>33 dk içinde</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>OFK Vrsac vs Bor 1919</t>
+          <t>Dibba AL Fujairah vs Al Ittifaq Dubai</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="D102" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="E102" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="F102" t="n">
-        <v>1.86</v>
+        <v>1.53</v>
       </c>
       <c r="G102" t="n">
-        <v>1.81</v>
+        <v>2.27</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -3691,28 +3693,28 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>33 dk içinde</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Metalac GM vs Graficar Beograd</t>
+          <t>Al Urooba vs Dubai City FC</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1.94</v>
+        <v>1.41</v>
       </c>
       <c r="D103" t="n">
-        <v>3.28</v>
+        <v>4.33</v>
       </c>
       <c r="E103" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="F103" t="n">
-        <v>2.01</v>
+        <v>1.47</v>
       </c>
       <c r="G103" t="n">
-        <v>1.71</v>
+        <v>2.4</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -3723,28 +3725,28 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Javor Ivanjica vs Proleter 023 Zrenjanin</t>
+          <t>Clube 1992 RS vs Ser Panambi Rs</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1.16</v>
+        <v>4.2</v>
       </c>
       <c r="D104" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="E104" t="n">
-        <v>12</v>
+        <v>1.64</v>
       </c>
       <c r="F104" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="G104" t="n">
-        <v>2.27</v>
+        <v>1.94</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -3755,28 +3757,28 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Napredak Krusevac vs Fk Smederevo</t>
+          <t>Abadia SC U20 vs Itaucu Esporte Clube U20</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>2.04</v>
+        <v>8.5</v>
       </c>
       <c r="D105" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="E105" t="n">
-        <v>3.28</v>
+        <v>1.2</v>
       </c>
       <c r="F105" t="n">
-        <v>2.22</v>
+        <v>1.47</v>
       </c>
       <c r="G105" t="n">
-        <v>1.57</v>
+        <v>2.36</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -3787,28 +3789,28 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub vs Loznica</t>
+          <t>City London FC U20 vs Criciuma U20</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="D106" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="E106" t="n">
-        <v>2.5</v>
+        <v>1.43</v>
       </c>
       <c r="F106" t="n">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="G106" t="n">
-        <v>1.62</v>
+        <v>2.04</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -3819,28 +3821,28 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Spartak Subotica vs Vozdovac</t>
+          <t>US Biskra vs JS Saoura</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1.72</v>
+        <v>2.27</v>
       </c>
       <c r="D107" t="n">
-        <v>3.5</v>
+        <v>2.54</v>
       </c>
       <c r="E107" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="F107" t="n">
-        <v>1.81</v>
+        <v>3.7</v>
       </c>
       <c r="G107" t="n">
-        <v>1.86</v>
+        <v>1.22</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -3851,28 +3853,28 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>ZFK Milutinac (W) vs TSC Kanjiza (K)</t>
+          <t>MC Alger vs MC Oran</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>21</v>
+        <v>1.55</v>
       </c>
       <c r="D108" t="n">
-        <v>9.5</v>
+        <v>3.4</v>
       </c>
       <c r="E108" t="n">
-        <v>1.06</v>
+        <v>5.5</v>
       </c>
       <c r="F108" t="n">
-        <v>1.25</v>
+        <v>2.36</v>
       </c>
       <c r="G108" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -3883,28 +3885,28 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Petrzalka 1898 vs FK Pohronie</t>
+          <t>AGF Aarhus (K) vs Nordsjaelland (K)</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1.62</v>
+        <v>19</v>
       </c>
       <c r="D109" t="n">
-        <v>3.8</v>
+        <v>8</v>
       </c>
       <c r="E109" t="n">
-        <v>4.25</v>
+        <v>1.07</v>
       </c>
       <c r="F109" t="n">
-        <v>1.58</v>
+        <v>1.35</v>
       </c>
       <c r="G109" t="n">
-        <v>2.18</v>
+        <v>2.77</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -3915,28 +3917,28 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>38 dk içinde</t>
+          <t>52 dk içinde</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>FK Kudrivka U21 vs Kolos Kovalivka U21</t>
+          <t>Johvi FC Phoenix U19 vs Tartu FC Helios U19</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>9.5</v>
+        <v>1.87</v>
       </c>
       <c r="D110" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="E110" t="n">
-        <v>1.18</v>
+        <v>2.59</v>
       </c>
       <c r="F110" t="n">
-        <v>1.8</v>
+        <v>1.03</v>
       </c>
       <c r="G110" t="n">
-        <v>1.85</v>
+        <v>9</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -3947,28 +3949,28 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>52 dk içinde</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Albion Reserves vs Defensor Sporting Reserves</t>
+          <t>Flora Tallinn U19 vs JK Trans Narva U19</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="D111" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="E111" t="n">
-        <v>2</v>
+        <v>1.28</v>
       </c>
       <c r="F111" t="n">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="G111" t="n">
-        <v>2.16</v>
+        <v>5.5</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -3979,28 +3981,28 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>52 dk içinde</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Deportivo Maldonado Reserves vs CA River Plate Montevideo Reserves</t>
+          <t>Lootos Polva U19 vs Pohja-Tallinna JK Volta U19</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1.81</v>
+        <v>7.5</v>
       </c>
       <c r="D112" t="n">
-        <v>3.6</v>
+        <v>7.5</v>
       </c>
       <c r="E112" t="n">
-        <v>3.4</v>
+        <v>1.14</v>
       </c>
       <c r="F112" t="n">
-        <v>1.58</v>
+        <v>1.11</v>
       </c>
       <c r="G112" t="n">
-        <v>2.16</v>
+        <v>13.25</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -4011,28 +4013,28 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>51 dk içinde</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Colon Montevideo Reserves vs Juventud De Las Piedras Reserves</t>
+          <t>Havadar SC vs Besat Kermanshah</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>3.15</v>
+        <v>2.45</v>
       </c>
       <c r="D113" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="E113" t="n">
-        <v>1.92</v>
+        <v>2.77</v>
       </c>
       <c r="F113" t="n">
-        <v>1.6</v>
+        <v>2.73</v>
       </c>
       <c r="G113" t="n">
-        <v>2.16</v>
+        <v>1.38</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -4043,28 +4045,28 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Club Oriental Reserves vs Ca Penarol Reserves</t>
+          <t>Naft Masjed Soleyman vs Palayesh Naft Bandar Abbas FC</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>4.33</v>
+        <v>2.6</v>
       </c>
       <c r="D114" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="E114" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="F114" t="n">
-        <v>1.68</v>
+        <v>2.7</v>
       </c>
       <c r="G114" t="n">
-        <v>2.01</v>
+        <v>1.4</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -4075,28 +4077,28 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Central Espanol Reserves vs Boston River Reserves</t>
+          <t>Naft Gachsaran vs Ario Eslamshahr</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>2.54</v>
+        <v>2.25</v>
       </c>
       <c r="D115" t="n">
-        <v>3.4</v>
+        <v>2.77</v>
       </c>
       <c r="E115" t="n">
-        <v>2.31</v>
+        <v>3.15</v>
       </c>
       <c r="F115" t="n">
-        <v>1.64</v>
+        <v>2.8</v>
       </c>
       <c r="G115" t="n">
-        <v>2.09</v>
+        <v>1.35</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -4107,28 +4109,28 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Cerro Largo FC Reserves vs Nacional de Montevideo Reserves</t>
+          <t>East Kilbride vs Celtic II</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="D116" t="n">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="E116" t="n">
-        <v>1.62</v>
+        <v>8</v>
       </c>
       <c r="F116" t="n">
-        <v>1.55</v>
+        <v>1.18</v>
       </c>
       <c r="G116" t="n">
-        <v>2.25</v>
+        <v>4.2</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -4139,28 +4141,28 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>CA Progreso Reserves vs Montevideo Wanderers Reserves</t>
+          <t>Elgin City vs Dundee FC II</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>3.15</v>
+        <v>1.13</v>
       </c>
       <c r="D117" t="n">
-        <v>3.4</v>
+        <v>7</v>
       </c>
       <c r="E117" t="n">
-        <v>1.92</v>
+        <v>12</v>
       </c>
       <c r="F117" t="n">
-        <v>1.66</v>
+        <v>1.25</v>
       </c>
       <c r="G117" t="n">
-        <v>2.07</v>
+        <v>3.5</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -4171,28 +4173,28 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>La Luz Reserves vs Liverpool Montevideo Reserves</t>
+          <t>FC Edinburgh vs Dundee Utd II</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="D118" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="E118" t="n">
-        <v>2.4</v>
+        <v>9</v>
       </c>
       <c r="F118" t="n">
-        <v>1.79</v>
+        <v>1.25</v>
       </c>
       <c r="G118" t="n">
-        <v>1.87</v>
+        <v>3.4</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -4203,28 +4205,28 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Pyrgos vs AE Larissa</t>
+          <t>Kelty Hearts vs Hearts II</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>3.8</v>
+        <v>1.33</v>
       </c>
       <c r="D119" t="n">
-        <v>3.2</v>
+        <v>4.75</v>
       </c>
       <c r="E119" t="n">
-        <v>1.85</v>
+        <v>6</v>
       </c>
       <c r="F119" t="n">
-        <v>2.16</v>
+        <v>1.37</v>
       </c>
       <c r="G119" t="n">
-        <v>1.62</v>
+        <v>2.77</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -4235,28 +4237,28 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>PAOK Salonic B vs Nestos Chrisoupolis</t>
+          <t>Clachnacuddin vs Ross County</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D120" t="n">
-        <v>3.05</v>
+        <v>8.5</v>
       </c>
       <c r="E120" t="n">
-        <v>3.4</v>
+        <v>1.08</v>
       </c>
       <c r="F120" t="n">
-        <v>2.33</v>
+        <v>1.22</v>
       </c>
       <c r="G120" t="n">
-        <v>1.53</v>
+        <v>3.8</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -4267,28 +4269,28 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Panthrakikos vs Niki Volou</t>
+          <t>Gala Fairydean Rovers vs Spartans FC</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="D121" t="n">
-        <v>3.28</v>
+        <v>5</v>
       </c>
       <c r="E121" t="n">
-        <v>1.8</v>
+        <v>1.28</v>
       </c>
       <c r="F121" t="n">
-        <v>2.16</v>
+        <v>1.22</v>
       </c>
       <c r="G121" t="n">
-        <v>1.62</v>
+        <v>3.5</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -4299,28 +4301,28 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Beijing Guoan U20 vs Shenzhen Peng City U20</t>
+          <t>Stirling Albion vs Cumbernauld Colts FC</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="D122" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="E122" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="F122" t="n">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="G122" t="n">
-        <v>2.26</v>
+        <v>2.9</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -4331,30 +4333,856 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Guangdong GZ-Power U20 vs Shandong Taishan U20</t>
+          <t>Formartine United FC vs Montrose</t>
         </is>
       </c>
       <c r="C123" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D123" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E123" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="F123" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G123" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Fraserburgh vs Cove Rangers</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>5</v>
+      </c>
+      <c r="D124" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G124" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Forfar Athletic vs Peterhead</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="D125" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E125" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G125" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Bonnyrigg Rose vs Airdrieonians FC</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D126" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G126" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Queen of the South vs Annan Athletic</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D127" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E127" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G127" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Alloa Athletic vs Hibernian B</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="D128" t="n">
+        <v>6</v>
+      </c>
+      <c r="E128" t="n">
+        <v>10</v>
+      </c>
+      <c r="F128" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G128" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Clyde FC vs Glasgow Rangers II</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D129" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="E129" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F129" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="G129" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Berwick Rangers vs Stranraer</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>4</v>
+      </c>
+      <c r="D130" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F130" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G130" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Clydebank vs St Mirren II</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="D131" t="n">
         <v>4.2</v>
       </c>
-      <c r="D123" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E123" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="F123" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="G123" t="n">
+      <c r="E131" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="F131" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G131" t="n">
+        <v>3</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Banks O'Dee F.C. vs Aberdeen FC II</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D132" t="n">
+        <v>4</v>
+      </c>
+      <c r="E132" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="F132" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G132" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Dumbarton vs Kilmarnock II</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="D133" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="E133" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G133" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Kilwinning Rangers vs Auchinleck Talbot FC</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="D134" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E134" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="F134" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G134" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Hapoel Ironi Acre U19 vs Maccabi Ironi Kiryat Ata U19</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>2</v>
+      </c>
+      <c r="D135" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E135" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Husqvarna FF (W) vs Vaxjo (K)</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D136" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E136" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="F136" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G136" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Breidablik/Augn/Smari U19 vs HK/Ymir U19</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="D137" t="n">
+        <v>6</v>
+      </c>
+      <c r="E137" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F137" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G137" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Al Mesaimeer SC vs Al Waab Sports Club</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="D138" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E138" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F138" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="G138" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Muaither SC vs Al-Khor</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D139" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E139" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="F139" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G139" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>50 dk içinde</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Belen Arco Zaragoza vs Los Embajadores</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>5</v>
+      </c>
+      <c r="D140" t="n">
+        <v>4</v>
+      </c>
+      <c r="E140" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F140" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G140" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>50 dk içinde</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Olimpia J.V. vs E.D.P IND. Medellin</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>10</v>
+      </c>
+      <c r="D141" t="n">
+        <v>6</v>
+      </c>
+      <c r="E141" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F141" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G141" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Dragones Toluca II vs Ajolotes Lerma</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="D142" t="n">
+        <v>4</v>
+      </c>
+      <c r="E142" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G142" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>50 dk içinde</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Boston Cancun FC vs Ejidatarios de Bonfil</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="D143" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E143" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F143" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G143" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Aztecas AMF vs Huracanes Izcalli FC</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="D144" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E144" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F144" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G144" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>AS Douanes de Niamey vs Urana</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D145" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E145" t="n">
+        <v>5</v>
+      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Skjetten vs Skjervoy</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="D146" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E146" t="n">
+        <v>6</v>
+      </c>
+      <c r="F146" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G146" t="n">
+        <v>5</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>3 de Febrero FBC vs River Plate Asuncion</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D147" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E147" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="F147" t="n">
+        <v>2</v>
+      </c>
+      <c r="G147" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>19 dk içinde</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Dumbravita vs CSM Resita</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>5</v>
+      </c>
+      <c r="D148" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E148" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F148" t="n">
         <v>1.76</v>
       </c>
-      <c r="H123" t="inlineStr">
+      <c r="G148" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>ASA Targu Mures vs CS Dinamo Bucuresti</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="D149" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E149" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="F149" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G149" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H149" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/bugun_oranlar.xlsx
+++ b/bugun_oranlar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H149"/>
+  <dimension ref="A1:H97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,28 +461,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>51 dk içinde</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bayern Munchen (K) vs Manchester City (K)</t>
+          <t>Oud-Heverlee Leuven (K) vs AS Roma (K)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.05</v>
+        <v>4.75</v>
       </c>
       <c r="D2" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8</v>
+        <v>1.55</v>
       </c>
       <c r="F2" t="n">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="G2" t="n">
-        <v>3.05</v>
+        <v>2.23</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -493,28 +493,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>51 dk içinde</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Inter Milano (K) vs BK Hacken (K)</t>
+          <t>Servette Chenois (K) vs Lyon (K)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2.07</v>
+        <v>46</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5</v>
+        <v>19</v>
       </c>
       <c r="E3" t="n">
-        <v>3.05</v>
+        <v>1.08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.74</v>
+        <v>1.08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.96</v>
+        <v>6</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -530,23 +530,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Real Madrid (K) vs Paris Saint Germain (K)</t>
+          <t>Barcelona (K) vs Paris FC (K)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.72</v>
+        <v>17</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8</v>
+        <v>36</v>
       </c>
       <c r="E4" t="n">
-        <v>3.8</v>
+        <v>1.08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5</v>
+        <v>1.08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4</v>
+        <v>6.5</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -562,23 +562,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Arsenal (K) vs Koge (K)</t>
+          <t>Chelsea (K) vs Austria Vienna (K)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.05</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="E5" t="n">
-        <v>23</v>
+        <v>1.18</v>
       </c>
       <c r="F5" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="G5" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -589,28 +589,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>6 dk içinde</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Juventus (K) vs SL Benfica (Kadınlar)</t>
+          <t>Breidablik Kopavogur (K) vs Czarni Sosnowiec (K)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="E6" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="F6" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="G6" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -621,28 +621,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>6 dk içinde</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Farnborough vs Uxbridge</t>
+          <t>Sparta Prague (K) vs Farul Constanta (K)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.6</v>
+        <v>1.05</v>
       </c>
       <c r="D7" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>4.33</v>
+        <v>21</v>
       </c>
       <c r="F7" t="n">
-        <v>1.43</v>
+        <v>1.27</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -653,28 +653,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>6 dk içinde</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wingate &amp; Finchley vs Hemel Hempstead Town</t>
+          <t>Brondby (K) vs Sporting (K)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="E8" t="n">
-        <v>1.58</v>
+        <v>2.27</v>
       </c>
       <c r="F8" t="n">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="G8" t="n">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -685,28 +685,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>51 dk içinde</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Truro vs Merthyr Town</t>
+          <t>St. Polten (K) vs Malmo FF (K)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.72</v>
+        <v>3.2</v>
       </c>
       <c r="D9" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="E9" t="n">
-        <v>3.7</v>
+        <v>1.87</v>
       </c>
       <c r="F9" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="G9" t="n">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -717,28 +717,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Gainsborough Trinity vs Leamington</t>
+          <t>Feyenoord (K) vs Valerenga (K)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.97</v>
+        <v>2.6</v>
       </c>
       <c r="D10" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="E10" t="n">
-        <v>3.15</v>
+        <v>2.2</v>
       </c>
       <c r="F10" t="n">
-        <v>1.74</v>
+        <v>1.47</v>
       </c>
       <c r="G10" t="n">
-        <v>1.97</v>
+        <v>2.39</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -749,28 +749,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chippenham Town vs Yate Town</t>
+          <t>PSV (K) vs Fortuna Hjorring (K)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.25</v>
+        <v>1.37</v>
       </c>
       <c r="D11" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="E11" t="n">
-        <v>2.7</v>
+        <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="G11" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -781,28 +781,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Worksop Town vs Telford</t>
+          <t>Hammarby IF (K) vs Rangers (K)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.18</v>
+        <v>1.3</v>
       </c>
       <c r="D12" t="n">
-        <v>3.4</v>
+        <v>4.75</v>
       </c>
       <c r="E12" t="n">
-        <v>2.73</v>
+        <v>6.5</v>
       </c>
       <c r="F12" t="n">
-        <v>1.68</v>
+        <v>1.43</v>
       </c>
       <c r="G12" t="n">
-        <v>2.04</v>
+        <v>2.59</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -813,28 +813,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dag &amp; Red vs Waltham Abbey</t>
+          <t>Wolfsburg (K) vs Sturm Graz (K)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.41</v>
+        <v>1.006</v>
       </c>
       <c r="D13" t="n">
-        <v>4.33</v>
+        <v>15</v>
       </c>
       <c r="E13" t="n">
-        <v>5.5</v>
+        <v>36</v>
       </c>
       <c r="F13" t="n">
-        <v>1.47</v>
+        <v>1.12</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -845,28 +845,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bowers &amp; Pitsea vs Grays Athletic</t>
+          <t>Ajax (K) vs Aktobe (K)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="D14" t="n">
-        <v>3.4</v>
+        <v>13.25</v>
       </c>
       <c r="E14" t="n">
-        <v>3.15</v>
+        <v>29</v>
       </c>
       <c r="F14" t="n">
-        <v>1.72</v>
+        <v>1.11</v>
       </c>
       <c r="G14" t="n">
-        <v>1.97</v>
+        <v>5.5</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -877,28 +877,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cambridge City vs Witham Town</t>
+          <t>Hearts (K) vs Real Sociedad (K)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1.62</v>
+        <v>6.5</v>
       </c>
       <c r="D15" t="n">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="E15" t="n">
-        <v>4.2</v>
+        <v>1.33</v>
       </c>
       <c r="F15" t="n">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="G15" t="n">
-        <v>2.18</v>
+        <v>2.7</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -909,28 +909,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Concord Rangers vs Buckhurst Hill</t>
+          <t>Liverpool (K) vs Sunderland (W)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.94</v>
+        <v>1.2</v>
       </c>
       <c r="D16" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1</v>
+        <v>9.5</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="G16" t="n">
-        <v>2.18</v>
+        <v>2.7</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -941,28 +941,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Newmarket Town vs Brightlingsea Regent</t>
+          <t>Everton (K) vs Birmingham (K)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="D17" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="E17" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="F17" t="n">
-        <v>1.58</v>
+        <v>1.87</v>
       </c>
       <c r="G17" t="n">
-        <v>2.14</v>
+        <v>1.79</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -973,28 +973,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Felixstowe &amp; Walton United FC vs AFC Sudbury</t>
+          <t>Tottenham (K) vs West Ham (K)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.64</v>
+        <v>1.25</v>
       </c>
       <c r="D18" t="n">
-        <v>3.7</v>
+        <v>4.75</v>
       </c>
       <c r="E18" t="n">
-        <v>4.15</v>
+        <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>1.66</v>
+        <v>1.47</v>
       </c>
       <c r="G18" t="n">
-        <v>2.08</v>
+        <v>2.34</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1005,28 +1005,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Wroxham vs Gorleston</t>
+          <t>Nottingham Forest (W) vs Aston Villa (K)</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.26</v>
+        <v>3.7</v>
       </c>
       <c r="D19" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="E19" t="n">
-        <v>2.6</v>
+        <v>1.71</v>
       </c>
       <c r="F19" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="G19" t="n">
-        <v>1.8</v>
+        <v>2.22</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1037,28 +1037,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fakenham Town vs Mulbarton Wanderers</t>
+          <t>Manchester United (K) vs Sheffield United FC (W)</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2.39</v>
+        <v>1.03</v>
       </c>
       <c r="D20" t="n">
-        <v>3.6</v>
+        <v>9.5</v>
       </c>
       <c r="E20" t="n">
-        <v>2.35</v>
+        <v>23</v>
       </c>
       <c r="F20" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="G20" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1069,28 +1069,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hashtag United vs Walthamstow</t>
+          <t>Crystal Palace (K) vs Watford (W)</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="D21" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="E21" t="n">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="F21" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="G21" t="n">
-        <v>2.4</v>
+        <v>3.05</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1101,28 +1101,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Takeley vs Redbridge</t>
+          <t>Leicester (K) vs London City Lionesses (K)</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3.28</v>
+        <v>9.5</v>
       </c>
       <c r="D22" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="E22" t="n">
-        <v>1.87</v>
+        <v>1.18</v>
       </c>
       <c r="F22" t="n">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="G22" t="n">
-        <v>2.22</v>
+        <v>2.8</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1138,23 +1138,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Egham Town vs Ascot United</t>
+          <t>Brighton (K) vs Charlton (K)</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.74</v>
+        <v>1.2</v>
       </c>
       <c r="D23" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>3.4</v>
+        <v>8.5</v>
       </c>
       <c r="F23" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="G23" t="n">
-        <v>2.4</v>
+        <v>2.59</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1170,23 +1170,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Binfield vs Moneyfields</t>
+          <t>Kingstonian vs Bedfont</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3.8</v>
+        <v>1.85</v>
       </c>
       <c r="D24" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="E24" t="n">
-        <v>1.66</v>
+        <v>3.2</v>
       </c>
       <c r="F24" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="G24" t="n">
-        <v>1.5</v>
+        <v>2.34</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1197,28 +1197,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Winchester City vs Bognor Regis Town</t>
+          <t>Sevenoaks Town vs Eastbourne Town</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="D25" t="n">
         <v>3.5</v>
       </c>
       <c r="E25" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="F25" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="G25" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1229,28 +1229,28 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>South Park Reigate vs Cray Valley Paper Mills</t>
+          <t>Boreham Wood vs Everton U21</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2.09</v>
+        <v>1.18</v>
       </c>
       <c r="D26" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="E26" t="n">
-        <v>2.8</v>
+        <v>10</v>
       </c>
       <c r="F26" t="n">
-        <v>1.55</v>
+        <v>1.28</v>
       </c>
       <c r="G26" t="n">
-        <v>2.22</v>
+        <v>3.2</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1266,23 +1266,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AFC Croydon Athletic vs Erith Town</t>
+          <t>Guisborough Town vs Ashington</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.45</v>
+        <v>1.83</v>
       </c>
       <c r="D27" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="F27" t="n">
-        <v>1.41</v>
+        <v>1.66</v>
       </c>
       <c r="G27" t="n">
-        <v>2.68</v>
+        <v>2.03</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1298,23 +1298,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Faversham Town vs Whitstable Town</t>
+          <t>Shifnal Town vs Nantwich Town</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1.66</v>
+        <v>2.5</v>
       </c>
       <c r="D28" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="E28" t="n">
-        <v>3.7</v>
+        <v>2.27</v>
       </c>
       <c r="F28" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="G28" t="n">
-        <v>2.77</v>
+        <v>2.25</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1330,23 +1330,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Brentwood Town vs Maldon &amp; Tiptree</t>
+          <t>Lower Breck vs Atherton Collieries</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.66</v>
+        <v>2.16</v>
       </c>
       <c r="D29" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="E29" t="n">
-        <v>3.8</v>
+        <v>2.63</v>
       </c>
       <c r="F29" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="G29" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1362,23 +1362,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Three Bridges vs Leatherhead</t>
+          <t>London Lions vs Biggleswade</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="D30" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="E30" t="n">
-        <v>1.93</v>
+        <v>1.58</v>
       </c>
       <c r="F30" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="G30" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1394,23 +1394,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>York vs Rotherham</t>
+          <t>Saguntino vs Navalcarnero</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2.14</v>
+        <v>2.6</v>
       </c>
       <c r="D31" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="F31" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="G31" t="n">
         <v>1.55</v>
-      </c>
-      <c r="G31" t="n">
-        <v>2.27</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1421,28 +1421,28 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Chesterfield vs Port Vale</t>
+          <t>Sant Andreu Barcelona vs Real Madrid B</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2.12</v>
+        <v>3</v>
       </c>
       <c r="D32" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="E32" t="n">
-        <v>2.8</v>
+        <v>2.11</v>
       </c>
       <c r="F32" t="n">
-        <v>1.58</v>
+        <v>2.01</v>
       </c>
       <c r="G32" t="n">
-        <v>2.23</v>
+        <v>1.7</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1458,23 +1458,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Notts County vs Grimsby</t>
+          <t>VV Zwaluwen Vlaardingen vs VPV Purmersteijn</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="D33" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="E33" t="n">
         <v>2.4</v>
       </c>
       <c r="F33" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="G33" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1490,23 +1490,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Leicester City vs Fulham U21</t>
+          <t>Tot Ons Genoegen Berkel vs ROHDA Raalte</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1.16</v>
+        <v>3.5</v>
       </c>
       <c r="D34" t="n">
-        <v>6.5</v>
+        <v>4.25</v>
       </c>
       <c r="E34" t="n">
-        <v>10</v>
+        <v>1.68</v>
       </c>
       <c r="F34" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="G34" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1522,23 +1522,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Swindon vs Newport</t>
+          <t>JOS/Watergraafsmeer vs Tielse EC</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1.96</v>
+        <v>4.33</v>
       </c>
       <c r="D35" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="E35" t="n">
-        <v>3.28</v>
+        <v>1.51</v>
       </c>
       <c r="F35" t="n">
-        <v>1.72</v>
+        <v>1.25</v>
       </c>
       <c r="G35" t="n">
-        <v>1.99</v>
+        <v>3.4</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1554,23 +1554,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Luton vs Ipswich U21</t>
+          <t>VV Sparta Nijkerk vs UDI '19</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1.2</v>
+        <v>2.08</v>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="E36" t="n">
-        <v>9</v>
+        <v>2.73</v>
       </c>
       <c r="F36" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="G36" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1586,23 +1586,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Crewe vs Aston Villa U21</t>
+          <t>IJsselmeervogels vs VV Gemert</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="D37" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="E37" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="F37" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="G37" t="n">
-        <v>3.15</v>
+        <v>2.4</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1618,23 +1618,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Gillingham vs Cambridge Utd</t>
+          <t>CA Sarmiento Reserves vs Atletico Rafaela Reserves</t>
         </is>
       </c>
       <c r="C38" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="D38" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E38" t="n">
         <v>2.8</v>
       </c>
-      <c r="D38" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="E38" t="n">
-        <v>2.25</v>
-      </c>
       <c r="F38" t="n">
-        <v>1.81</v>
+        <v>2.12</v>
       </c>
       <c r="G38" t="n">
-        <v>1.87</v>
+        <v>1.64</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1650,23 +1650,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Rochdale vs Liverpool U21</t>
+          <t>Gimnasia La Plata Reserves vs Estudiantes La Plata Reserves</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="D39" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="E39" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="F39" t="n">
-        <v>1.45</v>
+        <v>2.3</v>
       </c>
       <c r="G39" t="n">
-        <v>2.54</v>
+        <v>1.53</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -1682,23 +1682,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Burton vs Nottingham Forest U21</t>
+          <t>CA Aldosivi Reserves vs Quilmes Reserves</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1.51</v>
+        <v>2.58</v>
       </c>
       <c r="D40" t="n">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="E40" t="n">
-        <v>4.75</v>
+        <v>2.45</v>
       </c>
       <c r="F40" t="n">
-        <v>1.38</v>
+        <v>2.12</v>
       </c>
       <c r="G40" t="n">
-        <v>2.73</v>
+        <v>1.62</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -1714,23 +1714,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Barnsley vs Leeds U21</t>
+          <t>Defensa Y Justicia Reserves vs Tigre Reserves</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1.25</v>
+        <v>1.72</v>
       </c>
       <c r="D41" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="E41" t="n">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="F41" t="n">
-        <v>1.28</v>
+        <v>1.87</v>
       </c>
       <c r="G41" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -1741,28 +1741,28 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Oldham vs Fleetwood Town</t>
+          <t>Lanus Reserves vs Banfield Reserves</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2.16</v>
+        <v>1.71</v>
       </c>
       <c r="D42" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="E42" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="F42" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="G42" t="n">
-        <v>2.14</v>
+        <v>2.27</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -1773,28 +1773,28 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Plymouth vs Crystal Palace U21</t>
+          <t>CA Atlas Reserves vs Argentino de Rosario Reserves</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1.25</v>
+        <v>2.03</v>
       </c>
       <c r="D43" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="E43" t="n">
-        <v>7.5</v>
+        <v>2.9</v>
       </c>
       <c r="F43" t="n">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="G43" t="n">
-        <v>3.5</v>
+        <v>2.05</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -1805,28 +1805,28 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MK Dons vs Crawley</t>
+          <t>Canuelas FC Reserves vs Leones de Rosario Reserves</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1.35</v>
+        <v>1.94</v>
       </c>
       <c r="D44" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="E44" t="n">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="F44" t="n">
-        <v>1.28</v>
+        <v>1.84</v>
       </c>
       <c r="G44" t="n">
-        <v>3.2</v>
+        <v>1.85</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -1842,23 +1842,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Salford vs Sheffield Wednesday</t>
+          <t>Lanus (K) vs River Plate (K)</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2.9</v>
+        <v>4.75</v>
       </c>
       <c r="D45" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="E45" t="n">
-        <v>2.08</v>
+        <v>1.62</v>
       </c>
       <c r="F45" t="n">
-        <v>1.55</v>
+        <v>2.04</v>
       </c>
       <c r="G45" t="n">
-        <v>2.26</v>
+        <v>1.66</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -1869,28 +1869,28 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>3 dk içinde</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Walsall vs Stevenage</t>
+          <t>Tristan Suarez Reserves vs Defensores De Belgrano</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2.63</v>
+        <v>2.08</v>
       </c>
       <c r="D46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" t="n">
         <v>3.2</v>
       </c>
-      <c r="E46" t="n">
-        <v>2.4</v>
-      </c>
       <c r="F46" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="G46" t="n">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -1901,28 +1901,28 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tranmere vs Shrewsbury</t>
+          <t>Sportivo Desamparados vs Sportivo Rivadavia San Juan</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="D47" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="E47" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="F47" t="n">
-        <v>2.02</v>
+        <v>1.64</v>
       </c>
       <c r="G47" t="n">
-        <v>1.71</v>
+        <v>2.01</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -1933,28 +1933,28 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cheltenham vs Exeter</t>
+          <t>Sarmiento de Zonda vs CA Union Villa Krause</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2.35</v>
+        <v>4.25</v>
       </c>
       <c r="D48" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="E48" t="n">
-        <v>2.6</v>
+        <v>1.62</v>
       </c>
       <c r="F48" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="G48" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -1970,23 +1970,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Wigan vs Blackpool</t>
+          <t>Suudi Arabistan vs Kuveyt</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2.77</v>
+        <v>1.33</v>
       </c>
       <c r="D49" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="E49" t="n">
-        <v>2.12</v>
+        <v>7.5</v>
       </c>
       <c r="F49" t="n">
-        <v>1.45</v>
+        <v>1.68</v>
       </c>
       <c r="G49" t="n">
-        <v>2.45</v>
+        <v>2.06</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -1997,28 +1997,28 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Accrington vs Sunderland U21</t>
+          <t>SV Gerasdorf Stammersdorf vs Sportunion Mauer</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1.96</v>
+        <v>7</v>
       </c>
       <c r="D50" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="E50" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="F50" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="G50" t="n">
-        <v>2.77</v>
+        <v>2.31</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2034,23 +2034,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Peterborough vs Colchester</t>
+          <t>Itabirito (W) vs Cruzeiro (K)</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1.76</v>
+        <v>6</v>
       </c>
       <c r="D51" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="E51" t="n">
-        <v>3.6</v>
+        <v>1.38</v>
       </c>
       <c r="F51" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="G51" t="n">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2061,28 +2061,28 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Bromley vs Brentford U21</t>
+          <t>Perolas Negras U20 vs Audax Rio RJ U20</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="D52" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="E52" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="F52" t="n">
-        <v>1.62</v>
+        <v>2.16</v>
       </c>
       <c r="G52" t="n">
-        <v>2.16</v>
+        <v>1.58</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2093,28 +2093,28 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Bradford vs Newcastle U21</t>
+          <t>Sao Goncalo U20 vs Olaria RJ U20</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1.16</v>
+        <v>2.55</v>
       </c>
       <c r="D53" t="n">
-        <v>6.5</v>
+        <v>3.15</v>
       </c>
       <c r="E53" t="n">
-        <v>11</v>
+        <v>2.4</v>
       </c>
       <c r="F53" t="n">
-        <v>1.3</v>
+        <v>1.98</v>
       </c>
       <c r="G53" t="n">
-        <v>3.1</v>
+        <v>1.71</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2125,28 +2125,28 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Taunton Town vs Bath City</t>
+          <t>Sao Domingos U20 vs ASA (Agremiação Sportiva Arapiraquense) U20</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2.4</v>
+        <v>13.25</v>
       </c>
       <c r="D54" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="E54" t="n">
-        <v>2.36</v>
+        <v>1.11</v>
       </c>
       <c r="F54" t="n">
         <v>1.51</v>
       </c>
       <c r="G54" t="n">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -2157,28 +2157,28 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Hartpury University vs Worcester Raiders</t>
+          <t>Independente Atalaia U20 vs CS Esportiva U20</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1.85</v>
+        <v>6.5</v>
       </c>
       <c r="D55" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="E55" t="n">
-        <v>3.2</v>
+        <v>1.33</v>
       </c>
       <c r="F55" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="G55" t="n">
-        <v>2.4</v>
+        <v>2.09</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -2189,28 +2189,28 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Berkhamsted vs Hanworth Villa</t>
+          <t>Madureira RJ vs Sampaio Correa RJ</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="D56" t="n">
-        <v>3.28</v>
+        <v>2.9</v>
       </c>
       <c r="E56" t="n">
-        <v>2.39</v>
+        <v>2.68</v>
       </c>
       <c r="F56" t="n">
-        <v>1.84</v>
+        <v>2.37</v>
       </c>
       <c r="G56" t="n">
-        <v>1.84</v>
+        <v>1.5</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2221,28 +2221,28 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Chichester City vs Chertsey Town</t>
+          <t>Gramadense RS vs EC Pelotas</t>
         </is>
       </c>
       <c r="C57" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E57" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F57" t="n">
         <v>2.73</v>
       </c>
-      <c r="D57" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="E57" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="F57" t="n">
-        <v>1.35</v>
-      </c>
       <c r="G57" t="n">
-        <v>2.8</v>
+        <v>1.38</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2253,28 +2253,28 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Plymouth Parkway vs Frome Town</t>
+          <t>Gremio Esportivo Brasil RS vs Ge Gloria</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2.04</v>
+        <v>1.57</v>
       </c>
       <c r="D58" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="E58" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="F58" t="n">
-        <v>1.58</v>
+        <v>2.33</v>
       </c>
       <c r="G58" t="n">
-        <v>2.18</v>
+        <v>1.51</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2285,28 +2285,28 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Malvern Town vs Gloucester City</t>
+          <t>Esmac PA vs Pedreira EC</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D59" t="n">
-        <v>3.8</v>
+        <v>9.5</v>
       </c>
       <c r="E59" t="n">
-        <v>1.64</v>
+        <v>1.02</v>
       </c>
       <c r="F59" t="n">
-        <v>1.5</v>
+        <v>1.16</v>
       </c>
       <c r="G59" t="n">
-        <v>2.36</v>
+        <v>4.33</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -2317,28 +2317,28 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Blyth Spartans vs Ossett United</t>
+          <t>AD Confianca SE U20 vs Aracaju SE U20</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1.76</v>
+        <v>1.96</v>
       </c>
       <c r="D60" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="F60" t="n">
-        <v>1.64</v>
+        <v>1.97</v>
       </c>
       <c r="G60" t="n">
-        <v>2.09</v>
+        <v>1.74</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2349,28 +2349,28 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>West Auckland Town vs Heaton Stannington</t>
+          <t>Falcon SE U20 vs AA Guarany SE U20</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2.55</v>
+        <v>1.32</v>
       </c>
       <c r="D61" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="E61" t="n">
-        <v>2.27</v>
+        <v>6.5</v>
       </c>
       <c r="F61" t="n">
-        <v>1.66</v>
+        <v>1.32</v>
       </c>
       <c r="G61" t="n">
-        <v>2.06</v>
+        <v>3.05</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -2381,28 +2381,28 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Liversedge vs Silsden</t>
+          <t>GE Prudente U20 vs CA Juventus SP U20</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="D62" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="E62" t="n">
-        <v>4</v>
+        <v>2.11</v>
       </c>
       <c r="F62" t="n">
-        <v>1.51</v>
+        <v>1.78</v>
       </c>
       <c r="G62" t="n">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -2413,28 +2413,28 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Beverley Town FC vs Pontefract Collieries</t>
+          <t>Universidad O&amp;M FC vs Atlantico Puerto Plata FC</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3.05</v>
+        <v>1.5</v>
       </c>
       <c r="D63" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="E63" t="n">
-        <v>1.91</v>
+        <v>4.33</v>
       </c>
       <c r="F63" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="G63" t="n">
-        <v>2.31</v>
+        <v>3.3</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -2445,28 +2445,28 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Garforth Town vs Lincoln United</t>
+          <t>Salcedo FC vs Cibao FC</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1.84</v>
+        <v>2.9</v>
       </c>
       <c r="D64" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="E64" t="n">
-        <v>3.3</v>
+        <v>2.18</v>
       </c>
       <c r="F64" t="n">
-        <v>1.58</v>
+        <v>2.14</v>
       </c>
       <c r="G64" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -2477,28 +2477,28 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>32 dk içinde</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Rushden And Diamonds vs Bedworth United</t>
+          <t>Kuzey Kore U20 (K) vs Kolombiya U20 (K)</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2.16</v>
+        <v>1.07</v>
       </c>
       <c r="D65" t="n">
-        <v>3.3</v>
+        <v>8</v>
       </c>
       <c r="E65" t="n">
-        <v>2.77</v>
+        <v>23</v>
       </c>
       <c r="F65" t="n">
-        <v>1.76</v>
+        <v>1.47</v>
       </c>
       <c r="G65" t="n">
-        <v>1.92</v>
+        <v>2.39</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -2509,28 +2509,28 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>2 dk içinde</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Long Eaton United vs Loughborough Students</t>
+          <t>SC Wiedenbruck vs VfL Osnabruck</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2.68</v>
+        <v>8.5</v>
       </c>
       <c r="D66" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="E66" t="n">
-        <v>2.15</v>
+        <v>1.22</v>
       </c>
       <c r="F66" t="n">
-        <v>1.51</v>
+        <v>1.3</v>
       </c>
       <c r="G66" t="n">
-        <v>2.35</v>
+        <v>3.15</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -2541,28 +2541,28 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Nuneaton Town vs Grantham Town</t>
+          <t>West Ham U21 vs Valencia U21</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="D67" t="n">
         <v>3.5</v>
       </c>
       <c r="E67" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="F67" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="G67" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -2573,28 +2573,28 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Congleton Town vs Bootle</t>
+          <t>Middlesbrough U21 vs KRC Genk U21</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="D68" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="E68" t="n">
-        <v>1.43</v>
+        <v>1.97</v>
       </c>
       <c r="F68" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="G68" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -2605,28 +2605,28 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>2 dk içinde</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Mossley vs 1874 Northwich</t>
+          <t>Cebelitarık vs Sao Tome and Principe</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="D69" t="n">
-        <v>3.8</v>
+        <v>4.25</v>
       </c>
       <c r="E69" t="n">
         <v>5.5</v>
       </c>
       <c r="F69" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="G69" t="n">
-        <v>1.9</v>
+        <v>2.16</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -2637,28 +2637,28 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>2 dk içinde</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Chasetown vs Padiham</t>
+          <t>Azerbaycan vs Tacikistan</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="D70" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="E70" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="F70" t="n">
-        <v>1.58</v>
+        <v>2.14</v>
       </c>
       <c r="G70" t="n">
-        <v>2.18</v>
+        <v>1.64</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -2669,29 +2669,25 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>2 dk içinde</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Prescot Cables vs Lichfield City</t>
+          <t>Army Ladies FC (W) vs Epiphany Warriors (W)</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1.14</v>
+        <v>1.72</v>
       </c>
       <c r="D71" t="n">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="E71" t="n">
-        <v>11</v>
-      </c>
-      <c r="F71" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="G71" t="n">
-        <v>2.8</v>
-      </c>
+        <v>4.5</v>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>-</t>
@@ -2701,28 +2697,28 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Stafford Rangers vs Wythenshawe Town</t>
+          <t>Peru U19 vs Argentina U19</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1.95</v>
+        <v>7</v>
       </c>
       <c r="D72" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="E72" t="n">
-        <v>3.05</v>
+        <v>1.38</v>
       </c>
       <c r="F72" t="n">
-        <v>1.62</v>
+        <v>1.97</v>
       </c>
       <c r="G72" t="n">
-        <v>2.15</v>
+        <v>1.72</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -2733,28 +2729,28 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Leek Town vs Hyde United</t>
+          <t>Paraguay U19 vs Chile U19</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="D73" t="n">
         <v>3.4</v>
       </c>
       <c r="E73" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="F73" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="G73" t="n">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -2765,28 +2761,28 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Cleethorpes Town vs Redcar Athletic</t>
+          <t>Chile U20 (W) vs Venezuela U20 (W)</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2.4</v>
+        <v>1.74</v>
       </c>
       <c r="D74" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="E74" t="n">
-        <v>2.45</v>
+        <v>3.8</v>
       </c>
       <c r="F74" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G74" t="n">
         <v>1.87</v>
-      </c>
-      <c r="G74" t="n">
-        <v>1.79</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -2797,22 +2793,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Bristol City U21 vs Hull City U21</t>
+          <t>Hamilton Academical FC vs Cowdenbeath</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1.51</v>
+        <v>1.14</v>
       </c>
       <c r="D75" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="E75" t="n">
-        <v>4.25</v>
+        <v>11</v>
       </c>
       <c r="F75" t="n">
         <v>1.22</v>
@@ -2834,23 +2830,23 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Leiston vs Peterborough Sports</t>
+          <t>Cumnock Juniors FC vs Troon FC</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2.14</v>
+        <v>1.8</v>
       </c>
       <c r="D76" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="E76" t="n">
-        <v>2.77</v>
+        <v>3.28</v>
       </c>
       <c r="F76" t="n">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="G76" t="n">
-        <v>2.16</v>
+        <v>2.73</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -2861,28 +2857,28 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>1 dk içinde</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Bury Town vs Hitchin Town</t>
+          <t>Ironi Beit Shemesh vs Agudat Sport Nordia Jerusalem</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="D77" t="n">
         <v>4.15</v>
       </c>
       <c r="E77" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="F77" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="G77" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -2893,28 +2889,28 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>1 dk içinde</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Worcester City vs Banbury United</t>
+          <t>Hapoel Marmorek vs Shimshon Tel Aviv</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>2.3</v>
+        <v>4.15</v>
       </c>
       <c r="D78" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="E78" t="n">
-        <v>2.8</v>
+        <v>1.72</v>
       </c>
       <c r="F78" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="G78" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -2925,28 +2921,28 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Rushall Olympic vs Kettering Town</t>
+          <t>Sport Club Dimona vs Maccabi Kiryat Malakhi</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2.5</v>
+        <v>1.98</v>
       </c>
       <c r="D79" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E79" t="n">
         <v>3.3</v>
       </c>
-      <c r="E79" t="n">
-        <v>2.36</v>
-      </c>
       <c r="F79" t="n">
-        <v>1.71</v>
+        <v>2.06</v>
       </c>
       <c r="G79" t="n">
-        <v>1.98</v>
+        <v>1.66</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -2957,28 +2953,28 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Stratford Town vs Bromsgrove Sporting</t>
+          <t>Hapoel Ramat Hasharon vs Sderot FC</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>3.5</v>
+        <v>1.99</v>
       </c>
       <c r="D80" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="E80" t="n">
-        <v>1.81</v>
+        <v>3.1</v>
       </c>
       <c r="F80" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="G80" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -2989,28 +2985,28 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Stourbridge vs Real Bedford</t>
+          <t>Hapoel Herzliya vs MS Tzeirey Tira</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>3.8</v>
+        <v>1.85</v>
       </c>
       <c r="D81" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="E81" t="n">
-        <v>1.64</v>
+        <v>3.6</v>
       </c>
       <c r="F81" t="n">
-        <v>1.53</v>
+        <v>2.06</v>
       </c>
       <c r="G81" t="n">
-        <v>2.27</v>
+        <v>1.66</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -3021,28 +3017,28 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Anstey Nomads vs Alvechurch</t>
+          <t>Sport Club Tira vs Hapoel Bnei Musmus</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2.08</v>
+        <v>1.58</v>
       </c>
       <c r="D82" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="E82" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="F82" t="n">
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="G82" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -3053,28 +3049,28 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Academico Viseu U23 vs Estoril U23</t>
+          <t>Beitar Naharia vs Maccabi Neve Shaanan Eldad</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="D83" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E83" t="n">
         <v>3.6</v>
       </c>
-      <c r="E83" t="n">
-        <v>3.5</v>
-      </c>
       <c r="F83" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="G83" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -3085,28 +3081,28 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Volendam vs SV Spakenburg</t>
+          <t>Tzeirei Umm al-Fahm vs Hapoel Umm Al Fahm</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="D84" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="E84" t="n">
-        <v>1.86</v>
+        <v>1.6</v>
       </c>
       <c r="F84" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="G84" t="n">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -3117,28 +3113,28 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Sportlust '46 vs Excelsior Maassluis</t>
+          <t>Hapoel Ironi Baqa Al-Gharbiyye vs Hapoel Tirat HaCarmel</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2.9</v>
+        <v>1.78</v>
       </c>
       <c r="D85" t="n">
         <v>3.5</v>
       </c>
       <c r="E85" t="n">
-        <v>2.08</v>
+        <v>3.5</v>
       </c>
       <c r="F85" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="G85" t="n">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -3149,28 +3145,28 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>HHC Hardenberg vs BVV Barendrecht</t>
+          <t>Hapoel Bnei Lod vs Beitar Tel Aviv Holon</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="D86" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="E86" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="F86" t="n">
-        <v>1.47</v>
+        <v>1.87</v>
       </c>
       <c r="G86" t="n">
-        <v>2.45</v>
+        <v>1.79</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -3181,28 +3177,28 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>1 dk içinde</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Excelsior '31 FC vs AFC '34 Alkmaar</t>
+          <t>Sandvikens IF (W) vs Umea IK (W)</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1.25</v>
+        <v>4.2</v>
       </c>
       <c r="D87" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E87" t="n">
-        <v>8</v>
+        <v>1.58</v>
       </c>
       <c r="F87" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="G87" t="n">
-        <v>2.73</v>
+        <v>2.07</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -3218,17 +3214,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Staphorst vs SC Genemuiden</t>
+          <t>FC Haute-Ajoie vs FC Ajoie-Monterri</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="D88" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="E88" t="n">
-        <v>1.85</v>
+        <v>2.68</v>
       </c>
       <c r="F88" t="n">
         <v>1.57</v>
@@ -3245,28 +3241,28 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Eemdijk vs RBC Roosendaal</t>
+          <t>Turks and Caicos Islands vs Montserrat</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>2.8</v>
+        <v>12</v>
       </c>
       <c r="D89" t="n">
-        <v>3.8</v>
+        <v>6.5</v>
       </c>
       <c r="E89" t="n">
-        <v>2.02</v>
+        <v>1.16</v>
       </c>
       <c r="F89" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="G89" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -3277,28 +3273,28 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ACV Assen vs VV Hoogeveen</t>
+          <t>Bahamas vs Saint Martin</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1.25</v>
+        <v>15</v>
       </c>
       <c r="D90" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="E90" t="n">
-        <v>7.5</v>
+        <v>1.12</v>
       </c>
       <c r="F90" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="G90" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -3309,28 +3305,28 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>59 dk içinde</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>GVVV Veenendaal vs SV DVS'33 Ermelo</t>
+          <t>Necaxa U21 vs Atletico San Luis U21</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="D91" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="E91" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="F91" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="G91" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -3346,23 +3342,23 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Rijnvogels vs Vv Sint Bavo</t>
+          <t>Tlapa Mazatecochco vs Dragones de Oaxaca II</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="D92" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="E92" t="n">
-        <v>3.4</v>
+        <v>2.77</v>
       </c>
       <c r="F92" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="G92" t="n">
-        <v>2.27</v>
+        <v>2.12</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -3373,28 +3369,28 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Groene Ster vs Amsterdam Fc</t>
+          <t>Artesanos Metepec FC vs Toluca U21</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>3.8</v>
+        <v>2.45</v>
       </c>
       <c r="D93" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="E93" t="n">
-        <v>1.62</v>
+        <v>2.45</v>
       </c>
       <c r="F93" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="G93" t="n">
-        <v>2.73</v>
+        <v>1.93</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -3405,28 +3401,28 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Koninklijke HFC vs DOVO Veenendaal</t>
+          <t>Sportivo San Lorenzo vs 4 de Mayo</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1.64</v>
+        <v>1.11</v>
       </c>
       <c r="D94" t="n">
-        <v>3.8</v>
+        <v>7.5</v>
       </c>
       <c r="E94" t="n">
-        <v>4.15</v>
+        <v>15</v>
       </c>
       <c r="F94" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="G94" t="n">
-        <v>2.27</v>
+        <v>2.73</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -3437,28 +3433,28 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>EVV Echt vs RKSV Halsteren</t>
+          <t>Asociacion Deportiva Tarma vs Cienciano Cusco</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1.86</v>
+        <v>2.9</v>
       </c>
       <c r="D95" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="E95" t="n">
-        <v>3.1</v>
+        <v>2.11</v>
       </c>
       <c r="F95" t="n">
-        <v>1.33</v>
+        <v>1.66</v>
       </c>
       <c r="G95" t="n">
-        <v>3</v>
+        <v>2.08</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -3469,28 +3465,28 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>54 dk içinde</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>DC Power (W) vs Fort Lauderdale United (W)</t>
+          <t>Boston River vs Centro Atletico Fenix Montevideo</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1.55</v>
+        <v>2.01</v>
       </c>
       <c r="D96" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="E96" t="n">
-        <v>4.75</v>
+        <v>3.3</v>
       </c>
       <c r="F96" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="G96" t="n">
-        <v>1.93</v>
+        <v>1.6</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -3501,1688 +3497,30 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Velez Sarsfield Reserves vs Ferro Carril Oeste Reserves</t>
+          <t>Liverpool Montevideo vs Colon FC</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="D97" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="E97" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="F97" t="n">
-        <v>1.64</v>
+        <v>1.98</v>
       </c>
       <c r="G97" t="n">
-        <v>2.06</v>
+        <v>1.72</v>
       </c>
       <c r="H97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>San Lorenzo Reserves vs Ca Huracan Reserves</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="D98" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="E98" t="n">
-        <v>3</v>
-      </c>
-      <c r="F98" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="G98" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Uribelarrea FC vs Nautico Hacoaj</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="D99" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="E99" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="F99" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="G99" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>FCM Traiskirchen vs Kremser SC</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="D100" t="n">
-        <v>4</v>
-      </c>
-      <c r="E100" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F100" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="G100" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>20:45</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Austria Klagenfurt vs SV Donau Klagenfurt</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="D101" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="E101" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F101" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G101" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>33 dk içinde</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Dibba AL Fujairah vs Al Ittifaq Dubai</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="D102" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="E102" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F102" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="G102" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>33 dk içinde</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Al Urooba vs Dubai City FC</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="D103" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="E103" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F103" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="G103" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Clube 1992 RS vs Ser Panambi Rs</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D104" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="E104" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="F104" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="G104" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Abadia SC U20 vs Itaucu Esporte Clube U20</t>
-        </is>
-      </c>
-      <c r="C105" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="D105" t="n">
-        <v>5</v>
-      </c>
-      <c r="E105" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F105" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="G105" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>City London FC U20 vs Criciuma U20</t>
-        </is>
-      </c>
-      <c r="C106" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="D106" t="n">
-        <v>4</v>
-      </c>
-      <c r="E106" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="F106" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="G106" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>US Biskra vs JS Saoura</t>
-        </is>
-      </c>
-      <c r="C107" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="D107" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="E107" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="F107" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="G107" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>MC Alger vs MC Oran</t>
-        </is>
-      </c>
-      <c r="C108" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="D108" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E108" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F108" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="G108" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>AGF Aarhus (K) vs Nordsjaelland (K)</t>
-        </is>
-      </c>
-      <c r="C109" t="n">
-        <v>19</v>
-      </c>
-      <c r="D109" t="n">
-        <v>8</v>
-      </c>
-      <c r="E109" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="F109" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="G109" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>52 dk içinde</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Johvi FC Phoenix U19 vs Tartu FC Helios U19</t>
-        </is>
-      </c>
-      <c r="C110" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="D110" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E110" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="F110" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="G110" t="n">
-        <v>9</v>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>52 dk içinde</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Flora Tallinn U19 vs JK Trans Narva U19</t>
-        </is>
-      </c>
-      <c r="C111" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="D111" t="n">
-        <v>5</v>
-      </c>
-      <c r="E111" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="F111" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="G111" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>52 dk içinde</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Lootos Polva U19 vs Pohja-Tallinna JK Volta U19</t>
-        </is>
-      </c>
-      <c r="C112" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="D112" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E112" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="F112" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="G112" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>51 dk içinde</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Havadar SC vs Besat Kermanshah</t>
-        </is>
-      </c>
-      <c r="C113" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="D113" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E113" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="F113" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="G113" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Naft Masjed Soleyman vs Palayesh Naft Bandar Abbas FC</t>
-        </is>
-      </c>
-      <c r="C114" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="D114" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E114" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="F114" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="G114" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Naft Gachsaran vs Ario Eslamshahr</t>
-        </is>
-      </c>
-      <c r="C115" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="D115" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="E115" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="F115" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="G115" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>21:45</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>East Kilbride vs Celtic II</t>
-        </is>
-      </c>
-      <c r="C116" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="D116" t="n">
-        <v>6</v>
-      </c>
-      <c r="E116" t="n">
-        <v>8</v>
-      </c>
-      <c r="F116" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="G116" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>21:45</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Elgin City vs Dundee FC II</t>
-        </is>
-      </c>
-      <c r="C117" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="D117" t="n">
-        <v>7</v>
-      </c>
-      <c r="E117" t="n">
-        <v>12</v>
-      </c>
-      <c r="F117" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="G117" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>21:45</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>FC Edinburgh vs Dundee Utd II</t>
-        </is>
-      </c>
-      <c r="C118" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="D118" t="n">
-        <v>6</v>
-      </c>
-      <c r="E118" t="n">
-        <v>9</v>
-      </c>
-      <c r="F118" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="G118" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>21:45</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Kelty Hearts vs Hearts II</t>
-        </is>
-      </c>
-      <c r="C119" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="D119" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="E119" t="n">
-        <v>6</v>
-      </c>
-      <c r="F119" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="G119" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>21:45</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Clachnacuddin vs Ross County</t>
-        </is>
-      </c>
-      <c r="C120" t="n">
-        <v>17</v>
-      </c>
-      <c r="D120" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="E120" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="F120" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="G120" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>21:45</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Gala Fairydean Rovers vs Spartans FC</t>
-        </is>
-      </c>
-      <c r="C121" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="D121" t="n">
-        <v>5</v>
-      </c>
-      <c r="E121" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="F121" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="G121" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>21:45</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Stirling Albion vs Cumbernauld Colts FC</t>
-        </is>
-      </c>
-      <c r="C122" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="D122" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E122" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="F122" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="G122" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>21:45</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Formartine United FC vs Montrose</t>
-        </is>
-      </c>
-      <c r="C123" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D123" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="E123" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="F123" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="G123" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>21:45</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Fraserburgh vs Cove Rangers</t>
-        </is>
-      </c>
-      <c r="C124" t="n">
-        <v>5</v>
-      </c>
-      <c r="D124" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="E124" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="F124" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="G124" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>21:45</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Forfar Athletic vs Peterhead</t>
-        </is>
-      </c>
-      <c r="C125" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="D125" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="E125" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="F125" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="G125" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>21:45</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Bonnyrigg Rose vs Airdrieonians FC</t>
-        </is>
-      </c>
-      <c r="C126" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D126" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="E126" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="F126" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="G126" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>21:45</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Queen of the South vs Annan Athletic</t>
-        </is>
-      </c>
-      <c r="C127" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="D127" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E127" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F127" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="G127" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>21:45</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Alloa Athletic vs Hibernian B</t>
-        </is>
-      </c>
-      <c r="C128" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="D128" t="n">
-        <v>6</v>
-      </c>
-      <c r="E128" t="n">
-        <v>10</v>
-      </c>
-      <c r="F128" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="G128" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>21:45</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Clyde FC vs Glasgow Rangers II</t>
-        </is>
-      </c>
-      <c r="C129" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="D129" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="E129" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="F129" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="G129" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>21:45</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Berwick Rangers vs Stranraer</t>
-        </is>
-      </c>
-      <c r="C130" t="n">
-        <v>4</v>
-      </c>
-      <c r="D130" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="E130" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="F130" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="G130" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>21:45</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Clydebank vs St Mirren II</t>
-        </is>
-      </c>
-      <c r="C131" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="D131" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E131" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="F131" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="G131" t="n">
-        <v>3</v>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>21:45</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Banks O'Dee F.C. vs Aberdeen FC II</t>
-        </is>
-      </c>
-      <c r="C132" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D132" t="n">
-        <v>4</v>
-      </c>
-      <c r="E132" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="F132" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="G132" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>21:45</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Dumbarton vs Kilmarnock II</t>
-        </is>
-      </c>
-      <c r="C133" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="D133" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="E133" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F133" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="G133" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>21:45</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Kilwinning Rangers vs Auchinleck Talbot FC</t>
-        </is>
-      </c>
-      <c r="C134" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="D134" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="E134" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="F134" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="G134" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Hapoel Ironi Acre U19 vs Maccabi Ironi Kiryat Ata U19</t>
-        </is>
-      </c>
-      <c r="C135" t="n">
-        <v>2</v>
-      </c>
-      <c r="D135" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="E135" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Husqvarna FF (W) vs Vaxjo (K)</t>
-        </is>
-      </c>
-      <c r="C136" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="D136" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="E136" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="F136" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="G136" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Breidablik/Augn/Smari U19 vs HK/Ymir U19</t>
-        </is>
-      </c>
-      <c r="C137" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="D137" t="n">
-        <v>6</v>
-      </c>
-      <c r="E137" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F137" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="G137" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Al Mesaimeer SC vs Al Waab Sports Club</t>
-        </is>
-      </c>
-      <c r="C138" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="D138" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="E138" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="F138" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="G138" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Muaither SC vs Al-Khor</t>
-        </is>
-      </c>
-      <c r="C139" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="D139" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="E139" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="F139" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G139" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>50 dk içinde</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Belen Arco Zaragoza vs Los Embajadores</t>
-        </is>
-      </c>
-      <c r="C140" t="n">
-        <v>5</v>
-      </c>
-      <c r="D140" t="n">
-        <v>4</v>
-      </c>
-      <c r="E140" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="F140" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="G140" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>50 dk içinde</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Olimpia J.V. vs E.D.P IND. Medellin</t>
-        </is>
-      </c>
-      <c r="C141" t="n">
-        <v>10</v>
-      </c>
-      <c r="D141" t="n">
-        <v>6</v>
-      </c>
-      <c r="E141" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="F141" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="G141" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Dragones Toluca II vs Ajolotes Lerma</t>
-        </is>
-      </c>
-      <c r="C142" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="D142" t="n">
-        <v>4</v>
-      </c>
-      <c r="E142" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F142" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G142" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>50 dk içinde</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Boston Cancun FC vs Ejidatarios de Bonfil</t>
-        </is>
-      </c>
-      <c r="C143" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="D143" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="E143" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="F143" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="G143" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Aztecas AMF vs Huracanes Izcalli FC</t>
-        </is>
-      </c>
-      <c r="C144" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="D144" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="E144" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="F144" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="G144" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>AS Douanes de Niamey vs Urana</t>
-        </is>
-      </c>
-      <c r="C145" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="D145" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="E145" t="n">
-        <v>5</v>
-      </c>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Skjetten vs Skjervoy</t>
-        </is>
-      </c>
-      <c r="C146" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="D146" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E146" t="n">
-        <v>6</v>
-      </c>
-      <c r="F146" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="G146" t="n">
-        <v>5</v>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>3 de Febrero FBC vs River Plate Asuncion</t>
-        </is>
-      </c>
-      <c r="C147" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D147" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="E147" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="F147" t="n">
-        <v>2</v>
-      </c>
-      <c r="G147" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>19 dk içinde</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Dumbravita vs CSM Resita</t>
-        </is>
-      </c>
-      <c r="C148" t="n">
-        <v>5</v>
-      </c>
-      <c r="D148" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="E148" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="F148" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="G148" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>ASA Targu Mures vs CS Dinamo Bucuresti</t>
-        </is>
-      </c>
-      <c r="C149" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="D149" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E149" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="F149" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="G149" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H149" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/bugun_oranlar.xlsx
+++ b/bugun_oranlar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H97"/>
+  <dimension ref="A1:H95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,28 +461,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>51 dk içinde</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Oud-Heverlee Leuven (K) vs AS Roma (K)</t>
+          <t>Belçika U21 vs Belarus U21</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4.75</v>
+        <v>1.2</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="E2" t="n">
-        <v>1.55</v>
+        <v>12</v>
       </c>
       <c r="F2" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="G2" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -493,28 +493,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>51 dk içinde</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Servette Chenois (K) vs Lyon (K)</t>
+          <t>San Marino U21 vs Kosovo U21</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="F3" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -525,28 +525,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Barcelona (K) vs Paris FC (K)</t>
+          <t>Portekiz vs Galler</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>1.18</v>
       </c>
       <c r="D4" t="n">
-        <v>36</v>
+        <v>6.5</v>
       </c>
       <c r="E4" t="n">
-        <v>1.08</v>
+        <v>13.25</v>
       </c>
       <c r="F4" t="n">
-        <v>1.08</v>
+        <v>1.41</v>
       </c>
       <c r="G4" t="n">
-        <v>6.5</v>
+        <v>2.68</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -557,28 +557,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Chelsea (K) vs Austria Vienna (K)</t>
+          <t>Norveç vs Danimarka</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>1.81</v>
       </c>
       <c r="D5" t="n">
-        <v>46</v>
+        <v>3.8</v>
       </c>
       <c r="E5" t="n">
-        <v>1.18</v>
+        <v>3.8</v>
       </c>
       <c r="F5" t="n">
-        <v>1.18</v>
+        <v>1.62</v>
       </c>
       <c r="G5" t="n">
-        <v>4.2</v>
+        <v>2.25</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -589,28 +589,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6 dk içinde</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Breidablik Kopavogur (K) vs Czarni Sosnowiec (K)</t>
+          <t>Sırbistan vs Yunanistan</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2.2</v>
+        <v>2.73</v>
       </c>
       <c r="D6" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="E6" t="n">
         <v>2.6</v>
       </c>
       <c r="F6" t="n">
-        <v>1.47</v>
+        <v>2.22</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4</v>
+        <v>1.62</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -621,28 +621,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6 dk içinde</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sparta Prague (K) vs Farul Constanta (K)</t>
+          <t>Hollanda vs Almanya</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.05</v>
+        <v>2.5</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>3.8</v>
       </c>
       <c r="E7" t="n">
-        <v>21</v>
+        <v>2.45</v>
       </c>
       <c r="F7" t="n">
-        <v>1.27</v>
+        <v>1.43</v>
       </c>
       <c r="G7" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -653,28 +653,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6 dk içinde</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Brondby (K) vs Sporting (K)</t>
+          <t>Avusturya vs İsrail</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.6</v>
+        <v>1.43</v>
       </c>
       <c r="D8" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="E8" t="n">
-        <v>2.27</v>
+        <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>1.71</v>
+        <v>1.51</v>
       </c>
       <c r="G8" t="n">
-        <v>1.98</v>
+        <v>2.45</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -685,28 +685,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>51 dk içinde</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>St. Polten (K) vs Malmo FF (K)</t>
+          <t>Kosova vs İrlanda</t>
         </is>
       </c>
       <c r="C9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D9" t="n">
         <v>3.2</v>
       </c>
-      <c r="D9" t="n">
-        <v>3.6</v>
-      </c>
       <c r="E9" t="n">
-        <v>1.87</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="G9" t="n">
-        <v>2.16</v>
+        <v>1.58</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -717,28 +717,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Feyenoord (K) vs Valerenga (K)</t>
+          <t>Lihtenştayn vs Litvanya</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2.6</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="F10" t="n">
-        <v>1.47</v>
+        <v>2.05</v>
       </c>
       <c r="G10" t="n">
-        <v>2.39</v>
+        <v>1.68</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -749,28 +749,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PSV (K) vs Fortuna Hjorring (K)</t>
+          <t>Andorra vs Malta</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.37</v>
+        <v>3.28</v>
       </c>
       <c r="D11" t="n">
-        <v>4.33</v>
+        <v>2.8</v>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="F11" t="n">
-        <v>1.53</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>2.33</v>
+        <v>1.33</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -781,28 +781,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hammarby IF (K) vs Rangers (K)</t>
+          <t>Boldmere St. Michaels (W) vs Sutton Coldfield (W)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.3</v>
+        <v>1.07</v>
       </c>
       <c r="D12" t="n">
-        <v>4.75</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>6.5</v>
+        <v>13.25</v>
       </c>
       <c r="F12" t="n">
-        <v>1.43</v>
+        <v>1.72</v>
       </c>
       <c r="G12" t="n">
-        <v>2.59</v>
+        <v>2</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -813,28 +813,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Wolfsburg (K) vs Sturm Graz (K)</t>
+          <t>Stade Caen vs Rouen</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.006</v>
+        <v>2.54</v>
       </c>
       <c r="D13" t="n">
-        <v>15</v>
+        <v>3.2</v>
       </c>
       <c r="E13" t="n">
-        <v>36</v>
+        <v>2.4</v>
       </c>
       <c r="F13" t="n">
-        <v>1.12</v>
+        <v>1.84</v>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>1.83</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -845,28 +845,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ajax (K) vs Aktobe (K)</t>
+          <t>Al Dhaid U21 vs Shabab Al Ahli Dubai U21</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="D14" t="n">
-        <v>13.25</v>
+        <v>3.8</v>
       </c>
       <c r="E14" t="n">
-        <v>29</v>
+        <v>1.66</v>
       </c>
       <c r="F14" t="n">
-        <v>1.11</v>
+        <v>1.35</v>
       </c>
       <c r="G14" t="n">
-        <v>5.5</v>
+        <v>2.8</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -877,28 +877,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hearts (K) vs Real Sociedad (K)</t>
+          <t>Al Jazira SC U21 vs Al Orooba U21</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6.5</v>
+        <v>1.28</v>
       </c>
       <c r="D15" t="n">
         <v>4.75</v>
       </c>
       <c r="E15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F15" t="n">
         <v>1.33</v>
       </c>
-      <c r="F15" t="n">
-        <v>1.4</v>
-      </c>
       <c r="G15" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -914,23 +914,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Liverpool (K) vs Sunderland (W)</t>
+          <t>Portuguesa de Desportos U20 vs Ponte Preta SP U20</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.2</v>
+        <v>1.64</v>
       </c>
       <c r="D16" t="n">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="E16" t="n">
-        <v>9.5</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>1.37</v>
+        <v>1.62</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7</v>
+        <v>2.12</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -941,28 +941,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Everton (K) vs Birmingham (K)</t>
+          <t>Viborg U19 vs Brondby U19</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.87</v>
+        <v>2.45</v>
       </c>
       <c r="D17" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="E17" t="n">
-        <v>3.4</v>
+        <v>2.34</v>
       </c>
       <c r="F17" t="n">
-        <v>1.87</v>
+        <v>1.5</v>
       </c>
       <c r="G17" t="n">
-        <v>1.79</v>
+        <v>2.33</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -973,28 +973,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tottenham (K) vs West Ham (K)</t>
+          <t>Hartberg vs Kapfenberg</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="D18" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="E18" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F18" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="G18" t="n">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1005,28 +1005,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nottingham Forest (W) vs Aston Villa (K)</t>
+          <t>SF Siegen 1899 vs Borussia Monchengladbach</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3.7</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>3.7</v>
+        <v>13.25</v>
       </c>
       <c r="E19" t="n">
-        <v>1.71</v>
+        <v>1.02</v>
       </c>
       <c r="F19" t="n">
-        <v>1.55</v>
+        <v>1.14</v>
       </c>
       <c r="G19" t="n">
-        <v>2.22</v>
+        <v>4.5</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1037,28 +1037,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Manchester United (K) vs Sheffield United FC (W)</t>
+          <t>SC Rot-Weiss Oberhausen vs Schalke 04</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="E20" t="n">
-        <v>23</v>
+        <v>1.28</v>
       </c>
       <c r="F20" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="G20" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1069,28 +1069,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Crystal Palace (K) vs Watford (W)</t>
+          <t>Hollanda U19 vs Belçika U19</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1.18</v>
+        <v>2.09</v>
       </c>
       <c r="D21" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="E21" t="n">
-        <v>9</v>
+        <v>2.73</v>
       </c>
       <c r="F21" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="G21" t="n">
-        <v>3.05</v>
+        <v>2.37</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1101,28 +1101,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Leicester (K) vs London City Lionesses (K)</t>
+          <t>Sırbistan U19 vs Bulgaristan U19</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>9.5</v>
+        <v>1.98</v>
       </c>
       <c r="D22" t="n">
-        <v>5.5</v>
+        <v>3.3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.18</v>
+        <v>3.1</v>
       </c>
       <c r="F22" t="n">
-        <v>1.33</v>
+        <v>1.76</v>
       </c>
       <c r="G22" t="n">
-        <v>2.8</v>
+        <v>1.92</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1133,28 +1133,28 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Brighton (K) vs Charlton (K)</t>
+          <t>Romanya U19 vs Macaristan U19</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.2</v>
+        <v>2.16</v>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="E23" t="n">
-        <v>8.5</v>
+        <v>2.73</v>
       </c>
       <c r="F23" t="n">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="G23" t="n">
-        <v>2.59</v>
+        <v>2.06</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1165,28 +1165,28 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>30 dk içinde</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Kingstonian vs Bedfont</t>
+          <t>Japonya vs Uruguay</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="D24" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="E24" t="n">
-        <v>3.2</v>
+        <v>4.75</v>
       </c>
       <c r="F24" t="n">
-        <v>1.51</v>
+        <v>1.87</v>
       </c>
       <c r="G24" t="n">
-        <v>2.34</v>
+        <v>1.83</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1197,28 +1197,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sevenoaks Town vs Eastbourne Town</t>
+          <t>Kore Cumhuriyeti vs Ekvador</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="D25" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="E25" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="F25" t="n">
-        <v>1.57</v>
+        <v>2.12</v>
       </c>
       <c r="G25" t="n">
-        <v>2.22</v>
+        <v>1.66</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1229,28 +1229,28 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Boreham Wood vs Everton U21</t>
+          <t>Çin vs Maldives</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="D26" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E26" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="F26" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="G26" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1261,28 +1261,28 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Guisborough Town vs Ashington</t>
+          <t>Özbekistan vs Iran</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.83</v>
+        <v>2.77</v>
       </c>
       <c r="D27" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>3.4</v>
+        <v>2.59</v>
       </c>
       <c r="F27" t="n">
-        <v>1.66</v>
+        <v>2.45</v>
       </c>
       <c r="G27" t="n">
-        <v>2.03</v>
+        <v>1.47</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1293,28 +1293,28 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Shifnal Town vs Nantwich Town</t>
+          <t>Atletico Rojiblanco vs CD Cuenca Juniors</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2.5</v>
+        <v>1.99</v>
       </c>
       <c r="D28" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.27</v>
+        <v>3.6</v>
       </c>
       <c r="F28" t="n">
-        <v>1.55</v>
+        <v>2.45</v>
       </c>
       <c r="G28" t="n">
-        <v>2.25</v>
+        <v>1.45</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1325,28 +1325,28 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Lower Breck vs Atherton Collieries</t>
+          <t>Indepiendente Juniors vs Vinotinto Ecuador</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>2.16</v>
       </c>
       <c r="D29" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="F29" t="n">
-        <v>1.58</v>
+        <v>2.36</v>
       </c>
       <c r="G29" t="n">
-        <v>2.18</v>
+        <v>1.51</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1357,28 +1357,28 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>London Lions vs Biggleswade</t>
+          <t>FC Elva vs JK Tallinna Kalev</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4.2</v>
+        <v>2.63</v>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="E30" t="n">
-        <v>1.58</v>
+        <v>2.2</v>
       </c>
       <c r="F30" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="G30" t="n">
-        <v>2.63</v>
+        <v>2.35</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1389,28 +1389,28 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Saguntino vs Navalcarnero</t>
+          <t>FAR Rabat vs Raja Casablanca</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>2.35</v>
       </c>
       <c r="E31" t="n">
-        <v>2.45</v>
+        <v>3.5</v>
       </c>
       <c r="F31" t="n">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="G31" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1421,28 +1421,28 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sant Andreu Barcelona vs Real Madrid B</t>
+          <t>Amal Tiznit vs Ittihad Riadhi de Tanger</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="D32" t="n">
-        <v>3.2</v>
+        <v>2.77</v>
       </c>
       <c r="E32" t="n">
-        <v>2.11</v>
+        <v>2.31</v>
       </c>
       <c r="F32" t="n">
-        <v>2.01</v>
+        <v>2.9</v>
       </c>
       <c r="G32" t="n">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1453,28 +1453,28 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>VV Zwaluwen Vlaardingen vs VPV Purmersteijn</t>
+          <t>JyTy vs Abo CF</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2.33</v>
+        <v>1.51</v>
       </c>
       <c r="D33" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.4</v>
+        <v>4.33</v>
       </c>
       <c r="F33" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="G33" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1485,28 +1485,28 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tot Ons Genoegen Berkel vs ROHDA Raalte</t>
+          <t>Fc Kontu vs Lps</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="E34" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="F34" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="G34" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1517,28 +1517,28 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JOS/Watergraafsmeer vs Tielse EC</t>
+          <t>LAUTP/2 vs Kultsu</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4.33</v>
+        <v>19</v>
       </c>
       <c r="D35" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="E35" t="n">
-        <v>1.51</v>
+        <v>1.03</v>
       </c>
       <c r="F35" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="G35" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1549,28 +1549,28 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>VV Sparta Nijkerk vs UDI '19</t>
+          <t>Eif/Akademi vs HooGee</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2.08</v>
+        <v>1.41</v>
       </c>
       <c r="D36" t="n">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="E36" t="n">
-        <v>2.73</v>
+        <v>4.5</v>
       </c>
       <c r="F36" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="G36" t="n">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1581,28 +1581,28 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IJsselmeervogels vs VV Gemert</t>
+          <t>PPJ/Lauttasaari vs Pakkalan Palloseura</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1.28</v>
+        <v>1.05</v>
       </c>
       <c r="D37" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E37" t="n">
+        <v>15</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G37" t="n">
         <v>5</v>
-      </c>
-      <c r="E37" t="n">
-        <v>8</v>
-      </c>
-      <c r="F37" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="G37" t="n">
-        <v>2.4</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1613,28 +1613,28 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CA Sarmiento Reserves vs Atletico Rafaela Reserves</t>
+          <t>Fish United vs Saaksjaerven Loiske</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2.25</v>
+        <v>2.58</v>
       </c>
       <c r="D38" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="E38" t="n">
-        <v>2.8</v>
+        <v>2.12</v>
       </c>
       <c r="F38" t="n">
-        <v>2.12</v>
+        <v>1.27</v>
       </c>
       <c r="G38" t="n">
-        <v>1.64</v>
+        <v>3.15</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1645,28 +1645,28 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Gimnasia La Plata Reserves vs Estudiantes La Plata Reserves</t>
+          <t>MPS vs Poxyt</t>
         </is>
       </c>
       <c r="C39" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="D39" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E39" t="n">
         <v>2.45</v>
       </c>
-      <c r="D39" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E39" t="n">
-        <v>2.63</v>
-      </c>
       <c r="F39" t="n">
-        <v>2.3</v>
+        <v>1.35</v>
       </c>
       <c r="G39" t="n">
-        <v>1.53</v>
+        <v>2.73</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -1677,28 +1677,28 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CA Aldosivi Reserves vs Quilmes Reserves</t>
+          <t>NK Koprivnica vs NK Uskok</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="D40" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="E40" t="n">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="F40" t="n">
-        <v>2.12</v>
+        <v>1.53</v>
       </c>
       <c r="G40" t="n">
-        <v>1.62</v>
+        <v>2.26</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -1709,28 +1709,28 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>53 dk içinde</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Defensa Y Justicia Reserves vs Tigre Reserves</t>
+          <t>Rebels Fc vs Roots</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1.72</v>
+        <v>2.39</v>
       </c>
       <c r="D41" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="E41" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="F41" t="n">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="G41" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -1741,28 +1741,28 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Lanus Reserves vs Banfield Reserves</t>
+          <t>FC Jerusalem vs Maccabi Yavne</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1.71</v>
+        <v>2.09</v>
       </c>
       <c r="D42" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="E42" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="F42" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="G42" t="n">
-        <v>2.27</v>
+        <v>1.87</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -1773,28 +1773,28 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CA Atlas Reserves vs Argentino de Rosario Reserves</t>
+          <t>Hapoel Tzafririm Holon vs Kfar Saba 1928</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2.03</v>
+        <v>2.9</v>
       </c>
       <c r="D43" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="E43" t="n">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="F43" t="n">
-        <v>1.64</v>
+        <v>1.99</v>
       </c>
       <c r="G43" t="n">
-        <v>2.05</v>
+        <v>1.71</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -1805,28 +1805,28 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Canuelas FC Reserves vs Leones de Rosario Reserves</t>
+          <t>Hapoel Hadera vs Maccabi Ashdod</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1.94</v>
+        <v>1.76</v>
       </c>
       <c r="D44" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="E44" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="F44" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="G44" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -1837,28 +1837,28 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Lanus (K) vs River Plate (K)</t>
+          <t>Ironi Modiin vs MS Ashdod</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="D45" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="F45" t="n">
-        <v>2.04</v>
+        <v>1.7</v>
       </c>
       <c r="G45" t="n">
-        <v>1.66</v>
+        <v>2.03</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -1869,28 +1869,28 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3 dk içinde</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tristan Suarez Reserves vs Defensores De Belgrano</t>
+          <t>Maccabi Herzliya vs Kiryat Yam</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2.08</v>
+        <v>2.54</v>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.2</v>
+        <v>2.37</v>
       </c>
       <c r="F46" t="n">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="G46" t="n">
-        <v>1.55</v>
+        <v>1.92</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -1901,28 +1901,28 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sportivo Desamparados vs Sportivo Rivadavia San Juan</t>
+          <t>Hapoel Ironi Rishon Lezion vs Maccabi Ahi Nazareth FC</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="D47" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="E47" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="F47" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="G47" t="n">
-        <v>2.01</v>
+        <v>2.2</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -1933,28 +1933,28 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sarmiento de Zonda vs CA Union Villa Krause</t>
+          <t>Hapoel Akko FC vs Hapoel Afula</t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>4.25</v>
       </c>
       <c r="D48" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="E48" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="F48" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="G48" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -1965,28 +1965,28 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Suudi Arabistan vs Kuveyt</t>
+          <t>Maccabi Kiryat Ata Bialik vs Hapoel Ihud Bnei Jatt</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="D49" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="E49" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="F49" t="n">
-        <v>1.68</v>
+        <v>1.43</v>
       </c>
       <c r="G49" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -1997,28 +1997,28 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SV Gerasdorf Stammersdorf vs Sportunion Mauer</t>
+          <t>Maccabi Nujeidat Ahmed vs Hapoel Ironi Arraba</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>7</v>
+        <v>1.87</v>
       </c>
       <c r="D50" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="E50" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="F50" t="n">
-        <v>1.51</v>
+        <v>1.68</v>
       </c>
       <c r="G50" t="n">
-        <v>2.31</v>
+        <v>2.02</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2029,28 +2029,28 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Itabirito (W) vs Cruzeiro (K)</t>
+          <t>Hapoel Migdal Haemeq vs Hapoel Nof HaGalil</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="D51" t="n">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="E51" t="n">
-        <v>1.38</v>
+        <v>2.23</v>
       </c>
       <c r="F51" t="n">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="G51" t="n">
-        <v>2.23</v>
+        <v>1.78</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2061,28 +2061,28 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Perolas Negras U20 vs Audax Rio RJ U20</t>
+          <t>MS Shikun Hamizrah vs Bnei Eilat</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2.04</v>
+        <v>2.39</v>
       </c>
       <c r="D52" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="E52" t="n">
-        <v>3.2</v>
+        <v>2.36</v>
       </c>
       <c r="F52" t="n">
-        <v>2.16</v>
+        <v>1.55</v>
       </c>
       <c r="G52" t="n">
-        <v>1.58</v>
+        <v>2.25</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2093,28 +2093,28 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Sao Goncalo U20 vs Olaria RJ U20</t>
+          <t>Hapoel Bney Jdaide vs Maccabi Ihud Bnei Avtin</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2.55</v>
+        <v>3.15</v>
       </c>
       <c r="D53" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="E53" t="n">
-        <v>2.4</v>
+        <v>1.87</v>
       </c>
       <c r="F53" t="n">
-        <v>1.98</v>
+        <v>1.5</v>
       </c>
       <c r="G53" t="n">
-        <v>1.71</v>
+        <v>2.37</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2125,28 +2125,28 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Sao Domingos U20 vs ASA (Agremiação Sportiva Arapiraquense) U20</t>
+          <t>Hapoel Bnei Ein Mahel vs Maccabi Maghar</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>13.25</v>
+        <v>1.95</v>
       </c>
       <c r="D54" t="n">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="E54" t="n">
-        <v>1.11</v>
+        <v>2.8</v>
       </c>
       <c r="F54" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="G54" t="n">
-        <v>2.27</v>
+        <v>3</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -2157,28 +2157,28 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Independente Atalaia U20 vs CS Esportiva U20</t>
+          <t>Maccabi Isfiya vs Hapoel Givat Olga</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>6.5</v>
+        <v>1.96</v>
       </c>
       <c r="D55" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="E55" t="n">
-        <v>1.33</v>
+        <v>3</v>
       </c>
       <c r="F55" t="n">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="G55" t="n">
-        <v>2.09</v>
+        <v>2.55</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -2189,28 +2189,28 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Madureira RJ vs Sampaio Correa RJ</t>
+          <t>MK Tzofi Haifa vs Tzeirey Haifa SC</t>
         </is>
       </c>
       <c r="C56" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D56" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E56" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G56" t="n">
         <v>2.45</v>
-      </c>
-      <c r="D56" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E56" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="F56" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="G56" t="n">
-        <v>1.5</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2221,28 +2221,28 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Gramadense RS vs EC Pelotas</t>
+          <t>Ihud Bnei Baqa vs Hapoel Bnei Arrara Ara</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2.37</v>
+        <v>1.37</v>
       </c>
       <c r="D57" t="n">
-        <v>2.77</v>
+        <v>4.33</v>
       </c>
       <c r="E57" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="F57" t="n">
-        <v>2.73</v>
+        <v>1.41</v>
       </c>
       <c r="G57" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2253,28 +2253,28 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Gremio Esportivo Brasil RS vs Ge Gloria</t>
+          <t>Beitar Haifa Yakov vs FC Kababir</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1.57</v>
+        <v>1.14</v>
       </c>
       <c r="D58" t="n">
-        <v>3.4</v>
+        <v>6.5</v>
       </c>
       <c r="E58" t="n">
-        <v>5.5</v>
+        <v>11</v>
       </c>
       <c r="F58" t="n">
-        <v>2.33</v>
+        <v>1.25</v>
       </c>
       <c r="G58" t="n">
-        <v>1.51</v>
+        <v>3.5</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2285,28 +2285,28 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Esmac PA vs Pedreira EC</t>
+          <t>Maccabi Ironi Kfar Yona vs Hapoel Ramot Menashe</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>23</v>
+        <v>1.7</v>
       </c>
       <c r="D59" t="n">
-        <v>9.5</v>
+        <v>3.8</v>
       </c>
       <c r="E59" t="n">
-        <v>1.02</v>
+        <v>3.6</v>
       </c>
       <c r="F59" t="n">
-        <v>1.16</v>
+        <v>1.43</v>
       </c>
       <c r="G59" t="n">
-        <v>4.33</v>
+        <v>2.55</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -2317,28 +2317,28 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>AD Confianca SE U20 vs Aracaju SE U20</t>
+          <t>Hapoel Tel Aviv (W) vs Hapoel Raanana (W)</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1.96</v>
+        <v>2.55</v>
       </c>
       <c r="D60" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="E60" t="n">
-        <v>3.28</v>
+        <v>2.23</v>
       </c>
       <c r="F60" t="n">
-        <v>1.97</v>
+        <v>1.55</v>
       </c>
       <c r="G60" t="n">
-        <v>1.74</v>
+        <v>2.27</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2349,28 +2349,28 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Falcon SE U20 vs AA Guarany SE U20</t>
+          <t>Maccabi Kishronot Hadera (W) vs Maccabi Holon (W)</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="D61" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="E61" t="n">
-        <v>6.5</v>
+        <v>4.33</v>
       </c>
       <c r="F61" t="n">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="G61" t="n">
-        <v>3.05</v>
+        <v>2.4</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -2381,28 +2381,28 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>GE Prudente U20 vs CA Juventus SP U20</t>
+          <t>Hapoel Jerusalem (K) vs Kiryat Gat SC (W)</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2.8</v>
+        <v>2.16</v>
       </c>
       <c r="D62" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="E62" t="n">
-        <v>2.11</v>
+        <v>2.68</v>
       </c>
       <c r="F62" t="n">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="G62" t="n">
-        <v>1.9</v>
+        <v>2.23</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -2413,28 +2413,28 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Universidad O&amp;M FC vs Atlantico Puerto Plata FC</t>
+          <t>Ik Kongahalla vs Lindome GIF</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1.5</v>
+        <v>2.34</v>
       </c>
       <c r="D63" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="E63" t="n">
-        <v>4.33</v>
+        <v>2.34</v>
       </c>
       <c r="F63" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="G63" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -2445,28 +2445,28 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Salcedo FC vs Cibao FC</t>
+          <t>FC Bole vs FC Champagne Sport</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="D64" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="E64" t="n">
-        <v>2.18</v>
+        <v>1.87</v>
       </c>
       <c r="F64" t="n">
-        <v>2.14</v>
+        <v>1.55</v>
       </c>
       <c r="G64" t="n">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -2477,28 +2477,28 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>32 dk içinde</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Kuzey Kore U20 (K) vs Kolombiya U20 (K)</t>
+          <t>FC Saint-Blaise vs FC Bosna Neuchatel</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1.07</v>
+        <v>3.6</v>
       </c>
       <c r="D65" t="n">
-        <v>8</v>
+        <v>3.7</v>
       </c>
       <c r="E65" t="n">
-        <v>23</v>
+        <v>1.75</v>
       </c>
       <c r="F65" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="G65" t="n">
-        <v>2.39</v>
+        <v>2.27</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -2509,29 +2509,25 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2 dk içinde</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SC Wiedenbruck vs VfL Osnabruck</t>
+          <t>AL Gharafa U20 vs Al-Khor U20</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>8.5</v>
+        <v>1.45</v>
       </c>
       <c r="D66" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="E66" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="F66" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="G66" t="n">
-        <v>3.15</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
           <t>-</t>
@@ -2541,28 +2537,28 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>West Ham U21 vs Valencia U21</t>
+          <t>Umm Salal U20 vs Al-Markhiya U20</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="D67" t="n">
         <v>3.5</v>
       </c>
       <c r="E67" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="F67" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="G67" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -2573,28 +2569,28 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Middlesbrough U21 vs KRC Genk U21</t>
+          <t>Al Sadd U20 vs Mesaimeer U20</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2.8</v>
+        <v>1.76</v>
       </c>
       <c r="D68" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="E68" t="n">
-        <v>1.97</v>
+        <v>3.4</v>
       </c>
       <c r="F68" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="G68" t="n">
-        <v>2.63</v>
+        <v>2.26</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -2605,28 +2601,28 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2 dk içinde</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Cebelitarık vs Sao Tome and Principe</t>
+          <t>Al-Arabi Doha U20 vs Al-Duhail U20</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="D69" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="E69" t="n">
-        <v>5.5</v>
+        <v>4.15</v>
       </c>
       <c r="F69" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="G69" t="n">
-        <v>2.16</v>
+        <v>1.51</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -2637,28 +2633,28 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2 dk içinde</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Azerbaycan vs Tacikistan</t>
+          <t>Al-Wakrah U20 vs Qatar SC U20</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1.74</v>
+        <v>3.5</v>
       </c>
       <c r="D70" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="E70" t="n">
-        <v>4.5</v>
+        <v>1.97</v>
       </c>
       <c r="F70" t="n">
-        <v>2.14</v>
+        <v>1.43</v>
       </c>
       <c r="G70" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -2669,25 +2665,29 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2 dk içinde</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Army Ladies FC (W) vs Epiphany Warriors (W)</t>
+          <t>Cariari Pococi vs Pitbulls Santa Barbara</t>
         </is>
       </c>
       <c r="C71" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D71" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E71" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="F71" t="n">
         <v>1.72</v>
       </c>
-      <c r="D71" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="E71" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
+      <c r="G71" t="n">
+        <v>1.92</v>
+      </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>-</t>
@@ -2697,25 +2697,25 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Peru U19 vs Argentina U19</t>
+          <t>Porto Riko vs Guyana</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>7</v>
+        <v>2.7</v>
       </c>
       <c r="D72" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="E72" t="n">
-        <v>1.38</v>
+        <v>2.4</v>
       </c>
       <c r="F72" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="G72" t="n">
         <v>1.72</v>
@@ -2729,28 +2729,28 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Paraguay U19 vs Chile U19</t>
+          <t>Fk Teteks vs Rabotnicki Skopje</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="D73" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="E73" t="n">
-        <v>2.9</v>
+        <v>1.64</v>
       </c>
       <c r="F73" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="G73" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -2761,28 +2761,28 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Chile U20 (W) vs Venezuela U20 (W)</t>
+          <t>Detonit Plackovica vs Ohrid</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1.74</v>
+        <v>4.5</v>
       </c>
       <c r="D74" t="n">
         <v>3.5</v>
       </c>
       <c r="E74" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="F74" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="G74" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -2793,28 +2793,28 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Hamilton Academical FC vs Cowdenbeath</t>
+          <t>Mogila vs Aresimi 1973</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1.14</v>
+        <v>31</v>
       </c>
       <c r="D75" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E75" t="n">
-        <v>11</v>
+        <v>1.07</v>
       </c>
       <c r="F75" t="n">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="G75" t="n">
-        <v>3.6</v>
+        <v>6.5</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -2825,28 +2825,28 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cumnock Juniors FC vs Troon FC</t>
+          <t>Rivers United vs Kun Khalifat FC</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1.8</v>
+        <v>1.22</v>
       </c>
       <c r="D76" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="E76" t="n">
-        <v>3.28</v>
+        <v>8</v>
       </c>
       <c r="F76" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="G76" t="n">
-        <v>2.73</v>
+        <v>2.37</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -2857,28 +2857,28 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1 dk içinde</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ironi Beit Shemesh vs Agudat Sport Nordia Jerusalem</t>
+          <t>Grorud U19 vs Valerenga U19</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="D77" t="n">
-        <v>4.15</v>
+        <v>4.75</v>
       </c>
       <c r="E77" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="F77" t="n">
-        <v>1.47</v>
+        <v>1.12</v>
       </c>
       <c r="G77" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -2889,28 +2889,28 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1 dk içinde</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Hapoel Marmorek vs Shimshon Tel Aviv</t>
+          <t>Haslum IL U19 vs Asker U19</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>4.15</v>
+        <v>1.45</v>
       </c>
       <c r="D78" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="E78" t="n">
-        <v>1.72</v>
+        <v>4.25</v>
       </c>
       <c r="F78" t="n">
-        <v>2.07</v>
+        <v>1.08</v>
       </c>
       <c r="G78" t="n">
-        <v>1.66</v>
+        <v>6.5</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -2921,28 +2921,28 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Sport Club Dimona vs Maccabi Kiryat Malakhi</t>
+          <t>IF Ready U19 vs Skedsmo U19</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="D79" t="n">
-        <v>3.2</v>
+        <v>4.25</v>
       </c>
       <c r="E79" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="F79" t="n">
-        <v>2.06</v>
+        <v>1.13</v>
       </c>
       <c r="G79" t="n">
-        <v>1.66</v>
+        <v>5</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -2953,28 +2953,28 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Hasharon vs Sderot FC</t>
+          <t>Sprint/Jeloy U19 vs Sarpsborg 08 U19</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1.99</v>
+        <v>1.33</v>
       </c>
       <c r="D80" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="E80" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="F80" t="n">
-        <v>1.8</v>
+        <v>1.14</v>
       </c>
       <c r="G80" t="n">
-        <v>1.87</v>
+        <v>4.75</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -2985,28 +2985,28 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Hapoel Herzliya vs MS Tzeirey Tira</t>
+          <t>Christiania BK U19 vs Gjovik Lyn U19</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1.85</v>
+        <v>1.03</v>
       </c>
       <c r="D81" t="n">
-        <v>3.2</v>
+        <v>10</v>
       </c>
       <c r="E81" t="n">
-        <v>3.6</v>
+        <v>34</v>
       </c>
       <c r="F81" t="n">
-        <v>2.06</v>
+        <v>1.14</v>
       </c>
       <c r="G81" t="n">
-        <v>1.66</v>
+        <v>4.75</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -3017,28 +3017,28 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Sport Club Tira vs Hapoel Bnei Musmus</t>
+          <t>Baerum Sk U19 vs Ullern U19</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1.58</v>
+        <v>2.12</v>
       </c>
       <c r="D82" t="n">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
       <c r="E82" t="n">
-        <v>4.5</v>
+        <v>2.37</v>
       </c>
       <c r="F82" t="n">
-        <v>1.71</v>
+        <v>1.1</v>
       </c>
       <c r="G82" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -3049,28 +3049,28 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Beitar Naharia vs Maccabi Neve Shaanan Eldad</t>
+          <t>KFUM U19 vs Nordstrand U19</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1.81</v>
+        <v>1.2</v>
       </c>
       <c r="D83" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="E83" t="n">
-        <v>3.6</v>
+        <v>6.5</v>
       </c>
       <c r="F83" t="n">
-        <v>1.85</v>
+        <v>1.09</v>
       </c>
       <c r="G83" t="n">
-        <v>1.83</v>
+        <v>5.5</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -3081,28 +3081,28 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Tzeirei Umm al-Fahm vs Hapoel Umm Al Fahm</t>
+          <t>Follo U19 vs Lillehammer U19</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>4.15</v>
+        <v>1.55</v>
       </c>
       <c r="D84" t="n">
-        <v>3.8</v>
+        <v>4.25</v>
       </c>
       <c r="E84" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="F84" t="n">
-        <v>1.55</v>
+        <v>1.12</v>
       </c>
       <c r="G84" t="n">
-        <v>2.23</v>
+        <v>5</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -3113,28 +3113,28 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Hapoel Ironi Baqa Al-Gharbiyye vs Hapoel Tirat HaCarmel</t>
+          <t>Raelingen U19 vs Gjelleraasen U19</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1.78</v>
+        <v>23</v>
       </c>
       <c r="D85" t="n">
-        <v>3.5</v>
+        <v>9</v>
       </c>
       <c r="E85" t="n">
-        <v>3.5</v>
+        <v>1.05</v>
       </c>
       <c r="F85" t="n">
-        <v>1.64</v>
+        <v>1.12</v>
       </c>
       <c r="G85" t="n">
-        <v>2.07</v>
+        <v>5</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -3145,28 +3145,28 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Hapoel Bnei Lod vs Beitar Tel Aviv Holon</t>
+          <t>Lorenskog U19 vs Kjelsas U19</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1.62</v>
+        <v>5</v>
       </c>
       <c r="D86" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="E86" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="F86" t="n">
-        <v>1.87</v>
+        <v>1.14</v>
       </c>
       <c r="G86" t="n">
-        <v>1.79</v>
+        <v>4.75</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -3177,28 +3177,28 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1 dk içinde</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Sandvikens IF (W) vs Umea IK (W)</t>
+          <t>Oman Club vs Sur Club</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="D87" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="E87" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="F87" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G87" t="n">
         <v>1.58</v>
-      </c>
-      <c r="F87" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G87" t="n">
-        <v>2.07</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -3209,28 +3209,28 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>FC Haute-Ajoie vs FC Ajoie-Monterri</t>
+          <t>Sohar Club vs Al Seeb</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="D88" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="E88" t="n">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="F88" t="n">
-        <v>1.57</v>
+        <v>2.18</v>
       </c>
       <c r="G88" t="n">
-        <v>2.25</v>
+        <v>1.58</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -3241,28 +3241,28 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Turks and Caicos Islands vs Montserrat</t>
+          <t>FK Podkonice vs MFK Ruzomberok B</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>12</v>
+        <v>2.58</v>
       </c>
       <c r="D89" t="n">
-        <v>6.5</v>
+        <v>3.3</v>
       </c>
       <c r="E89" t="n">
-        <v>1.16</v>
+        <v>2.31</v>
       </c>
       <c r="F89" t="n">
-        <v>1.4</v>
+        <v>1.74</v>
       </c>
       <c r="G89" t="n">
-        <v>2.7</v>
+        <v>1.96</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -3273,28 +3273,28 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Bahamas vs Saint Martin</t>
+          <t>Montevideo City Torque vs Atenas</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>15</v>
+        <v>1.53</v>
       </c>
       <c r="D90" t="n">
-        <v>7.5</v>
+        <v>3.7</v>
       </c>
       <c r="E90" t="n">
-        <v>1.12</v>
+        <v>5</v>
       </c>
       <c r="F90" t="n">
-        <v>1.32</v>
+        <v>1.79</v>
       </c>
       <c r="G90" t="n">
-        <v>3.05</v>
+        <v>1.87</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -3305,28 +3305,28 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>59 dk içinde</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Necaxa U21 vs Atletico San Luis U21</t>
+          <t>Danubio vs Penarol Montevideo</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1.95</v>
+        <v>3.3</v>
       </c>
       <c r="D91" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="E91" t="n">
-        <v>2.9</v>
+        <v>2.05</v>
       </c>
       <c r="F91" t="n">
-        <v>1.37</v>
+        <v>2.27</v>
       </c>
       <c r="G91" t="n">
-        <v>2.8</v>
+        <v>1.53</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -3337,28 +3337,28 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Tlapa Mazatecochco vs Dragones de Oaxaca II</t>
+          <t>AL Ahli Amman vs Ma'an</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="D92" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="E92" t="n">
-        <v>2.77</v>
+        <v>4.2</v>
       </c>
       <c r="F92" t="n">
-        <v>1.58</v>
+        <v>1.81</v>
       </c>
       <c r="G92" t="n">
-        <v>2.12</v>
+        <v>1.86</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -3369,28 +3369,28 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Artesanos Metepec FC vs Toluca U21</t>
+          <t>Sahl Horan SC vs Hayy Al-Amir Hassan</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="D93" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="E93" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="F93" t="n">
-        <v>1.72</v>
+        <v>2.22</v>
       </c>
       <c r="G93" t="n">
-        <v>1.93</v>
+        <v>1.55</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -3401,28 +3401,28 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Sportivo San Lorenzo vs 4 de Mayo</t>
+          <t>Nashama Al-Mustaqbal (W) vs Al Orthodoxi (W)</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="D94" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="E94" t="n">
-        <v>15</v>
+        <v>2.8</v>
       </c>
       <c r="F94" t="n">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="G94" t="n">
-        <v>2.73</v>
+        <v>2.2</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -3433,94 +3433,30 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Asociacion Deportiva Tarma vs Cienciano Cusco</t>
+          <t>Uhamiaji FC vs Raskazone</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="D95" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="E95" t="n">
-        <v>2.11</v>
+        <v>5.5</v>
       </c>
       <c r="F95" t="n">
-        <v>1.66</v>
+        <v>1.96</v>
       </c>
       <c r="G95" t="n">
-        <v>2.08</v>
+        <v>1.72</v>
       </c>
       <c r="H95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Boston River vs Centro Atletico Fenix Montevideo</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="D96" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="E96" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="F96" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="G96" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Liverpool Montevideo vs Colon FC</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D97" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="E97" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F97" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="G97" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="H97" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/bugun_oranlar.xlsx
+++ b/bugun_oranlar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H95"/>
+  <dimension ref="A1:H249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,28 +461,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Belçika U21 vs Belarus U21</t>
+          <t>Türkiye vs Fransa</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>12</v>
+        <v>1.35</v>
       </c>
       <c r="F2" t="n">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="G2" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -493,28 +493,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>San Marino U21 vs Kosovo U21</t>
+          <t>İtalya vs Belçika</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36</v>
+        <v>2.22</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>3.6</v>
       </c>
       <c r="E3" t="n">
-        <v>1.12</v>
+        <v>2.9</v>
       </c>
       <c r="F3" t="n">
-        <v>1.12</v>
+        <v>1.66</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>2.16</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -530,23 +530,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Portekiz vs Galler</t>
+          <t>İsveç vs Romanya</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.18</v>
+        <v>1.45</v>
       </c>
       <c r="D4" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="E4" t="n">
-        <v>13.25</v>
+        <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="G4" t="n">
-        <v>2.68</v>
+        <v>2.26</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -562,23 +562,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Norveç vs Danimarka</t>
+          <t>Polonya vs Bosna-Hersek</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.81</v>
+        <v>1.64</v>
       </c>
       <c r="D5" t="n">
         <v>3.8</v>
       </c>
       <c r="E5" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="G5" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -589,28 +589,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sırbistan vs Yunanistan</t>
+          <t>Gürcistan vs Kuzey İrlanda</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2.73</v>
+        <v>1.86</v>
       </c>
       <c r="D6" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="E6" t="n">
-        <v>2.6</v>
+        <v>4.15</v>
       </c>
       <c r="F6" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="G6" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -626,23 +626,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hollanda vs Almanya</t>
+          <t>Macaristan vs Ukrayna</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="D7" t="n">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="E7" t="n">
-        <v>2.45</v>
+        <v>3.05</v>
       </c>
       <c r="F7" t="n">
-        <v>1.43</v>
+        <v>2.16</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6</v>
+        <v>1.64</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -653,28 +653,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Avusturya vs İsrail</t>
+          <t>Ermenistan vs Letonya</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.43</v>
+        <v>1.87</v>
       </c>
       <c r="D8" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="F8" t="n">
-        <v>1.51</v>
+        <v>2.07</v>
       </c>
       <c r="G8" t="n">
-        <v>2.45</v>
+        <v>1.72</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -690,23 +690,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kosova vs İrlanda</t>
+          <t>Karadağ vs Kıbrıs</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2.4</v>
+        <v>1.78</v>
       </c>
       <c r="D9" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="G9" t="n">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -717,28 +717,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lihtenştayn vs Litvanya</t>
+          <t>Azerbaycan U21 vs Çek Cumhuriyeti U21</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="E10" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="F10" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="G10" t="n">
-        <v>1.68</v>
+        <v>2.25</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -749,28 +749,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Andorra vs Malta</t>
+          <t>İzlanda U21 vs France U21</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3.28</v>
+        <v>8.5</v>
       </c>
       <c r="D11" t="n">
-        <v>2.8</v>
+        <v>4.75</v>
       </c>
       <c r="E11" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>1.68</v>
       </c>
       <c r="G11" t="n">
-        <v>1.33</v>
+        <v>2.04</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -781,28 +781,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Boldmere St. Michaels (W) vs Sutton Coldfield (W)</t>
+          <t>Bulgaristan U21 vs Portekiz U21</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.07</v>
+        <v>12</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>13.25</v>
+        <v>1.18</v>
       </c>
       <c r="F12" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -813,28 +813,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Stade Caen vs Rouen</t>
+          <t>Finlandiya U21 vs İspanya U21</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.54</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4</v>
+        <v>1.51</v>
       </c>
       <c r="F13" t="n">
-        <v>1.84</v>
+        <v>1.62</v>
       </c>
       <c r="G13" t="n">
-        <v>1.83</v>
+        <v>2.12</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -845,28 +845,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Al Dhaid U21 vs Shabab Al Ahli Dubai U21</t>
+          <t>Kıbrıs U21 vs Romanya U21</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3.4</v>
+        <v>6.5</v>
       </c>
       <c r="D14" t="n">
         <v>3.8</v>
       </c>
       <c r="E14" t="n">
-        <v>1.66</v>
+        <v>1.45</v>
       </c>
       <c r="F14" t="n">
-        <v>1.35</v>
+        <v>1.98</v>
       </c>
       <c r="G14" t="n">
-        <v>2.8</v>
+        <v>1.72</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -877,28 +877,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Al Jazira SC U21 vs Al Orooba U21</t>
+          <t>Estonia U21 vs Faroe Adaları U21</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1.28</v>
+        <v>2.7</v>
       </c>
       <c r="D15" t="n">
-        <v>4.75</v>
+        <v>3.3</v>
       </c>
       <c r="E15" t="n">
-        <v>6.5</v>
+        <v>2.39</v>
       </c>
       <c r="F15" t="n">
-        <v>1.33</v>
+        <v>1.94</v>
       </c>
       <c r="G15" t="n">
-        <v>2.8</v>
+        <v>1.76</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -909,28 +909,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Portuguesa de Desportos U20 vs Ponte Preta SP U20</t>
+          <t>Slovakia U21 vs Ireland U21</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.64</v>
+        <v>2.04</v>
       </c>
       <c r="D16" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="F16" t="n">
-        <v>1.62</v>
+        <v>1.93</v>
       </c>
       <c r="G16" t="n">
-        <v>2.12</v>
+        <v>1.78</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -941,28 +941,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Viborg U19 vs Brondby U19</t>
+          <t>Hollanda U21 vs Norveç U21</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2.45</v>
+        <v>1.79</v>
       </c>
       <c r="D17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E17" t="n">
         <v>3.6</v>
       </c>
-      <c r="E17" t="n">
-        <v>2.34</v>
-      </c>
       <c r="F17" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="G17" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -973,28 +973,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hartberg vs Kapfenberg</t>
+          <t>İsviçre U21 vs Lüksemburg U21</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="D18" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="E18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="G18" t="n">
-        <v>2.6</v>
+        <v>2.26</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1005,28 +1005,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SF Siegen 1899 vs Borussia Monchengladbach</t>
+          <t>İngiltere U21 vs Kazakistan U21</t>
         </is>
       </c>
       <c r="C19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="D19" t="n">
+        <v>11</v>
+      </c>
+      <c r="E19" t="n">
         <v>31</v>
       </c>
-      <c r="D19" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="E19" t="n">
-        <v>1.02</v>
-      </c>
       <c r="F19" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="G19" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1037,28 +1037,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SC Rot-Weiss Oberhausen vs Schalke 04</t>
+          <t>Biggleswade vs Three Bridges</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>2.16</v>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="E20" t="n">
-        <v>1.28</v>
+        <v>2.68</v>
       </c>
       <c r="F20" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="G20" t="n">
-        <v>3.5</v>
+        <v>2.45</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1069,28 +1069,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hollanda U19 vs Belçika U19</t>
+          <t>Aveley vs Ware</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2.09</v>
+        <v>1.25</v>
       </c>
       <c r="D21" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="E21" t="n">
-        <v>2.73</v>
+        <v>7.5</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="G21" t="n">
-        <v>2.37</v>
+        <v>3.3</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1101,28 +1101,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sırbistan U19 vs Bulgaristan U19</t>
+          <t>Bedfont vs Jersey Bulls</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.98</v>
+        <v>3.5</v>
       </c>
       <c r="D22" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="E22" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="F22" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="G22" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1133,28 +1133,28 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Romanya U19 vs Macaristan U19</t>
+          <t>Barnsley U21 vs Sheffield Utd U21</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2.16</v>
+        <v>2.58</v>
       </c>
       <c r="D23" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="E23" t="n">
-        <v>2.73</v>
+        <v>2.18</v>
       </c>
       <c r="F23" t="n">
-        <v>1.66</v>
+        <v>1.35</v>
       </c>
       <c r="G23" t="n">
-        <v>2.06</v>
+        <v>2.77</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1165,28 +1165,28 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>30 dk içinde</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Japonya vs Uruguay</t>
+          <t>Colchester U21 vs Sheffield Wednesday U21</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1.64</v>
+        <v>2.8</v>
       </c>
       <c r="D24" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>4.75</v>
+        <v>1.98</v>
       </c>
       <c r="F24" t="n">
-        <v>1.87</v>
+        <v>1.25</v>
       </c>
       <c r="G24" t="n">
-        <v>1.83</v>
+        <v>3.3</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1197,28 +1197,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kore Cumhuriyeti vs Ekvador</t>
+          <t>Girona vs Albacete</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.18</v>
+        <v>1.51</v>
       </c>
       <c r="D25" t="n">
-        <v>3.2</v>
+        <v>4.15</v>
       </c>
       <c r="E25" t="n">
-        <v>3.15</v>
+        <v>5</v>
       </c>
       <c r="F25" t="n">
-        <v>2.12</v>
+        <v>1.64</v>
       </c>
       <c r="G25" t="n">
-        <v>1.66</v>
+        <v>2.14</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1229,28 +1229,28 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Çin vs Maldives</t>
+          <t>Atletico Madrid B vs Villarreal CF B</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.02</v>
+        <v>2.3</v>
       </c>
       <c r="D26" t="n">
-        <v>17</v>
+        <v>3.3</v>
       </c>
       <c r="E26" t="n">
-        <v>46</v>
+        <v>2.59</v>
       </c>
       <c r="F26" t="n">
-        <v>1.12</v>
+        <v>1.72</v>
       </c>
       <c r="G26" t="n">
-        <v>5</v>
+        <v>1.98</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1261,28 +1261,28 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>22:15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Özbekistan vs Iran</t>
+          <t>UD Ibiza Eivissa vs Real Zaragoza</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2.77</v>
+        <v>2.39</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="F27" t="n">
-        <v>2.45</v>
+        <v>1.97</v>
       </c>
       <c r="G27" t="n">
-        <v>1.47</v>
+        <v>1.72</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1293,28 +1293,28 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Atletico Rojiblanco vs CD Cuenca Juniors</t>
+          <t>Sanvicenteno vs Valdelacalzada</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1.99</v>
+        <v>1.27</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="E28" t="n">
-        <v>3.6</v>
+        <v>8</v>
       </c>
       <c r="F28" t="n">
-        <v>2.45</v>
+        <v>1.64</v>
       </c>
       <c r="G28" t="n">
-        <v>1.45</v>
+        <v>2.07</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1325,28 +1325,28 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Indepiendente Juniors vs Vinotinto Ecuador</t>
+          <t>Tenerife C vs Anaza</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2.16</v>
+        <v>1.55</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="E29" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="F29" t="n">
-        <v>2.36</v>
+        <v>1.72</v>
       </c>
       <c r="G29" t="n">
-        <v>1.51</v>
+        <v>1.98</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1357,28 +1357,28 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FC Elva vs JK Tallinna Kalev</t>
+          <t>Union la Estrella CF vs UD Las Palmas C</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="D30" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="E30" t="n">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="F30" t="n">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="G30" t="n">
-        <v>2.35</v>
+        <v>1.87</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1389,28 +1389,28 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FAR Rabat vs Raja Casablanca</t>
+          <t>PSG U19 vs SM Caen U19</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="D31" t="n">
-        <v>2.35</v>
+        <v>4.75</v>
       </c>
       <c r="E31" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="F31" t="n">
-        <v>2.35</v>
+        <v>1.2</v>
       </c>
       <c r="G31" t="n">
-        <v>1.51</v>
+        <v>3.7</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1421,28 +1421,28 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Amal Tiznit vs Ittihad Riadhi de Tanger</t>
+          <t>Havelse vs Fortuna Koln</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="D32" t="n">
-        <v>2.77</v>
+        <v>3.4</v>
       </c>
       <c r="E32" t="n">
-        <v>2.31</v>
+        <v>2.22</v>
       </c>
       <c r="F32" t="n">
-        <v>2.9</v>
+        <v>1.72</v>
       </c>
       <c r="G32" t="n">
-        <v>1.35</v>
+        <v>2.01</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1453,28 +1453,28 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>JyTy vs Abo CF</t>
+          <t>FC Astoria Walldorf vs SV 1916 Sandhausen</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1.51</v>
+        <v>2.8</v>
       </c>
       <c r="D33" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="E33" t="n">
-        <v>4.33</v>
+        <v>2.02</v>
       </c>
       <c r="F33" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="G33" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1485,28 +1485,28 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fc Kontu vs Lps</t>
+          <t>Magdeburg II vs VSG Altglienicke</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="D34" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="E34" t="n">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="F34" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="G34" t="n">
-        <v>4</v>
+        <v>2.77</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1517,28 +1517,28 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LAUTP/2 vs Kultsu</t>
+          <t>Schoningen vs Drochtersen / Assel</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>19</v>
+        <v>3.5</v>
       </c>
       <c r="D35" t="n">
-        <v>10</v>
+        <v>3.8</v>
       </c>
       <c r="E35" t="n">
-        <v>1.03</v>
+        <v>1.76</v>
       </c>
       <c r="F35" t="n">
-        <v>1.11</v>
+        <v>1.41</v>
       </c>
       <c r="G35" t="n">
-        <v>5.5</v>
+        <v>2.63</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1549,28 +1549,28 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Eif/Akademi vs HooGee</t>
+          <t>Maritimo U23 vs Benfica U23</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1.41</v>
+        <v>4.5</v>
       </c>
       <c r="D36" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="E36" t="n">
-        <v>4.5</v>
+        <v>1.53</v>
       </c>
       <c r="F36" t="n">
-        <v>1.14</v>
+        <v>1.51</v>
       </c>
       <c r="G36" t="n">
-        <v>5</v>
+        <v>2.34</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1581,28 +1581,28 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PPJ/Lauttasaari vs Pakkalan Palloseura</t>
+          <t>Dordrecht vs Almere City</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1.05</v>
+        <v>2.9</v>
       </c>
       <c r="D37" t="n">
-        <v>9.5</v>
+        <v>3.8</v>
       </c>
       <c r="E37" t="n">
-        <v>15</v>
+        <v>2.04</v>
       </c>
       <c r="F37" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="G37" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1613,28 +1613,28 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Fish United vs Saaksjaerven Loiske</t>
+          <t>Namibia U20 vs Mozambique U20</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2.58</v>
+        <v>4.33</v>
       </c>
       <c r="D38" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.12</v>
+        <v>1.76</v>
       </c>
       <c r="F38" t="n">
-        <v>1.27</v>
+        <v>2.4</v>
       </c>
       <c r="G38" t="n">
-        <v>3.15</v>
+        <v>1.47</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1645,28 +1645,28 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MPS vs Poxyt</t>
+          <t>Gambia vs Somalia</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2.27</v>
+        <v>1.13</v>
       </c>
       <c r="D39" t="n">
-        <v>3.7</v>
+        <v>6.5</v>
       </c>
       <c r="E39" t="n">
-        <v>2.45</v>
+        <v>15</v>
       </c>
       <c r="F39" t="n">
-        <v>1.35</v>
+        <v>1.58</v>
       </c>
       <c r="G39" t="n">
-        <v>2.73</v>
+        <v>2.2</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -1682,23 +1682,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NK Koprivnica vs NK Uskok</t>
+          <t>Nijer vs Lesotho</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2.45</v>
+        <v>1.74</v>
       </c>
       <c r="D40" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.31</v>
+        <v>4.5</v>
       </c>
       <c r="F40" t="n">
-        <v>1.53</v>
+        <v>2.18</v>
       </c>
       <c r="G40" t="n">
-        <v>2.26</v>
+        <v>1.6</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -1709,28 +1709,28 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>53 dk içinde</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Rebels Fc vs Roots</t>
+          <t>Fas vs Gabon</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2.39</v>
+        <v>1.14</v>
       </c>
       <c r="D41" t="n">
-        <v>3.1</v>
+        <v>6.5</v>
       </c>
       <c r="E41" t="n">
-        <v>2.6</v>
+        <v>15</v>
       </c>
       <c r="F41" t="n">
-        <v>2.04</v>
+        <v>1.55</v>
       </c>
       <c r="G41" t="n">
-        <v>1.66</v>
+        <v>2.27</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -1741,28 +1741,28 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>FC Jerusalem vs Maccabi Yavne</t>
+          <t>Tanzanya vs Gine Bissau</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="D42" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" t="n">
         <v>3.3</v>
       </c>
-      <c r="E42" t="n">
-        <v>2.9</v>
-      </c>
       <c r="F42" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="G42" t="n">
-        <v>1.87</v>
+        <v>1.45</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -1773,28 +1773,28 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Hapoel Tzafririm Holon vs Kfar Saba 1928</t>
+          <t>Nijerya vs Madagaskar</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2.9</v>
+        <v>1.18</v>
       </c>
       <c r="D43" t="n">
-        <v>3.15</v>
+        <v>5.5</v>
       </c>
       <c r="E43" t="n">
-        <v>2.15</v>
+        <v>13</v>
       </c>
       <c r="F43" t="n">
-        <v>1.99</v>
+        <v>1.71</v>
       </c>
       <c r="G43" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -1805,28 +1805,28 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Hapoel Hadera vs Maccabi Ashdod</t>
+          <t>Burkina Faso vs Benin</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="D44" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="E44" t="n">
-        <v>3.7</v>
+        <v>6.5</v>
       </c>
       <c r="F44" t="n">
-        <v>1.79</v>
+        <v>2.31</v>
       </c>
       <c r="G44" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -1842,23 +1842,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ironi Modiin vs MS Ashdod</t>
+          <t>Malavi vs Günay Sudan</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>6</v>
+        <v>1.64</v>
       </c>
       <c r="D45" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="E45" t="n">
-        <v>1.4</v>
+        <v>5</v>
       </c>
       <c r="F45" t="n">
-        <v>1.7</v>
+        <v>2.26</v>
       </c>
       <c r="G45" t="n">
-        <v>2.03</v>
+        <v>1.57</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -1869,28 +1869,28 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya vs Kiryat Yam</t>
+          <t>Mısır vs Angola</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2.54</v>
+        <v>1.35</v>
       </c>
       <c r="D46" t="n">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="E46" t="n">
-        <v>2.37</v>
+        <v>8.5</v>
       </c>
       <c r="F46" t="n">
-        <v>1.76</v>
+        <v>2.12</v>
       </c>
       <c r="G46" t="n">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -1901,28 +1901,28 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Hapoel Ironi Rishon Lezion vs Maccabi Ahi Nazareth FC</t>
+          <t>Mozambik vs Senegal</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1.6</v>
+        <v>9.5</v>
       </c>
       <c r="D47" t="n">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="E47" t="n">
-        <v>4.33</v>
+        <v>1.25</v>
       </c>
       <c r="F47" t="n">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="G47" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -1938,23 +1938,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Hapoel Akko FC vs Hapoel Afula</t>
+          <t>Sudan vs Etiyopya</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4.25</v>
+        <v>1.83</v>
       </c>
       <c r="D48" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="E48" t="n">
-        <v>1.64</v>
+        <v>4.15</v>
       </c>
       <c r="F48" t="n">
-        <v>1.66</v>
+        <v>2.39</v>
       </c>
       <c r="G48" t="n">
-        <v>2.06</v>
+        <v>1.5</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -1965,28 +1965,28 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Ata Bialik vs Hapoel Ihud Bnei Jatt</t>
+          <t>Togo vs Burundi</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1.18</v>
+        <v>1.58</v>
       </c>
       <c r="D49" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E49" t="n">
         <v>5.5</v>
       </c>
-      <c r="E49" t="n">
-        <v>10</v>
-      </c>
       <c r="F49" t="n">
-        <v>1.43</v>
+        <v>2.27</v>
       </c>
       <c r="G49" t="n">
-        <v>2.02</v>
+        <v>1.55</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -1997,28 +1997,28 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Maccabi Nujeidat Ahmed vs Hapoel Ironi Arraba</t>
+          <t>Cezayir vs Zambiya</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1.87</v>
+        <v>1.22</v>
       </c>
       <c r="D50" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="E50" t="n">
-        <v>3.3</v>
+        <v>12</v>
       </c>
       <c r="F50" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="G50" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2029,28 +2029,28 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Hapoel Migdal Haemeq vs Hapoel Nof HaGalil</t>
+          <t>Ruanda vs Liberya</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2.8</v>
+        <v>1.72</v>
       </c>
       <c r="D51" t="n">
         <v>3.2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.23</v>
+        <v>4.5</v>
       </c>
       <c r="F51" t="n">
-        <v>1.9</v>
+        <v>2.33</v>
       </c>
       <c r="G51" t="n">
-        <v>1.78</v>
+        <v>1.53</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2061,28 +2061,28 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MS Shikun Hamizrah vs Bnei Eilat</t>
+          <t>Mali vs Yeşil Burun Adaları</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2.39</v>
+        <v>2.09</v>
       </c>
       <c r="D52" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="E52" t="n">
-        <v>2.36</v>
+        <v>3.6</v>
       </c>
       <c r="F52" t="n">
-        <v>1.55</v>
+        <v>2.63</v>
       </c>
       <c r="G52" t="n">
-        <v>2.25</v>
+        <v>1.41</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2093,28 +2093,28 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Hapoel Bney Jdaide vs Maccabi Ihud Bnei Avtin</t>
+          <t>Colon Reserves vs Union Santa Fe Reserves</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="D53" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="E53" t="n">
-        <v>1.87</v>
+        <v>2.27</v>
       </c>
       <c r="F53" t="n">
-        <v>1.5</v>
+        <v>2.37</v>
       </c>
       <c r="G53" t="n">
-        <v>2.37</v>
+        <v>1.43</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2125,28 +2125,28 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Hapoel Bnei Ein Mahel vs Maccabi Maghar</t>
+          <t>San Martin de San Juan Reserves vs Godoy Cruz Reserves</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1.95</v>
+        <v>4.5</v>
       </c>
       <c r="D54" t="n">
         <v>3.8</v>
       </c>
       <c r="E54" t="n">
-        <v>2.8</v>
+        <v>1.55</v>
       </c>
       <c r="F54" t="n">
-        <v>1.33</v>
+        <v>1.58</v>
       </c>
       <c r="G54" t="n">
-        <v>3</v>
+        <v>2.18</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -2157,28 +2157,28 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Maccabi Isfiya vs Hapoel Givat Olga</t>
+          <t>CA Independiente (K) vs Ferro Carril Oeste (K)</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1.96</v>
+        <v>3.6</v>
       </c>
       <c r="D55" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="E55" t="n">
-        <v>3</v>
+        <v>1.87</v>
       </c>
       <c r="F55" t="n">
-        <v>1.41</v>
+        <v>2</v>
       </c>
       <c r="G55" t="n">
-        <v>2.55</v>
+        <v>1.7</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -2189,28 +2189,28 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MK Tzofi Haifa vs Tzeirey Haifa SC</t>
+          <t>Arsenal de Sarandi U20 vs Talleres de Remedios de Escalada U20</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2.7</v>
+        <v>1.58</v>
       </c>
       <c r="D56" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="E56" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G56" t="n">
         <v>2.11</v>
-      </c>
-      <c r="F56" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="G56" t="n">
-        <v>2.45</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2221,28 +2221,28 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ihud Bnei Baqa vs Hapoel Bnei Arrara Ara</t>
+          <t>Endonezya vs Singapur</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1.37</v>
+        <v>1.16</v>
       </c>
       <c r="D57" t="n">
-        <v>4.33</v>
+        <v>6</v>
       </c>
       <c r="E57" t="n">
-        <v>5.5</v>
+        <v>11</v>
       </c>
       <c r="F57" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="G57" t="n">
-        <v>1.53</v>
+        <v>2.12</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2253,28 +2253,28 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>25 dk içinde</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Beitar Haifa Yakov vs FC Kababir</t>
+          <t>Güney Kore U23 vs Vietnam U23</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="D58" t="n">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="E58" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F58" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="G58" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2285,28 +2285,28 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>25 dk içinde</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Maccabi Ironi Kfar Yona vs Hapoel Ramot Menashe</t>
+          <t>Güney Kore (K) vs Özbekistan (K)</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1.7</v>
+        <v>1.07</v>
       </c>
       <c r="D59" t="n">
-        <v>3.8</v>
+        <v>8.5</v>
       </c>
       <c r="E59" t="n">
-        <v>3.6</v>
+        <v>19</v>
       </c>
       <c r="F59" t="n">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="G59" t="n">
-        <v>2.55</v>
+        <v>3.15</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -2317,28 +2317,28 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>25 dk içinde</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv (W) vs Hapoel Raanana (W)</t>
+          <t>Japonya (K) vs Filipinler (K)</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2.55</v>
+        <v>23</v>
       </c>
       <c r="D60" t="n">
-        <v>3.5</v>
+        <v>41</v>
       </c>
       <c r="E60" t="n">
-        <v>2.23</v>
+        <v>4.5</v>
       </c>
       <c r="F60" t="n">
-        <v>1.55</v>
+        <v>1.28</v>
       </c>
       <c r="G60" t="n">
-        <v>2.27</v>
+        <v>3.15</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2349,22 +2349,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Maccabi Kishronot Hadera (W) vs Maccabi Holon (W)</t>
+          <t>SC ESV Parndorf 1919 vs Favoritner AC</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="D61" t="n">
-        <v>3.8</v>
+        <v>4.25</v>
       </c>
       <c r="E61" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="F61" t="n">
         <v>1.47</v>
@@ -2381,28 +2381,28 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Hapoel Jerusalem (K) vs Kiryat Gat SC (W)</t>
+          <t>Marchfeld Donauauen vs Oberwart</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2.16</v>
+        <v>1.62</v>
       </c>
       <c r="D62" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="E62" t="n">
-        <v>2.68</v>
+        <v>3.8</v>
       </c>
       <c r="F62" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="G62" t="n">
-        <v>2.23</v>
+        <v>2.77</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -2413,28 +2413,28 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ik Kongahalla vs Lindome GIF</t>
+          <t>SV Horn vs FCM Traiskirchen</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="D63" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="E63" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="F63" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="G63" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -2445,28 +2445,28 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FC Bole vs FC Champagne Sport</t>
+          <t>Kremser SC vs Mattersburger SV 2020</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="E64" t="n">
-        <v>1.87</v>
+        <v>3</v>
       </c>
       <c r="F64" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="G64" t="n">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -2477,28 +2477,28 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FC Saint-Blaise vs FC Bosna Neuchatel</t>
+          <t>Asco Atsv Wolfsberg vs SVG Bleiburg</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3.6</v>
+        <v>2.37</v>
       </c>
       <c r="D65" t="n">
         <v>3.7</v>
       </c>
       <c r="E65" t="n">
-        <v>1.75</v>
+        <v>2.27</v>
       </c>
       <c r="F65" t="n">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="G65" t="n">
-        <v>2.27</v>
+        <v>2.9</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -2509,25 +2509,29 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AL Gharafa U20 vs Al-Khor U20</t>
+          <t>SV Allerheiligen vs Deutschlandsberger SC</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1.45</v>
+        <v>2.59</v>
       </c>
       <c r="D66" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="E66" t="n">
-        <v>6</v>
-      </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
+        <v>2.09</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="G66" t="n">
+        <v>3.28</v>
+      </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>-</t>
@@ -2537,28 +2541,28 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Umm Salal U20 vs Al-Markhiya U20</t>
+          <t>Atus Velden vs Vst Voelkermarkt</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="D67" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="E67" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="F67" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="G67" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -2569,28 +2573,28 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Al Sadd U20 vs Mesaimeer U20</t>
+          <t>SV Rohrbach/Lafnitz vs USV Gnas</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1.76</v>
+        <v>2.68</v>
       </c>
       <c r="D68" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="E68" t="n">
-        <v>3.4</v>
+        <v>2.16</v>
       </c>
       <c r="F68" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="G68" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -2601,28 +2605,28 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Al-Arabi Doha U20 vs Al-Duhail U20</t>
+          <t>St. Anna vs TUS Bad Waltersdorf</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="D69" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="E69" t="n">
-        <v>4.15</v>
+        <v>3.1</v>
       </c>
       <c r="F69" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="G69" t="n">
-        <v>1.51</v>
+        <v>2.33</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -2633,28 +2637,28 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Al-Wakrah U20 vs Qatar SC U20</t>
+          <t>UFC Fehring vs SV Pachern</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>3.5</v>
+        <v>1.92</v>
       </c>
       <c r="D70" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="E70" t="n">
-        <v>1.97</v>
+        <v>3.05</v>
       </c>
       <c r="F70" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="G70" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -2665,28 +2669,28 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cariari Pococi vs Pitbulls Santa Barbara</t>
+          <t>TWL Elektra vs Floridsdorfer AC Wien II</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="D71" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="E71" t="n">
-        <v>2.73</v>
+        <v>3.7</v>
       </c>
       <c r="F71" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="G71" t="n">
-        <v>1.92</v>
+        <v>2.27</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -2697,28 +2701,28 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Porto Riko vs Guyana</t>
+          <t>1.ZS Simmeringer SC vs SV Post Vienna</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="D72" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="E72" t="n">
-        <v>2.4</v>
+        <v>1.81</v>
       </c>
       <c r="F72" t="n">
-        <v>1.99</v>
+        <v>1.41</v>
       </c>
       <c r="G72" t="n">
-        <v>1.72</v>
+        <v>2.63</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -2729,28 +2733,28 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Fk Teteks vs Rabotnicki Skopje</t>
+          <t>KAC 1909 vs Spittal</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>4.2</v>
+        <v>1.68</v>
       </c>
       <c r="D73" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="E73" t="n">
-        <v>1.64</v>
+        <v>3.7</v>
       </c>
       <c r="F73" t="n">
-        <v>1.72</v>
+        <v>1.43</v>
       </c>
       <c r="G73" t="n">
-        <v>1.95</v>
+        <v>2.58</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -2761,28 +2765,28 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Detonit Plackovica vs Ohrid</t>
+          <t>St. Veit vs SV Matrei</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>4.5</v>
+        <v>1.3</v>
       </c>
       <c r="D74" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="E74" t="n">
-        <v>1.6</v>
+        <v>6.5</v>
       </c>
       <c r="F74" t="n">
-        <v>1.87</v>
+        <v>1.28</v>
       </c>
       <c r="G74" t="n">
-        <v>1.78</v>
+        <v>3.15</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -2793,28 +2797,28 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Mogila vs Aresimi 1973</t>
+          <t>Sc Bad Sauerbrunn vs FC Deutschkreutz</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>31</v>
+        <v>1.87</v>
       </c>
       <c r="D75" t="n">
-        <v>17</v>
+        <v>3.7</v>
       </c>
       <c r="E75" t="n">
-        <v>1.07</v>
+        <v>3.1</v>
       </c>
       <c r="F75" t="n">
-        <v>1.07</v>
+        <v>1.47</v>
       </c>
       <c r="G75" t="n">
-        <v>6.5</v>
+        <v>2.4</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -2825,28 +2829,28 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Rivers United vs Kun Khalifat FC</t>
+          <t>Klingenbach vs ASK Kohfidisch</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1.22</v>
+        <v>1.79</v>
       </c>
       <c r="D76" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="E76" t="n">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="F76" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="G76" t="n">
-        <v>2.37</v>
+        <v>2.22</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -2862,23 +2866,23 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Grorud U19 vs Valerenga U19</t>
+          <t>USV Halbturn vs SC Oberpullendorf</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1.35</v>
+        <v>1.76</v>
       </c>
       <c r="D77" t="n">
-        <v>4.75</v>
+        <v>3.7</v>
       </c>
       <c r="E77" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F77" t="n">
-        <v>1.12</v>
+        <v>1.51</v>
       </c>
       <c r="G77" t="n">
-        <v>5</v>
+        <v>2.31</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -2889,28 +2893,28 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Haslum IL U19 vs Asker U19</t>
+          <t>SV Sedda Bad Schallerbach vs SV Kuchl</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1.45</v>
+        <v>1.84</v>
       </c>
       <c r="D78" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="E78" t="n">
-        <v>4.25</v>
+        <v>3.15</v>
       </c>
       <c r="F78" t="n">
-        <v>1.08</v>
+        <v>1.4</v>
       </c>
       <c r="G78" t="n">
-        <v>6.5</v>
+        <v>2.63</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -2921,28 +2925,28 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>IF Ready U19 vs Skedsmo U19</t>
+          <t>Precision FC vs Arabian Falcons FC</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1.84</v>
+        <v>1.28</v>
       </c>
       <c r="D79" t="n">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="E79" t="n">
-        <v>2.8</v>
+        <v>8</v>
       </c>
       <c r="F79" t="n">
-        <v>1.13</v>
+        <v>1.62</v>
       </c>
       <c r="G79" t="n">
-        <v>5</v>
+        <v>2.14</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -2953,28 +2957,28 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Sprint/Jeloy U19 vs Sarpsborg 08 U19</t>
+          <t>Modern Sport Dubai vs Masfout Club</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1.33</v>
+        <v>2.2</v>
       </c>
       <c r="D80" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="E80" t="n">
-        <v>5</v>
+        <v>2.58</v>
       </c>
       <c r="F80" t="n">
-        <v>1.14</v>
+        <v>1.51</v>
       </c>
       <c r="G80" t="n">
-        <v>4.75</v>
+        <v>2.34</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -2985,28 +2989,28 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Christiania BK U19 vs Gjovik Lyn U19</t>
+          <t>Genk (K) vs KAA Gent (W)</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1.03</v>
+        <v>1.74</v>
       </c>
       <c r="D81" t="n">
-        <v>10</v>
+        <v>3.6</v>
       </c>
       <c r="E81" t="n">
-        <v>34</v>
+        <v>3.7</v>
       </c>
       <c r="F81" t="n">
-        <v>1.14</v>
+        <v>1.6</v>
       </c>
       <c r="G81" t="n">
-        <v>4.75</v>
+        <v>2.14</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -3017,28 +3021,28 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Baerum Sk U19 vs Ullern U19</t>
+          <t>Kommunalnik Slonim vs BATE Borisov Reserves</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2.12</v>
+        <v>1.55</v>
       </c>
       <c r="D82" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="E82" t="n">
-        <v>2.37</v>
+        <v>4.33</v>
       </c>
       <c r="F82" t="n">
-        <v>1.1</v>
+        <v>1.45</v>
       </c>
       <c r="G82" t="n">
-        <v>6</v>
+        <v>1.53</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -3049,28 +3053,28 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>KFUM U19 vs Nordstrand U19</t>
+          <t>FC Lida vs FC Smorgon</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1.2</v>
+        <v>1.96</v>
       </c>
       <c r="D83" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="E83" t="n">
-        <v>6.5</v>
+        <v>2.9</v>
       </c>
       <c r="F83" t="n">
-        <v>1.09</v>
+        <v>1.57</v>
       </c>
       <c r="G83" t="n">
-        <v>5.5</v>
+        <v>2.15</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -3081,28 +3085,28 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Follo U19 vs Lillehammer U19</t>
+          <t>Thimphu FC vs Tensung FC</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
       <c r="D84" t="n">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="E84" t="n">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="F84" t="n">
-        <v>1.12</v>
+        <v>1.45</v>
       </c>
       <c r="G84" t="n">
-        <v>5</v>
+        <v>1.71</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -3113,28 +3117,28 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Raelingen U19 vs Gjelleraasen U19</t>
+          <t>San Antonio Bulo Bulo vs Real Potosi</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>23</v>
+        <v>2.12</v>
       </c>
       <c r="D85" t="n">
-        <v>9</v>
+        <v>3.5</v>
       </c>
       <c r="E85" t="n">
-        <v>1.05</v>
+        <v>2.8</v>
       </c>
       <c r="F85" t="n">
-        <v>1.12</v>
+        <v>1.62</v>
       </c>
       <c r="G85" t="n">
-        <v>5</v>
+        <v>2.11</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -3145,28 +3149,28 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Lorenskog U19 vs Kjelsas U19</t>
+          <t>Itabirito FC MG U20 vs America MG U20</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="D86" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="E86" t="n">
-        <v>1.3</v>
+        <v>1.58</v>
       </c>
       <c r="F86" t="n">
-        <v>1.14</v>
+        <v>1.64</v>
       </c>
       <c r="G86" t="n">
-        <v>4.75</v>
+        <v>2.06</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -3177,28 +3181,28 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Oman Club vs Sur Club</t>
+          <t>Marica RJ U20 vs Volta Redonda U20</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>3.8</v>
+        <v>2.09</v>
       </c>
       <c r="D87" t="n">
         <v>3.2</v>
       </c>
       <c r="E87" t="n">
-        <v>1.81</v>
+        <v>3.05</v>
       </c>
       <c r="F87" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="G87" t="n">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -3209,28 +3213,28 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Sohar Club vs Al Seeb</t>
+          <t>AA Carapebus vs Sao Cristovao</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>2.23</v>
+        <v>4.5</v>
       </c>
       <c r="D88" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="E88" t="n">
-        <v>2.9</v>
+        <v>1.72</v>
       </c>
       <c r="F88" t="n">
-        <v>2.18</v>
+        <v>2.37</v>
       </c>
       <c r="G88" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -3241,28 +3245,28 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>FK Podkonice vs MFK Ruzomberok B</t>
+          <t>Aparecidense U20 vs Guanabara City GO U20</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>2.58</v>
+        <v>3.5</v>
       </c>
       <c r="D89" t="n">
         <v>3.3</v>
       </c>
       <c r="E89" t="n">
-        <v>2.31</v>
+        <v>1.86</v>
       </c>
       <c r="F89" t="n">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="G89" t="n">
-        <v>1.96</v>
+        <v>1.76</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -3273,28 +3277,28 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Montevideo City Torque vs Atenas</t>
+          <t>Inter De Minas vs Nacional MG</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1.53</v>
+        <v>3.2</v>
       </c>
       <c r="D90" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="E90" t="n">
-        <v>5</v>
+        <v>1.91</v>
       </c>
       <c r="F90" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="G90" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -3305,28 +3309,28 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Danubio vs Penarol Montevideo</t>
+          <t>Corinthians U20 vs EC XV de Novembro de Jau SP U20</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="D91" t="n">
-        <v>3.05</v>
+        <v>5.5</v>
       </c>
       <c r="E91" t="n">
-        <v>2.05</v>
+        <v>10</v>
       </c>
       <c r="F91" t="n">
-        <v>2.27</v>
+        <v>1.45</v>
       </c>
       <c r="G91" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -3337,28 +3341,28 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>AL Ahli Amman vs Ma'an</t>
+          <t>Santos FC U20 vs Jabaquara SP U20</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1.66</v>
+        <v>1.12</v>
       </c>
       <c r="D92" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="E92" t="n">
-        <v>4.2</v>
+        <v>13.25</v>
       </c>
       <c r="F92" t="n">
-        <v>1.81</v>
+        <v>1.37</v>
       </c>
       <c r="G92" t="n">
-        <v>1.86</v>
+        <v>2.8</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -3369,28 +3373,28 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Sahl Horan SC vs Hayy Al-Amir Hassan</t>
+          <t>Guarani SP U20 vs Uniao Suzano AC U20</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2.2</v>
+        <v>1.33</v>
       </c>
       <c r="D93" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="E93" t="n">
-        <v>2.9</v>
+        <v>6.5</v>
       </c>
       <c r="F93" t="n">
-        <v>2.22</v>
+        <v>1.6</v>
       </c>
       <c r="G93" t="n">
-        <v>1.55</v>
+        <v>2.14</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -3401,28 +3405,28 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Nashama Al-Mustaqbal (W) vs Al Orthodoxi (W)</t>
+          <t>Sao Paulo FC U20 vs Sao Bernardo SP U20</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2.04</v>
+        <v>1.33</v>
       </c>
       <c r="D94" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="E94" t="n">
-        <v>2.8</v>
+        <v>7</v>
       </c>
       <c r="F94" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="G94" t="n">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -3433,30 +3437,4958 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Sfera SP U20 vs XV de Novembro (Piracicaba) U20</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="D95" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E95" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F95" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G95" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Desportivo Brasil U20 vs Osasco Sporting SP U20</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="D96" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E96" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="F96" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G96" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Santo Andre U20 vs Sertaozinho U20</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="D97" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E97" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="F97" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G97" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>EC Agua Santa U20 vs Capivariano Sp U20</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="D98" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E98" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F98" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G98" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Palmeiras U20 vs Ituano SP U20</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="D99" t="n">
+        <v>6</v>
+      </c>
+      <c r="E99" t="n">
+        <v>12</v>
+      </c>
+      <c r="F99" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G99" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>JS El Biar U20 vs USM Alger U20</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="D100" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E100" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G100" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>FK Morkovice vs Luhacovice</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D101" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E101" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="F101" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G101" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Fc Slovacko B vs Zbrojovka Brno B</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="D102" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E102" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="F102" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="G102" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>MFK Karvina B vs SK Artis Brno II</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D103" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E103" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G103" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Zlin B vs MFK Vitkovice</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="D104" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E104" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G104" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>FC Pisek vs Pribram B</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="D105" t="n">
+        <v>4</v>
+      </c>
+      <c r="E105" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F105" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G105" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>TJ Tatran Bohunice vs FC Sparta Brno</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D106" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E106" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G106" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>FK Slavoj Vysehrad vs Sokol Hostoun</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D107" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E107" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F107" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G107" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>SK Batov vs FK Nove Sady</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="D108" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E108" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F108" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G108" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>FC Chomutov vs 1. FC Karlovy Vary</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="D109" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E109" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F109" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G109" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>54 dk içinde</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Wuxi Wugou vs Guangxi Hengchen</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D110" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E110" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F110" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G110" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Hellerup vs Roskilde</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>5</v>
+      </c>
+      <c r="D111" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E111" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F111" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G111" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Elite 3000 Helsingor vs Holbaek</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="D112" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E112" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="F112" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G112" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>24 dk içinde</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Zurich vs Neuchatel Xamax FC</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="D113" t="n">
+        <v>4</v>
+      </c>
+      <c r="E113" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F113" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="G113" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>FK Gornji Rahic vs Sarajevo</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>12</v>
+      </c>
+      <c r="D114" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E114" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="F114" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G114" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>VfB Stuttgart vs Heidenheim</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="D115" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E115" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="G115" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Penafiel vs Deportivo A Coruña</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D116" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E116" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="F116" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G116" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Chaves vs Vitoria Guimaraes</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>4</v>
+      </c>
+      <c r="D117" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="G117" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Fransa U19 vs İtalya U19</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D118" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E118" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G118" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Slovakya U19 vs Kazakistan U19</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D119" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E119" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G119" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>İngiltere U19 vs İrlanda U19</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="D120" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E120" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G120" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Almanya vs Fransa U20</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="D121" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E121" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="F121" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G121" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Hindistan vs Panama</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>9</v>
+      </c>
+      <c r="D122" t="n">
+        <v>5</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G122" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Persiba Balikpapan vs Dejan FC</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D123" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E123" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="F123" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G123" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Nokian Palloseura vs TPV II</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="D124" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E124" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="G124" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>NuPS vs PPJ/Ruoholahti</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="D125" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E125" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G125" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>EsPa vs GrIFK Reservi</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D126" t="n">
+        <v>4</v>
+      </c>
+      <c r="E126" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G126" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Toukolan Teras vs HPS II</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="D127" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E127" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="G127" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>KTP vs Mikkelin Palloilijat</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="D128" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E128" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F128" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G128" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Kapa/Pule vs Haka Valkeakoski</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>5</v>
+      </c>
+      <c r="D129" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E129" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="F129" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G129" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Tampere United vs JJK Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="D130" t="n">
+        <v>5</v>
+      </c>
+      <c r="E130" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F130" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="G130" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Afan Lido vs Newport City FC</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D131" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E131" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="F131" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G131" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Baglan Dragons vs Carmarthen Town Afc</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D132" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E132" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="F132" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G132" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Caerphilly Athletic FC vs Pontypridd Town</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="D133" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E133" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G133" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Aberystwyth Town FC vs Pure Swansea FC</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D134" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E134" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F134" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G134" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Bangor 1876 vs Buckley Town</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="D135" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="E135" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F135" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G135" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Ruthin Town vs Penrhyncoch</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="D136" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E136" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="F136" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G136" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Attram De Visser vs Accra Lions</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="D137" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E137" t="n">
+        <v>4</v>
+      </c>
+      <c r="F137" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="G137" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Uhamiaji FC vs Raskazone</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Chile U19 vs Peru U19</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="D138" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E138" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="F138" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G138" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>GNK Dinamo Zagreb U21 vs NK Mladost Zdralovi</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="D139" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E139" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="F139" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G139" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>NK Uljanik vs NK Slavonija Pozega</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="D140" t="n">
+        <v>4</v>
+      </c>
+      <c r="E140" t="n">
+        <v>5</v>
+      </c>
+      <c r="F140" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G140" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>NK Hrvatski Dragovoljac vs Radnik Krizevci</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="D141" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E141" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F141" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G141" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Aizawl vs MLS FC Lawngtlai</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="D142" t="n">
+        <v>10</v>
+      </c>
+      <c r="E142" t="n">
+        <v>26</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G142" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Motagua Reserves vs Genesis de Comayagua Reserves</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="D143" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E143" t="n">
+        <v>6</v>
+      </c>
+      <c r="F143" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G143" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Lobos UPNFM Reserves vs CD Choloma Reserves</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="D144" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E144" t="n">
+        <v>7</v>
+      </c>
+      <c r="F144" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G144" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>University College Dublin FC vs Bray Wanderers AFC</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="D145" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E145" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="F145" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G145" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Cobh Ramblers vs Athlone Town FC</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D146" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E146" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F146" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G146" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Kerry FC vs Wexford FC</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D147" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E147" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="F147" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G147" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Treaty United FC vs Finn Harps FC</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D148" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E148" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="F148" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G148" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Galway United vs Shelbourne</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="D149" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E149" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="F149" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G149" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Kilbarrack United vs Killester United</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="D150" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E150" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F150" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="G150" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Wayside Celtic FC vs Tolka Rovers AFC</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D151" t="n">
+        <v>5</v>
+      </c>
+      <c r="E151" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F151" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="G151" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Inchicore Athletic FC vs St Francis FC Senior Sunday</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="D152" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E152" t="n">
+        <v>10</v>
+      </c>
+      <c r="F152" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="G152" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Spartans FC vs Dundee FC II</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="D153" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E153" t="n">
+        <v>10</v>
+      </c>
+      <c r="F153" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G153" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Strathspey Thistle vs Forres Mechanics</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="D154" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E154" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F154" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G154" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Inverness vs Greenock Morton</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="D155" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E155" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F155" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G155" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Ayr United vs Stenhousemuir</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D156" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E156" t="n">
+        <v>3</v>
+      </c>
+      <c r="F156" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G156" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Arbroath vs Queen's Park</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="D157" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="E157" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="F157" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="G157" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Raith Rovers vs Livingston</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="D158" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E158" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="F158" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="G158" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Vanersborgs IF vs Ahlafors IF</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D159" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E159" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F159" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G159" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Hammarby Talang Ff vs IFK Stocksund</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D160" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E160" t="n">
+        <v>8</v>
+      </c>
+      <c r="F160" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="G160" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Orebro SK Soder (W) vs Linkopings FC (W)</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>5</v>
+      </c>
+      <c r="D161" t="n">
+        <v>4</v>
+      </c>
+      <c r="E161" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F161" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G161" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Lunds BK vs Kristianstad Fc</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="D162" t="n">
+        <v>4</v>
+      </c>
+      <c r="E162" t="n">
+        <v>5</v>
+      </c>
+      <c r="F162" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G162" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Rappe GOIF vs Vaxjo Norra</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D163" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E163" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="F163" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G163" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Landvetter IS vs Torslanda IK</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="D164" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="E164" t="n">
+        <v>5</v>
+      </c>
+      <c r="F164" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G164" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Dalstorps IF vs IF Boljan Falkenberg</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="D165" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="E165" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="F165" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G165" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>FC Concordia Lausanne vs Stade Lausanne-Ouchy II</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>3</v>
+      </c>
+      <c r="D166" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E166" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="F166" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G166" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Team Vaud Lausanne Ii vs Fc Echallens Region</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="D167" t="n">
+        <v>4</v>
+      </c>
+      <c r="E167" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="F167" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G167" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Thor Akureyri (K) vs Fram Reykjavik (K)</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="D168" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E168" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F168" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G168" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Valur Reykjavik (K) vs Vikingur Reykjavik (K)</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="D169" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E169" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="F169" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G169" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Llaneros Villavicencio U19 vs Independiente Santa Fe U19</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D170" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E170" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="F170" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G170" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Orsomarso U19 vs Aguilas Doradas U19</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D171" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E171" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="F171" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G171" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Coleraine vs Linfield</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="D172" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E172" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F172" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G172" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Linfield (W) vs Cliftonville (W)</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D173" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E173" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F173" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G173" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Derry City (W) vs Larne FC (W)</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="D174" t="n">
+        <v>7</v>
+      </c>
+      <c r="E174" t="n">
+        <v>12</v>
+      </c>
+      <c r="F174" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="G174" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Lisburn LFC (W) vs Crusaders Strikers FC (W)</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D175" t="n">
+        <v>4</v>
+      </c>
+      <c r="E175" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="F175" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G175" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Newry City vs Harland and Wolff Welders</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D176" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E176" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="F176" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G176" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Glenavon FC vs Loughgall</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="D177" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E177" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F177" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G177" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Rathfriland Rangers vs Warrenpoint Town</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D178" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E178" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="F178" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="G178" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Bermuda vs Guadeloupe</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="D179" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E179" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F179" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G179" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>FC Koeppchen Wormeldange vs FC Berdenia Berbourg</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="D180" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E180" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="F180" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G180" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>50 dk içinde</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Pecsi MFC (K) vs Ujpest (K)</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D181" t="n">
+        <v>5</v>
+      </c>
+      <c r="E181" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F181" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G181" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Zfk Istatov (W) vs ZFK Ljuboten (K)</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D182" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E182" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F182" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="G182" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Kedah vs Kelantan WTS</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="D183" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E183" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F183" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G183" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Atlante FC U21 vs CF Monterrey U21</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D184" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E184" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="F184" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G184" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>FC Politecnico vs Aztecas AMF</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
         <v>1.5</v>
       </c>
-      <c r="D95" t="n">
+      <c r="D185" t="n">
+        <v>4</v>
+      </c>
+      <c r="E185" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="F185" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G185" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Around Soccer vs Deportivo Muxes</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D186" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E186" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="F186" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G186" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Pachuca III vs Aguilas Teotihuacan</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="D187" t="n">
+        <v>11</v>
+      </c>
+      <c r="E187" t="n">
+        <v>21</v>
+      </c>
+      <c r="F187" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="G187" t="n">
+        <v>5</v>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Correcaminos III vs Fut-Car</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="D188" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E188" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="F188" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G188" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Valle de Xico FC vs Halcones Zuniga SC</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="D189" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E189" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F189" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="G189" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Haras El Hodood vs Dayrout</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D190" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E190" t="n">
+        <v>13</v>
+      </c>
+      <c r="F190" t="n">
+        <v>2</v>
+      </c>
+      <c r="G190" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Delta United vs Ismaily SC</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="D191" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E191" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F191" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="G191" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>We Sporting Club vs La Viena FC</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="D192" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E192" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="F192" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G192" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>El Terasanah vs Baladiyet El Mahallah</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="D193" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E193" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="F193" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G193" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>El Entag El Harby vs Tanta</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="D194" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E194" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F194" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="G194" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Raa SC vs Misr Insurance FC</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="D195" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="E195" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F195" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G195" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Banha vs Gomhoryet Shebin</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="D196" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="E196" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F196" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="G196" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Al-Shanwani vs Diamond SC</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="D197" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E197" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F197" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="G197" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Cascada FC vs Orange Sport FSI</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="D198" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E198" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F198" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G198" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Al Qanater vs Levels FC</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D199" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="E199" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="F199" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="G199" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Shabab El Obour SC vs El Ilamayeen</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="D200" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="E200" t="n">
+        <v>4</v>
+      </c>
+      <c r="F200" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G200" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Varhaug vs Staal Jorpeland</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D201" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E201" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="F201" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="G201" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Aalesund FK II vs Rosenborg BK II</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="D202" t="n">
+        <v>4</v>
+      </c>
+      <c r="E202" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="F202" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="G202" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Bodo/Glimt (K) vs Roa (K)</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D203" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E203" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F203" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G203" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Fanja vs Al Nasr SC</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D204" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E204" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="F204" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G204" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Al-Samail vs Dhofar SCSC</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D205" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E205" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="F205" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G205" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Saham vs Al-Musannah SC</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="D206" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E206" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F206" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="G206" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Ibri Club vs Al Nahda</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D207" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E207" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="F207" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G207" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Costa Del Este Reserves vs Costa Del Este</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="D208" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E208" t="n">
+        <v>5</v>
+      </c>
+      <c r="F208" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G208" t="n">
+        <v>2</v>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Sportivo Luqueno vs Guarani Asuncion</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D209" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E209" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="F209" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G209" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Independiente FBC vs Club Sportivo Carapegua</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="D210" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E210" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F210" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G210" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>50 dk içinde</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Nacional Asunción Reserve vs Sportivo Ameliano Reserves</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="D211" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E211" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F211" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G211" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Club Olimpia De Ita vs Club Sport Colombia</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D212" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E212" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="F212" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G212" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Atlantida SC vs 29 de Septiembre</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="D213" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E213" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F213" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G213" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Club Asociacion Deportiva Agropecuaria Jaen vs Deportivo Llacuabamba</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="D214" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E214" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F214" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G214" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>23:15</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>AD Comerciantes FC vs Sport Huancayo Reserves</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="D215" t="n">
         <v>3.7</v>
       </c>
-      <c r="E95" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F95" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="G95" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="H95" t="inlineStr">
+      <c r="E215" t="n">
+        <v>5</v>
+      </c>
+      <c r="F215" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G215" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Sport Boys Reserves vs Centro Social Pariacoto</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="D216" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E216" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F216" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G216" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>FC Killas (W) vs Flamengo FBC (W)</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="D217" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E217" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="F217" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G217" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>KS Lublinianka Wieniawa Lublin vs Swidniczanka Swidnik</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D218" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E218" t="n">
+        <v>5</v>
+      </c>
+      <c r="F218" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G218" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>KS Wierzyca Pelplin vs Sokol Bozepole Wielkie</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="D219" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E219" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="F219" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G219" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Unia Tarnow vs MKS Limanovia Limanowa</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D220" t="n">
+        <v>4</v>
+      </c>
+      <c r="E220" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="F220" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G220" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Tecza Biskupiec vs Mazur Elk</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="D221" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E221" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F221" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G221" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Swit Nowy Dwór Mazowiecki vs LKS Lomza</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D222" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E222" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="F222" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G222" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Zabkovia Zabki vs Mlawianka Mlawa</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="D223" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E223" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F223" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="G223" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Wisla Plock II vs Jagiellonia Bialystok II</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="D224" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E224" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="F224" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G224" t="n">
+        <v>3</v>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>49 dk içinde</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Wisla Krakow B vs MKS Czarni Polaniec</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="D225" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E225" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F225" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G225" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Wislanie Jaskowice vs Wisloka Debica</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="D226" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E226" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F226" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G226" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>KF Ferizaj vs KF 2 Korriku</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="D227" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E227" t="n">
+        <v>6</v>
+      </c>
+      <c r="F227" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G227" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Oxigen Bucuresti vs SC FC Voluntari SA 2</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="D228" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E228" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F228" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="G228" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>LPS HD Clinceni vs SC Dinamo 1948 SA 2</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="D229" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E229" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F229" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G229" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>ACS Viitorul Corbeanca vs CS Paulesti</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D230" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E230" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="F230" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G230" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>CS Blejoi vs Petrolul Berca</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D231" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E231" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="F231" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G231" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Cs Sanatatea Servicii Publice Cluj vs Lotus Baile Felix</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="D232" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E232" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F232" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G232" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>CS Timisul Sag vs Universitatea Alba Iulia</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="D233" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E233" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F233" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G233" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>ACS Medias 2022 vs Tricolorul Breaza</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D234" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E234" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F234" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G234" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>ACSO Filiasi vs ASFC Pausesti Otasau</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="D235" t="n">
+        <v>4</v>
+      </c>
+      <c r="E235" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="F235" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="G235" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>ZFK Masinac Nis (K) vs ZFK Milutinac (W)</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="D236" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E236" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="F236" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G236" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>FK Pohronie vs Inter Bratislava</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D237" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E237" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="F237" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G237" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Slavia Tu Kosice vs Spartak Medzev</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="D238" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E238" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F238" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G238" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>KFC Komarno B vs Banik Prievidza</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="D239" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E239" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="F239" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G239" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Spartak Myjava vs SK 1923 Gabcikovo</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="D240" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E240" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F240" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G240" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Jadran Dekani vs Nk Ilirija</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="D241" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E241" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F241" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G241" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Al-Nassr Riyadh (K) vs Al-Ula FC (W)</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D242" t="n">
+        <v>4</v>
+      </c>
+      <c r="E242" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F242" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G242" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Al Ittihad Jeddah (W) vs Al Quadisiya Al Khubar (W)</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D243" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E243" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F243" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G243" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Deportes Iquique (W) vs Colo Colo (W)</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>96</v>
+      </c>
+      <c r="D244" t="n">
+        <v>23</v>
+      </c>
+      <c r="E244" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F244" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="G244" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>CA Lito vs Los Halcones</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="D245" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E245" t="n">
+        <v>23</v>
+      </c>
+      <c r="F245" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G245" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Sama Al Sarhan vs Al Aqaba</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="D246" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E246" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F246" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G246" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Amman FC vs Ittihad AL Ramtha</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="D247" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E247" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="F247" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G247" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Academia Puerto Cabello II vs Atletico El Vigia</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="D248" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E248" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F248" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G248" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Mafunzo FC vs Mwembe Makumbi City</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="D249" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E249" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F249" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="G249" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="H249" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/bugun_oranlar.xlsx
+++ b/bugun_oranlar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H133"/>
+  <dimension ref="A1:H87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,23 +466,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Almanya vs Yunanistan</t>
+          <t>Belçika vs Fransa</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.45</v>
+        <v>3.8</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>1.85</v>
       </c>
       <c r="F2" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -498,23 +498,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Norveç vs Portekiz</t>
+          <t>Türkiye vs İtalya</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="F3" t="n">
-        <v>1.45</v>
+        <v>1.75</v>
       </c>
       <c r="G3" t="n">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -530,23 +530,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>İsrail vs İrlanda</t>
+          <t>Romanya vs Bosna-Hersek</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.63</v>
+        <v>2.27</v>
       </c>
       <c r="D4" t="n">
         <v>3.3</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="F4" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -557,28 +557,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Real Oviedo vs Sporting Gijon</t>
+          <t>İsveç vs Polonya</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4</v>
+        <v>1.71</v>
       </c>
       <c r="G5" t="n">
-        <v>1.51</v>
+        <v>2.08</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -589,28 +589,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>30 dk içinde</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CD Teruel vs SD Huesca</t>
+          <t>Gürcistan vs Ukrayna</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="D6" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="E6" t="n">
-        <v>2.03</v>
+        <v>2.7</v>
       </c>
       <c r="F6" t="n">
-        <v>2.45</v>
+        <v>2.16</v>
       </c>
       <c r="G6" t="n">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -621,28 +621,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Real Madrid B vs Alcorcon</t>
+          <t>Kuzey İrlanda vs Macaristan</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.92</v>
+        <v>2.8</v>
       </c>
       <c r="D7" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="F7" t="n">
-        <v>1.91</v>
+        <v>2.16</v>
       </c>
       <c r="G7" t="n">
-        <v>1.76</v>
+        <v>1.47</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -653,28 +653,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>30 dk içinde</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva vs UD Castellonense</t>
+          <t>Letonya vs Kıbrıs</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.12</v>
+        <v>2.6</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="E8" t="n">
-        <v>3.2</v>
+        <v>2.77</v>
       </c>
       <c r="F8" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="G8" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -685,28 +685,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>30 dk içinde</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CA Antoniano vs CD Ciudad de Lucena</t>
+          <t>Ermenistan vs Karadağ</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="D9" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="E9" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="F9" t="n">
-        <v>2.37</v>
+        <v>2.23</v>
       </c>
       <c r="G9" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -717,28 +717,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>30 dk içinde</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Recreativo Huelva vs Xerez CD</t>
+          <t>Danimarka U21 vs Belarus U21</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="D10" t="n">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F10" t="n">
-        <v>2.36</v>
+        <v>1.53</v>
       </c>
       <c r="G10" t="n">
-        <v>1.51</v>
+        <v>2.31</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -749,28 +749,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>30 dk içinde</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Atletico Central vs Sevilla Atletico</t>
+          <t>Punjab United vs AFC Croydon Athletic</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.8</v>
+        <v>5.5</v>
       </c>
       <c r="D11" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="E11" t="n">
-        <v>2.25</v>
+        <v>1.41</v>
       </c>
       <c r="F11" t="n">
-        <v>2.18</v>
+        <v>1.43</v>
       </c>
       <c r="G11" t="n">
-        <v>1.58</v>
+        <v>2.6</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -781,28 +781,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>30 dk içinde</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bollullos CF vs CD San Roque de Lepe</t>
+          <t>St Ives Town vs Nuneaton Town</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="D12" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="E12" t="n">
-        <v>3.1</v>
+        <v>1.74</v>
       </c>
       <c r="F12" t="n">
-        <v>2.18</v>
+        <v>1.47</v>
       </c>
       <c r="G12" t="n">
-        <v>1.6</v>
+        <v>2.45</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -813,28 +813,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>30 dk içinde</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bala Azul vs Alcantarilla FC</t>
+          <t>Coleshill Town vs Belper Town</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.83</v>
+        <v>2.26</v>
       </c>
       <c r="D13" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="E13" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="F13" t="n">
-        <v>2.16</v>
+        <v>1.76</v>
       </c>
       <c r="G13" t="n">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -845,28 +845,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>30 dk içinde</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Union Molinense CF 2020 vs Mazarron</t>
+          <t>Swansea City U21 vs Queens Park Rangers U21</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.31</v>
+        <v>1.81</v>
       </c>
       <c r="D14" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3</v>
+        <v>1.22</v>
       </c>
       <c r="G14" t="n">
-        <v>1.53</v>
+        <v>3.4</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -877,28 +877,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>30 dk içinde</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Puebla Calzada vs Cd Quintana</t>
+          <t>Biggleswade vs Hertford Town</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="D15" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="E15" t="n">
-        <v>4.75</v>
+        <v>3.3</v>
       </c>
       <c r="F15" t="n">
-        <v>2.04</v>
+        <v>1.47</v>
       </c>
       <c r="G15" t="n">
-        <v>1.66</v>
+        <v>2.4</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -909,28 +909,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>30 dk içinde</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FC Marbelli vs UD Torre del Mar</t>
+          <t>Leganes vs Castellon</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.98</v>
+        <v>3.05</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="E16" t="n">
-        <v>3.5</v>
+        <v>2.22</v>
       </c>
       <c r="F16" t="n">
-        <v>2.37</v>
+        <v>1.87</v>
       </c>
       <c r="G16" t="n">
-        <v>1.51</v>
+        <v>1.83</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -941,28 +941,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>30 dk içinde</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Motril CF vs Alhaurino</t>
+          <t>Leixoes U23 vs Vizela U23</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.47</v>
+        <v>2.33</v>
       </c>
       <c r="D17" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="E17" t="n">
-        <v>5.5</v>
+        <v>2.63</v>
       </c>
       <c r="F17" t="n">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="G17" t="n">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -973,28 +973,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Albinoleffe vs Alcione Milano</t>
+          <t>Ekvator Ginesi vs Sierra Leone</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2.12</v>
+        <v>1.97</v>
       </c>
       <c r="D18" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="E18" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="G18" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1005,28 +1005,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pescara vs Spezia</t>
+          <t>Zimbabve vs Demokratik Kongo Cumhuryeti</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="E19" t="n">
-        <v>2.22</v>
+        <v>1.72</v>
       </c>
       <c r="F19" t="n">
-        <v>1.74</v>
+        <v>2.4</v>
       </c>
       <c r="G19" t="n">
-        <v>1.97</v>
+        <v>1.5</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1037,28 +1037,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Foggia vs Sorrento</t>
+          <t>Tunus vs Botsvana</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2.37</v>
+        <v>1.2</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="E20" t="n">
-        <v>2.73</v>
+        <v>12</v>
       </c>
       <c r="F20" t="n">
-        <v>2.26</v>
+        <v>1.85</v>
       </c>
       <c r="G20" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1069,28 +1069,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Casarano vs Monopoli</t>
+          <t>Orta Afrika Cumhuriyeti vs Burkina Faso</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2.26</v>
+        <v>8.5</v>
       </c>
       <c r="D21" t="n">
-        <v>3.28</v>
+        <v>4.2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.73</v>
+        <v>1.35</v>
       </c>
       <c r="F21" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="G21" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1101,28 +1101,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>New York Cosmos vs Richmond Kickers</t>
+          <t>Kenya U23 vs Tanzania U23</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.6</v>
+        <v>2.22</v>
       </c>
       <c r="D22" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="E22" t="n">
-        <v>4.2</v>
+        <v>2.77</v>
       </c>
       <c r="F22" t="n">
-        <v>1.53</v>
+        <v>1.93</v>
       </c>
       <c r="G22" t="n">
-        <v>2.27</v>
+        <v>1.75</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1133,28 +1133,28 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CA Atlas vs Sportivo Barracas</t>
+          <t>Mauritania U23 vs DR Congo U23</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2.37</v>
+        <v>3.8</v>
       </c>
       <c r="D23" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>1.91</v>
       </c>
       <c r="F23" t="n">
-        <v>2.77</v>
+        <v>2.6</v>
       </c>
       <c r="G23" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1170,23 +1170,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Berazategui vs Sacachispas</t>
+          <t>Leones de Rosario vs Club Lujan</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="D24" t="n">
-        <v>2.77</v>
+        <v>2.63</v>
       </c>
       <c r="E24" t="n">
-        <v>3.15</v>
+        <v>2.58</v>
       </c>
       <c r="F24" t="n">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="G24" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1202,23 +1202,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Canuelas vs CA Fenix</t>
+          <t>Centro Espanyol vs Defensores de Cambaceres</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="D25" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="E25" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="F25" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="G25" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1229,28 +1229,28 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CA Atlanta vs Agropecuario</t>
+          <t>JJ Urquiza vs Club Leandro Niceforo Alem</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.91</v>
+        <v>2.14</v>
       </c>
       <c r="D26" t="n">
-        <v>3.05</v>
+        <v>2.54</v>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="F26" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="G26" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1261,28 +1261,28 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CA Los Andes vs Deportivo Moron</t>
+          <t>Flandria vs CS Dock Sud</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2.45</v>
+        <v>2.14</v>
       </c>
       <c r="D27" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="E27" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="F27" t="n">
-        <v>3.05</v>
+        <v>2.4</v>
       </c>
       <c r="G27" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1293,28 +1293,28 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CA Defensores de Belgrano vs Ferro Carril Oeste</t>
+          <t>Villa San Carlos Reserves vs Deportivo Laferrere Reserves</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="E28" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="F28" t="n">
-        <v>3.3</v>
+        <v>2.07</v>
       </c>
       <c r="G28" t="n">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1325,28 +1325,28 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Almagro vs Nueva Chicago</t>
+          <t>CS Dock Sud Reserves vs Defensores Unidos Reserves</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2.34</v>
+        <v>1.33</v>
       </c>
       <c r="D29" t="n">
-        <v>2.8</v>
+        <v>4.33</v>
       </c>
       <c r="E29" t="n">
-        <v>3.15</v>
+        <v>7</v>
       </c>
       <c r="F29" t="n">
-        <v>2.8</v>
+        <v>1.72</v>
       </c>
       <c r="G29" t="n">
-        <v>1.35</v>
+        <v>1.94</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1357,28 +1357,28 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre vs CA San Telmo</t>
+          <t>Social Atletico Television (K) vs Gimnasia Y Esgrima La Plata (K)</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="D30" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="E30" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="F30" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="G30" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1389,28 +1389,28 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CA Patronato vs San Martin de San Juan</t>
+          <t>Malezya vs Endonezya</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2.6</v>
+        <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="E31" t="n">
-        <v>2.73</v>
+        <v>1.47</v>
       </c>
       <c r="F31" t="n">
-        <v>2.77</v>
+        <v>1.64</v>
       </c>
       <c r="G31" t="n">
-        <v>1.38</v>
+        <v>2.12</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1421,28 +1421,28 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ferrocarril Midland vs Tristan Suarez</t>
+          <t>Al Ittifaq Dubai vs Al Urooba</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="D32" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="E32" t="n">
-        <v>3.4</v>
+        <v>1.68</v>
       </c>
       <c r="F32" t="n">
-        <v>2.9</v>
+        <v>1.62</v>
       </c>
       <c r="G32" t="n">
-        <v>1.33</v>
+        <v>2.14</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1453,28 +1453,28 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CD Maipu vs Temperley</t>
+          <t>Al Arabi Umm Al Quwain vs Al Dhaid</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="D33" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="E33" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="F33" t="n">
-        <v>2.45</v>
+        <v>1.72</v>
       </c>
       <c r="G33" t="n">
-        <v>1.47</v>
+        <v>1.98</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1485,28 +1485,28 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Racing de Cordoba vs Godoy Cruz</t>
+          <t>Barra Mansa FC vs Se Buzios Rj</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="D34" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="E34" t="n">
-        <v>2.27</v>
+        <v>4.75</v>
       </c>
       <c r="F34" t="n">
-        <v>2.6</v>
+        <v>1.79</v>
       </c>
       <c r="G34" t="n">
-        <v>1.43</v>
+        <v>1.87</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1517,28 +1517,28 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Racing Club vs Boca Juniors</t>
+          <t>Planalto EC GO (W) vs Anapolina Saf GO (W)</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>2.27</v>
       </c>
       <c r="D35" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="E35" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="F35" t="n">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="G35" t="n">
-        <v>1.5</v>
+        <v>1.99</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1549,28 +1549,28 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Argentino Quilmes vs Comunicaciones de Bueno Aires</t>
+          <t>Belenense FC vs Gaviao Kyikateje</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2.73</v>
+        <v>2.07</v>
       </c>
       <c r="D36" t="n">
-        <v>2.73</v>
+        <v>3.15</v>
       </c>
       <c r="E36" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="F36" t="n">
-        <v>3</v>
+        <v>1.93</v>
       </c>
       <c r="G36" t="n">
-        <v>1.32</v>
+        <v>1.75</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1581,28 +1581,28 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Villa Dalmine vs CD UAI Urquiza</t>
+          <t>NK Maribor vs Gorica</t>
         </is>
       </c>
       <c r="C37" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="D37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="F37" t="n">
         <v>1.6</v>
       </c>
-      <c r="D37" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="E37" t="n">
-        <v>5</v>
-      </c>
-      <c r="F37" t="n">
-        <v>2.4</v>
-      </c>
       <c r="G37" t="n">
-        <v>1.47</v>
+        <v>2.14</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1613,28 +1613,28 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano VR vs Club Atletico Alvarado</t>
+          <t>OFK Petrovac vs Mladost DG</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2.63</v>
+        <v>1.71</v>
       </c>
       <c r="D38" t="n">
-        <v>2.77</v>
+        <v>3.6</v>
       </c>
       <c r="E38" t="n">
-        <v>2.63</v>
+        <v>3.8</v>
       </c>
       <c r="F38" t="n">
-        <v>2.8</v>
+        <v>1.64</v>
       </c>
       <c r="G38" t="n">
-        <v>1.35</v>
+        <v>2.08</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1645,28 +1645,28 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Olimpo vs Gimnasia Y Esgrima De Chivilcoy</t>
+          <t>Hırvatistan U19 vs Fransa U19</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1.47</v>
+        <v>3.8</v>
       </c>
       <c r="D39" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="E39" t="n">
-        <v>8.5</v>
+        <v>1.72</v>
       </c>
       <c r="F39" t="n">
-        <v>3.5</v>
+        <v>1.66</v>
       </c>
       <c r="G39" t="n">
-        <v>1.25</v>
+        <v>2.06</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -1677,28 +1677,28 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Union Santa Fe (K) vs Boca Juniors (K)</t>
+          <t>Türkiye U19 vs İtalya U19</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="D40" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="E40" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="F40" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="G40" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -1709,28 +1709,28 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>San Luis (K) vs Lanus (K)</t>
+          <t>Slovakya U19 vs Polonya U19</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1.74</v>
+        <v>4.33</v>
       </c>
       <c r="D41" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="E41" t="n">
-        <v>4</v>
+        <v>1.64</v>
       </c>
       <c r="F41" t="n">
-        <v>2.02</v>
+        <v>1.86</v>
       </c>
       <c r="G41" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -1741,28 +1741,28 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Viamonte FC vs Villa Belgrano</t>
+          <t>North Macedonia U21 vs Russia U21</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2.7</v>
+        <v>6.5</v>
       </c>
       <c r="D42" t="n">
-        <v>3.15</v>
+        <v>4.33</v>
       </c>
       <c r="E42" t="n">
-        <v>2.27</v>
+        <v>1.37</v>
       </c>
       <c r="F42" t="n">
-        <v>2.01</v>
+        <v>1.62</v>
       </c>
       <c r="G42" t="n">
-        <v>1.71</v>
+        <v>2.12</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -1773,28 +1773,28 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>35 dk içinde</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ezeiza vs San Lorenzo de Villa Castells</t>
+          <t>Kore Cumhuriyeti vs Uruguay</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="D43" t="n">
         <v>3.2</v>
       </c>
       <c r="E43" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="F43" t="n">
-        <v>2.01</v>
+        <v>2.18</v>
       </c>
       <c r="G43" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -1805,28 +1805,28 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Crucero Del Norte vs CA Barrio Obrero</t>
+          <t>Tacikistan vs Filistin</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1.45</v>
+        <v>2.9</v>
       </c>
       <c r="D44" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="E44" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="F44" t="n">
-        <v>2.01</v>
+        <v>2.11</v>
       </c>
       <c r="G44" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -1837,28 +1837,28 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Formento Los Hornos vs Napoli Argentino</t>
+          <t>Kırgızistan vs Maldives</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1.47</v>
+        <v>1.05</v>
       </c>
       <c r="D45" t="n">
-        <v>3.8</v>
+        <v>11</v>
       </c>
       <c r="E45" t="n">
-        <v>5.5</v>
+        <v>26</v>
       </c>
       <c r="F45" t="n">
-        <v>1.75</v>
+        <v>1.3</v>
       </c>
       <c r="G45" t="n">
-        <v>1.93</v>
+        <v>3.2</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -1869,28 +1869,28 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>General Paz Juniors vs CA Quilmes de Villa Allende</t>
+          <t>Pk Keski-Uusimaa (W) vs HJK Akatemia (K)</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1.41</v>
+        <v>1.97</v>
       </c>
       <c r="D46" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="E46" t="n">
-        <v>7</v>
+        <v>2.8</v>
       </c>
       <c r="F46" t="n">
-        <v>2.18</v>
+        <v>1.33</v>
       </c>
       <c r="G46" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -1901,28 +1901,28 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>5 dk içinde</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Bahreyn vs Birleşik Arap Emirlikleri</t>
+          <t>Stride Sports vs Hindustan Aeronautics</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="D47" t="n">
         <v>3.4</v>
       </c>
       <c r="E47" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="F47" t="n">
         <v>1.62</v>
       </c>
-      <c r="F47" t="n">
-        <v>2.2</v>
-      </c>
       <c r="G47" t="n">
-        <v>1.6</v>
+        <v>2.12</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -1933,28 +1933,28 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>20 dk içinde</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GV Club Deportivo San Jose de Oruro vs Independiente Petrolero</t>
+          <t>Eastern District U22 vs Kowloon City U22</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2.02</v>
+        <v>1.71</v>
       </c>
       <c r="D48" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="E48" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="F48" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="G48" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -1965,28 +1965,28 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Universitario de Sucre vs Universitario De Tarija</t>
+          <t>Saipa vs Niroye Zamini</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="D49" t="n">
-        <v>7.5</v>
+        <v>3.05</v>
       </c>
       <c r="E49" t="n">
-        <v>15</v>
+        <v>4.75</v>
       </c>
       <c r="F49" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="G49" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -1997,28 +1997,28 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Virginia Usc vs Tiquipaya</t>
+          <t>Ario Eslamshahr vs Havadar SC</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1.47</v>
+        <v>1.79</v>
       </c>
       <c r="D50" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="E50" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="F50" t="n">
-        <v>1.45</v>
+        <v>2.7</v>
       </c>
       <c r="G50" t="n">
-        <v>2.45</v>
+        <v>1.4</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2029,28 +2029,28 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CE Minera Huanuni vs Deportivo FATIC</t>
+          <t>Palayesh Naft Bandar Abbas FC vs Naft Gachsaran</t>
         </is>
       </c>
       <c r="C51" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D51" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E51" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="F51" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G51" t="n">
         <v>1.4</v>
-      </c>
-      <c r="D51" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="E51" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F51" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="G51" t="n">
-        <v>1.62</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2061,28 +2061,28 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Primero de Mayo FC vs Ciudad Nueva Santa Cruz</t>
+          <t>Pars Jonoubi Jam vs Naft Masjed Soleyman</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1.47</v>
+        <v>2.45</v>
       </c>
       <c r="D52" t="n">
-        <v>4.33</v>
+        <v>3.28</v>
       </c>
       <c r="E52" t="n">
-        <v>4.75</v>
+        <v>2.4</v>
       </c>
       <c r="F52" t="n">
-        <v>1.35</v>
+        <v>1.66</v>
       </c>
       <c r="G52" t="n">
-        <v>2.77</v>
+        <v>2.06</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2093,28 +2093,28 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Hiska Nacional vs Club 26 de Febrero Colquiri</t>
+          <t>Maccabi Kiryat Gat Sports Club vs KAFR Qasim</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1.47</v>
+        <v>2.3</v>
       </c>
       <c r="D53" t="n">
-        <v>4.25</v>
+        <v>3.2</v>
       </c>
       <c r="E53" t="n">
-        <v>4.75</v>
+        <v>2.73</v>
       </c>
       <c r="F53" t="n">
-        <v>1.41</v>
+        <v>2</v>
       </c>
       <c r="G53" t="n">
-        <v>2.63</v>
+        <v>1.7</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2125,25 +2125,25 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>10 de Noviembre Wilstermann Cooperativa vs CD Mineros Potosi</t>
+          <t>Hapoel Kfar-Saba vs Bnei-Yehuda Tel-Aviv</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1.58</v>
+        <v>5</v>
       </c>
       <c r="D54" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="E54" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="F54" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="G54" t="n">
         <v>2.37</v>
@@ -2157,28 +2157,28 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CS Esportiva U20 vs CS Alagoano U20</t>
+          <t>Hapoel Kfar Shelem vs Maccabi Yafo Kabilyo</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2.9</v>
+        <v>1.81</v>
       </c>
       <c r="D55" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E55" t="n">
         <v>3.4</v>
       </c>
-      <c r="E55" t="n">
-        <v>2.04</v>
-      </c>
       <c r="F55" t="n">
-        <v>1.66</v>
+        <v>1.51</v>
       </c>
       <c r="G55" t="n">
-        <v>2.06</v>
+        <v>2.34</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -2189,28 +2189,28 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Inter Alagoano U20 vs Clube de Regatas Brasil U20</t>
+          <t>Maccabi Bnei Raina vs Hapoel Raanana</t>
         </is>
       </c>
       <c r="C56" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="D56" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E56" t="n">
         <v>2.9</v>
       </c>
-      <c r="D56" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="E56" t="n">
-        <v>1.98</v>
-      </c>
       <c r="F56" t="n">
-        <v>1.47</v>
+        <v>1.66</v>
       </c>
       <c r="G56" t="n">
-        <v>2.4</v>
+        <v>2.09</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2221,28 +2221,28 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CRB Clube de Regatas Brasil vs Cuiaba MT</t>
+          <t>Al Kharitiyath vs Al-Wakra</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1.97</v>
+        <v>2.63</v>
       </c>
       <c r="D57" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="E57" t="n">
-        <v>3.5</v>
+        <v>2.23</v>
       </c>
       <c r="F57" t="n">
-        <v>2.16</v>
+        <v>1.7</v>
       </c>
       <c r="G57" t="n">
-        <v>1.62</v>
+        <v>2.01</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2253,28 +2253,28 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Taguatinga vs Planaltina EC DF</t>
+          <t>Al Sailiya vs Al-Rayyan</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1.72</v>
+        <v>3.8</v>
       </c>
       <c r="D58" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="E58" t="n">
-        <v>4.25</v>
+        <v>1.68</v>
       </c>
       <c r="F58" t="n">
-        <v>2.16</v>
+        <v>1.6</v>
       </c>
       <c r="G58" t="n">
-        <v>1.58</v>
+        <v>2.15</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2285,28 +2285,28 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Sampaio Correa FE RJ U20 vs Boavista Saquarema RJ U20</t>
+          <t>Al Shahaniya vs Al Duhail</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2.01</v>
+        <v>2.8</v>
       </c>
       <c r="D59" t="n">
         <v>3.4</v>
       </c>
       <c r="E59" t="n">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="F59" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="G59" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -2317,28 +2317,28 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Serra Macaense vs Rio de Janeiro</t>
+          <t>Zetech Sparks FC (W) vs Kenya Police Bullets (W)</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1.47</v>
+        <v>4.33</v>
       </c>
       <c r="D60" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="E60" t="n">
-        <v>5</v>
+        <v>1.62</v>
       </c>
       <c r="F60" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="G60" t="n">
-        <v>2.14</v>
+        <v>1.9</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2349,28 +2349,28 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SE Paraty RJ vs Paduano EC</t>
+          <t>Independiente Yumbo vs Orsomarso</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>5</v>
+        <v>1.91</v>
       </c>
       <c r="D61" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="E61" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="F61" t="n">
-        <v>1.6</v>
+        <v>2.27</v>
       </c>
       <c r="G61" t="n">
-        <v>2.14</v>
+        <v>1.53</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -2381,28 +2381,28 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Santa Cruz RJ vs Cardoso Moreira FC</t>
+          <t>Envigado U19 vs Atletico Nacional Medellin U19</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="D62" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="E62" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="F62" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="G62" t="n">
-        <v>1.87</v>
+        <v>2.14</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -2413,28 +2413,28 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Campos Atletico Associacao vs 7 De Abril RJ</t>
+          <t>Guadeloupe vs Barbados</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="D63" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="E63" t="n">
-        <v>2.45</v>
+        <v>3.05</v>
       </c>
       <c r="F63" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="G63" t="n">
-        <v>2.12</v>
+        <v>1.76</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -2445,28 +2445,28 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Fc Acopiara Ce vs Vila Real FC CE</t>
+          <t>FK Haugesund II vs Hinna Fotball</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2.23</v>
+        <v>1.18</v>
       </c>
       <c r="D64" t="n">
-        <v>3.15</v>
+        <v>6.5</v>
       </c>
       <c r="E64" t="n">
-        <v>2.8</v>
+        <v>8</v>
       </c>
       <c r="F64" t="n">
-        <v>2.04</v>
+        <v>1.12</v>
       </c>
       <c r="G64" t="n">
-        <v>1.68</v>
+        <v>5</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -2477,28 +2477,28 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Azuriz FC PR vs Londrina EC PR</t>
+          <t>Sportivo San Lorenzo vs Deportivo Recoleta</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="D65" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="E65" t="n">
-        <v>2.73</v>
+        <v>2.27</v>
       </c>
       <c r="F65" t="n">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="G65" t="n">
-        <v>1.45</v>
+        <v>1.81</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -2509,28 +2509,28 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Parana Clube PR vs AC Paranavai PR</t>
+          <t>Club Atletico Tembetary vs Paraguari AC</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1.74</v>
+        <v>2.63</v>
       </c>
       <c r="D66" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="E66" t="n">
-        <v>4.25</v>
+        <v>2.5</v>
       </c>
       <c r="F66" t="n">
-        <v>2.23</v>
+        <v>1.97</v>
       </c>
       <c r="G66" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -2541,28 +2541,28 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Metropolitano SC vs Figueirense FC</t>
+          <t>Sportivo Luqueno Reserves vs Club Guarani Asuncion Reserves</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2.8</v>
+        <v>4.75</v>
       </c>
       <c r="D67" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="E67" t="n">
-        <v>2.15</v>
+        <v>1.51</v>
       </c>
       <c r="F67" t="n">
-        <v>1.79</v>
+        <v>1.58</v>
       </c>
       <c r="G67" t="n">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -2573,28 +2573,28 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Sport Clube Gaucho vs Santa Cruz RS</t>
+          <t>Deportivo Pinoza vs Club Oriental</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="D68" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="E68" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="F68" t="n">
-        <v>2.68</v>
+        <v>1.91</v>
       </c>
       <c r="G68" t="n">
-        <v>1.4</v>
+        <v>1.76</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -2610,23 +2610,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Aimore vs Esportivo Bento Rs</t>
+          <t>Atletico Juventud Loma Pyta vs Club Pilcomayo FBC</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1.81</v>
+        <v>3.1</v>
       </c>
       <c r="D69" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="E69" t="n">
-        <v>4</v>
+        <v>1.91</v>
       </c>
       <c r="F69" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="G69" t="n">
-        <v>1.47</v>
+        <v>2.07</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -2637,28 +2637,28 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>APAFUT Caxias Do Sul RS vs Lajeadense Rs</t>
+          <t>Olimpia Asuncion (K) vs Nacional-Humaita (K)</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="D70" t="n">
-        <v>3.6</v>
+        <v>11</v>
       </c>
       <c r="E70" t="n">
-        <v>6.5</v>
+        <v>34</v>
       </c>
       <c r="F70" t="n">
-        <v>2.18</v>
+        <v>1.6</v>
       </c>
       <c r="G70" t="n">
-        <v>1.58</v>
+        <v>2.07</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -2669,28 +2669,28 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Veranopolis Rs vs Passo Fundo</t>
+          <t>Sportivo San Lorenzo (K) vs Club Guarani (K)</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="D71" t="n">
-        <v>2.77</v>
+        <v>5</v>
       </c>
       <c r="E71" t="n">
-        <v>2.9</v>
+        <v>1.33</v>
       </c>
       <c r="F71" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="G71" t="n">
-        <v>1.35</v>
+        <v>2.07</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -2706,23 +2706,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ec Guarani Rs vs Uniao Frederiquense</t>
+          <t>Cesar Vallejo Reserves vs Juventus Huamachuco FC</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2.8</v>
+        <v>1.53</v>
       </c>
       <c r="D72" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="E72" t="n">
-        <v>2.35</v>
+        <v>4.75</v>
       </c>
       <c r="F72" t="n">
-        <v>2.45</v>
+        <v>1.74</v>
       </c>
       <c r="G72" t="n">
-        <v>1.45</v>
+        <v>1.94</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -2733,28 +2733,28 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ge Gloria vs Gramadense RS</t>
+          <t>Graficar Beograd vs Teleoptik Zemun</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2.37</v>
+        <v>1.76</v>
       </c>
       <c r="D73" t="n">
-        <v>2.77</v>
+        <v>3.4</v>
       </c>
       <c r="E73" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="F73" t="n">
-        <v>2.8</v>
+        <v>1.72</v>
       </c>
       <c r="G73" t="n">
-        <v>1.37</v>
+        <v>1.96</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -2765,28 +2765,28 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Gremio Esportivo Bage vs Gremio Esportivo Brasil RS</t>
+          <t>Bor 1919 vs Metalac GM</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3.4</v>
+        <v>2.31</v>
       </c>
       <c r="D74" t="n">
-        <v>2.77</v>
+        <v>3.2</v>
       </c>
       <c r="E74" t="n">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="F74" t="n">
-        <v>3</v>
+        <v>1.98</v>
       </c>
       <c r="G74" t="n">
-        <v>1.33</v>
+        <v>1.72</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -2797,28 +2797,28 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EC Pelotas vs Brasil Farroupilha</t>
+          <t>Dubocica vs Javor Ivanjica</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1.98</v>
+        <v>3.8</v>
       </c>
       <c r="D75" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="E75" t="n">
-        <v>3.6</v>
+        <v>1.74</v>
       </c>
       <c r="F75" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="G75" t="n">
-        <v>1.41</v>
+        <v>2.02</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -2829,28 +2829,28 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Flamengo Sao Pedro RS (W) vs Juventude (K)</t>
+          <t>Proleter 023 Zrenjanin vs Jedinstvo Ub</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>15</v>
+        <v>1.87</v>
       </c>
       <c r="D76" t="n">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="E76" t="n">
-        <v>1.11</v>
+        <v>3.6</v>
       </c>
       <c r="F76" t="n">
-        <v>2.6</v>
+        <v>2.07</v>
       </c>
       <c r="G76" t="n">
-        <v>1.41</v>
+        <v>1.64</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -2861,28 +2861,28 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Fc Trindade vs Gremio Anapolis Gg</t>
+          <t>Loznica vs Spartak Subotica</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1.93</v>
+        <v>2.55</v>
       </c>
       <c r="D77" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="F77" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="G77" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -2893,28 +2893,28 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Goianesia vs Mineiros GO</t>
+          <t>NK Rudar Velenje vs Dravinja</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="D78" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="E78" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="F78" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="G78" t="n">
-        <v>1.72</v>
+        <v>2.16</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -2925,28 +2925,28 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Morrinhos vs Sao Luis AC</t>
+          <t>CA River Plate Montevideo Reserves vs Montevideo City Torque Reserve</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2.06</v>
+        <v>3.2</v>
       </c>
       <c r="D79" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="E79" t="n">
-        <v>3.28</v>
+        <v>1.87</v>
       </c>
       <c r="F79" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G79" t="n">
         <v>2.18</v>
-      </c>
-      <c r="G79" t="n">
-        <v>1.6</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -2957,28 +2957,28 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Venus vs Pinheirense EC</t>
+          <t>Racing Club de Montevideo Reserves vs Colon Montevideo Reserves</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2.11</v>
+        <v>1.84</v>
       </c>
       <c r="D80" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="E80" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="F80" t="n">
-        <v>2.04</v>
+        <v>1.64</v>
       </c>
       <c r="G80" t="n">
-        <v>1.68</v>
+        <v>2.08</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -2989,28 +2989,28 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Sao Paulo Crystal vs Auto Esporte</t>
+          <t>Club Oriental Reserves vs Cerro Largo FC Reserves</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>3.6</v>
+        <v>2.45</v>
       </c>
       <c r="D81" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="E81" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G81" t="n">
         <v>2.02</v>
-      </c>
-      <c r="F81" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="G81" t="n">
-        <v>1.8</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -3026,23 +3026,23 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Aracaju SE U20 vs Falcon SE U20</t>
+          <t>Nacional de Montevideo Reserves vs Central Espanol Reserves</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>6</v>
+        <v>1.51</v>
       </c>
       <c r="D82" t="n">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="E82" t="n">
-        <v>1.38</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="G82" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -3058,23 +3058,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Red Bull Bragantino SP U20 vs CA Bandeirante SP U20</t>
+          <t>Juventud De Las Piedras Reserves vs La Luz Reserves</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1.03</v>
+        <v>2</v>
       </c>
       <c r="D83" t="n">
-        <v>10</v>
+        <v>3.3</v>
       </c>
       <c r="E83" t="n">
-        <v>23</v>
+        <v>3.05</v>
       </c>
       <c r="F83" t="n">
-        <v>1.18</v>
+        <v>1.58</v>
       </c>
       <c r="G83" t="n">
-        <v>3.8</v>
+        <v>2.18</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -3090,23 +3090,23 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Societe Omnisport De L'armée vs Stella Club d Adjame</t>
+          <t>Deportivo Maldonado Reserves vs Ca Penarol Reserves</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="D84" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.77</v>
+        <v>2.09</v>
       </c>
       <c r="F84" t="n">
-        <v>2.55</v>
+        <v>1.72</v>
       </c>
       <c r="G84" t="n">
-        <v>1.41</v>
+        <v>1.96</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -3117,28 +3117,28 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Universidad O&amp;M FC vs Salcedo FC</t>
+          <t>FC Marko vs Panthrakikos</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3.2</v>
+        <v>1.55</v>
       </c>
       <c r="D85" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="E85" t="n">
-        <v>1.99</v>
+        <v>5.5</v>
       </c>
       <c r="F85" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="G85" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -3149,28 +3149,28 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>28 dk içinde</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ürdün vs Suriye</t>
+          <t>Kallithea vs Asteras Tripolis B</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="D86" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="E86" t="n">
-        <v>6</v>
+        <v>4.25</v>
       </c>
       <c r="F86" t="n">
-        <v>2.01</v>
+        <v>2.27</v>
       </c>
       <c r="G86" t="n">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -3181,1502 +3181,30 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Bolivya vs Paraguay</t>
+          <t>Kipanga FC vs Black Sailor</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>6</v>
+        <v>1.81</v>
       </c>
       <c r="D87" t="n">
-        <v>4.15</v>
+        <v>3.05</v>
       </c>
       <c r="E87" t="n">
-        <v>1.47</v>
+        <v>4</v>
       </c>
       <c r="F87" t="n">
-        <v>1.81</v>
+        <v>2.12</v>
       </c>
       <c r="G87" t="n">
-        <v>1.87</v>
+        <v>1.58</v>
       </c>
       <c r="H87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>CD Santo Domingo vs Gualaceo SC</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="D88" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="E88" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="F88" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="G88" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>28 dk içinde</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>CD Platense Zacatecoluca (W) vs Fuerte San Francisco (W)</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>5</v>
-      </c>
-      <c r="D89" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E89" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F89" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="G89" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>CD Platense Zacatecoluca Reserves vs Fuerte San Francisco Reserves</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="D90" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E90" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="F90" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="G90" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Maghreb de Fes vs Renaissance Zemamra</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="D91" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="E91" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="F91" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="G91" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Kawkab AC Marrakech vs HUSA Agadir</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="D92" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E92" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F92" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="G92" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Coban Imperial vs Aurora FC</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="D93" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="E93" t="n">
-        <v>5</v>
-      </c>
-      <c r="F93" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="G93" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>27 dk içinde</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Mictlán vs CS Deportivo Sacachispas</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="D94" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="E94" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="F94" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="G94" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>27 dk içinde</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Santa Lucia Cotzumalguapa FC vs Huehuetecos FC</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="D95" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="E95" t="n">
-        <v>5</v>
-      </c>
-      <c r="F95" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="G95" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>27 dk içinde</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Deportivo Colomba vs FC Ocos</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="D96" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="E96" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="F96" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="G96" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>57 dk içinde</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Beitar Ramat Gan vs Beitar Kfar Saba Shlomi</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="D97" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E97" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="F97" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="G97" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Portmore United vs Humble Lions</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="D98" t="n">
-        <v>5</v>
-      </c>
-      <c r="E98" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="F98" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="G98" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Molynes United FC vs Tru-Juice</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="D99" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="E99" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="F99" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="G99" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Tivoli Gardens vs Chapelton Maroons FC</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="D100" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="E100" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F100" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="G100" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Cavaliers FC vs Arnett Gardens FC</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="D101" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="E101" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="F101" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="G101" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Dunbeholden FC vs Mount Pleasant FC</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="D102" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="E102" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="F102" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="G102" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Inter Toronto vs Pacific FC</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="D103" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="E103" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F103" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="G103" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Envigado vs Atletico Cali F.C.</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="D104" t="n">
-        <v>4</v>
-      </c>
-      <c r="E104" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F104" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="G104" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Guadalupe FC vs Pitbulls Santa Barbara</t>
-        </is>
-      </c>
-      <c r="C105" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="D105" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E105" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="F105" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="G105" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Quepos Cambute vs AD Municipal Grecia</t>
-        </is>
-      </c>
-      <c r="C106" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="D106" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="E106" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="F106" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="G106" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>AD Sarchi vs ADR Jicaral</t>
-        </is>
-      </c>
-      <c r="C107" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="D107" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="E107" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="F107" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="G107" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>26 dk içinde</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Moravia (K) vs Upala Carrillo (W)</t>
-        </is>
-      </c>
-      <c r="C108" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="D108" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="E108" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="F108" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="G108" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Guyana vs Cayman Islands</t>
-        </is>
-      </c>
-      <c r="C109" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="D109" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="E109" t="n">
-        <v>26</v>
-      </c>
-      <c r="F109" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="G109" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Pumas UNAM vs Atletico de San Luis</t>
-        </is>
-      </c>
-      <c r="C110" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="D110" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="E110" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="F110" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="G110" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Puebla (K) vs Monterrey (K)</t>
-        </is>
-      </c>
-      <c r="C111" t="n">
-        <v>41</v>
-      </c>
-      <c r="D111" t="n">
-        <v>15</v>
-      </c>
-      <c r="E111" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="F111" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="G111" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Guerreros del Pacifico II vs Irapuato Olimpo FC</t>
-        </is>
-      </c>
-      <c r="C112" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="D112" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="E112" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="F112" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="G112" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>25 dk içinde</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>H20 Purepechas FC vs Los Cabos United</t>
-        </is>
-      </c>
-      <c r="C113" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="D113" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="E113" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="F113" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="G113" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Montaneses FC vs Inter Playa del Carmen</t>
-        </is>
-      </c>
-      <c r="C114" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="D114" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="E114" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="F114" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="G114" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>55 dk içinde</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Leon U19 vs Juarez FC U19</t>
-        </is>
-      </c>
-      <c r="C115" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="D115" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="E115" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="F115" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="G115" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>55 dk içinde</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Unam Pumas U19 vs Atletico San Luis U19</t>
-        </is>
-      </c>
-      <c r="C116" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="D116" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="E116" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="F116" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="G116" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>56 dk içinde</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Necaxa U19 vs Club America U19</t>
-        </is>
-      </c>
-      <c r="C117" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="D117" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="E117" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="F117" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="G117" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Sport Boys vs Alianza Atletico</t>
-        </is>
-      </c>
-      <c r="C118" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="D118" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="E118" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="F118" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="G118" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>23:15</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Asociacion Deportiva Tarma vs Sporting Cristal Lima</t>
-        </is>
-      </c>
-      <c r="C119" t="n">
-        <v>3</v>
-      </c>
-      <c r="D119" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="E119" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="F119" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="G119" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Alianza Universidad vs Bentin Tacna Heroica</t>
-        </is>
-      </c>
-      <c r="C120" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="D120" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="E120" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="F120" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="G120" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>23:15</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Union Comercio vs Molinos El Pirata</t>
-        </is>
-      </c>
-      <c r="C121" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="D121" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="E121" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F121" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="G121" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Deportes Concepcion vs Curico Unido</t>
-        </is>
-      </c>
-      <c r="C122" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="D122" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="E122" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F122" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="G122" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Universidad de Chile vs Everton Vina del Mar</t>
-        </is>
-      </c>
-      <c r="C123" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="D123" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="E123" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="F123" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="G123" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>24 dk içinde</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Huachipato (W) vs Universidad de Chile (W)</t>
-        </is>
-      </c>
-      <c r="C124" t="n">
-        <v>9</v>
-      </c>
-      <c r="D124" t="n">
-        <v>5</v>
-      </c>
-      <c r="E124" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="F124" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G124" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Deportes Colina vs Real Juventud San Joaquin</t>
-        </is>
-      </c>
-      <c r="C125" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="D125" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E125" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="F125" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="G125" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Club Aguara vs Comunal Cabrero</t>
-        </is>
-      </c>
-      <c r="C126" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="D126" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E126" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="F126" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="G126" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>CD Imperial Unido vs Chimbarongo FC</t>
-        </is>
-      </c>
-      <c r="C127" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="D127" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E127" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="F127" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="G127" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Juventud Piedras vs Club Atletico Cerro</t>
-        </is>
-      </c>
-      <c r="C128" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="D128" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="E128" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="F128" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="G128" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Mar de Fondo vs Sud America</t>
-        </is>
-      </c>
-      <c r="C129" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="D129" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="E129" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="F129" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="G129" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Cerrito CS vs La Luz</t>
-        </is>
-      </c>
-      <c r="C130" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="D130" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="E130" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="F130" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="G130" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Aragua FC vs Atletico Avila FC</t>
-        </is>
-      </c>
-      <c r="C131" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="D131" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="E131" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F131" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="G131" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Monagas II vs Mineros Guayana</t>
-        </is>
-      </c>
-      <c r="C132" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="D132" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="E132" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="F132" t="n">
-        <v>2</v>
-      </c>
-      <c r="G132" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Dynamo Puerto Fc vs Bolivar SC</t>
-        </is>
-      </c>
-      <c r="C133" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="D133" t="n">
-        <v>3</v>
-      </c>
-      <c r="E133" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="F133" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="G133" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="H133" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/bugun_oranlar.xlsx
+++ b/bugun_oranlar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H87"/>
+  <dimension ref="A1:H159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,23 +466,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Belçika vs Fransa</t>
+          <t>Çekya vs İngiltere</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3.8</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>1.85</v>
+        <v>1.35</v>
       </c>
       <c r="F2" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="G2" t="n">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -498,23 +498,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Türkiye vs İtalya</t>
+          <t>İspanya vs Hırvatistan</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2.63</v>
+        <v>1.2</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5</v>
+        <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>1.75</v>
+        <v>1.41</v>
       </c>
       <c r="G3" t="n">
-        <v>2.05</v>
+        <v>2.68</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -530,23 +530,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Romanya vs Bosna-Hersek</t>
+          <t>İskoçya vs İsviçre</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.27</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1</v>
+        <v>1.87</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="G4" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -562,23 +562,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>İsveç vs Polonya</t>
+          <t>Slovenya vs Kuzey Makedonya</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2.06</v>
+        <v>1.64</v>
       </c>
       <c r="D5" t="n">
         <v>3.6</v>
       </c>
       <c r="E5" t="n">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="F5" t="n">
-        <v>1.71</v>
+        <v>2.31</v>
       </c>
       <c r="G5" t="n">
-        <v>2.08</v>
+        <v>1.55</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -594,23 +594,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Gürcistan vs Ukrayna</t>
+          <t>Finlandiya vs Belarus</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2.7</v>
+        <v>1.55</v>
       </c>
       <c r="D6" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7</v>
+        <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="G6" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -626,23 +626,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kuzey İrlanda vs Macaristan</t>
+          <t>San Marino vs Arnavutluk</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2.8</v>
+        <v>31</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>2.63</v>
+        <v>1.07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.16</v>
+        <v>1.4</v>
       </c>
       <c r="G7" t="n">
-        <v>1.47</v>
+        <v>2.73</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -658,23 +658,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Letonya vs Kıbrıs</t>
+          <t>Moldova vs Faroe Adaları</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="D8" t="n">
         <v>3.05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="G8" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -685,28 +685,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ermenistan vs Karadağ</t>
+          <t>Slovakya vs Kazakistan</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2.8</v>
+        <v>1.27</v>
       </c>
       <c r="D9" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="F9" t="n">
-        <v>2.23</v>
+        <v>1.68</v>
       </c>
       <c r="G9" t="n">
-        <v>1.6</v>
+        <v>2.08</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -717,28 +717,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Danimarka U21 vs Belarus U21</t>
+          <t>Bulgaristan vs Estonya</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.2</v>
+        <v>1.81</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="E10" t="n">
-        <v>11</v>
+        <v>4.5</v>
       </c>
       <c r="F10" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="G10" t="n">
-        <v>2.31</v>
+        <v>1.58</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -754,23 +754,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Punjab United vs AFC Croydon Athletic</t>
+          <t>Lüksemburg vs İzlanda</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5.5</v>
+        <v>3.3</v>
       </c>
       <c r="D11" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="E11" t="n">
-        <v>1.41</v>
+        <v>2.16</v>
       </c>
       <c r="F11" t="n">
-        <v>1.43</v>
+        <v>2.12</v>
       </c>
       <c r="G11" t="n">
-        <v>2.6</v>
+        <v>1.66</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -781,28 +781,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>St Ives Town vs Nuneaton Town</t>
+          <t>Slovenya U21 vs İsrail U21</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3.5</v>
+        <v>2.12</v>
       </c>
       <c r="D12" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="E12" t="n">
-        <v>1.74</v>
+        <v>3.3</v>
       </c>
       <c r="F12" t="n">
-        <v>1.47</v>
+        <v>2.23</v>
       </c>
       <c r="G12" t="n">
-        <v>2.45</v>
+        <v>1.58</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -813,28 +813,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Coleshill Town vs Belper Town</t>
+          <t>İzlanda U21 vs İsviçre U21</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.26</v>
+        <v>3.1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="F13" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="G13" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -845,28 +845,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Swansea City U21 vs Queens Park Rangers U21</t>
+          <t>Estonia U21 vs France U21</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.81</v>
+        <v>26</v>
       </c>
       <c r="D14" t="n">
-        <v>4.2</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>3.15</v>
+        <v>1.03</v>
       </c>
       <c r="F14" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="G14" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -877,28 +877,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Biggleswade vs Hertford Town</t>
+          <t>Norveç U21 vs Bosnia and Herzegovina U21</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1.79</v>
+        <v>1.25</v>
       </c>
       <c r="D15" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3</v>
+        <v>9.5</v>
       </c>
       <c r="F15" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="G15" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -909,28 +909,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Leganes vs Castellon</t>
+          <t>Ireland U21 vs Kazakistan U21</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3.05</v>
+        <v>1.22</v>
       </c>
       <c r="D16" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="E16" t="n">
-        <v>2.22</v>
+        <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>1.87</v>
+        <v>1.51</v>
       </c>
       <c r="G16" t="n">
-        <v>1.83</v>
+        <v>2.31</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -941,28 +941,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Leixoes U23 vs Vizela U23</t>
+          <t>Belçika U21 vs Galler U21</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2.33</v>
+        <v>1.2</v>
       </c>
       <c r="D17" t="n">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="E17" t="n">
-        <v>2.63</v>
+        <v>11</v>
       </c>
       <c r="F17" t="n">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="G17" t="n">
-        <v>2.07</v>
+        <v>2.45</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -973,28 +973,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>29 dk içinde</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ekvator Ginesi vs Sierra Leone</t>
+          <t>Derby County Reserves vs Rotherham United Reserves</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="D18" t="n">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="E18" t="n">
-        <v>3.8</v>
+        <v>2.77</v>
       </c>
       <c r="F18" t="n">
-        <v>2.39</v>
+        <v>1.33</v>
       </c>
       <c r="G18" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1005,28 +1005,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>29 dk içinde</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Zimbabve vs Demokratik Kongo Cumhuryeti</t>
+          <t>Preston Reserves vs Wrexham Reserves</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>2.16</v>
       </c>
       <c r="D19" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="E19" t="n">
-        <v>1.72</v>
+        <v>2.5</v>
       </c>
       <c r="F19" t="n">
-        <v>2.4</v>
+        <v>1.33</v>
       </c>
       <c r="G19" t="n">
-        <v>1.5</v>
+        <v>3.05</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1037,28 +1037,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tunus vs Botsvana</t>
+          <t>Fakenham Town vs Felixstowe &amp; Walton United FC</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="E20" t="n">
-        <v>12</v>
+        <v>1.98</v>
       </c>
       <c r="F20" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="G20" t="n">
-        <v>1.85</v>
+        <v>2.26</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1069,28 +1069,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Orta Afrika Cumhuriyeti vs Burkina Faso</t>
+          <t>Brightlingsea Regent vs AFC Sudbury</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>8.5</v>
+        <v>2.73</v>
       </c>
       <c r="D21" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="E21" t="n">
-        <v>1.35</v>
+        <v>2.18</v>
       </c>
       <c r="F21" t="n">
-        <v>2.05</v>
+        <v>1.68</v>
       </c>
       <c r="G21" t="n">
-        <v>1.68</v>
+        <v>2.01</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1101,28 +1101,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kenya U23 vs Tanzania U23</t>
+          <t>Canvey Island vs Newmarket Town</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="D22" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="E22" t="n">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="F22" t="n">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="G22" t="n">
-        <v>1.75</v>
+        <v>2.01</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1133,28 +1133,28 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mauritania U23 vs DR Congo U23</t>
+          <t>Windsor &amp; Eton vs AFC Stoneham</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3.8</v>
+        <v>1.87</v>
       </c>
       <c r="D23" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="E23" t="n">
-        <v>1.91</v>
+        <v>3.2</v>
       </c>
       <c r="F23" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="G23" t="n">
-        <v>1.41</v>
+        <v>2.39</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1165,28 +1165,28 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Leones de Rosario vs Club Lujan</t>
+          <t>Hendon vs Ashford Town (Middx) Lfc</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2.8</v>
+        <v>1.68</v>
       </c>
       <c r="D24" t="n">
-        <v>2.63</v>
+        <v>3.8</v>
       </c>
       <c r="E24" t="n">
-        <v>2.58</v>
+        <v>3.8</v>
       </c>
       <c r="F24" t="n">
-        <v>2.59</v>
+        <v>1.47</v>
       </c>
       <c r="G24" t="n">
-        <v>1.41</v>
+        <v>2.45</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1197,28 +1197,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Centro Espanyol vs Defensores de Cambaceres</t>
+          <t>Dulwich Hamlet vs Aveley</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="D25" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="E25" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="F25" t="n">
-        <v>2.4</v>
+        <v>1.51</v>
       </c>
       <c r="G25" t="n">
-        <v>1.47</v>
+        <v>2.37</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1229,28 +1229,28 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JJ Urquiza vs Club Leandro Niceforo Alem</t>
+          <t>Maldon &amp; Tiptree vs Cray Wanderers</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2.14</v>
+        <v>2.8</v>
       </c>
       <c r="D26" t="n">
-        <v>2.54</v>
+        <v>3.6</v>
       </c>
       <c r="E26" t="n">
-        <v>3.8</v>
+        <v>2.06</v>
       </c>
       <c r="F26" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="G26" t="n">
-        <v>1.22</v>
+        <v>2.37</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1261,28 +1261,28 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Flandria vs CS Dock Sud</t>
+          <t>Dartford vs Whitehawk</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2.14</v>
+        <v>1.41</v>
       </c>
       <c r="D27" t="n">
-        <v>2.8</v>
+        <v>4.33</v>
       </c>
       <c r="E27" t="n">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="F27" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G27" t="n">
         <v>2.4</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1.47</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1293,28 +1293,28 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Villa San Carlos Reserves vs Deportivo Laferrere Reserves</t>
+          <t>Wimborne Town vs Yate Town</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="D28" t="n">
         <v>3.2</v>
       </c>
       <c r="E28" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="F28" t="n">
-        <v>2.07</v>
+        <v>1.87</v>
       </c>
       <c r="G28" t="n">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1325,28 +1325,28 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CS Dock Sud Reserves vs Defensores Unidos Reserves</t>
+          <t>Hanworth Villa vs Chichester City</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.33</v>
+        <v>1.87</v>
       </c>
       <c r="D29" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="E29" t="n">
-        <v>7</v>
+        <v>3.2</v>
       </c>
       <c r="F29" t="n">
-        <v>1.72</v>
+        <v>1.51</v>
       </c>
       <c r="G29" t="n">
-        <v>1.94</v>
+        <v>2.34</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1357,28 +1357,28 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Social Atletico Television (K) vs Gimnasia Y Esgrima La Plata (K)</t>
+          <t>Evesham United vs Chippenham Town</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1.8</v>
+        <v>2.34</v>
       </c>
       <c r="D30" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="E30" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="F30" t="n">
-        <v>2.39</v>
+        <v>1.68</v>
       </c>
       <c r="G30" t="n">
-        <v>1.5</v>
+        <v>2.03</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1389,28 +1389,28 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Malezya vs Endonezya</t>
+          <t>Sholing vs Berkhamsted</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>2.23</v>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="E31" t="n">
-        <v>1.47</v>
+        <v>2.8</v>
       </c>
       <c r="F31" t="n">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="G31" t="n">
-        <v>2.12</v>
+        <v>1.86</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1421,28 +1421,28 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Al Ittifaq Dubai vs Al Urooba</t>
+          <t>Bath City vs Malvern Town</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3.8</v>
+        <v>1.45</v>
       </c>
       <c r="D32" t="n">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="E32" t="n">
-        <v>1.68</v>
+        <v>5</v>
       </c>
       <c r="F32" t="n">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="G32" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1453,28 +1453,28 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Al Arabi Umm Al Quwain vs Al Dhaid</t>
+          <t>Chertsey Town vs Poole Town</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="D33" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="E33" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="F33" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="G33" t="n">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1485,28 +1485,28 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Barra Mansa FC vs Se Buzios Rj</t>
+          <t>Gloucester City vs Plymouth Parkway</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1.6</v>
+        <v>2.12</v>
       </c>
       <c r="D34" t="n">
         <v>3.5</v>
       </c>
       <c r="E34" t="n">
-        <v>4.75</v>
+        <v>2.73</v>
       </c>
       <c r="F34" t="n">
-        <v>1.79</v>
+        <v>1.53</v>
       </c>
       <c r="G34" t="n">
-        <v>1.87</v>
+        <v>2.27</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1517,28 +1517,28 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Planalto EC GO (W) vs Anapolina Saf GO (W)</t>
+          <t>Havant &amp; Waterloville vs Hanwell Town</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="D35" t="n">
         <v>3.4</v>
       </c>
       <c r="E35" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="F35" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="G35" t="n">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1549,28 +1549,28 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Belenense FC vs Gaviao Kyikateje</t>
+          <t>Uxbridge vs Basingstoke Town Lfc</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="D36" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="E36" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="F36" t="n">
-        <v>1.93</v>
+        <v>1.6</v>
       </c>
       <c r="G36" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1581,28 +1581,28 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NK Maribor vs Gorica</t>
+          <t>Boreham Wood vs Kidderminster</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1.96</v>
+        <v>1.38</v>
       </c>
       <c r="D37" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="E37" t="n">
-        <v>3.15</v>
+        <v>6</v>
       </c>
       <c r="F37" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="G37" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1613,28 +1613,28 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>OFK Petrovac vs Mladost DG</t>
+          <t>Yeovil vs Worthing</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="D38" t="n">
         <v>3.6</v>
       </c>
       <c r="E38" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="F38" t="n">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="G38" t="n">
-        <v>2.08</v>
+        <v>2.45</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1645,28 +1645,28 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Hırvatistan U19 vs Fransa U19</t>
+          <t>Barrow vs Scunthorpe</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3.8</v>
+        <v>2.02</v>
       </c>
       <c r="D39" t="n">
         <v>3.5</v>
       </c>
       <c r="E39" t="n">
-        <v>1.72</v>
+        <v>3</v>
       </c>
       <c r="F39" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="G39" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -1677,28 +1677,28 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Türkiye U19 vs İtalya U19</t>
+          <t>Gateshead vs Altrincham</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>6.5</v>
+        <v>4.25</v>
       </c>
       <c r="D40" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="E40" t="n">
-        <v>1.35</v>
+        <v>1.62</v>
       </c>
       <c r="F40" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="G40" t="n">
-        <v>1.97</v>
+        <v>2.22</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -1709,28 +1709,28 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Slovakya U19 vs Polonya U19</t>
+          <t>AFC Fylde vs Carlisle</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4.33</v>
+        <v>2.27</v>
       </c>
       <c r="D41" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="E41" t="n">
-        <v>1.64</v>
+        <v>2.58</v>
       </c>
       <c r="F41" t="n">
-        <v>1.86</v>
+        <v>1.43</v>
       </c>
       <c r="G41" t="n">
-        <v>1.81</v>
+        <v>2.58</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -1741,28 +1741,28 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>North Macedonia U21 vs Russia U21</t>
+          <t>Hartlepool vs Harrogate</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>6.5</v>
+        <v>3.4</v>
       </c>
       <c r="D42" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="E42" t="n">
-        <v>1.37</v>
+        <v>1.87</v>
       </c>
       <c r="F42" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="G42" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -1773,28 +1773,28 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>35 dk içinde</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Kore Cumhuriyeti vs Uruguay</t>
+          <t>Forest Green vs Wealdstone</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="D43" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="E43" t="n">
-        <v>2.63</v>
+        <v>3.8</v>
       </c>
       <c r="F43" t="n">
-        <v>2.18</v>
+        <v>1.45</v>
       </c>
       <c r="G43" t="n">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -1805,28 +1805,28 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tacikistan vs Filistin</t>
+          <t>Woking vs Solihull Moors</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2.9</v>
+        <v>1.87</v>
       </c>
       <c r="D44" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="E44" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="F44" t="n">
-        <v>2.11</v>
+        <v>1.58</v>
       </c>
       <c r="G44" t="n">
-        <v>1.64</v>
+        <v>2.22</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -1837,28 +1837,28 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Kırgızistan vs Maldives</t>
+          <t>AFC Hornchurch vs Aldershot</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1.05</v>
+        <v>2.09</v>
       </c>
       <c r="D45" t="n">
-        <v>11</v>
+        <v>3.5</v>
       </c>
       <c r="E45" t="n">
-        <v>26</v>
+        <v>2.9</v>
       </c>
       <c r="F45" t="n">
-        <v>1.3</v>
+        <v>1.66</v>
       </c>
       <c r="G45" t="n">
-        <v>3.2</v>
+        <v>2.07</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -1869,28 +1869,28 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Pk Keski-Uusimaa (W) vs HJK Akatemia (K)</t>
+          <t>Halifax vs Boston United</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="D46" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="E46" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="F46" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="G46" t="n">
-        <v>2.9</v>
+        <v>2.03</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -1901,28 +1901,28 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5 dk içinde</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Stride Sports vs Hindustan Aeronautics</t>
+          <t>Brackley vs South Shields</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="D47" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="E47" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="F47" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="G47" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -1933,28 +1933,28 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20 dk içinde</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Eastern District U22 vs Kowloon City U22</t>
+          <t>Slough Town vs Ebbsfleet United</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1.71</v>
+        <v>5</v>
       </c>
       <c r="D48" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.8</v>
+        <v>1.45</v>
       </c>
       <c r="F48" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="G48" t="n">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -1965,28 +1965,28 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Saipa vs Niroye Zamini</t>
+          <t>Ossett United vs Bridlington Town</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1.7</v>
+        <v>2.77</v>
       </c>
       <c r="D49" t="n">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="E49" t="n">
-        <v>4.75</v>
+        <v>2.12</v>
       </c>
       <c r="F49" t="n">
-        <v>2.6</v>
+        <v>1.45</v>
       </c>
       <c r="G49" t="n">
-        <v>1.4</v>
+        <v>2.45</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -1997,28 +1997,28 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ario Eslamshahr vs Havadar SC</t>
+          <t>Garforth Town vs Stocksbridge</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1.79</v>
+        <v>1.96</v>
       </c>
       <c r="D50" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="E50" t="n">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="F50" t="n">
-        <v>2.7</v>
+        <v>1.68</v>
       </c>
       <c r="G50" t="n">
-        <v>1.4</v>
+        <v>2.04</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2029,28 +2029,28 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Palayesh Naft Bandar Abbas FC vs Naft Gachsaran</t>
+          <t>Matlock Town vs Bradford Park Avenue</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="D51" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="E51" t="n">
-        <v>4.75</v>
+        <v>2.4</v>
       </c>
       <c r="F51" t="n">
-        <v>2.7</v>
+        <v>1.58</v>
       </c>
       <c r="G51" t="n">
-        <v>1.4</v>
+        <v>2.18</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2061,28 +2061,28 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Pars Jonoubi Jam vs Naft Masjed Soleyman</t>
+          <t>Dunston Uts vs Guisborough Town</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2.45</v>
+        <v>1.72</v>
       </c>
       <c r="D52" t="n">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="E52" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="F52" t="n">
         <v>1.66</v>
       </c>
       <c r="G52" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2093,28 +2093,28 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat Sports Club vs KAFR Qasim</t>
+          <t>West Auckland Town vs Ashington</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="D53" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="E53" t="n">
-        <v>2.73</v>
+        <v>3.3</v>
       </c>
       <c r="F53" t="n">
-        <v>2</v>
+        <v>1.58</v>
       </c>
       <c r="G53" t="n">
-        <v>1.7</v>
+        <v>2.18</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2125,28 +2125,28 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Hapoel Kfar-Saba vs Bnei-Yehuda Tel-Aviv</t>
+          <t>Beverley Town FC vs Lincoln United</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>5</v>
+        <v>2.09</v>
       </c>
       <c r="D54" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="E54" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="F54" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="G54" t="n">
-        <v>2.37</v>
+        <v>2.23</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -2157,28 +2157,28 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shelem vs Maccabi Yafo Kabilyo</t>
+          <t>Liversedge vs North Ferriby</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="D55" t="n">
         <v>3.6</v>
       </c>
       <c r="E55" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="F55" t="n">
-        <v>1.51</v>
+        <v>1.66</v>
       </c>
       <c r="G55" t="n">
-        <v>2.34</v>
+        <v>2.06</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -2189,28 +2189,28 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina vs Hapoel Raanana</t>
+          <t>Loughborough Students vs Basford United</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="D56" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="E56" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="F56" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="G56" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2221,28 +2221,28 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Al Kharitiyath vs Al-Wakra</t>
+          <t>Shepshed Dynamo vs Boldmere St Michaels</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2.63</v>
+        <v>1.98</v>
       </c>
       <c r="D57" t="n">
         <v>3.4</v>
       </c>
       <c r="E57" t="n">
-        <v>2.23</v>
+        <v>3.1</v>
       </c>
       <c r="F57" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="G57" t="n">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2253,28 +2253,28 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Al Sailiya vs Al-Rayyan</t>
+          <t>Bedworth United vs Grantham Town</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3.8</v>
+        <v>1.92</v>
       </c>
       <c r="D58" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="E58" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="F58" t="n">
         <v>1.68</v>
       </c>
-      <c r="F58" t="n">
-        <v>1.6</v>
-      </c>
       <c r="G58" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2285,28 +2285,28 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Al Shahaniya vs Al Duhail</t>
+          <t>Sutton Coldfield Town vs Mickleover Sports</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2.8</v>
+        <v>2.27</v>
       </c>
       <c r="D59" t="n">
         <v>3.4</v>
       </c>
       <c r="E59" t="n">
-        <v>2.15</v>
+        <v>2.54</v>
       </c>
       <c r="F59" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="G59" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -2317,28 +2317,28 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Zetech Sparks FC (W) vs Kenya Police Bullets (W)</t>
+          <t>Clitheroe vs Runcorn Linnets</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>4.33</v>
+        <v>1.81</v>
       </c>
       <c r="D60" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="E60" t="n">
-        <v>1.62</v>
+        <v>3.4</v>
       </c>
       <c r="F60" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="G60" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2349,28 +2349,28 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Independiente Yumbo vs Orsomarso</t>
+          <t>Kidsgrove Athletic vs Lichfield City</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1.91</v>
+        <v>1.22</v>
       </c>
       <c r="D61" t="n">
-        <v>3.1</v>
+        <v>5.5</v>
       </c>
       <c r="E61" t="n">
-        <v>3.8</v>
+        <v>8.5</v>
       </c>
       <c r="F61" t="n">
-        <v>2.27</v>
+        <v>1.27</v>
       </c>
       <c r="G61" t="n">
-        <v>1.53</v>
+        <v>3.4</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -2381,28 +2381,28 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Envigado U19 vs Atletico Nacional Medellin U19</t>
+          <t>Bootle vs Nantwich Town</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2.8</v>
+        <v>1.51</v>
       </c>
       <c r="D62" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="E62" t="n">
-        <v>2.05</v>
+        <v>4.75</v>
       </c>
       <c r="F62" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="G62" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -2413,28 +2413,28 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Guadeloupe vs Barbados</t>
+          <t>Atherton Collieries vs Vauxhall Motors</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="D63" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="E63" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="F63" t="n">
-        <v>1.95</v>
+        <v>1.51</v>
       </c>
       <c r="G63" t="n">
-        <v>1.76</v>
+        <v>2.37</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -2445,28 +2445,28 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FK Haugesund II vs Hinna Fotball</t>
+          <t>Wythenshawe Town vs Padiham</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1.18</v>
+        <v>1.6</v>
       </c>
       <c r="D64" t="n">
-        <v>6.5</v>
+        <v>3.8</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
-        <v>1.12</v>
+        <v>1.53</v>
       </c>
       <c r="G64" t="n">
-        <v>5</v>
+        <v>2.35</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -2477,28 +2477,28 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Sportivo San Lorenzo vs Deportivo Recoleta</t>
+          <t>Emley vs Workington</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="D65" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="E65" t="n">
-        <v>2.27</v>
+        <v>2.14</v>
       </c>
       <c r="F65" t="n">
-        <v>1.87</v>
+        <v>1.64</v>
       </c>
       <c r="G65" t="n">
-        <v>1.81</v>
+        <v>2.08</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -2509,28 +2509,28 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Club Atletico Tembetary vs Paraguari AC</t>
+          <t>Alfreton Town vs Guiseley</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="D66" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="E66" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="F66" t="n">
-        <v>1.97</v>
+        <v>1.68</v>
       </c>
       <c r="G66" t="n">
-        <v>1.72</v>
+        <v>2.03</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -2541,28 +2541,28 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Sportivo Luqueno Reserves vs Club Guarani Asuncion Reserves</t>
+          <t>Warrington Town vs Gainsborough Trinity</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>4.75</v>
+        <v>2.55</v>
       </c>
       <c r="D67" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="E67" t="n">
-        <v>1.51</v>
+        <v>2.39</v>
       </c>
       <c r="F67" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="G67" t="n">
-        <v>2.18</v>
+        <v>1.97</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -2573,28 +2573,28 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Deportivo Pinoza vs Club Oriental</t>
+          <t>Whitby Town vs Lancaster City</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="D68" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="E68" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="F68" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="G68" t="n">
-        <v>1.76</v>
+        <v>1.96</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -2605,28 +2605,28 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Atletico Juventud Loma Pyta vs Club Pilcomayo FBC</t>
+          <t>Ilkeston vs Warrington Rylands</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3.1</v>
+        <v>2.77</v>
       </c>
       <c r="D69" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="E69" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="F69" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="G69" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -2637,28 +2637,28 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>29 dk içinde</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Olimpia Asuncion (K) vs Nacional-Humaita (K)</t>
+          <t>Wigan U21 vs Huddersfield U21</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1.01</v>
+        <v>2.77</v>
       </c>
       <c r="D70" t="n">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="E70" t="n">
-        <v>34</v>
+        <v>1.96</v>
       </c>
       <c r="F70" t="n">
-        <v>1.6</v>
+        <v>1.16</v>
       </c>
       <c r="G70" t="n">
-        <v>2.07</v>
+        <v>4.33</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -2669,28 +2669,28 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>29 dk içinde</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Sportivo San Lorenzo (K) vs Club Guarani (K)</t>
+          <t>Charlton Athletic U21 vs Millwall U21</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>6</v>
+        <v>1.62</v>
       </c>
       <c r="D71" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="E71" t="n">
-        <v>1.33</v>
+        <v>3.8</v>
       </c>
       <c r="F71" t="n">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="G71" t="n">
-        <v>2.07</v>
+        <v>3.28</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -2701,28 +2701,28 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>29 dk içinde</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Cesar Vallejo Reserves vs Juventus Huamachuco FC</t>
+          <t>Coventry City U21 vs Colchester U21</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="D72" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="E72" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="F72" t="n">
-        <v>1.74</v>
+        <v>1.14</v>
       </c>
       <c r="G72" t="n">
-        <v>1.94</v>
+        <v>4.5</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -2733,28 +2733,28 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>29 dk içinde</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Graficar Beograd vs Teleoptik Zemun</t>
+          <t>Hull City U21 vs Bolton Wanderers U21</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1.76</v>
+        <v>3</v>
       </c>
       <c r="D73" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="E73" t="n">
-        <v>3.8</v>
+        <v>1.87</v>
       </c>
       <c r="F73" t="n">
-        <v>1.72</v>
+        <v>1.28</v>
       </c>
       <c r="G73" t="n">
-        <v>1.96</v>
+        <v>3.3</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -2765,28 +2765,28 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>29 dk içinde</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Bor 1919 vs Metalac GM</t>
+          <t>Peterborough United U21 vs Fleetwood Town U21</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2.31</v>
+        <v>1.33</v>
       </c>
       <c r="D74" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="E74" t="n">
-        <v>2.63</v>
+        <v>5.5</v>
       </c>
       <c r="F74" t="n">
-        <v>1.98</v>
+        <v>1.16</v>
       </c>
       <c r="G74" t="n">
-        <v>1.72</v>
+        <v>4.25</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -2797,28 +2797,28 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Dubocica vs Javor Ivanjica</t>
+          <t>Peterborough Sports vs Redditch United</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3.8</v>
+        <v>2.01</v>
       </c>
       <c r="D75" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="E75" t="n">
-        <v>1.74</v>
+        <v>2.9</v>
       </c>
       <c r="F75" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="G75" t="n">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -2829,28 +2829,28 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Proleter 023 Zrenjanin vs Jedinstvo Ub</t>
+          <t>Racing Club Warwick vs Worcester City</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1.87</v>
+        <v>2.45</v>
       </c>
       <c r="D76" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="E76" t="n">
-        <v>3.6</v>
+        <v>2.45</v>
       </c>
       <c r="F76" t="n">
-        <v>2.07</v>
+        <v>1.78</v>
       </c>
       <c r="G76" t="n">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -2861,28 +2861,28 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Loznica vs Spartak Subotica</t>
+          <t>Thame United FC vs Beaconsfield Town</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2.55</v>
+        <v>1.55</v>
       </c>
       <c r="D77" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="E77" t="n">
-        <v>2.5</v>
+        <v>4.25</v>
       </c>
       <c r="F77" t="n">
-        <v>2</v>
+        <v>1.41</v>
       </c>
       <c r="G77" t="n">
-        <v>1.71</v>
+        <v>2.63</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -2893,28 +2893,28 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NK Rudar Velenje vs Dravinja</t>
+          <t>Needham Market vs Stamford</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1.79</v>
+        <v>1.35</v>
       </c>
       <c r="D78" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="E78" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="F78" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="G78" t="n">
-        <v>2.16</v>
+        <v>2.27</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -2925,28 +2925,28 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CA River Plate Montevideo Reserves vs Montevideo City Torque Reserve</t>
+          <t>Halesowen Town vs Rushall Olympic</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="D79" t="n">
         <v>3.5</v>
       </c>
       <c r="E79" t="n">
-        <v>1.87</v>
+        <v>2.63</v>
       </c>
       <c r="F79" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="G79" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -2957,12 +2957,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Racing Club de Montevideo Reserves vs Colon Montevideo Reserves</t>
+          <t>Alvechurch vs Stourbridge</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -2972,13 +2972,13 @@
         <v>3.4</v>
       </c>
       <c r="E80" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="F80" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="G80" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -2989,28 +2989,28 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Club Oriental Reserves vs Cerro Largo FC Reserves</t>
+          <t>Real Bedford vs Leiston</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>2.45</v>
+        <v>1.41</v>
       </c>
       <c r="D81" t="n">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="E81" t="n">
-        <v>2.4</v>
+        <v>5.5</v>
       </c>
       <c r="F81" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="G81" t="n">
-        <v>2.02</v>
+        <v>2.63</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -3021,28 +3021,28 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Nacional de Montevideo Reserves vs Central Espanol Reserves</t>
+          <t>Hitchin Town vs Leighton Town</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1.51</v>
+        <v>2.45</v>
       </c>
       <c r="D82" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="F82" t="n">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="G82" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -3053,28 +3053,28 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Juventud De Las Piedras Reserves vs La Luz Reserves</t>
+          <t>Kettering Town vs Anstey Nomads</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="D83" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="E83" t="n">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="F83" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="G83" t="n">
-        <v>2.18</v>
+        <v>2.03</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -3085,28 +3085,28 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Deportivo Maldonado Reserves vs Ca Penarol Reserves</t>
+          <t>Bishop's Stortford vs Bury Town</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="D84" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="E84" t="n">
-        <v>2.09</v>
+        <v>1.96</v>
       </c>
       <c r="F84" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="G84" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -3117,28 +3117,28 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>FC Marko vs Panthrakikos</t>
+          <t>Bromsgrove Sporting vs Leamington</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="D85" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="E85" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="F85" t="n">
-        <v>1.98</v>
+        <v>1.64</v>
       </c>
       <c r="G85" t="n">
-        <v>1.72</v>
+        <v>2.08</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -3149,28 +3149,28 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Kallithea vs Asteras Tripolis B</t>
+          <t>Banbury United vs Stratford Town</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="D86" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="E86" t="n">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="F86" t="n">
-        <v>2.27</v>
+        <v>1.86</v>
       </c>
       <c r="G86" t="n">
-        <v>1.55</v>
+        <v>1.81</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -3181,30 +3181,2334 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Leverstock Green vs Ware</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="D87" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E87" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F87" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G87" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Huesca (W) vs Osasuna (K)</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D88" t="n">
+        <v>5</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G88" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>SpVgg Unterhaching vs TSV Buchbach</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="D89" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E89" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G89" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>22:15</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Rio Ave U23 vs Penafiel U23</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="D90" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E90" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G90" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Kipanga FC vs Black Sailor</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Lesotho vs Fas</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>26</v>
+      </c>
+      <c r="D91" t="n">
+        <v>11</v>
+      </c>
+      <c r="E91" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="G91" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Gabon vs Nijer</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="D92" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E92" t="n">
+        <v>5</v>
+      </c>
+      <c r="F92" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="G92" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Gana vs Gambia</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="D93" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E93" t="n">
+        <v>6</v>
+      </c>
+      <c r="F93" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G93" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Somalia vs Fildişi Sahili</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>21</v>
+      </c>
+      <c r="D94" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="F94" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G94" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>28 dk içinde</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Comoros vs Namibya</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="D95" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E95" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="F95" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G95" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Kongo vs Kamerun</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>5</v>
+      </c>
+      <c r="D96" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F96" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G96" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Madagaskar vs Tanzanya</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="D97" t="n">
+        <v>3</v>
+      </c>
+      <c r="E97" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="F97" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G97" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Gine Bissau vs Nijerya</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>6</v>
+      </c>
+      <c r="D98" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E98" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="F98" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="G98" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Etiyopya vs Senegal</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>9</v>
+      </c>
+      <c r="D99" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E99" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="F99" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="G99" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Mozambik vs Sudan</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="D100" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E100" t="n">
+        <v>5</v>
+      </c>
+      <c r="F100" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="G100" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Burundi vs Cezayir</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>10</v>
+      </c>
+      <c r="D101" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E101" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F101" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G101" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Zambiya vs Togo</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="D102" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="E102" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F102" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G102" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Uganda vs Libya</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="D103" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="E103" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F103" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G103" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Günay Sudan vs Mısır</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="D104" t="n">
+        <v>5</v>
+      </c>
+      <c r="E104" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G104" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Yeşil Burun Adaları vs Ruanda</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="D105" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E105" t="n">
+        <v>7</v>
+      </c>
+      <c r="F105" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G105" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Liberya vs Mali</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>6</v>
+      </c>
+      <c r="D106" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E106" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F106" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G106" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Benin vs Moritanya</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="D107" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E107" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F107" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G107" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Tunisia U23 vs Benin U23</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="D108" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="E108" t="n">
+        <v>8</v>
+      </c>
+      <c r="F108" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G108" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Deportivo Muniz vs El Porvenir</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D109" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E109" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="F109" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="G109" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Atletico Rafaela Reserves vs Ferro Carril Oeste Reserves</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="D110" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E110" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F110" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G110" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>San Lorenzo Reserves vs CA Aldosivi Reserves</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="D111" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E111" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F111" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G111" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Banfield Reserves vs Atletico Tucuman Reserves</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="D112" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="E112" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="F112" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G112" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Estudiantes La Plata Reserves vs Defensa Y Justicia Reserves</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D113" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E113" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F113" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="G113" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Tigre Reserves vs Gimnasia La Plata Reserves</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="D114" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E114" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="F114" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G114" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Flandria U20 vs CA San Miguel U20</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="D115" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E115" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F115" t="n">
         <v>1.81</v>
       </c>
-      <c r="D87" t="n">
+      <c r="G115" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Uribelarrea FC vs Defensores de Glew</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D116" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E116" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="F116" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G116" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>58 dk içinde</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Tayland vs Vietnam</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="D117" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E117" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="F117" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Suudi Arabistan vs Irak</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>2</v>
+      </c>
+      <c r="D118" t="n">
+        <v>3</v>
+      </c>
+      <c r="E118" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F118" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Oman Sultanlığı vs Kuveyt</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="D119" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E119" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F119" t="n">
+        <v>2</v>
+      </c>
+      <c r="G119" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>SV Kuchl vs SV Wals-Grünau</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D120" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E120" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G120" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Fujairah FC vs Al Jazira Hamra</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="D121" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E121" t="n">
+        <v>6</v>
+      </c>
+      <c r="F121" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="G121" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Fc Palm City vs Dibba Al-Hisn</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="D122" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E122" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G122" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Universitario De Vinto vs Guabira Santa Cruz</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="D123" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E123" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F123" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G123" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>CA Juventus SP U20 vs GE Prudente U20</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="D124" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E124" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G124" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>FC Slovan Rosice vs Boskovice</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="D125" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E125" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G125" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Odense Q (K) vs AGF Aarhus (K)</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="D126" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="E126" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G126" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Jagiellonia Białystok vs FK Suduva Marijampole</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="D127" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E127" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G127" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>57 dk içinde</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Bulgaristan U19 vs Romanya U19</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D128" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E128" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="F128" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G128" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>İngiltere U19 vs Norveç U19</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D129" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E129" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F129" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G129" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Sırbistan U19 vs Macaristan U19</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="D130" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E130" t="n">
+        <v>3</v>
+      </c>
+      <c r="F130" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G130" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Almanya vs Italy U20</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D131" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E131" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="F131" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G131" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Polonya U20 vs Çek Cumhuriyeti U20</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="D132" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="E132" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F132" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G132" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Rusya vs Iran</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="D133" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E133" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="G133" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Flora Tallinn U19 vs Tallinna FC Ajax U19</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>3</v>
+      </c>
+      <c r="D134" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E134" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="F134" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="G134" t="n">
+        <v>7</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Nomme United U19 vs Johvi FC Phoenix U19</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D135" t="n">
+        <v>5</v>
+      </c>
+      <c r="E135" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="F135" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="G135" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Harju JK Laagri U19 vs JK Trans Narva U19</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="D136" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E136" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F136" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="G136" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Cardiff Metropolitan University vs Haverfordwest County</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="D137" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E137" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F137" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G137" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Aizawl vs Chanmari</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="D138" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E138" t="n">
+        <v>4</v>
+      </c>
+      <c r="F138" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G138" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Mes Rafsanjan vs Besat Kermanshah</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="D139" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E139" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F139" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="G139" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>St. Mary's FC vs Midleton FC</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D140" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E140" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="F140" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G140" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Forfar Athletic vs Formartine United FC</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="D141" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E141" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="F141" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G141" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Jitex Molndal (W) vs Vittsjo GIK (K)</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>7</v>
+      </c>
+      <c r="D142" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Linkopings FC (W) vs IFK Norrkoping (K)</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D143" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E143" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="F143" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G143" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Al-Khor vs Umm Salal</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D144" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E144" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="F144" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G144" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Al Markhiya vs Al-Ahli Doha</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D145" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E145" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="F145" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G145" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Al Waab Sports Club vs Lusail City</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D146" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E146" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="F146" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G146" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Deportivo Pereira vs Independiente Santa Fe</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D147" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="E147" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="F147" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G147" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Dimelo Jara vs Los Embajadores</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D148" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E148" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="F148" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G148" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>British Virgin Islands vs Turks and Caicos Islands</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D149" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E149" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="F149" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G149" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>FK Union Carl Berner vs KFUM 2</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="D150" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E150" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F150" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G150" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Toten U19 vs Storhamar Fotball U19</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D151" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E151" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="F151" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G151" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>29 de Septiembre vs 24 de Setiembre</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="D152" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E152" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="F152" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G152" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Sportivo Trinidense (K) vs 2 de Mayo (K)</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="D153" t="n">
+        <v>6</v>
+      </c>
+      <c r="E153" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F153" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G153" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Cerro Porteno (K) vs Libertad (K)</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D154" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E154" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="F154" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G154" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Vozdovac vs Napredak Krusevac</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="D155" t="n">
         <v>3.05</v>
       </c>
-      <c r="E87" t="n">
+      <c r="E155" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F155" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G155" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Inter Bratislava vs Podbrezova</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D156" t="n">
         <v>4</v>
       </c>
-      <c r="F87" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="G87" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="H87" t="inlineStr">
+      <c r="E156" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F156" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G156" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>NK Podvinci vs NK Ljutomer</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="D157" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E157" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F157" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G157" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Liverpool Montevideo Reserves vs Montevideo Wanderers Reserves</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="D158" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E158" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F158" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G158" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Boston River Reserves vs Albion Reserves</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="D159" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E159" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F159" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G159" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H159" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/bugun_oranlar.xlsx
+++ b/bugun_oranlar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H159"/>
+  <dimension ref="A1:H132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,23 +466,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Çekya vs İngiltere</t>
+          <t>Yunanistan vs Hollanda</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>3.2</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="E2" t="n">
-        <v>1.35</v>
+        <v>2.06</v>
       </c>
       <c r="F2" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="G2" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -498,11 +498,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>İspanya vs Hırvatistan</t>
+          <t>Almanya vs Sırbistan</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="D3" t="n">
         <v>6.5</v>
@@ -511,10 +511,10 @@
         <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="G3" t="n">
-        <v>2.68</v>
+        <v>3.1</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -530,23 +530,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>İskoçya vs İsviçre</t>
+          <t>Galler vs Norveç</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="E4" t="n">
-        <v>1.87</v>
+        <v>1.45</v>
       </c>
       <c r="F4" t="n">
-        <v>2.12</v>
+        <v>1.53</v>
       </c>
       <c r="G4" t="n">
-        <v>1.68</v>
+        <v>2.4</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -562,23 +562,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Slovenya vs Kuzey Makedonya</t>
+          <t>Danimarka vs Portekiz</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.64</v>
+        <v>3.3</v>
       </c>
       <c r="D5" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="E5" t="n">
-        <v>5.5</v>
+        <v>2.01</v>
       </c>
       <c r="F5" t="n">
-        <v>2.31</v>
+        <v>1.68</v>
       </c>
       <c r="G5" t="n">
-        <v>1.55</v>
+        <v>2.12</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -589,28 +589,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Finlandiya vs Belarus</t>
+          <t>İsrail vs Kosova</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.55</v>
+        <v>3.05</v>
       </c>
       <c r="D6" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>2.23</v>
       </c>
       <c r="F6" t="n">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="G6" t="n">
-        <v>1.66</v>
+        <v>1.84</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -626,23 +626,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>San Marino vs Arnavutluk</t>
+          <t>İrlanda vs Avusturya</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>31</v>
+        <v>3.28</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>3.28</v>
       </c>
       <c r="E7" t="n">
-        <v>1.07</v>
+        <v>2.2</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4</v>
+        <v>2.18</v>
       </c>
       <c r="G7" t="n">
-        <v>2.73</v>
+        <v>1.62</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -658,23 +658,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Moldova vs Faroe Adaları</t>
+          <t>Azerbaycan vs Lihtenştayn</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.73</v>
+        <v>1.13</v>
       </c>
       <c r="D8" t="n">
-        <v>3.05</v>
+        <v>7.5</v>
       </c>
       <c r="E8" t="n">
-        <v>2.7</v>
+        <v>21</v>
       </c>
       <c r="F8" t="n">
-        <v>2.55</v>
+        <v>1.64</v>
       </c>
       <c r="G8" t="n">
-        <v>1.45</v>
+        <v>2.16</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -690,23 +690,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Slovakya vs Kazakistan</t>
+          <t>Malta vs Cebelitarık</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1.27</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="E9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F9" t="n">
-        <v>1.68</v>
+        <v>2.04</v>
       </c>
       <c r="G9" t="n">
-        <v>2.08</v>
+        <v>1.71</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -717,28 +717,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bulgaristan vs Estonya</t>
+          <t>Yunanistan U21 vs Letonya U21</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.81</v>
+        <v>1.07</v>
       </c>
       <c r="D10" t="n">
-        <v>3.4</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>4.5</v>
+        <v>21</v>
       </c>
       <c r="F10" t="n">
-        <v>2.25</v>
+        <v>1.32</v>
       </c>
       <c r="G10" t="n">
-        <v>1.58</v>
+        <v>3.05</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -749,28 +749,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lüksemburg vs İzlanda</t>
+          <t>North Macedonia U21 vs Karadağ U21</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3.3</v>
+        <v>2.73</v>
       </c>
       <c r="D11" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="E11" t="n">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="F11" t="n">
-        <v>2.12</v>
+        <v>1.99</v>
       </c>
       <c r="G11" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -781,28 +781,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Slovenya U21 vs İsrail U21</t>
+          <t>Armenia U21 vs İtalya U21</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.12</v>
+        <v>21</v>
       </c>
       <c r="D12" t="n">
-        <v>3.1</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>3.3</v>
+        <v>1.06</v>
       </c>
       <c r="F12" t="n">
-        <v>2.23</v>
+        <v>1.22</v>
       </c>
       <c r="G12" t="n">
-        <v>1.58</v>
+        <v>3.6</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -813,28 +813,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>İzlanda U21 vs İsviçre U21</t>
+          <t>Macaristan U21 vs Litvanya U21</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3.1</v>
+        <v>1.45</v>
       </c>
       <c r="D13" t="n">
-        <v>3.5</v>
+        <v>4.15</v>
       </c>
       <c r="E13" t="n">
-        <v>2.05</v>
+        <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -845,28 +845,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Estonia U21 vs France U21</t>
+          <t>Kuzey İrlanda U21 vs Gürcistan U21</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>26</v>
+        <v>1.9</v>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>3.3</v>
       </c>
       <c r="E14" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="F14" t="n">
-        <v>1.14</v>
+        <v>2.04</v>
       </c>
       <c r="G14" t="n">
-        <v>5</v>
+        <v>1.68</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -877,28 +877,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Norveç U21 vs Bosnia and Herzegovina U21</t>
+          <t>Koge (K) vs Servette Chenois (K)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="D15" t="n">
         <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="F15" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="G15" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -909,28 +909,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ireland U21 vs Kazakistan U21</t>
+          <t>Austria Vienna (K) vs Inter Milano (K)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.22</v>
+        <v>3.8</v>
       </c>
       <c r="D16" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="E16" t="n">
-        <v>10</v>
+        <v>1.78</v>
       </c>
       <c r="F16" t="n">
-        <v>1.51</v>
+        <v>1.78</v>
       </c>
       <c r="G16" t="n">
-        <v>2.31</v>
+        <v>1.93</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -941,28 +941,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Belçika U21 vs Galler U21</t>
+          <t>Paris Saint Germain (K) vs Oud-Heverlee Leuven (K)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="D17" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
         <v>11</v>
       </c>
       <c r="F17" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="G17" t="n">
-        <v>2.45</v>
+        <v>2.68</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -973,28 +973,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>29 dk içinde</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Derby County Reserves vs Rotherham United Reserves</t>
+          <t>Manchester City (K) vs Real Madrid (K)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2.02</v>
+        <v>1.68</v>
       </c>
       <c r="D18" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>2.77</v>
+        <v>4</v>
       </c>
       <c r="F18" t="n">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="G18" t="n">
-        <v>2.9</v>
+        <v>2.36</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1005,28 +1005,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>29 dk içinde</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Preston Reserves vs Wrexham Reserves</t>
+          <t>UD Santa Marta vs Salamanca CF UDS</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.16</v>
+        <v>3.1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="E19" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="F19" t="n">
-        <v>1.33</v>
+        <v>2.12</v>
       </c>
       <c r="G19" t="n">
-        <v>3.05</v>
+        <v>1.62</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1042,23 +1042,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fakenham Town vs Felixstowe &amp; Walton United FC</t>
+          <t>Bastia vs Orléans</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>2.23</v>
       </c>
       <c r="D20" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="E20" t="n">
-        <v>1.98</v>
+        <v>2.9</v>
       </c>
       <c r="F20" t="n">
-        <v>1.55</v>
+        <v>2.16</v>
       </c>
       <c r="G20" t="n">
-        <v>2.26</v>
+        <v>1.6</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1069,28 +1069,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Brightlingsea Regent vs AFC Sudbury</t>
+          <t>Gine vs Kenya</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2.73</v>
+        <v>1.55</v>
       </c>
       <c r="D21" t="n">
         <v>3.4</v>
       </c>
       <c r="E21" t="n">
-        <v>2.18</v>
+        <v>6</v>
       </c>
       <c r="F21" t="n">
-        <v>1.68</v>
+        <v>2.45</v>
       </c>
       <c r="G21" t="n">
-        <v>2.01</v>
+        <v>1.47</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1101,28 +1101,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Canvey Island vs Newmarket Town</t>
+          <t>Barracas Central Reserves vs Gimnasia Mendoza Reserves</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="D22" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="E22" t="n">
-        <v>2.73</v>
+        <v>2.36</v>
       </c>
       <c r="F22" t="n">
-        <v>1.68</v>
+        <v>2.16</v>
       </c>
       <c r="G22" t="n">
-        <v>2.01</v>
+        <v>1.6</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1133,28 +1133,28 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Windsor &amp; Eton vs AFC Stoneham</t>
+          <t>San Martin de San Juan Reserves vs Lanus Reserves</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.87</v>
+        <v>5.5</v>
       </c>
       <c r="D23" t="n">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="E23" t="n">
-        <v>3.2</v>
+        <v>1.41</v>
       </c>
       <c r="F23" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="G23" t="n">
-        <v>2.39</v>
+        <v>2.31</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1165,28 +1165,28 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hendon vs Ashford Town (Middx) Lfc</t>
+          <t>Colon Reserves vs Deportivo Riestra Reserves</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1.68</v>
+        <v>2.73</v>
       </c>
       <c r="D24" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="E24" t="n">
-        <v>3.8</v>
+        <v>2.37</v>
       </c>
       <c r="F24" t="n">
-        <v>1.47</v>
+        <v>2.27</v>
       </c>
       <c r="G24" t="n">
-        <v>2.45</v>
+        <v>1.55</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1197,28 +1197,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dulwich Hamlet vs Aveley</t>
+          <t>Ca Independiente Reserves vs Boca Juniors Reserves</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="D25" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="E25" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="F25" t="n">
-        <v>1.51</v>
+        <v>2.15</v>
       </c>
       <c r="G25" t="n">
-        <v>2.37</v>
+        <v>1.6</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1234,23 +1234,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Maldon &amp; Tiptree vs Cray Wanderers</t>
+          <t>Velez Sarsfield Reserves vs Argentinos Juniors Reserves</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2.8</v>
+        <v>1.55</v>
       </c>
       <c r="D26" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="E26" t="n">
-        <v>2.06</v>
+        <v>5</v>
       </c>
       <c r="F26" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G26" t="n">
-        <v>2.37</v>
+        <v>1.71</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1261,28 +1261,28 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Dartford vs Whitehawk</t>
+          <t>Ca Talleres De Cordoba Reserves vs Godoy Cruz Reserves</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.41</v>
+        <v>1.74</v>
       </c>
       <c r="D27" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="E27" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="F27" t="n">
-        <v>1.47</v>
+        <v>1.72</v>
       </c>
       <c r="G27" t="n">
-        <v>2.4</v>
+        <v>1.96</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1293,28 +1293,28 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Wimborne Town vs Yate Town</t>
+          <t>Defensores de Cambaceres Reserves vs Sacachispas Reserves</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2.09</v>
+        <v>1.71</v>
       </c>
       <c r="D28" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="E28" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="F28" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="G28" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1325,28 +1325,28 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Hanworth Villa vs Chichester City</t>
+          <t>JJ Urquiza Reserves vs CA Atlas Reserves</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="D29" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="E29" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="F29" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="G29" t="n">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1357,28 +1357,28 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Evesham United vs Chippenham Town</t>
+          <t>Villa San Carlos Reserves vs UAI Urquiza Reserves</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="D30" t="n">
         <v>3.3</v>
       </c>
       <c r="E30" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="F30" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="G30" t="n">
-        <v>2.03</v>
+        <v>1.87</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1389,28 +1389,28 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sholing vs Berkhamsted</t>
+          <t>Deportivo Camioneros Reserves vs Arsenal De Sarandi Reserves</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2.23</v>
+        <v>2.8</v>
       </c>
       <c r="D31" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="E31" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="F31" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="G31" t="n">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1421,28 +1421,28 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bath City vs Malvern Town</t>
+          <t>Club Comunicaciones Reserves vs Deportivo Laferrere Reserves</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="D32" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="E32" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="F32" t="n">
-        <v>1.47</v>
+        <v>1.71</v>
       </c>
       <c r="G32" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1453,28 +1453,28 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Chertsey Town vs Poole Town</t>
+          <t>Sportivo Italiano Reserves vs Excursionistas Reserves</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2.02</v>
+        <v>2.9</v>
       </c>
       <c r="D33" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="E33" t="n">
-        <v>2.9</v>
+        <v>2.03</v>
       </c>
       <c r="F33" t="n">
-        <v>1.58</v>
+        <v>1.87</v>
       </c>
       <c r="G33" t="n">
-        <v>2.18</v>
+        <v>1.81</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1485,28 +1485,28 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Gloucester City vs Plymouth Parkway</t>
+          <t>Argentino Quilmes Reserves vs Deportivo Armenio Reserves</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>2.12</v>
       </c>
       <c r="D34" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="E34" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="F34" t="n">
-        <v>1.53</v>
+        <v>1.94</v>
       </c>
       <c r="G34" t="n">
-        <v>2.27</v>
+        <v>1.68</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1517,28 +1517,28 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Havant &amp; Waterloville vs Hanwell Town</t>
+          <t>CA San Miguel Reserves vs Temperley Reserves</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2.23</v>
+        <v>4.5</v>
       </c>
       <c r="D35" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="E35" t="n">
-        <v>2.63</v>
+        <v>1.62</v>
       </c>
       <c r="F35" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="G35" t="n">
-        <v>2.15</v>
+        <v>1.72</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1549,28 +1549,28 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Uxbridge vs Basingstoke Town Lfc</t>
+          <t>Club Atletico Mitre Reserves vs Talleres Remedios Reserves</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="D36" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="F36" t="n">
-        <v>1.6</v>
+        <v>2.03</v>
       </c>
       <c r="G36" t="n">
-        <v>2.15</v>
+        <v>1.68</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1581,28 +1581,28 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Boreham Wood vs Kidderminster</t>
+          <t>Estudiantes Caseros Reserves vs Nueva Chicago Reserves</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1.38</v>
+        <v>2.4</v>
       </c>
       <c r="D37" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>6</v>
+        <v>2.63</v>
       </c>
       <c r="F37" t="n">
-        <v>1.47</v>
+        <v>2.26</v>
       </c>
       <c r="G37" t="n">
-        <v>2.4</v>
+        <v>1.55</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1613,28 +1613,28 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Yeovil vs Worthing</t>
+          <t>Almirante Brown Reserves vs Chacarita Juniors Reserves</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2.1</v>
+        <v>4.33</v>
       </c>
       <c r="D38" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="E38" t="n">
-        <v>2.8</v>
+        <v>1.68</v>
       </c>
       <c r="F38" t="n">
-        <v>1.47</v>
+        <v>2.07</v>
       </c>
       <c r="G38" t="n">
-        <v>2.45</v>
+        <v>1.66</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1645,28 +1645,28 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Barrow vs Scunthorpe</t>
+          <t>Ferrocarril Midland Reserves vs CA Agropecuario Reserves</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2.02</v>
+        <v>3.5</v>
       </c>
       <c r="D39" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="E39" t="n">
-        <v>3</v>
+        <v>1.74</v>
       </c>
       <c r="F39" t="n">
-        <v>1.64</v>
+        <v>1.43</v>
       </c>
       <c r="G39" t="n">
-        <v>2.12</v>
+        <v>2.58</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -1677,28 +1677,28 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Gateshead vs Altrincham</t>
+          <t>All Boys Reserves vs Almagro Reserves</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4.25</v>
+        <v>1.68</v>
       </c>
       <c r="D40" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.62</v>
+        <v>4.33</v>
       </c>
       <c r="F40" t="n">
-        <v>1.58</v>
+        <v>2.14</v>
       </c>
       <c r="G40" t="n">
-        <v>2.22</v>
+        <v>1.64</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -1709,28 +1709,28 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AFC Fylde vs Carlisle</t>
+          <t>CA Colegiales Reserves vs Tristan Suarez Reserves</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2.27</v>
+        <v>10</v>
       </c>
       <c r="D41" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="E41" t="n">
-        <v>2.58</v>
+        <v>1.2</v>
       </c>
       <c r="F41" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="G41" t="n">
-        <v>2.58</v>
+        <v>2.73</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -1741,28 +1741,28 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Hartlepool vs Harrogate</t>
+          <t>Los Andes Reserves vs Deportivo Moron Reserves</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3.4</v>
+        <v>2.26</v>
       </c>
       <c r="D42" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.87</v>
+        <v>2.7</v>
       </c>
       <c r="F42" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="G42" t="n">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -1773,28 +1773,28 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Forest Green vs Wealdstone</t>
+          <t>Malezya vs Singapur</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="D43" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="E43" t="n">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="F43" t="n">
-        <v>1.45</v>
+        <v>1.68</v>
       </c>
       <c r="G43" t="n">
-        <v>1.47</v>
+        <v>2.03</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -1805,28 +1805,28 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Woking vs Solihull Moors</t>
+          <t>Endonezya vs Bangladesh</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="D44" t="n">
-        <v>3.6</v>
+        <v>13</v>
       </c>
       <c r="E44" t="n">
-        <v>3.3</v>
+        <v>41</v>
       </c>
       <c r="F44" t="n">
-        <v>1.58</v>
+        <v>1.28</v>
       </c>
       <c r="G44" t="n">
-        <v>2.22</v>
+        <v>3.2</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -1837,28 +1837,28 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AFC Hornchurch vs Aldershot</t>
+          <t>SKN Sankt Polten II vs Zwettl</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2.09</v>
+        <v>3.4</v>
       </c>
       <c r="D45" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="E45" t="n">
-        <v>2.9</v>
+        <v>1.78</v>
       </c>
       <c r="F45" t="n">
-        <v>1.66</v>
+        <v>1.41</v>
       </c>
       <c r="G45" t="n">
-        <v>2.07</v>
+        <v>2.59</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -1869,28 +1869,28 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Halifax vs Boston United</t>
+          <t>Union Weisskirchen vs Union Vocklamarkt</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2.03</v>
+        <v>1.47</v>
       </c>
       <c r="D46" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="E46" t="n">
-        <v>3.05</v>
+        <v>4.75</v>
       </c>
       <c r="F46" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="G46" t="n">
-        <v>2.03</v>
+        <v>3</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -1901,28 +1901,28 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Brackley vs South Shields</t>
+          <t>Al Sharjah SCC vs AL Dhafra</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3.5</v>
+        <v>1.55</v>
       </c>
       <c r="D47" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="E47" t="n">
-        <v>1.83</v>
+        <v>4.5</v>
       </c>
       <c r="F47" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="G47" t="n">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -1933,28 +1933,28 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Slough Town vs Ebbsfleet United</t>
+          <t>Dubai United FC vs Hatta Dubai</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5</v>
+        <v>1.92</v>
       </c>
       <c r="D48" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="E48" t="n">
-        <v>1.45</v>
+        <v>3.2</v>
       </c>
       <c r="F48" t="n">
-        <v>1.45</v>
+        <v>1.68</v>
       </c>
       <c r="G48" t="n">
-        <v>2.45</v>
+        <v>2.03</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -1965,28 +1965,28 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ossett United vs Bridlington Town</t>
+          <t>Baniyas FC vs Al Wahda Abu Dhabi</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2.77</v>
+        <v>3.5</v>
       </c>
       <c r="D49" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="E49" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G49" t="n">
         <v>2.12</v>
-      </c>
-      <c r="F49" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="G49" t="n">
-        <v>2.45</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -1997,28 +1997,28 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Garforth Town vs Stocksbridge</t>
+          <t>Se Buzios Rj vs SE Paraty RJ</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1.96</v>
+        <v>2.9</v>
       </c>
       <c r="D50" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="E50" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="F50" t="n">
-        <v>1.68</v>
+        <v>2.01</v>
       </c>
       <c r="G50" t="n">
-        <v>2.04</v>
+        <v>1.7</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2029,28 +2029,28 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Matlock Town vs Bradford Park Avenue</t>
+          <t>SE Belford Roxo vs Santa Cruz RJ</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2.4</v>
+        <v>2.77</v>
       </c>
       <c r="D51" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="E51" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="F51" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="G51" t="n">
-        <v>2.18</v>
+        <v>1.72</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2061,28 +2061,28 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Dunston Uts vs Guisborough Town</t>
+          <t>Cardoso Moreira FC vs Serra Macaense</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1.72</v>
+        <v>2.15</v>
       </c>
       <c r="D52" t="n">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="E52" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="F52" t="n">
-        <v>1.66</v>
+        <v>1.93</v>
       </c>
       <c r="G52" t="n">
-        <v>2.03</v>
+        <v>1.75</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2093,28 +2093,28 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>West Auckland Town vs Ashington</t>
+          <t>Rio de Janeiro vs Barra Mansa FC</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1.84</v>
+        <v>3.15</v>
       </c>
       <c r="D53" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="E53" t="n">
-        <v>3.3</v>
+        <v>2.08</v>
       </c>
       <c r="F53" t="n">
-        <v>1.58</v>
+        <v>1.94</v>
       </c>
       <c r="G53" t="n">
-        <v>2.18</v>
+        <v>1.74</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2125,28 +2125,28 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Beverley Town FC vs Lincoln United</t>
+          <t>Spartax FC vs Lagoa Seca</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="D54" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="E54" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="F54" t="n">
-        <v>1.58</v>
+        <v>1.94</v>
       </c>
       <c r="G54" t="n">
-        <v>2.23</v>
+        <v>1.74</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -2157,28 +2157,28 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>15 dk içinde</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Liversedge vs North Ferriby</t>
+          <t>NK Olimpija Ljubljana vs Slaven Belupo</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1.72</v>
+        <v>2.12</v>
       </c>
       <c r="D55" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="E55" t="n">
-        <v>3.8</v>
+        <v>2.77</v>
       </c>
       <c r="F55" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="G55" t="n">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -2189,28 +2189,28 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Loughborough Students vs Basford United</t>
+          <t>Jahn Regensburg vs WSG Tirol</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2.2</v>
+        <v>2.58</v>
       </c>
       <c r="D56" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="E56" t="n">
-        <v>2.63</v>
+        <v>2.23</v>
       </c>
       <c r="F56" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="G56" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2221,28 +2221,28 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Shepshed Dynamo vs Boldmere St Michaels</t>
+          <t>Juve Stabia vs U.S. Palmese 1912</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1.98</v>
+        <v>1.04</v>
       </c>
       <c r="D57" t="n">
-        <v>3.4</v>
+        <v>10</v>
       </c>
       <c r="E57" t="n">
-        <v>3.1</v>
+        <v>23</v>
       </c>
       <c r="F57" t="n">
-        <v>1.66</v>
+        <v>1.25</v>
       </c>
       <c r="G57" t="n">
-        <v>1.94</v>
+        <v>3.5</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2253,28 +2253,28 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Bedworth United vs Grantham Town</t>
+          <t>VfL Wolfsburg vs Havelse</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1.92</v>
+        <v>1.14</v>
       </c>
       <c r="D58" t="n">
-        <v>3.4</v>
+        <v>7</v>
       </c>
       <c r="E58" t="n">
-        <v>3.28</v>
+        <v>12</v>
       </c>
       <c r="F58" t="n">
-        <v>1.68</v>
+        <v>1.22</v>
       </c>
       <c r="G58" t="n">
-        <v>2.02</v>
+        <v>3.6</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2285,28 +2285,28 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Sutton Coldfield Town vs Mickleover Sports</t>
+          <t>VfB Stuttgart vs Greuther Furth</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2.27</v>
+        <v>1.25</v>
       </c>
       <c r="D59" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="E59" t="n">
-        <v>2.54</v>
+        <v>7.5</v>
       </c>
       <c r="F59" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="G59" t="n">
-        <v>2.12</v>
+        <v>3.15</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -2317,28 +2317,28 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Clitheroe vs Runcorn Linnets</t>
+          <t>Real Betis vs AD Ceuta</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1.81</v>
+        <v>1.33</v>
       </c>
       <c r="D60" t="n">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="E60" t="n">
-        <v>3.4</v>
+        <v>6.5</v>
       </c>
       <c r="F60" t="n">
-        <v>1.66</v>
+        <v>1.38</v>
       </c>
       <c r="G60" t="n">
-        <v>1.94</v>
+        <v>2.68</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2349,28 +2349,28 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>60 dk içinde</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Kidsgrove Athletic vs Lichfield City</t>
+          <t>Fransa U19 vs Türkiye U19</t>
         </is>
       </c>
       <c r="C61" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="D61" t="n">
+        <v>7</v>
+      </c>
+      <c r="E61" t="n">
+        <v>11</v>
+      </c>
+      <c r="F61" t="n">
         <v>1.22</v>
       </c>
-      <c r="D61" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E61" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="F61" t="n">
-        <v>1.27</v>
-      </c>
       <c r="G61" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -2381,28 +2381,28 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Bootle vs Nantwich Town</t>
+          <t>Hırvatistan U19 vs İtalya U19</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1.51</v>
+        <v>3.2</v>
       </c>
       <c r="D62" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="E62" t="n">
-        <v>4.75</v>
+        <v>1.9</v>
       </c>
       <c r="F62" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="G62" t="n">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -2413,28 +2413,28 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Atherton Collieries vs Vauxhall Motors</t>
+          <t>Faroe Adaları U19 vs Slovenia U19</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2.06</v>
+        <v>15</v>
       </c>
       <c r="D63" t="n">
-        <v>3.6</v>
+        <v>7.5</v>
       </c>
       <c r="E63" t="n">
-        <v>2.8</v>
+        <v>1.11</v>
       </c>
       <c r="F63" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="G63" t="n">
-        <v>2.37</v>
+        <v>3</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -2445,28 +2445,28 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Wythenshawe Town vs Padiham</t>
+          <t>Qatar U19 vs İrlanda U19</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1.6</v>
+        <v>4.33</v>
       </c>
       <c r="D64" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>1.58</v>
       </c>
       <c r="F64" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="G64" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -2477,28 +2477,28 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Emley vs Workington</t>
+          <t>Azerbaycan vs United Arab Emirates U19</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2.73</v>
+        <v>2.09</v>
       </c>
       <c r="D65" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="E65" t="n">
-        <v>2.14</v>
+        <v>2.8</v>
       </c>
       <c r="F65" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="G65" t="n">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -2509,28 +2509,28 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Alfreton Town vs Guiseley</t>
+          <t>USA U20 vs Brazil U20</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="D66" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="E66" t="n">
-        <v>2.55</v>
+        <v>1.92</v>
       </c>
       <c r="F66" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="G66" t="n">
-        <v>2.03</v>
+        <v>2.33</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -2541,28 +2541,28 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>25 dk içinde</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Warrington Town vs Gainsborough Trinity</t>
+          <t>Japonya vs Ekvador</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2.55</v>
+        <v>1.45</v>
       </c>
       <c r="D67" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="E67" t="n">
-        <v>2.39</v>
+        <v>6</v>
       </c>
       <c r="F67" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="G67" t="n">
-        <v>1.97</v>
+        <v>2.09</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -2573,28 +2573,28 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Whitby Town vs Lancaster City</t>
+          <t>Maldives vs Lübnan</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2.63</v>
+        <v>31</v>
       </c>
       <c r="D68" t="n">
-        <v>3.3</v>
+        <v>10</v>
       </c>
       <c r="E68" t="n">
-        <v>2.25</v>
+        <v>1.07</v>
       </c>
       <c r="F68" t="n">
-        <v>1.72</v>
+        <v>1.43</v>
       </c>
       <c r="G68" t="n">
-        <v>1.96</v>
+        <v>2.6</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -2605,28 +2605,28 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ilkeston vs Warrington Rylands</t>
+          <t>Özbekistan vs Suriye</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2.77</v>
+        <v>1.38</v>
       </c>
       <c r="D69" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="E69" t="n">
-        <v>2.15</v>
+        <v>8</v>
       </c>
       <c r="F69" t="n">
-        <v>1.68</v>
+        <v>1.94</v>
       </c>
       <c r="G69" t="n">
-        <v>2.02</v>
+        <v>1.76</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -2637,28 +2637,28 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>29 dk içinde</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Wigan U21 vs Huddersfield U21</t>
+          <t>Cumbaya FC vs CD Santo Domingo</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2.77</v>
+        <v>1.84</v>
       </c>
       <c r="D70" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="E70" t="n">
-        <v>1.96</v>
+        <v>4</v>
       </c>
       <c r="F70" t="n">
-        <v>1.16</v>
+        <v>2.45</v>
       </c>
       <c r="G70" t="n">
-        <v>4.33</v>
+        <v>1.47</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -2669,28 +2669,28 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>29 dk içinde</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Charlton Athletic U21 vs Millwall U21</t>
+          <t>CD FAS Reserves vs AD Isidro Metapan Reserves</t>
         </is>
       </c>
       <c r="C71" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="D71" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E71" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F71" t="n">
         <v>1.62</v>
       </c>
-      <c r="D71" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E71" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="F71" t="n">
-        <v>1.28</v>
-      </c>
       <c r="G71" t="n">
-        <v>3.28</v>
+        <v>2.08</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -2701,28 +2701,28 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>29 dk içinde</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Coventry City U21 vs Colchester U21</t>
+          <t>Fuerte San Francisco Reserves vs Luis Angel Firpo Reserves</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="D72" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="E72" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="F72" t="n">
-        <v>1.14</v>
+        <v>1.64</v>
       </c>
       <c r="G72" t="n">
-        <v>4.5</v>
+        <v>2.09</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -2733,28 +2733,28 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>29 dk içinde</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Hull City U21 vs Bolton Wanderers U21</t>
+          <t>LAUTP/2 vs Kumu</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>3</v>
+        <v>2.06</v>
       </c>
       <c r="D73" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="E73" t="n">
-        <v>1.87</v>
+        <v>2.63</v>
       </c>
       <c r="F73" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="G73" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -2765,28 +2765,28 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>29 dk içinde</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Peterborough United U21 vs Fleetwood Town U21</t>
+          <t>Asante Kotoko vs Karela</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="D74" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="E74" t="n">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="F74" t="n">
-        <v>1.16</v>
+        <v>2.06</v>
       </c>
       <c r="G74" t="n">
-        <v>4.25</v>
+        <v>1.64</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -2797,28 +2797,28 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Peterborough Sports vs Redditch United</t>
+          <t>Langsning vs Shillong Lajong Reserves</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2.01</v>
+        <v>2.45</v>
       </c>
       <c r="D75" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="E75" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="F75" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="G75" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -2829,28 +2829,28 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>44 dk içinde</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Racing Club Warwick vs Worcester City</t>
+          <t>Parikrama vs ASC And Center</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2.45</v>
+        <v>2.27</v>
       </c>
       <c r="D76" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="E76" t="n">
         <v>2.45</v>
       </c>
       <c r="F76" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="G76" t="n">
-        <v>1.92</v>
+        <v>2.18</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -2861,28 +2861,28 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Thame United FC vs Beaconsfield Town</t>
+          <t>Shatin vs R&amp;F Fc</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1.55</v>
+        <v>1.96</v>
       </c>
       <c r="D77" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="E77" t="n">
-        <v>4.25</v>
+        <v>3</v>
       </c>
       <c r="F77" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G77" t="n">
         <v>1.41</v>
-      </c>
-      <c r="G77" t="n">
-        <v>2.63</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -2893,28 +2893,28 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Needham Market vs Stamford</t>
+          <t>Hapoel Raanana vs KAFR Qasim</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1.35</v>
+        <v>1.91</v>
       </c>
       <c r="D78" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="E78" t="n">
-        <v>6.5</v>
+        <v>3.4</v>
       </c>
       <c r="F78" t="n">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="G78" t="n">
-        <v>2.27</v>
+        <v>1.87</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -2925,28 +2925,28 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Halesowen Town vs Rushall Olympic</t>
+          <t>Maccabi Bnei Raina vs Hapoel Kfar Shelem</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="D79" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="E79" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="F79" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="G79" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -2957,28 +2957,28 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Alvechurch vs Stourbridge</t>
+          <t>MS Ashdod vs Maccabi Herzliya</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1.84</v>
+        <v>1.47</v>
       </c>
       <c r="D80" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="E80" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="F80" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="G80" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -2989,28 +2989,28 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Real Bedford vs Leiston</t>
+          <t>Maccabi Yafo Kabilyo vs Hapoel Akko FC</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1.41</v>
+        <v>1.79</v>
       </c>
       <c r="D81" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="E81" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="F81" t="n">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="G81" t="n">
-        <v>2.63</v>
+        <v>2.06</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -3021,28 +3021,28 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Hitchin Town vs Leighton Town</t>
+          <t>Hapoel Afula vs Hapoel Ironi Rishon Lezion</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="D82" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="E82" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="F82" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="G82" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -3053,28 +3053,28 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Kettering Town vs Anstey Nomads</t>
+          <t>Bnei-Yehuda Tel-Aviv vs Maccabi Kiryat Gat Sports Club</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2.26</v>
+        <v>1.28</v>
       </c>
       <c r="D83" t="n">
-        <v>3.4</v>
+        <v>4.75</v>
       </c>
       <c r="E83" t="n">
-        <v>2.6</v>
+        <v>7.5</v>
       </c>
       <c r="F83" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="G83" t="n">
-        <v>2.03</v>
+        <v>2.37</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -3085,28 +3085,28 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Bishop's Stortford vs Bury Town</t>
+          <t>Kiryat Yam vs Hapoel Kfar-Saba</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3.2</v>
+        <v>1.71</v>
       </c>
       <c r="D84" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="E84" t="n">
-        <v>1.96</v>
+        <v>3.7</v>
       </c>
       <c r="F84" t="n">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="G84" t="n">
-        <v>1.99</v>
+        <v>2.58</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -3117,28 +3117,28 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Bromsgrove Sporting vs Leamington</t>
+          <t>Maccabi Ahi Nazareth FC vs Ironi Modiin</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1.53</v>
+        <v>2.23</v>
       </c>
       <c r="D85" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.75</v>
+        <v>2.73</v>
       </c>
       <c r="F85" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="G85" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -3149,28 +3149,28 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Banbury United vs Stratford Town</t>
+          <t>Hapoel Ihud Bnei Jatt vs Maccabi Nujeidat Ahmed</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1.86</v>
+        <v>3.2</v>
       </c>
       <c r="D86" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="E86" t="n">
-        <v>3.5</v>
+        <v>1.91</v>
       </c>
       <c r="F86" t="n">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="G86" t="n">
-        <v>1.81</v>
+        <v>2.09</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -3181,28 +3181,28 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Leverstock Green vs Ware</t>
+          <t>Hapoel Umm Al Fahm vs Hapoel Ironi Karmiel</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="D87" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="E87" t="n">
         <v>2.4</v>
       </c>
       <c r="F87" t="n">
-        <v>1.43</v>
+        <v>1.85</v>
       </c>
       <c r="G87" t="n">
-        <v>2.55</v>
+        <v>1.85</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -3213,28 +3213,28 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Huesca (W) vs Osasuna (K)</t>
+          <t>Maccabi Yavne vs Ironi Beit Shemesh</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="D88" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E88" t="n">
         <v>5</v>
       </c>
-      <c r="E88" t="n">
-        <v>1.25</v>
-      </c>
       <c r="F88" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="G88" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -3245,28 +3245,28 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SpVgg Unterhaching vs TSV Buchbach</t>
+          <t>Sderot FC vs Hapoel Azor</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="D89" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="E89" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="F89" t="n">
-        <v>1.35</v>
+        <v>2.01</v>
       </c>
       <c r="G89" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -3277,28 +3277,28 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>22:15</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Rio Ave U23 vs Penafiel U23</t>
+          <t>Kfar Saba 1928 vs Hapoel Marmorek</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1.76</v>
+        <v>2.02</v>
       </c>
       <c r="D90" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="E90" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="F90" t="n">
-        <v>1.68</v>
+        <v>2.12</v>
       </c>
       <c r="G90" t="n">
-        <v>2.01</v>
+        <v>1.62</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -3309,28 +3309,28 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Lesotho vs Fas</t>
+          <t>FC Kababir vs MK Tzofi Haifa</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>26</v>
+        <v>3.8</v>
       </c>
       <c r="D91" t="n">
-        <v>11</v>
+        <v>3.6</v>
       </c>
       <c r="E91" t="n">
-        <v>1.04</v>
+        <v>1.71</v>
       </c>
       <c r="F91" t="n">
-        <v>1.27</v>
+        <v>1.68</v>
       </c>
       <c r="G91" t="n">
-        <v>3.3</v>
+        <v>2.03</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -3341,28 +3341,28 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Gabon vs Nijer</t>
+          <t>Maccabi Ihud Bnei Avtin vs Hapoel Bnei Bi'ina</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="D92" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="E92" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F92" t="n">
-        <v>2.27</v>
+        <v>1.43</v>
       </c>
       <c r="G92" t="n">
-        <v>1.55</v>
+        <v>2.55</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -3378,23 +3378,23 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Gana vs Gambia</t>
+          <t>Hapoel Givat Olga vs Maccabi Ironi Kfar Yona</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1.45</v>
+        <v>2.7</v>
       </c>
       <c r="D93" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>2.15</v>
       </c>
       <c r="F93" t="n">
-        <v>2.06</v>
+        <v>1.55</v>
       </c>
       <c r="G93" t="n">
-        <v>1.66</v>
+        <v>2.27</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -3405,28 +3405,28 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Somalia vs Fildişi Sahili</t>
+          <t>Beitar Kfar Saba Shlomi vs Beitar Tel Aviv Holon</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>21</v>
+        <v>2.25</v>
       </c>
       <c r="D94" t="n">
-        <v>9.5</v>
+        <v>3.4</v>
       </c>
       <c r="E94" t="n">
-        <v>1.07</v>
+        <v>2.6</v>
       </c>
       <c r="F94" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="G94" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -3437,28 +3437,28 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>28 dk içinde</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Comoros vs Namibya</t>
+          <t>Ironi Beit Dagan vs Hapoel Hod Hasharon Irony</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="D95" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="E95" t="n">
-        <v>4.15</v>
+        <v>2.8</v>
       </c>
       <c r="F95" t="n">
-        <v>1.3</v>
+        <v>1.72</v>
       </c>
       <c r="G95" t="n">
-        <v>1.45</v>
+        <v>1.96</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -3469,28 +3469,28 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Kongo vs Kamerun</t>
+          <t>Ihud Tzeirey Abu Gosh vs Maccabi Beer Sheva</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>5</v>
+        <v>1.57</v>
       </c>
       <c r="D96" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="E96" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="F96" t="n">
-        <v>2.18</v>
+        <v>1.4</v>
       </c>
       <c r="G96" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -3501,28 +3501,28 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Madagaskar vs Tanzanya</t>
+          <t>AS Holon Mor vs Bnei Jaffa Ortodoxim</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>2.33</v>
+        <v>2.73</v>
       </c>
       <c r="D97" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="E97" t="n">
-        <v>3.05</v>
+        <v>2.16</v>
       </c>
       <c r="F97" t="n">
-        <v>2.18</v>
+        <v>1.7</v>
       </c>
       <c r="G97" t="n">
-        <v>1.45</v>
+        <v>2.01</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -3533,28 +3533,28 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Gine Bissau vs Nijerya</t>
+          <t>FH Hafnarfjordur U19 vs Keflavik U19</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>6</v>
+        <v>2.2</v>
       </c>
       <c r="D98" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="E98" t="n">
-        <v>1.51</v>
+        <v>2.35</v>
       </c>
       <c r="F98" t="n">
-        <v>2.27</v>
+        <v>1.16</v>
       </c>
       <c r="G98" t="n">
-        <v>1.55</v>
+        <v>4</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -3565,28 +3565,28 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Etiyopya vs Senegal</t>
+          <t>Al-Gharafa vs Al Mesaimeer SC</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>9</v>
+        <v>1.72</v>
       </c>
       <c r="D99" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="E99" t="n">
-        <v>1.32</v>
+        <v>3.7</v>
       </c>
       <c r="F99" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="G99" t="n">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -3597,28 +3597,28 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Mozambik vs Sudan</t>
+          <t>Al-Shamal vs Muaither SC</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="D100" t="n">
-        <v>3.2</v>
+        <v>4.15</v>
       </c>
       <c r="E100" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="F100" t="n">
-        <v>2.55</v>
+        <v>1.51</v>
       </c>
       <c r="G100" t="n">
-        <v>1.43</v>
+        <v>2.35</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -3629,28 +3629,28 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Burundi vs Cezayir</t>
+          <t>Qatar SC Doha vs Al Bidda SC</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>10</v>
+        <v>1.62</v>
       </c>
       <c r="D101" t="n">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="E101" t="n">
-        <v>1.25</v>
+        <v>4</v>
       </c>
       <c r="F101" t="n">
-        <v>1.79</v>
+        <v>1.53</v>
       </c>
       <c r="G101" t="n">
-        <v>1.91</v>
+        <v>2.33</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -3661,28 +3661,28 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Zambiya vs Togo</t>
+          <t>Mombasa United vs Kariobangi Sharks</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1.98</v>
+        <v>2.63</v>
       </c>
       <c r="D102" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="E102" t="n">
-        <v>3.7</v>
+        <v>2.55</v>
       </c>
       <c r="F102" t="n">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="G102" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -3693,28 +3693,28 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Uganda vs Libya</t>
+          <t>Envigado vs Orsomarso</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1.97</v>
+        <v>1.64</v>
       </c>
       <c r="D103" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="E103" t="n">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="F103" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="G103" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -3725,28 +3725,28 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Günay Sudan vs Mısır</t>
+          <t>British Virgin Islands vs Montserrat</t>
         </is>
       </c>
       <c r="C104" t="n">
         <v>13.25</v>
       </c>
       <c r="D104" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E104" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="F104" t="n">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="G104" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -3757,28 +3757,28 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Yeşil Burun Adaları vs Ruanda</t>
+          <t>US Virgin Islands vs Saint Martin</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1.43</v>
+        <v>8.5</v>
       </c>
       <c r="D105" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="E105" t="n">
-        <v>7</v>
+        <v>1.25</v>
       </c>
       <c r="F105" t="n">
-        <v>2.2</v>
+        <v>1.41</v>
       </c>
       <c r="G105" t="n">
-        <v>1.58</v>
+        <v>2.68</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -3789,28 +3789,28 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Liberya vs Mali</t>
+          <t>Mighty Wanderers (W) vs Ascent Academy (W)</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="D106" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="E106" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="F106" t="n">
-        <v>2.16</v>
+        <v>1.79</v>
       </c>
       <c r="G106" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -3821,28 +3821,28 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Benin vs Moritanya</t>
+          <t>Rumphi Sisters (W) vs Ntopwa FC (W)</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>2.45</v>
+        <v>5</v>
       </c>
       <c r="D107" t="n">
-        <v>2.9</v>
+        <v>4.25</v>
       </c>
       <c r="E107" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="F107" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G107" t="n">
         <v>2.6</v>
-      </c>
-      <c r="G107" t="n">
-        <v>1.41</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -3853,28 +3853,28 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Tunisia U23 vs Benin U23</t>
+          <t>Touchtronics FC U20 vs Terengganu U20</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1.32</v>
+        <v>5</v>
       </c>
       <c r="D108" t="n">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="E108" t="n">
-        <v>8</v>
+        <v>1.51</v>
       </c>
       <c r="F108" t="n">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="G108" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -3885,28 +3885,28 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Deportivo Muniz vs El Porvenir</t>
+          <t>Mgarr United (K) vs Swieqi United (W)</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>2.7</v>
+        <v>1.38</v>
       </c>
       <c r="D109" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="E109" t="n">
-        <v>2.35</v>
+        <v>5.5</v>
       </c>
       <c r="F109" t="n">
-        <v>2.45</v>
+        <v>1.5</v>
       </c>
       <c r="G109" t="n">
-        <v>1.41</v>
+        <v>2.25</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -3917,28 +3917,28 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Atletico Rafaela Reserves vs Ferro Carril Oeste Reserves</t>
+          <t>Pharco vs El Terasanah</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1.98</v>
+        <v>2.31</v>
       </c>
       <c r="D110" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="E110" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="F110" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="G110" t="n">
-        <v>1.76</v>
+        <v>1.35</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -3949,28 +3949,28 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>San Lorenzo Reserves vs CA Aldosivi Reserves</t>
+          <t>El Mansoura vs FC Masar</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1.86</v>
+        <v>3.4</v>
       </c>
       <c r="D111" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="E111" t="n">
-        <v>3.6</v>
+        <v>2.06</v>
       </c>
       <c r="F111" t="n">
-        <v>2.08</v>
+        <v>2.45</v>
       </c>
       <c r="G111" t="n">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -3981,28 +3981,28 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Banfield Reserves vs Atletico Tucuman Reserves</t>
+          <t>La Viena FC vs Al Nasr Cairo</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="D112" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="E112" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F112" t="n">
         <v>2.73</v>
       </c>
-      <c r="F112" t="n">
-        <v>2.16</v>
-      </c>
       <c r="G112" t="n">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -4013,28 +4013,28 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Estudiantes La Plata Reserves vs Defensa Y Justicia Reserves</t>
+          <t>El Sekka El Hadid SC vs El Entag El Harby</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>2.4</v>
+        <v>2.68</v>
       </c>
       <c r="D113" t="n">
-        <v>3.15</v>
+        <v>2.77</v>
       </c>
       <c r="E113" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="F113" t="n">
-        <v>2.01</v>
+        <v>2.77</v>
       </c>
       <c r="G113" t="n">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -4045,28 +4045,28 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Tigre Reserves vs Gimnasia La Plata Reserves</t>
+          <t>Sila SC vs Asyut Cement Petroleum</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>2.54</v>
+        <v>1.68</v>
       </c>
       <c r="D114" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="E114" t="n">
-        <v>2.59</v>
+        <v>4.15</v>
       </c>
       <c r="F114" t="n">
-        <v>2.4</v>
+        <v>1.76</v>
       </c>
       <c r="G114" t="n">
-        <v>1.47</v>
+        <v>1.91</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -4077,28 +4077,28 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Flandria U20 vs CA San Miguel U20</t>
+          <t>Gjelleraasen U19 vs Grorud U19</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1.76</v>
+        <v>2.4</v>
       </c>
       <c r="D115" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="E115" t="n">
-        <v>3.7</v>
+        <v>2.05</v>
       </c>
       <c r="F115" t="n">
-        <v>1.81</v>
+        <v>1.16</v>
       </c>
       <c r="G115" t="n">
-        <v>1.86</v>
+        <v>4</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -4109,28 +4109,28 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Uribelarrea FC vs Defensores de Glew</t>
+          <t>Ullensaker/Kisa U19 vs Haslum IL U19</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>2.9</v>
+        <v>31</v>
       </c>
       <c r="D116" t="n">
-        <v>2.9</v>
+        <v>13.25</v>
       </c>
       <c r="E116" t="n">
-        <v>2.25</v>
+        <v>1.01</v>
       </c>
       <c r="F116" t="n">
-        <v>2.4</v>
+        <v>1.16</v>
       </c>
       <c r="G116" t="n">
-        <v>1.47</v>
+        <v>4</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -4141,28 +4141,28 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>58 dk içinde</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Tayland vs Vietnam</t>
+          <t>Sarpsborg 08 U19 vs Klofta U19</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>2.37</v>
+        <v>1.33</v>
       </c>
       <c r="D117" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="E117" t="n">
-        <v>2.73</v>
+        <v>5</v>
       </c>
       <c r="F117" t="n">
-        <v>2.08</v>
+        <v>1.08</v>
       </c>
       <c r="G117" t="n">
-        <v>1.66</v>
+        <v>6</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -4173,28 +4173,28 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Suudi Arabistan vs Irak</t>
+          <t>Nordstrand U19 vs Follo U19</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="D118" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="E118" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="F118" t="n">
-        <v>2.4</v>
+        <v>1.12</v>
       </c>
       <c r="G118" t="n">
-        <v>1.47</v>
+        <v>5</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -4205,28 +4205,28 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Oman Sultanlığı vs Kuveyt</t>
+          <t>Skedsmo U19 vs Skeid U19</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="D119" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="E119" t="n">
-        <v>4.5</v>
+        <v>2.45</v>
       </c>
       <c r="F119" t="n">
-        <v>2</v>
+        <v>1.14</v>
       </c>
       <c r="G119" t="n">
-        <v>1.72</v>
+        <v>4.75</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -4237,28 +4237,28 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SV Kuchl vs SV Wals-Grünau</t>
+          <t>Baerum SK Sandvika vs Lillestrom</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>2.3</v>
+        <v>15</v>
       </c>
       <c r="D120" t="n">
-        <v>3.7</v>
+        <v>8</v>
       </c>
       <c r="E120" t="n">
-        <v>2.45</v>
+        <v>1.11</v>
       </c>
       <c r="F120" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="G120" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -4269,28 +4269,28 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Fujairah FC vs Al Jazira Hamra</t>
+          <t>Madla vs Viking</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1.38</v>
+        <v>17</v>
       </c>
       <c r="D121" t="n">
-        <v>4.33</v>
+        <v>9</v>
       </c>
       <c r="E121" t="n">
-        <v>6</v>
+        <v>1.09</v>
       </c>
       <c r="F121" t="n">
-        <v>1.51</v>
+        <v>1.2</v>
       </c>
       <c r="G121" t="n">
-        <v>2.31</v>
+        <v>3.8</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -4301,28 +4301,28 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Fc Palm City vs Dibba Al-Hisn</t>
+          <t>Al Nasr SC vs Al-Samail</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>2.54</v>
+        <v>1.78</v>
       </c>
       <c r="D122" t="n">
         <v>3.5</v>
       </c>
       <c r="E122" t="n">
-        <v>2.27</v>
+        <v>3.6</v>
       </c>
       <c r="F122" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="G122" t="n">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -4333,28 +4333,28 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Universitario De Vinto vs Guabira Santa Cruz</t>
+          <t>Bahla Club vs Fanja</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>2.05</v>
+        <v>1.28</v>
       </c>
       <c r="D123" t="n">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
       <c r="E123" t="n">
-        <v>2.8</v>
+        <v>7.5</v>
       </c>
       <c r="F123" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="G123" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -4365,28 +4365,28 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>CA Juventus SP U20 vs GE Prudente U20</t>
+          <t>Al-Musannah SC vs Ibri Club</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="D124" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="E124" t="n">
-        <v>4.15</v>
+        <v>3.2</v>
       </c>
       <c r="F124" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="G124" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -4397,28 +4397,28 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>FC Slovan Rosice vs Boskovice</t>
+          <t>San Francisco II vs Cd Universitario Reserves</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>2.77</v>
+        <v>1.8</v>
       </c>
       <c r="D125" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="E125" t="n">
-        <v>2.02</v>
+        <v>3.2</v>
       </c>
       <c r="F125" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="G125" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -4429,28 +4429,28 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Odense Q (K) vs AGF Aarhus (K)</t>
+          <t>CD Plaza Amador (W) vs UMECIT (W)</t>
         </is>
       </c>
       <c r="C126" t="n">
+        <v>6</v>
+      </c>
+      <c r="D126" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="G126" t="n">
         <v>2.6</v>
-      </c>
-      <c r="D126" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="E126" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="F126" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="G126" t="n">
-        <v>1.91</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -4461,28 +4461,28 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok vs FK Suduva Marijampole</t>
+          <t>Sporting Cristal Lima vs Asociacion Deportiva Tarma</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
       <c r="D127" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="E127" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="F127" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="G127" t="n">
-        <v>2.23</v>
+        <v>2.01</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -4493,28 +4493,28 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>57 dk içinde</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Bulgaristan U19 vs Romanya U19</t>
+          <t>Przemsza Siewierz vs Rozwoj Katowice</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="D128" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="E128" t="n">
-        <v>2.11</v>
+        <v>3.8</v>
       </c>
       <c r="F128" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="G128" t="n">
-        <v>1.85</v>
+        <v>3.2</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -4525,28 +4525,28 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>İngiltere U19 vs Norveç U19</t>
+          <t>MKS Podlasie Biala Podlaska vs Juventa Starachowice</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1.7</v>
+        <v>2.11</v>
       </c>
       <c r="D129" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="E129" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="F129" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="G129" t="n">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -4557,28 +4557,28 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Sırbistan U19 vs Macaristan U19</t>
+          <t>Al Yarmouk vs Amman FC</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1.99</v>
+        <v>2.77</v>
       </c>
       <c r="D130" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="E130" t="n">
-        <v>3</v>
+        <v>2.27</v>
       </c>
       <c r="F130" t="n">
-        <v>1.66</v>
+        <v>2.12</v>
       </c>
       <c r="G130" t="n">
-        <v>2.06</v>
+        <v>1.62</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -4589,28 +4589,28 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Almanya vs Italy U20</t>
+          <t>Jerash SC vs AL Ahli Amman</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="D131" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="E131" t="n">
-        <v>4.33</v>
+        <v>2.55</v>
       </c>
       <c r="F131" t="n">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="G131" t="n">
-        <v>2.05</v>
+        <v>1.55</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -4626,889 +4626,25 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Polonya U20 vs Çek Cumhuriyeti U20</t>
+          <t>Ittihad AL Ramtha vs Sama Al Sarhan</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>2.16</v>
+        <v>2.27</v>
       </c>
       <c r="D132" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="E132" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="F132" t="n">
-        <v>1.81</v>
+        <v>2.25</v>
       </c>
       <c r="G132" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="H132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Rusya vs Iran</t>
-        </is>
-      </c>
-      <c r="C133" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="D133" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="E133" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="F133" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="G133" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Flora Tallinn U19 vs Tallinna FC Ajax U19</t>
-        </is>
-      </c>
-      <c r="C134" t="n">
-        <v>3</v>
-      </c>
-      <c r="D134" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E134" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="F134" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="G134" t="n">
-        <v>7</v>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Nomme United U19 vs Johvi FC Phoenix U19</t>
-        </is>
-      </c>
-      <c r="C135" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="D135" t="n">
-        <v>5</v>
-      </c>
-      <c r="E135" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="F135" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="G135" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Harju JK Laagri U19 vs JK Trans Narva U19</t>
-        </is>
-      </c>
-      <c r="C136" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="D136" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="E136" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="F136" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="G136" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>21:45</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Cardiff Metropolitan University vs Haverfordwest County</t>
-        </is>
-      </c>
-      <c r="C137" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="D137" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E137" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="F137" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="G137" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Aizawl vs Chanmari</t>
-        </is>
-      </c>
-      <c r="C138" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="D138" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="E138" t="n">
-        <v>4</v>
-      </c>
-      <c r="F138" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G138" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Mes Rafsanjan vs Besat Kermanshah</t>
-        </is>
-      </c>
-      <c r="C139" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="D139" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="E139" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="F139" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="G139" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>St. Mary's FC vs Midleton FC</t>
-        </is>
-      </c>
-      <c r="C140" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D140" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E140" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="F140" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="G140" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>21:45</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Forfar Athletic vs Formartine United FC</t>
-        </is>
-      </c>
-      <c r="C141" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="D141" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E141" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="F141" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="G141" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Jitex Molndal (W) vs Vittsjo GIK (K)</t>
-        </is>
-      </c>
-      <c r="C142" t="n">
-        <v>7</v>
-      </c>
-      <c r="D142" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="E142" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="F142" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="G142" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Linkopings FC (W) vs IFK Norrkoping (K)</t>
-        </is>
-      </c>
-      <c r="C143" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D143" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="E143" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="F143" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="G143" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Al-Khor vs Umm Salal</t>
-        </is>
-      </c>
-      <c r="C144" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="D144" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E144" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="F144" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G144" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Al Markhiya vs Al-Ahli Doha</t>
-        </is>
-      </c>
-      <c r="C145" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="D145" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E145" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="F145" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="G145" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Al Waab Sports Club vs Lusail City</t>
-        </is>
-      </c>
-      <c r="C146" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D146" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E146" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="F146" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="G146" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Deportivo Pereira vs Independiente Santa Fe</t>
-        </is>
-      </c>
-      <c r="C147" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D147" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="E147" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="F147" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="G147" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Dimelo Jara vs Los Embajadores</t>
-        </is>
-      </c>
-      <c r="C148" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="D148" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E148" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="F148" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G148" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>British Virgin Islands vs Turks and Caicos Islands</t>
-        </is>
-      </c>
-      <c r="C149" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="D149" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="E149" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="F149" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="G149" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>21:15</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>FK Union Carl Berner vs KFUM 2</t>
-        </is>
-      </c>
-      <c r="C150" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="D150" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E150" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="F150" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="G150" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Toten U19 vs Storhamar Fotball U19</t>
-        </is>
-      </c>
-      <c r="C151" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="D151" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="E151" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="F151" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="G151" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>29 de Septiembre vs 24 de Setiembre</t>
-        </is>
-      </c>
-      <c r="C152" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="D152" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="E152" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="F152" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G152" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Sportivo Trinidense (K) vs 2 de Mayo (K)</t>
-        </is>
-      </c>
-      <c r="C153" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="D153" t="n">
-        <v>6</v>
-      </c>
-      <c r="E153" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F153" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="G153" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Cerro Porteno (K) vs Libertad (K)</t>
-        </is>
-      </c>
-      <c r="C154" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D154" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="E154" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="F154" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="G154" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Vozdovac vs Napredak Krusevac</t>
-        </is>
-      </c>
-      <c r="C155" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="D155" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="E155" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="F155" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="G155" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Inter Bratislava vs Podbrezova</t>
-        </is>
-      </c>
-      <c r="C156" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D156" t="n">
-        <v>4</v>
-      </c>
-      <c r="E156" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="F156" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="G156" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>NK Podvinci vs NK Ljutomer</t>
-        </is>
-      </c>
-      <c r="C157" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="D157" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="E157" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F157" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="G157" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Liverpool Montevideo Reserves vs Montevideo Wanderers Reserves</t>
-        </is>
-      </c>
-      <c r="C158" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="D158" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="E158" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="F158" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="G158" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Boston River Reserves vs Albion Reserves</t>
-        </is>
-      </c>
-      <c r="C159" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="D159" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="E159" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F159" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="G159" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="H159" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/bugun_oranlar.xlsx
+++ b/bugun_oranlar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H132"/>
+  <dimension ref="A1:H201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,23 +466,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Yunanistan vs Hollanda</t>
+          <t>Belçika vs Türkiye</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3.2</v>
+        <v>1.57</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="E2" t="n">
-        <v>2.06</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>1.68</v>
+        <v>1.43</v>
       </c>
       <c r="G2" t="n">
-        <v>2.12</v>
+        <v>2.63</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -498,23 +498,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Almanya vs Sırbistan</t>
+          <t>Fransa vs İtalya</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="D3" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="G3" t="n">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -530,23 +530,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Galler vs Norveç</t>
+          <t>Bosna-Hersek vs İsveç</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>2.63</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="E4" t="n">
-        <v>1.45</v>
+        <v>2.4</v>
       </c>
       <c r="F4" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -562,23 +562,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Danimarka vs Portekiz</t>
+          <t>Polonya vs Romanya</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="D5" t="n">
-        <v>3.7</v>
+        <v>4.15</v>
       </c>
       <c r="E5" t="n">
-        <v>2.01</v>
+        <v>4.75</v>
       </c>
       <c r="F5" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="G5" t="n">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -594,23 +594,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>İsrail vs Kosova</t>
+          <t>Ukrayna vs Kuzey İrlanda</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3.05</v>
+        <v>1.99</v>
       </c>
       <c r="D6" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="E6" t="n">
-        <v>2.23</v>
+        <v>3.8</v>
       </c>
       <c r="F6" t="n">
-        <v>1.91</v>
+        <v>2.39</v>
       </c>
       <c r="G6" t="n">
-        <v>1.84</v>
+        <v>1.51</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -626,23 +626,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>İrlanda vs Avusturya</t>
+          <t>Macaristan vs Gürcistan</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3.28</v>
+        <v>2.27</v>
       </c>
       <c r="D7" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="E7" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="F7" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G7" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -658,23 +658,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Azerbaycan vs Lihtenştayn</t>
+          <t>Letonya vs Karadağ</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.13</v>
+        <v>4.5</v>
       </c>
       <c r="D8" t="n">
-        <v>7.5</v>
+        <v>3.6</v>
       </c>
       <c r="E8" t="n">
-        <v>21</v>
+        <v>1.75</v>
       </c>
       <c r="F8" t="n">
-        <v>1.64</v>
+        <v>2.05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.16</v>
+        <v>1.71</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -685,28 +685,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Malta vs Cebelitarık</t>
+          <t>Kıbrıs vs Ermenistan</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.27</v>
+        <v>2.22</v>
       </c>
       <c r="D9" t="n">
-        <v>4.75</v>
+        <v>3.3</v>
       </c>
       <c r="E9" t="n">
-        <v>12</v>
+        <v>3.2</v>
       </c>
       <c r="F9" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G9" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -717,28 +717,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>60 dk içinde</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Yunanistan U21 vs Letonya U21</t>
+          <t>Kazakistan vs Moldova</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.07</v>
+        <v>1.93</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="E10" t="n">
-        <v>21</v>
+        <v>4.2</v>
       </c>
       <c r="F10" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="G10" t="n">
-        <v>3.05</v>
+        <v>1.47</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -749,28 +749,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>North Macedonia U21 vs Karadağ U21</t>
+          <t>Faroe Adaları vs Slovakya</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.73</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="E11" t="n">
-        <v>2.34</v>
+        <v>1.53</v>
       </c>
       <c r="F11" t="n">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="G11" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -781,28 +781,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Armenia U21 vs İtalya U21</t>
+          <t>Ukrayna U21 vs Hırvatistan U21</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21</v>
+        <v>3.5</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>3.5</v>
       </c>
       <c r="E12" t="n">
-        <v>1.06</v>
+        <v>1.93</v>
       </c>
       <c r="F12" t="n">
-        <v>1.22</v>
+        <v>1.81</v>
       </c>
       <c r="G12" t="n">
-        <v>3.6</v>
+        <v>1.87</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -813,28 +813,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Macaristan U21 vs Litvanya U21</t>
+          <t>Slovenya U21 vs Hollanda U21</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.45</v>
+        <v>7.5</v>
       </c>
       <c r="D13" t="n">
-        <v>4.15</v>
+        <v>4.75</v>
       </c>
       <c r="E13" t="n">
-        <v>6</v>
+        <v>1.32</v>
       </c>
       <c r="F13" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="G13" t="n">
-        <v>1.93</v>
+        <v>2.27</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -845,28 +845,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kuzey İrlanda U21 vs Gürcistan U21</t>
+          <t>Austria U21 vs Danimarka U21</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.9</v>
+        <v>2.63</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7</v>
+        <v>2.37</v>
       </c>
       <c r="F14" t="n">
-        <v>2.04</v>
+        <v>1.76</v>
       </c>
       <c r="G14" t="n">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -877,28 +877,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Koge (K) vs Servette Chenois (K)</t>
+          <t>Andorra U21 vs Moldova U21</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1.32</v>
+        <v>2.18</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="E15" t="n">
-        <v>7.5</v>
+        <v>3.1</v>
       </c>
       <c r="F15" t="n">
-        <v>1.55</v>
+        <v>2.16</v>
       </c>
       <c r="G15" t="n">
-        <v>2.27</v>
+        <v>1.6</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -909,28 +909,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Austria Vienna (K) vs Inter Milano (K)</t>
+          <t>İngiltere U21 vs Slovakia U21</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3.8</v>
+        <v>1.18</v>
       </c>
       <c r="D16" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>1.78</v>
+        <v>11</v>
       </c>
       <c r="F16" t="n">
-        <v>1.78</v>
+        <v>1.41</v>
       </c>
       <c r="G16" t="n">
-        <v>1.93</v>
+        <v>2.63</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -941,28 +941,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Paris Saint Germain (K) vs Oud-Heverlee Leuven (K)</t>
+          <t>Eldense vs Real Oviedo</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.18</v>
+        <v>2.45</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>11</v>
+        <v>2.8</v>
       </c>
       <c r="F17" t="n">
-        <v>1.41</v>
+        <v>2.45</v>
       </c>
       <c r="G17" t="n">
-        <v>2.68</v>
+        <v>1.47</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -978,23 +978,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Manchester City (K) vs Real Madrid (K)</t>
+          <t>Puertos de Las Palmas U19 vs Arucas Cf Under 19</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.68</v>
+        <v>1.18</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>9.5</v>
       </c>
       <c r="F18" t="n">
-        <v>1.51</v>
+        <v>1.85</v>
       </c>
       <c r="G18" t="n">
-        <v>2.36</v>
+        <v>1.79</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1005,28 +1005,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>22:15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>UD Santa Marta vs Salamanca CF UDS</t>
+          <t>Real Madrid B vs Atletico Madrid B</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3.1</v>
+        <v>1.76</v>
       </c>
       <c r="D19" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="E19" t="n">
-        <v>2.12</v>
+        <v>3.6</v>
       </c>
       <c r="F19" t="n">
-        <v>2.12</v>
+        <v>1.6</v>
       </c>
       <c r="G19" t="n">
-        <v>1.62</v>
+        <v>2.16</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1037,28 +1037,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bastia vs Orléans</t>
+          <t>Real Aviles CF vs Lugo</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="D20" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="E20" t="n">
         <v>2.9</v>
       </c>
       <c r="F20" t="n">
-        <v>2.16</v>
+        <v>1.94</v>
       </c>
       <c r="G20" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1069,28 +1069,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Gine vs Kenya</t>
+          <t>Real Union de Tenerife Santa Cruz vs CD Laguna SAD</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="D21" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="E21" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="F21" t="n">
-        <v>2.45</v>
+        <v>1.72</v>
       </c>
       <c r="G21" t="n">
-        <v>1.47</v>
+        <v>1.99</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1101,28 +1101,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>30 dk içinde</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Barracas Central Reserves vs Gimnasia Mendoza Reserves</t>
+          <t>Vis Pesaro U19 vs ASD Torres Calcio U19</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2.7</v>
+        <v>1.83</v>
       </c>
       <c r="D22" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="E22" t="n">
-        <v>2.36</v>
+        <v>3.1</v>
       </c>
       <c r="F22" t="n">
-        <v>2.16</v>
+        <v>1.51</v>
       </c>
       <c r="G22" t="n">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1133,28 +1133,28 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>San Martin de San Juan Reserves vs Lanus Reserves</t>
+          <t>Stade Briochin vs FC Lorient 2</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5.5</v>
+        <v>1.72</v>
       </c>
       <c r="D23" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="E23" t="n">
-        <v>1.41</v>
+        <v>4</v>
       </c>
       <c r="F23" t="n">
-        <v>1.47</v>
+        <v>1.81</v>
       </c>
       <c r="G23" t="n">
-        <v>2.31</v>
+        <v>1.87</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1170,23 +1170,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Colon Reserves vs Deportivo Riestra Reserves</t>
+          <t>FC Chauray vs Avranches</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>2.73</v>
       </c>
       <c r="D24" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="E24" t="n">
-        <v>2.37</v>
+        <v>2.23</v>
       </c>
       <c r="F24" t="n">
-        <v>2.27</v>
+        <v>1.81</v>
       </c>
       <c r="G24" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1197,28 +1197,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ca Independiente Reserves vs Boca Juniors Reserves</t>
+          <t>Borussia Monchengladbach II vs VFL Bochum II</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3.1</v>
+        <v>1.43</v>
       </c>
       <c r="D25" t="n">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="E25" t="n">
-        <v>2.12</v>
+        <v>5</v>
       </c>
       <c r="F25" t="n">
-        <v>2.15</v>
+        <v>1.45</v>
       </c>
       <c r="G25" t="n">
-        <v>1.6</v>
+        <v>2.58</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1229,28 +1229,28 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Velez Sarsfield Reserves vs Argentinos Juniors Reserves</t>
+          <t>SV Stuttgarter Kickers vs Kickers Offenbach</t>
         </is>
       </c>
       <c r="C26" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F26" t="n">
         <v>1.55</v>
       </c>
-      <c r="D26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E26" t="n">
-        <v>5</v>
-      </c>
-      <c r="F26" t="n">
-        <v>2</v>
-      </c>
       <c r="G26" t="n">
-        <v>1.71</v>
+        <v>2.27</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1261,28 +1261,28 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ca Talleres De Cordoba Reserves vs Godoy Cruz Reserves</t>
+          <t>Bayer Leverkusen (K) vs Werder Bremen (K)</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="D27" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="E27" t="n">
         <v>3.8</v>
       </c>
       <c r="F27" t="n">
-        <v>1.72</v>
+        <v>1.51</v>
       </c>
       <c r="G27" t="n">
-        <v>1.96</v>
+        <v>2.31</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1293,28 +1293,28 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Defensores de Cambaceres Reserves vs Sacachispas Reserves</t>
+          <t>Helmond Sport vs Heracles Almelo</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1.71</v>
+        <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="E28" t="n">
-        <v>4</v>
+        <v>1.47</v>
       </c>
       <c r="F28" t="n">
-        <v>1.83</v>
+        <v>1.43</v>
       </c>
       <c r="G28" t="n">
-        <v>1.86</v>
+        <v>2.58</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1325,28 +1325,28 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JJ Urquiza Reserves vs CA Atlas Reserves</t>
+          <t>Racing Club (K) vs CA Belgrano (K)</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="D29" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="E29" t="n">
         <v>3.8</v>
       </c>
       <c r="F29" t="n">
-        <v>1.6</v>
+        <v>2.36</v>
       </c>
       <c r="G29" t="n">
-        <v>2.14</v>
+        <v>1.51</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1357,28 +1357,28 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Villa San Carlos Reserves vs UAI Urquiza Reserves</t>
+          <t>Ferro Carril Oeste (K) vs Union Santa Fe (K)</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2.4</v>
+        <v>1.35</v>
       </c>
       <c r="D30" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="E30" t="n">
-        <v>2.4</v>
+        <v>7</v>
       </c>
       <c r="F30" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="G30" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1389,28 +1389,28 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Deportivo Camioneros Reserves vs Arsenal De Sarandi Reserves</t>
+          <t>San Lorenzo (K) vs Huracan (K)</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2.8</v>
+        <v>1.32</v>
       </c>
       <c r="D31" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="E31" t="n">
-        <v>2.2</v>
+        <v>8.5</v>
       </c>
       <c r="F31" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="G31" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1421,28 +1421,28 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Club Comunicaciones Reserves vs Deportivo Laferrere Reserves</t>
+          <t>Gloggnitz vs FCM Traiskirchen</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="E32" t="n">
-        <v>5.5</v>
+        <v>1.72</v>
       </c>
       <c r="F32" t="n">
-        <v>1.71</v>
+        <v>1.28</v>
       </c>
       <c r="G32" t="n">
-        <v>1.91</v>
+        <v>3.3</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1453,28 +1453,28 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Sportivo Italiano Reserves vs Excursionistas Reserves</t>
+          <t>Favoritner AC vs Marchfeld Donauauen</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>3.28</v>
+        <v>4.25</v>
       </c>
       <c r="E33" t="n">
-        <v>2.03</v>
+        <v>1.47</v>
       </c>
       <c r="F33" t="n">
-        <v>1.87</v>
+        <v>1.47</v>
       </c>
       <c r="G33" t="n">
-        <v>1.81</v>
+        <v>2.4</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1485,28 +1485,28 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Argentino Quilmes Reserves vs Deportivo Armenio Reserves</t>
+          <t>Oberwart vs SV Horn</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2.12</v>
+        <v>1.7</v>
       </c>
       <c r="D34" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="E34" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="F34" t="n">
-        <v>1.94</v>
+        <v>1.51</v>
       </c>
       <c r="G34" t="n">
-        <v>1.68</v>
+        <v>2.39</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1517,28 +1517,28 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CA San Miguel Reserves vs Temperley Reserves</t>
+          <t>Kremser SC vs Wiener Sport-Club</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="D35" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="E35" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="F35" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="G35" t="n">
-        <v>1.72</v>
+        <v>2.22</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1549,28 +1549,28 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Club Atletico Mitre Reserves vs Talleres Remedios Reserves</t>
+          <t>Gleisdorf vs Su Tillmitsch</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1.87</v>
+        <v>2.7</v>
       </c>
       <c r="D36" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="E36" t="n">
-        <v>3.5</v>
+        <v>2.14</v>
       </c>
       <c r="F36" t="n">
-        <v>2.03</v>
+        <v>1.53</v>
       </c>
       <c r="G36" t="n">
-        <v>1.68</v>
+        <v>2.27</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1581,28 +1581,28 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros Reserves vs Nueva Chicago Reserves</t>
+          <t>Atus Velden vs SK Treibach</t>
         </is>
       </c>
       <c r="C37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D37" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G37" t="n">
         <v>2.4</v>
-      </c>
-      <c r="D37" t="n">
-        <v>3</v>
-      </c>
-      <c r="E37" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="F37" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="G37" t="n">
-        <v>1.55</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1613,28 +1613,28 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Almirante Brown Reserves vs Chacarita Juniors Reserves</t>
+          <t>TUS Bad Waltersdorf vs FC Hohenhaus Tenne Schladming</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4.33</v>
+        <v>1.96</v>
       </c>
       <c r="D38" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="E38" t="n">
-        <v>1.68</v>
+        <v>3</v>
       </c>
       <c r="F38" t="n">
-        <v>2.07</v>
+        <v>1.51</v>
       </c>
       <c r="G38" t="n">
-        <v>1.66</v>
+        <v>2.31</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1650,23 +1650,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ferrocarril Midland Reserves vs CA Agropecuario Reserves</t>
+          <t>SC Stadtwerke Bruck/Mur vs SV Wildon</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="D39" t="n">
         <v>3.8</v>
       </c>
       <c r="E39" t="n">
-        <v>1.74</v>
+        <v>1.97</v>
       </c>
       <c r="F39" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="G39" t="n">
-        <v>2.58</v>
+        <v>3</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -1682,23 +1682,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>All Boys Reserves vs Almagro Reserves</t>
+          <t>SV Lebring vs UFC Fehring</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="D40" t="n">
-        <v>3.3</v>
+        <v>4.25</v>
       </c>
       <c r="E40" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="F40" t="n">
-        <v>2.14</v>
+        <v>1.33</v>
       </c>
       <c r="G40" t="n">
-        <v>1.64</v>
+        <v>3</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -1709,28 +1709,28 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CA Colegiales Reserves vs Tristan Suarez Reserves</t>
+          <t>USV Gnas vs Furstenfeld</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>10</v>
+        <v>1.76</v>
       </c>
       <c r="D41" t="n">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="E41" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="F41" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="G41" t="n">
-        <v>2.73</v>
+        <v>2.45</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -1741,28 +1741,28 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Los Andes Reserves vs Deportivo Moron Reserves</t>
+          <t>SV Gerasdorf Stammersdorf vs FC 1980 Wien</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="D42" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="E42" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="F42" t="n">
-        <v>1.95</v>
+        <v>1.51</v>
       </c>
       <c r="G42" t="n">
-        <v>1.75</v>
+        <v>2.36</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -1773,28 +1773,28 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Malezya vs Singapur</t>
+          <t>SC Red Star Penzing vs TWL Elektra</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1.4</v>
+        <v>1.81</v>
       </c>
       <c r="D43" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="E43" t="n">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="F43" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="G43" t="n">
-        <v>2.03</v>
+        <v>2.4</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -1805,28 +1805,28 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Endonezya vs Bangladesh</t>
+          <t>SV Schwechat vs 1.ZS Simmeringer SC</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="D44" t="n">
-        <v>13</v>
+        <v>4.5</v>
       </c>
       <c r="E44" t="n">
-        <v>41</v>
+        <v>5.5</v>
       </c>
       <c r="F44" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="G44" t="n">
-        <v>3.2</v>
+        <v>2.73</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -1842,23 +1842,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SKN Sankt Polten II vs Zwettl</t>
+          <t>FC Deutschkreutz vs SV Leithaprodersdorf</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="D45" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="E45" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="F45" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="G45" t="n">
-        <v>2.59</v>
+        <v>2.45</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -1869,28 +1869,28 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Union Weisskirchen vs Union Vocklamarkt</t>
+          <t>ATUS Ferlach vs Nussdorfer AC</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="D46" t="n">
-        <v>4.33</v>
+        <v>5.5</v>
       </c>
       <c r="E46" t="n">
-        <v>4.75</v>
+        <v>8.5</v>
       </c>
       <c r="F46" t="n">
         <v>1.3</v>
       </c>
       <c r="G46" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -1901,28 +1901,28 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Al Sharjah SCC vs AL Dhafra</t>
+          <t>Admira Wacker Modling II vs SC Wiener Neustadter</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1.55</v>
+        <v>2.45</v>
       </c>
       <c r="D47" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="E47" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="F47" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="G47" t="n">
-        <v>2.22</v>
+        <v>2.45</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -1933,28 +1933,28 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Dubai United FC vs Hatta Dubai</t>
+          <t>SV Seekirchen vs Union Gurten</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1.92</v>
+        <v>2.9</v>
       </c>
       <c r="D48" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="E48" t="n">
-        <v>3.2</v>
+        <v>2.07</v>
       </c>
       <c r="F48" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="G48" t="n">
-        <v>2.03</v>
+        <v>2.22</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -1965,28 +1965,28 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Baniyas FC vs Al Wahda Abu Dhabi</t>
+          <t>Union Edelweiss Linz vs Gmunden</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3.5</v>
+        <v>1.45</v>
       </c>
       <c r="D49" t="n">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="E49" t="n">
-        <v>1.81</v>
+        <v>5</v>
       </c>
       <c r="F49" t="n">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="G49" t="n">
-        <v>2.12</v>
+        <v>2.55</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -1997,28 +1997,28 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14 dk içinde</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Se Buzios Rj vs SE Paraty RJ</t>
+          <t>Al Ain vs Ajman Club</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2.9</v>
+        <v>1.33</v>
       </c>
       <c r="D50" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="E50" t="n">
-        <v>2.2</v>
+        <v>6.5</v>
       </c>
       <c r="F50" t="n">
-        <v>2.01</v>
+        <v>1.47</v>
       </c>
       <c r="G50" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2029,28 +2029,28 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14 dk içinde</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SE Belford Roxo vs Santa Cruz RJ</t>
+          <t>Al Wasl vs Ittihad Kalba</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2.77</v>
+        <v>1.5</v>
       </c>
       <c r="D51" t="n">
-        <v>3.15</v>
+        <v>4.25</v>
       </c>
       <c r="E51" t="n">
-        <v>2.31</v>
+        <v>4.5</v>
       </c>
       <c r="F51" t="n">
-        <v>1.95</v>
+        <v>1.38</v>
       </c>
       <c r="G51" t="n">
-        <v>1.72</v>
+        <v>2.8</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2061,28 +2061,28 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cardoso Moreira FC vs Serra Macaense</t>
+          <t>Al Khaleej Khor Fakkan vs Al Jazira SC</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2.15</v>
+        <v>4.75</v>
       </c>
       <c r="D52" t="n">
-        <v>3.28</v>
+        <v>4</v>
       </c>
       <c r="E52" t="n">
-        <v>2.9</v>
+        <v>1.47</v>
       </c>
       <c r="F52" t="n">
-        <v>1.93</v>
+        <v>1.51</v>
       </c>
       <c r="G52" t="n">
-        <v>1.75</v>
+        <v>2.36</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2093,28 +2093,28 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Rio de Janeiro vs Barra Mansa FC</t>
+          <t>Shabab Al Ahli Dubai vs Al-Nasr</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3.15</v>
+        <v>1.55</v>
       </c>
       <c r="D53" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="E53" t="n">
-        <v>2.08</v>
+        <v>4.33</v>
       </c>
       <c r="F53" t="n">
-        <v>1.94</v>
+        <v>1.41</v>
       </c>
       <c r="G53" t="n">
-        <v>1.74</v>
+        <v>2.63</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2125,28 +2125,28 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Spartax FC vs Lagoa Seca</t>
+          <t>Sporting Hasselt U21 vs KV Kortrijk U21</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>4.25</v>
       </c>
       <c r="D54" t="n">
-        <v>3.15</v>
+        <v>4.25</v>
       </c>
       <c r="E54" t="n">
-        <v>3.4</v>
+        <v>1.51</v>
       </c>
       <c r="F54" t="n">
-        <v>1.94</v>
+        <v>1.28</v>
       </c>
       <c r="G54" t="n">
-        <v>1.74</v>
+        <v>3.05</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -2157,28 +2157,28 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>15 dk içinde</t>
+          <t>58 dk içinde</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NK Olimpija Ljubljana vs Slaven Belupo</t>
+          <t>BATE Borisov Reserves vs Ostrovets</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2.12</v>
+        <v>5.5</v>
       </c>
       <c r="D55" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="E55" t="n">
-        <v>2.77</v>
+        <v>1.41</v>
       </c>
       <c r="F55" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="G55" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -2189,28 +2189,28 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Jahn Regensburg vs WSG Tirol</t>
+          <t>Volna Pinsk vs FC Lida</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="D56" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="E56" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="F56" t="n">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="G56" t="n">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2221,28 +2221,28 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Juve Stabia vs U.S. Palmese 1912</t>
+          <t>San Antonio Bulo Bulo vs Academia de Balompie Boliviano</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1.04</v>
+        <v>1.37</v>
       </c>
       <c r="D57" t="n">
-        <v>10</v>
+        <v>4.75</v>
       </c>
       <c r="E57" t="n">
-        <v>23</v>
+        <v>5.5</v>
       </c>
       <c r="F57" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="G57" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2253,28 +2253,28 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg vs Havelse</t>
+          <t>Coimbra EC U20 vs Atletico Mineiro U20</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1.14</v>
+        <v>3.6</v>
       </c>
       <c r="D58" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="E58" t="n">
-        <v>12</v>
+        <v>1.76</v>
       </c>
       <c r="F58" t="n">
-        <v>1.22</v>
+        <v>1.66</v>
       </c>
       <c r="G58" t="n">
-        <v>3.6</v>
+        <v>2.05</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2285,28 +2285,28 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>VfB Stuttgart vs Greuther Furth</t>
+          <t>America MG U20 vs Itabirito FC MG U20</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="D59" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="E59" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="F59" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="G59" t="n">
-        <v>3.15</v>
+        <v>2.22</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -2322,23 +2322,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Real Betis vs AD Ceuta</t>
+          <t>Flamengo RJ U20 vs Sampaio Correa FE RJ U20</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="D60" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="E60" t="n">
-        <v>6.5</v>
+        <v>10</v>
       </c>
       <c r="F60" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="G60" t="n">
-        <v>2.68</v>
+        <v>2.33</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2349,28 +2349,28 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>60 dk içinde</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Fransa U19 vs Türkiye U19</t>
+          <t>7 De Abril RJ vs Friburguense Rj</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1.14</v>
+        <v>2.8</v>
       </c>
       <c r="D61" t="n">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="E61" t="n">
-        <v>11</v>
+        <v>2.18</v>
       </c>
       <c r="F61" t="n">
-        <v>1.22</v>
+        <v>1.7</v>
       </c>
       <c r="G61" t="n">
-        <v>3.6</v>
+        <v>1.95</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -2381,28 +2381,28 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Hırvatistan U19 vs İtalya U19</t>
+          <t>Gremio Esportivo Anapolis FC U20 vs Royal U20</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>3.2</v>
+        <v>1.76</v>
       </c>
       <c r="D62" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="E62" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
       <c r="F62" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="G62" t="n">
-        <v>1.97</v>
+        <v>2.12</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -2413,28 +2413,28 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Faroe Adaları U19 vs Slovenia U19</t>
+          <t>Comercial FC Tiete U20 vs Brasilis FC U20</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>15</v>
+        <v>1.28</v>
       </c>
       <c r="D63" t="n">
-        <v>7.5</v>
+        <v>4.25</v>
       </c>
       <c r="E63" t="n">
-        <v>1.11</v>
+        <v>8.5</v>
       </c>
       <c r="F63" t="n">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="G63" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -2445,28 +2445,28 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Qatar U19 vs İrlanda U19</t>
+          <t>Salitas vs Real du Faso</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>4.33</v>
+        <v>2.63</v>
       </c>
       <c r="D64" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="E64" t="n">
-        <v>1.58</v>
+        <v>2.63</v>
       </c>
       <c r="F64" t="n">
-        <v>1.68</v>
+        <v>2.7</v>
       </c>
       <c r="G64" t="n">
-        <v>2.05</v>
+        <v>1.4</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -2477,28 +2477,28 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>58 dk içinde</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Azerbaycan vs United Arab Emirates U19</t>
+          <t>Us Chaouia vs As Khroub</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2.09</v>
+        <v>1.64</v>
       </c>
       <c r="D65" t="n">
         <v>3.3</v>
       </c>
       <c r="E65" t="n">
-        <v>2.8</v>
+        <v>4.75</v>
       </c>
       <c r="F65" t="n">
-        <v>1.72</v>
+        <v>2.16</v>
       </c>
       <c r="G65" t="n">
-        <v>1.99</v>
+        <v>1.6</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -2509,28 +2509,28 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>58 dk içinde</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>USA U20 vs Brazil U20</t>
+          <t>MO Constantine vs CR Beni Thour</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="D66" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="E66" t="n">
-        <v>1.92</v>
+        <v>6</v>
       </c>
       <c r="F66" t="n">
-        <v>1.53</v>
+        <v>2.35</v>
       </c>
       <c r="G66" t="n">
-        <v>2.33</v>
+        <v>1.51</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -2541,28 +2541,28 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>25 dk içinde</t>
+          <t>58 dk içinde</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Japonya vs Ekvador</t>
+          <t>CA Batna vs MSP Batna</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1.45</v>
+        <v>2.02</v>
       </c>
       <c r="D67" t="n">
-        <v>4.33</v>
+        <v>2.9</v>
       </c>
       <c r="E67" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="F67" t="n">
-        <v>1.68</v>
+        <v>2.6</v>
       </c>
       <c r="G67" t="n">
-        <v>2.09</v>
+        <v>1.41</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -2573,28 +2573,28 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>58 dk içinde</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Maldives vs Lübnan</t>
+          <t>Usm Annaba vs Paradou AC</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>31</v>
+        <v>2.37</v>
       </c>
       <c r="D68" t="n">
-        <v>10</v>
+        <v>2.73</v>
       </c>
       <c r="E68" t="n">
-        <v>1.07</v>
+        <v>3</v>
       </c>
       <c r="F68" t="n">
-        <v>1.43</v>
+        <v>3</v>
       </c>
       <c r="G68" t="n">
-        <v>2.6</v>
+        <v>1.33</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -2605,28 +2605,28 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>58 dk içinde</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Özbekistan vs Suriye</t>
+          <t>NRB Telaghema vs NC Magra</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1.38</v>
+        <v>2.06</v>
       </c>
       <c r="D69" t="n">
-        <v>4.33</v>
+        <v>2.9</v>
       </c>
       <c r="E69" t="n">
-        <v>8</v>
+        <v>3.4</v>
       </c>
       <c r="F69" t="n">
-        <v>1.94</v>
+        <v>2.45</v>
       </c>
       <c r="G69" t="n">
-        <v>1.76</v>
+        <v>1.45</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -2637,28 +2637,28 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>58 dk içinde</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Cumbaya FC vs CD Santo Domingo</t>
+          <t>MO Bejaia vs IRB Nezla</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1.84</v>
+        <v>1.62</v>
       </c>
       <c r="D70" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="E70" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F70" t="n">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="G70" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -2669,28 +2669,28 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CD FAS Reserves vs AD Isidro Metapan Reserves</t>
+          <t>USM Alger U20 vs MC Alger U20</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1.84</v>
+        <v>2.45</v>
       </c>
       <c r="D71" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="E71" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="F71" t="n">
-        <v>1.62</v>
+        <v>2.37</v>
       </c>
       <c r="G71" t="n">
-        <v>2.08</v>
+        <v>1.47</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -2701,28 +2701,28 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Fuerte San Francisco Reserves vs Luis Angel Firpo Reserves</t>
+          <t>SK Hranice vs SK Artis Brno II</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2.2</v>
+        <v>4.15</v>
       </c>
       <c r="D72" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="E72" t="n">
-        <v>2.7</v>
+        <v>1.62</v>
       </c>
       <c r="F72" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="G72" t="n">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -2738,23 +2738,23 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>LAUTP/2 vs Kumu</t>
+          <t>FC Hlucin vs Novy Jicin</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2.06</v>
+        <v>1.4</v>
       </c>
       <c r="D73" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="E73" t="n">
-        <v>2.63</v>
+        <v>5.5</v>
       </c>
       <c r="F73" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="G73" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -2770,23 +2770,23 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Asante Kotoko vs Karela</t>
+          <t>TJ Hluboka nad Vltavou vs FK Krimice</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1.7</v>
+        <v>2.45</v>
       </c>
       <c r="D74" t="n">
         <v>3.3</v>
       </c>
       <c r="E74" t="n">
-        <v>4.33</v>
+        <v>2.36</v>
       </c>
       <c r="F74" t="n">
-        <v>2.06</v>
+        <v>1.64</v>
       </c>
       <c r="G74" t="n">
-        <v>1.64</v>
+        <v>2.09</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -2797,28 +2797,28 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Langsning vs Shillong Lajong Reserves</t>
+          <t>Dukla Prague vs Jablonec</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2.45</v>
+        <v>4.5</v>
       </c>
       <c r="D75" t="n">
         <v>3.4</v>
       </c>
       <c r="E75" t="n">
-        <v>2.4</v>
+        <v>1.68</v>
       </c>
       <c r="F75" t="n">
-        <v>1.62</v>
+        <v>2.04</v>
       </c>
       <c r="G75" t="n">
-        <v>2.12</v>
+        <v>1.68</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -2829,28 +2829,28 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>44 dk içinde</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Parikrama vs ASC And Center</t>
+          <t>Naestved vs Nykobing</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2.27</v>
+        <v>2.7</v>
       </c>
       <c r="D76" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="F76" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="G76" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -2861,28 +2861,28 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Shatin vs R&amp;F Fc</t>
+          <t>Fremad Amager vs B93 Kopenhagen</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1.96</v>
+        <v>2.31</v>
       </c>
       <c r="D77" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="E77" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="F77" t="n">
-        <v>1.45</v>
+        <v>1.76</v>
       </c>
       <c r="G77" t="n">
-        <v>1.41</v>
+        <v>1.92</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -2893,25 +2893,25 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Hapoel Raanana vs KAFR Qasim</t>
+          <t>VSK Arhus vs Brabrand</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="D78" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="E78" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="F78" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="G78" t="n">
         <v>1.87</v>
@@ -2925,28 +2925,28 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>28 dk içinde</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina vs Hapoel Kfar Shelem</t>
+          <t>Eintracht Frankfurt vs Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1.97</v>
+        <v>1.47</v>
       </c>
       <c r="D79" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="E79" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="F79" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="G79" t="n">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -2957,28 +2957,28 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>28 dk içinde</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MS Ashdod vs Maccabi Herzliya</t>
+          <t>Wolfsberger vs Voitsberg</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="D80" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E80" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="F80" t="n">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="G80" t="n">
-        <v>2.2</v>
+        <v>3.05</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -2989,28 +2989,28 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>58 dk içinde</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Maccabi Yafo Kabilyo vs Hapoel Akko FC</t>
+          <t>Noah vs FC Dinamo Batumi</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="D81" t="n">
         <v>3.6</v>
       </c>
       <c r="E81" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="F81" t="n">
-        <v>1.66</v>
+        <v>1.45</v>
       </c>
       <c r="G81" t="n">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -3021,28 +3021,28 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>58 dk içinde</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Hapoel Afula vs Hapoel Ironi Rishon Lezion</t>
+          <t>MFK Karvina vs Stal Rzeszow</t>
         </is>
       </c>
       <c r="C82" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="D82" t="n">
+        <v>4</v>
+      </c>
+      <c r="E82" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F82" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G82" t="n">
         <v>2.8</v>
-      </c>
-      <c r="D82" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E82" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="F82" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G82" t="n">
-        <v>2.15</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -3053,28 +3053,28 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Bnei-Yehuda Tel-Aviv vs Maccabi Kiryat Gat Sports Club</t>
+          <t>FC Aarau vs Young Boys</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1.28</v>
+        <v>5.5</v>
       </c>
       <c r="D83" t="n">
         <v>4.75</v>
       </c>
       <c r="E83" t="n">
-        <v>7.5</v>
+        <v>1.37</v>
       </c>
       <c r="F83" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="G83" t="n">
-        <v>2.37</v>
+        <v>3.05</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -3085,28 +3085,28 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Kiryat Yam vs Hapoel Kfar-Saba</t>
+          <t>RB Salzburg vs BW Linz</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1.71</v>
+        <v>1.38</v>
       </c>
       <c r="D84" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="E84" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="F84" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="G84" t="n">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -3117,28 +3117,28 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth FC vs Ironi Modiin</t>
+          <t>Brondby vs IK Sirius FK</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="D85" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="E85" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="F85" t="n">
-        <v>1.76</v>
+        <v>1.41</v>
       </c>
       <c r="G85" t="n">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -3149,28 +3149,28 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Hapoel Ihud Bnei Jatt vs Maccabi Nujeidat Ahmed</t>
+          <t>Rapid Bükreş vs Genoa</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3.2</v>
+        <v>2.09</v>
       </c>
       <c r="D86" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="E86" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F86" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G86" t="n">
         <v>1.91</v>
-      </c>
-      <c r="F86" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="G86" t="n">
-        <v>2.09</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -3181,28 +3181,28 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Hapoel Umm Al Fahm vs Hapoel Ironi Karmiel</t>
+          <t>Kaiserslautern vs Sonnenhof</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2.55</v>
+        <v>1.45</v>
       </c>
       <c r="D87" t="n">
-        <v>3.2</v>
+        <v>4.25</v>
       </c>
       <c r="E87" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="F87" t="n">
-        <v>1.85</v>
+        <v>1.41</v>
       </c>
       <c r="G87" t="n">
-        <v>1.85</v>
+        <v>2.6</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -3213,28 +3213,28 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Maccabi Yavne vs Ironi Beit Shemesh</t>
+          <t>Teplice vs Dynamo Dresden</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="D88" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="E88" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="F88" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="G88" t="n">
-        <v>1.95</v>
+        <v>3.4</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -3250,23 +3250,23 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Sderot FC vs Hapoel Azor</t>
+          <t>Grenoble vs FC Stade Lausanne Ouchy</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1.98</v>
+        <v>2.45</v>
       </c>
       <c r="D89" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="E89" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="F89" t="n">
-        <v>2.01</v>
+        <v>1.68</v>
       </c>
       <c r="G89" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -3282,23 +3282,23 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Kfar Saba 1928 vs Hapoel Marmorek</t>
+          <t>Saarbrucken vs AS Nancy Lorraine</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2.02</v>
+        <v>2.73</v>
       </c>
       <c r="D90" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="E90" t="n">
-        <v>3.3</v>
+        <v>2.16</v>
       </c>
       <c r="F90" t="n">
-        <v>2.12</v>
+        <v>1.6</v>
       </c>
       <c r="G90" t="n">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -3309,28 +3309,28 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>FC Kababir vs MK Tzofi Haifa</t>
+          <t>Real Sociedad vs Athletic Bilbao</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>3.8</v>
+        <v>2.45</v>
       </c>
       <c r="D91" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="E91" t="n">
-        <v>1.71</v>
+        <v>2.5</v>
       </c>
       <c r="F91" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="G91" t="n">
-        <v>2.03</v>
+        <v>1.87</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -3341,28 +3341,28 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Maccabi Ihud Bnei Avtin vs Hapoel Bnei Bi'ina</t>
+          <t>Deportivo A Coruña vs Porto</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1.35</v>
+        <v>2.31</v>
       </c>
       <c r="D92" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="E92" t="n">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="F92" t="n">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="G92" t="n">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -3373,28 +3373,28 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Hapoel Givat Olga vs Maccabi Ironi Kfar Yona</t>
+          <t>Stade Laval vs Rennes FC</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="D93" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="E93" t="n">
-        <v>2.15</v>
+        <v>1.64</v>
       </c>
       <c r="F93" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="G93" t="n">
-        <v>2.27</v>
+        <v>2.54</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -3405,28 +3405,28 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Beitar Kfar Saba Shlomi vs Beitar Tel Aviv Holon</t>
+          <t>Sevilla vs Aston Villa</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2.25</v>
+        <v>2.73</v>
       </c>
       <c r="D94" t="n">
         <v>3.4</v>
       </c>
       <c r="E94" t="n">
-        <v>2.6</v>
+        <v>2.23</v>
       </c>
       <c r="F94" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="G94" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -3437,28 +3437,28 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>28 dk içinde</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Ironi Beit Dagan vs Hapoel Hod Hasharon Irony</t>
+          <t>Belçika U19 vs Kuzey İrlanda U19</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>2.1</v>
+        <v>1.25</v>
       </c>
       <c r="D95" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="E95" t="n">
-        <v>2.8</v>
+        <v>8</v>
       </c>
       <c r="F95" t="n">
-        <v>1.72</v>
+        <v>1.47</v>
       </c>
       <c r="G95" t="n">
-        <v>1.96</v>
+        <v>2.45</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -3469,28 +3469,28 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>28 dk içinde</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ihud Tzeirey Abu Gosh vs Maccabi Beer Sheva</t>
+          <t>Arnavutluk U19 vs Litvanya Under 19</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1.57</v>
+        <v>2.03</v>
       </c>
       <c r="D96" t="n">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="E96" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="F96" t="n">
-        <v>1.4</v>
+        <v>1.84</v>
       </c>
       <c r="G96" t="n">
-        <v>1.5</v>
+        <v>1.84</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -3501,28 +3501,28 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>58 dk içinde</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>AS Holon Mor vs Bnei Jaffa Ortodoxim</t>
+          <t>Gürcistan vs Letonya U19</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>2.73</v>
+        <v>2.08</v>
       </c>
       <c r="D97" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="E97" t="n">
-        <v>2.16</v>
+        <v>3</v>
       </c>
       <c r="F97" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="G97" t="n">
-        <v>2.01</v>
+        <v>1.79</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -3533,28 +3533,28 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>58 dk içinde</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>FH Hafnarfjordur U19 vs Keflavik U19</t>
+          <t>Karadağ U19 vs İsrail U19</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="D98" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="E98" t="n">
-        <v>2.35</v>
+        <v>1.91</v>
       </c>
       <c r="F98" t="n">
-        <v>1.16</v>
+        <v>1.8</v>
       </c>
       <c r="G98" t="n">
-        <v>4</v>
+        <v>1.87</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -3565,28 +3565,28 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Al-Gharafa vs Al Mesaimeer SC</t>
+          <t>İngiltere U19 vs USA U19</t>
         </is>
       </c>
       <c r="C99" t="n">
         <v>1.72</v>
       </c>
       <c r="D99" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="E99" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="F99" t="n">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="G99" t="n">
-        <v>2.12</v>
+        <v>2.55</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -3597,28 +3597,28 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>58 dk içinde</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Al-Shamal vs Muaither SC</t>
+          <t>Portekiz U20 vs Çek Cumhuriyeti U20</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1.47</v>
+        <v>2.14</v>
       </c>
       <c r="D100" t="n">
-        <v>4.15</v>
+        <v>3.4</v>
       </c>
       <c r="E100" t="n">
-        <v>4.75</v>
+        <v>2.73</v>
       </c>
       <c r="F100" t="n">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="G100" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -3629,28 +3629,28 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Qatar SC Doha vs Al Bidda SC</t>
+          <t>Sırbistan U21 vs Russia U21</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1.62</v>
+        <v>2.36</v>
       </c>
       <c r="D101" t="n">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="E101" t="n">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="F101" t="n">
-        <v>1.53</v>
+        <v>1.86</v>
       </c>
       <c r="G101" t="n">
-        <v>2.33</v>
+        <v>1.84</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -3661,28 +3661,28 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Mombasa United vs Kariobangi Sharks</t>
+          <t>San Antonio FC Cotacachi vs Vinotinto Ecuador</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>2.63</v>
+        <v>4.75</v>
       </c>
       <c r="D102" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="E102" t="n">
-        <v>2.55</v>
+        <v>1.58</v>
       </c>
       <c r="F102" t="n">
-        <v>2.54</v>
+        <v>1.87</v>
       </c>
       <c r="G102" t="n">
-        <v>1.41</v>
+        <v>1.79</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -3698,23 +3698,23 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Envigado vs Orsomarso</t>
+          <t>CD Cuenca Juniors vs Indepiendente Juniors</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1.64</v>
+        <v>2.54</v>
       </c>
       <c r="D103" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="E103" t="n">
-        <v>4.75</v>
+        <v>2.73</v>
       </c>
       <c r="F103" t="n">
-        <v>2.27</v>
+        <v>2.68</v>
       </c>
       <c r="G103" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -3725,28 +3725,28 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>27 dk içinde</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>British Virgin Islands vs Montserrat</t>
+          <t>Persiraja Aceh vs Sumsel United</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>13.25</v>
+        <v>1.18</v>
       </c>
       <c r="D104" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="E104" t="n">
-        <v>1.16</v>
+        <v>10</v>
       </c>
       <c r="F104" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="G104" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -3757,28 +3757,28 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>US Virgin Islands vs Saint Martin</t>
+          <t>JK Tammeka Tartu vs Viimsi Jk</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>8.5</v>
+        <v>1.43</v>
       </c>
       <c r="D105" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E105" t="n">
         <v>5</v>
       </c>
-      <c r="E105" t="n">
-        <v>1.25</v>
-      </c>
       <c r="F105" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="G105" t="n">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -3789,28 +3789,28 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Mighty Wanderers (W) vs Ascent Academy (W)</t>
+          <t>RSB Berkane vs FAR Rabat</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="D106" t="n">
-        <v>3.5</v>
+        <v>2.45</v>
       </c>
       <c r="E106" t="n">
-        <v>1.74</v>
+        <v>2.9</v>
       </c>
       <c r="F106" t="n">
-        <v>1.79</v>
+        <v>2.4</v>
       </c>
       <c r="G106" t="n">
-        <v>1.91</v>
+        <v>1.47</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -3821,28 +3821,28 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Rumphi Sisters (W) vs Ntopwa FC (W)</t>
+          <t>FUS de Rabat vs Amal Tiznit</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>5</v>
+        <v>1.72</v>
       </c>
       <c r="D107" t="n">
-        <v>4.25</v>
+        <v>3.3</v>
       </c>
       <c r="E107" t="n">
-        <v>1.4</v>
+        <v>4.33</v>
       </c>
       <c r="F107" t="n">
-        <v>1.4</v>
+        <v>2.22</v>
       </c>
       <c r="G107" t="n">
-        <v>2.6</v>
+        <v>1.57</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -3853,28 +3853,28 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Touchtronics FC U20 vs Terengganu U20</t>
+          <t>Widad Temara vs Union Touarga Sports</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>5</v>
+        <v>2.68</v>
       </c>
       <c r="D108" t="n">
-        <v>3.8</v>
+        <v>2.77</v>
       </c>
       <c r="E108" t="n">
-        <v>1.51</v>
+        <v>2.68</v>
       </c>
       <c r="F108" t="n">
-        <v>1.79</v>
+        <v>2.77</v>
       </c>
       <c r="G108" t="n">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -3885,28 +3885,28 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Mgarr United (K) vs Swieqi United (W)</t>
+          <t>Ittihad Riadhi de Tanger vs Maghrib Association Tetouan</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1.38</v>
+        <v>1.87</v>
       </c>
       <c r="D109" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="E109" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="F109" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="G109" t="n">
-        <v>2.25</v>
+        <v>1.47</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -3917,29 +3917,25 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Pharco vs El Terasanah</t>
+          <t>Saaksjaerven Loiske vs TP 49</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>2.31</v>
+        <v>1.41</v>
       </c>
       <c r="D110" t="n">
-        <v>2.8</v>
+        <v>4.75</v>
       </c>
       <c r="E110" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="F110" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="G110" t="n">
-        <v>1.35</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
           <t>-</t>
@@ -3949,28 +3945,28 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>El Mansoura vs FC Masar</t>
+          <t>HPS II vs MPS/Atletico Malmi</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="D111" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="E111" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="F111" t="n">
-        <v>2.45</v>
+        <v>1.18</v>
       </c>
       <c r="G111" t="n">
-        <v>1.47</v>
+        <v>4</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -3981,28 +3977,28 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>La Viena FC vs Al Nasr Cairo</t>
+          <t>Valtti vs VJS Vantaa II</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="D112" t="n">
-        <v>2.8</v>
+        <v>4.25</v>
       </c>
       <c r="E112" t="n">
-        <v>2.9</v>
+        <v>2.37</v>
       </c>
       <c r="F112" t="n">
-        <v>2.73</v>
+        <v>1.12</v>
       </c>
       <c r="G112" t="n">
-        <v>1.38</v>
+        <v>5</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -4013,28 +4009,28 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>El Sekka El Hadid SC vs El Entag El Harby</t>
+          <t>Lps vs TiPS</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>2.68</v>
+        <v>1.6</v>
       </c>
       <c r="D113" t="n">
-        <v>2.77</v>
+        <v>4.5</v>
       </c>
       <c r="E113" t="n">
-        <v>2.63</v>
+        <v>3.6</v>
       </c>
       <c r="F113" t="n">
-        <v>2.77</v>
+        <v>1.14</v>
       </c>
       <c r="G113" t="n">
-        <v>1.37</v>
+        <v>4.5</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -4045,28 +4041,28 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Sila SC vs Asyut Cement Petroleum</t>
+          <t>Pakkalan Palloseura vs Fc Kontu</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1.68</v>
+        <v>4.5</v>
       </c>
       <c r="D114" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="E114" t="n">
-        <v>4.15</v>
+        <v>1.43</v>
       </c>
       <c r="F114" t="n">
-        <v>1.76</v>
+        <v>1.11</v>
       </c>
       <c r="G114" t="n">
-        <v>1.91</v>
+        <v>5.5</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -4077,16 +4073,16 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Gjelleraasen U19 vs Grorud U19</t>
+          <t>Toolon Taisto vs Toukolan Teras</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="D115" t="n">
         <v>4</v>
@@ -4095,10 +4091,10 @@
         <v>2.05</v>
       </c>
       <c r="F115" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="G115" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -4109,28 +4105,28 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Ullensaker/Kisa U19 vs Haslum IL U19</t>
+          <t>Atlantis FC/PM vs PPJ/Lauttasaari</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="D116" t="n">
-        <v>13.25</v>
+        <v>5</v>
       </c>
       <c r="E116" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="F116" t="n">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="G116" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -4141,28 +4137,28 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Sarpsborg 08 U19 vs Klofta U19</t>
+          <t>PK-35 Vantaa (K) vs FC Honka (W)</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="D117" t="n">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="E117" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="F117" t="n">
-        <v>1.08</v>
+        <v>1.37</v>
       </c>
       <c r="G117" t="n">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -4173,28 +4169,28 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Nordstrand U19 vs Follo U19</t>
+          <t>Llanelli Town Afc vs Baglan Dragons</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="D118" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="E118" t="n">
-        <v>1.6</v>
+        <v>2.04</v>
       </c>
       <c r="F118" t="n">
-        <v>1.12</v>
+        <v>1.64</v>
       </c>
       <c r="G118" t="n">
-        <v>5</v>
+        <v>2.07</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -4210,23 +4206,23 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Skedsmo U19 vs Skeid U19</t>
+          <t>Carmarthen Town Afc vs Llantwit Major</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="D119" t="n">
         <v>4</v>
       </c>
       <c r="E119" t="n">
-        <v>2.45</v>
+        <v>4.33</v>
       </c>
       <c r="F119" t="n">
-        <v>1.14</v>
+        <v>1.47</v>
       </c>
       <c r="G119" t="n">
-        <v>4.75</v>
+        <v>2.39</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -4237,28 +4233,28 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Baerum SK Sandvika vs Lillestrom</t>
+          <t>Caerau Ely vs Afan Lido</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>15</v>
+        <v>1.43</v>
       </c>
       <c r="D120" t="n">
-        <v>8</v>
+        <v>4.33</v>
       </c>
       <c r="E120" t="n">
-        <v>1.11</v>
+        <v>5</v>
       </c>
       <c r="F120" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="G120" t="n">
-        <v>4.2</v>
+        <v>2.55</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -4269,28 +4265,28 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Madla vs Viking</t>
+          <t>Denbigh Town vs Holyhead Hotspur</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>17</v>
+        <v>1.76</v>
       </c>
       <c r="D121" t="n">
-        <v>9</v>
+        <v>3.8</v>
       </c>
       <c r="E121" t="n">
-        <v>1.09</v>
+        <v>3.4</v>
       </c>
       <c r="F121" t="n">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="G121" t="n">
-        <v>3.8</v>
+        <v>2.45</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -4301,28 +4297,28 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Al Nasr SC vs Al-Samail</t>
+          <t>Nsuopun Fidelity vs New Edubiase FC</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1.78</v>
+        <v>1.51</v>
       </c>
       <c r="D122" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="E122" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="F122" t="n">
-        <v>1.66</v>
+        <v>1.97</v>
       </c>
       <c r="G122" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -4333,28 +4329,28 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Bahla Club vs Fanja</t>
+          <t>7th Wave FC vs Home Stars FC</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1.28</v>
+        <v>1.91</v>
       </c>
       <c r="D123" t="n">
-        <v>4.75</v>
+        <v>2.9</v>
       </c>
       <c r="E123" t="n">
-        <v>7.5</v>
+        <v>3.7</v>
       </c>
       <c r="F123" t="n">
-        <v>1.47</v>
+        <v>2.45</v>
       </c>
       <c r="G123" t="n">
-        <v>2.45</v>
+        <v>1.4</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -4365,28 +4361,28 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Al-Musannah SC vs Ibri Club</t>
+          <t>Accra Lions vs Inter Allies</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="D124" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="E124" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="F124" t="n">
-        <v>1.76</v>
+        <v>2.03</v>
       </c>
       <c r="G124" t="n">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -4397,28 +4393,28 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>San Francisco II vs Cd Universitario Reserves</t>
+          <t>Yapei United vs Techiman Liberty Youth</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="D125" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="E125" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="F125" t="n">
-        <v>1.41</v>
+        <v>2.15</v>
       </c>
       <c r="G125" t="n">
-        <v>2.4</v>
+        <v>1.51</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -4429,28 +4425,28 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>57 dk içinde</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>CD Plaza Amador (W) vs UMECIT (W)</t>
+          <t>Copper Belts FC (W) vs Stellenbosch FC (W)</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>6</v>
+        <v>1.53</v>
       </c>
       <c r="D126" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="E126" t="n">
-        <v>1.35</v>
+        <v>5</v>
       </c>
       <c r="F126" t="n">
-        <v>1.37</v>
+        <v>1.84</v>
       </c>
       <c r="G126" t="n">
-        <v>2.6</v>
+        <v>1.84</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -4461,28 +4457,28 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>27 dk içinde</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Sporting Cristal Lima vs Asociacion Deportiva Tarma</t>
+          <t>NK Junak vs HNK Val Kastel Stari</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="D127" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="E127" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="F127" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="G127" t="n">
-        <v>2.01</v>
+        <v>1.78</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -4493,28 +4489,28 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>27 dk içinde</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Przemsza Siewierz vs Rozwoj Katowice</t>
+          <t>NK HV Posedarje vs NK GOSK Dubrovnik</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="D128" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="E128" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="F128" t="n">
-        <v>1.3</v>
+        <v>1.66</v>
       </c>
       <c r="G128" t="n">
-        <v>3.2</v>
+        <v>2.05</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -4525,28 +4521,28 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>MKS Podlasie Biala Podlaska vs Juventa Starachowice</t>
+          <t>NK Precko vs Gaj Mace</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>2.11</v>
+        <v>2.39</v>
       </c>
       <c r="D129" t="n">
         <v>3.4</v>
       </c>
       <c r="E129" t="n">
-        <v>2.9</v>
+        <v>2.39</v>
       </c>
       <c r="F129" t="n">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="G129" t="n">
-        <v>1.91</v>
+        <v>2.23</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -4557,28 +4553,28 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>26 dk içinde</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Al Yarmouk vs Amman FC</t>
+          <t>Ramthar vs Aizawl</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>2.77</v>
+        <v>19</v>
       </c>
       <c r="D130" t="n">
-        <v>3.05</v>
+        <v>8.5</v>
       </c>
       <c r="E130" t="n">
-        <v>2.27</v>
+        <v>1.08</v>
       </c>
       <c r="F130" t="n">
-        <v>2.12</v>
+        <v>1.32</v>
       </c>
       <c r="G130" t="n">
-        <v>1.62</v>
+        <v>3</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -4589,28 +4585,28 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Jerash SC vs AL Ahli Amman</t>
+          <t>Bray Wanderers AFC vs Cobh Ramblers</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>2.5</v>
+        <v>1.64</v>
       </c>
       <c r="D131" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="E131" t="n">
-        <v>2.55</v>
+        <v>4.15</v>
       </c>
       <c r="F131" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="G131" t="n">
-        <v>1.55</v>
+        <v>2.27</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -4621,30 +4617,2234 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Athlone Town FC vs Cork City FC</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="D132" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E132" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="F132" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G132" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Finn Harps FC vs Kerry FC</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D133" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G133" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Treaty United FC vs University College Dublin FC</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D134" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E134" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="F134" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G134" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Wexford FC vs Longford Town</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="D135" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E135" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F135" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G135" t="n">
+        <v>2</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Dundalk FC vs Bohemian</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D136" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E136" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="F136" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G136" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Montpelier FC vs Crumlin United FC</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D137" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E137" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F137" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G137" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Kilbarrack United vs Malahide</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="D138" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E138" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F138" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G138" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>St Mochtas vs Killester United</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>2</v>
+      </c>
+      <c r="D139" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E139" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F139" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G139" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>St Francis FC Senior Sunday vs Glebe North FC</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="D140" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="E140" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F140" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G140" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Douglas Hall vs Castleview</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="D141" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="E141" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F141" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G141" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Cumnock Juniors FC vs Auchinleck Talbot FC</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D142" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E142" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G142" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Smedby Ais vs Nykopings BIS</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D143" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E143" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="F143" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G143" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Foc Farsta vs Fittja IF</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="D144" t="n">
+        <v>5</v>
+      </c>
+      <c r="E144" t="n">
+        <v>7</v>
+      </c>
+      <c r="F144" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G144" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Karlbergs BK vs Sollentuna Utd FF</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="D145" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E145" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F145" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G145" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Jitex Molndal (W) vs Linkopings FC (W)</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D146" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E146" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="F146" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G146" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Lunds BK vs Laholms Fk</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="D147" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E147" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F147" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G147" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Kristianstad Fc vs Ariana Malmo FC</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>3</v>
+      </c>
+      <c r="D148" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E148" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="F148" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G148" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Kungsangens IF vs Sunnersta AIF</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D149" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E149" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F149" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G149" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Lilla Torg FF vs Nosaby IF</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="D150" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E150" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="F150" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G150" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Staffanstorp United vs Solvesborgs GoIF</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D151" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E151" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F151" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G151" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Torslanda IK vs Ik Kongahalla</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D152" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E152" t="n">
+        <v>3</v>
+      </c>
+      <c r="F152" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G152" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Hestrafors IF vs Onsala BK</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="D153" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E153" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F153" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G153" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Lindome GIF vs Galtabacks BK</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="D154" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="E154" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F154" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="G154" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Qviding FIF vs Landvetter IS</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D155" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E155" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="F155" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G155" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>SV Schaffhausen vs Seuzach</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="D156" t="n">
+        <v>4</v>
+      </c>
+      <c r="E156" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F156" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G156" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>FC Collex Bossy vs FC Veyrier Sports</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="D157" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E157" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="F157" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G157" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Grasshopper (K) vs Zurich (K)</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="D158" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E158" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="F158" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G158" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Fram Reykjavik (K) vs Valur Reykjavik (K)</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D159" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E159" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F159" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G159" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Vikingur Reykjavik (K) vs Thor Akureyri (K)</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="D160" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E160" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F160" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G160" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Stjarnan (K) vs Grindavik/Njardvik (K)</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="D161" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E161" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F161" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G161" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>31 dk içinde</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Al-Duhail U20 vs Al-Markhiya U20</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="D162" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E162" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F162" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="G162" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>31 dk içinde</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Al Sadd U20 vs Umm Salal U20</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="D163" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E163" t="n">
+        <v>4</v>
+      </c>
+      <c r="F163" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G163" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>31 dk içinde</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Al-Rayyan U20 vs Al-Wakrah U20</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="D164" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E164" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F164" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G164" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Consultants Desamparados vs Carmelita</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="D165" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E165" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="F165" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G165" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Strabane Athletic vs Armagh City</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="D166" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E166" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F166" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="G166" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Dollingstown vs Ballymacash Rangers</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="D167" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E167" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="F167" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G167" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Saint Lucia vs Guadeloupe</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="D168" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E168" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="F168" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G168" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Ittihad AL Ramtha vs Sama Al Sarhan</t>
-        </is>
-      </c>
-      <c r="C132" t="n">
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Dainava II vs FK Sveikata Kybartai</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>19</v>
+      </c>
+      <c r="D169" t="n">
+        <v>10</v>
+      </c>
+      <c r="E169" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="F169" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="G169" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>FM Klaipedos vs Banga Gargzdai II</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="D170" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E170" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F170" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G170" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>FKS Ukmerge vs FK Nevezis Kedainiai</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D171" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E171" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="F171" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="G171" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>55 dk içinde</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Minija Kretinga vs Kauno Zalgiris II</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="D172" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E172" t="n">
+        <v>12</v>
+      </c>
+      <c r="F172" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G172" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>FK Garliava vs DFK Dainava Alytus</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D173" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E173" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="F173" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G173" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Birkirkara Fc vs Hibernians FC (W)</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="D174" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E174" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="F174" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G174" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>CH Futbol Club vs Colegio Once Mexico</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="D175" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E175" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F175" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G175" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Club de Ciervos FC II vs Club Union FC</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="D176" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E176" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="F176" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G176" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Aztecas AMF vs CD Mexiquense</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="D177" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E177" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="F177" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G177" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Club Necaxa II vs Cefor 30-30</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="D178" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E178" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F178" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="G178" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Chivas Guadalajara U21 vs Juarez FC U21</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="D179" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E179" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F179" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G179" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Ranheim vs Egersund</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="D180" t="n">
+        <v>4</v>
+      </c>
+      <c r="E180" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F180" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="G180" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Hinna Fotball vs Staal Jorpeland</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="D181" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E181" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F181" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G181" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Molde (A) vs Herd</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D182" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E182" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="F182" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="G182" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Rosenborg BK II vs Melhus Il</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
         <v>2.27</v>
       </c>
-      <c r="D132" t="n">
+      <c r="D183" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E183" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="F183" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G183" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>24 dk içinde</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Dhofar SCSC vs Oman Club</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="D184" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E184" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="F184" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="G184" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Al Shabab vs Saham</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="D185" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E185" t="n">
+        <v>5</v>
+      </c>
+      <c r="F185" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G185" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Al Nahda vs Sohar Club</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="D186" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E186" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="F186" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="G186" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>54 dk içinde</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>CA Independiente de La Chorrera Reserves vs Herrera Reserves</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="D187" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E187" t="n">
+        <v>17</v>
+      </c>
+      <c r="F187" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="G187" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>54 dk içinde</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Costa Del Este Reserves vs Tauro Fc Reserves</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="D188" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E188" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F188" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G188" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Encarnacion FC vs Resistencia SC</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="D189" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E189" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F189" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G189" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Stal Lancut vs Legion Pilzno</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="D190" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E190" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="F190" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G190" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>UKS NAKI Olsztyn vs MKS Rominta Goldap</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="D191" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E191" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="F191" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G191" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Polonia Nysa vs Miedz Legnica ll</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D192" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E192" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="F192" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G192" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Wisloka Debica vs Pogon Sokol Lubaczow</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="D193" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E193" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="F193" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G193" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Sportowa Czworka Radom (K) vs Resovia Rzeszow (W)</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="D194" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="E194" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="F194" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G194" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Inter Stars Sibiu vs CSO Teleajenul Valeni de Munte</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="D195" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E195" t="n">
+        <v>5</v>
+      </c>
+      <c r="F195" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G195" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>MSK Senec vs Spartak Myjava</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D196" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E196" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F196" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G196" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Al Quadisiya Al Khubar (W) vs Neom SC (W)</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="D197" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E197" t="n">
+        <v>19</v>
+      </c>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr"/>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>AL Ahli Saudi FC (W) vs Al-Nassr Riyadh (K)</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>13</v>
+      </c>
+      <c r="D198" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E198" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="F198" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="G198" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>AL Sareeh vs Ma'an</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="D199" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E199" t="n">
         <v>3</v>
       </c>
-      <c r="E132" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F132" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="G132" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="H132" t="inlineStr">
+      <c r="F199" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="G199" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Hayy Al-Amir Hassan vs Al Hashemeya</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="D200" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E200" t="n">
+        <v>3</v>
+      </c>
+      <c r="F200" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G200" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Al Aqaba vs Sahl Horan SC</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D201" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E201" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F201" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G201" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H201" t="inlineStr">
         <is>
           <t>-</t>
         </is>
